--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="172" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="171">
   <si>
     <t>id</t>
   </si>
@@ -98,6 +98,9 @@
     <t>美术资源名称与路径</t>
   </si>
   <si>
+    <t>资源描述</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -111,6 +114,9 @@
   </si>
   <si>
     <t>resourcePath</t>
+  </si>
+  <si>
+    <t>Dec</t>
   </si>
   <si>
     <t>头像1</t>
@@ -756,12 +762,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1559,8 +1565,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="5"/>
+  <dimension ref="A1:G84"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
@@ -1568,7 +1574,7 @@
     <col min="7" max="7" width="12.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:6">
+    <row r="1" customFormat="1" spans="1:7">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1582,38 +1588,47 @@
       <c r="F1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" customFormat="1" spans="1:6">
+      <c r="G1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:7">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
+        <v>6</v>
+      </c>
+      <c r="G2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" customFormat="1" spans="1:6">
+    <row r="3" customFormat="1" spans="1:7">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:6">
+        <v>9</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="1">
         <f>C5*1000+B5</f>
         <v>1</v>
@@ -1630,13 +1645,16 @@
         <v>100001</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:6">
+        <v>12</v>
+      </c>
+      <c r="G5" s="1">
+        <v>200001</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="1">
         <f t="shared" ref="A6:A46" si="0">C6*1000+B6</f>
         <v>2</v>
@@ -1653,13 +1671,16 @@
         <v>100002</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:6">
+        <v>14</v>
+      </c>
+      <c r="G6" s="1">
+        <v>200002</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:7">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1676,13 +1697,16 @@
         <v>100003</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:6">
+        <v>16</v>
+      </c>
+      <c r="G7" s="1">
+        <v>200003</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:7">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1699,13 +1723,16 @@
         <v>100004</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:6">
+        <v>18</v>
+      </c>
+      <c r="G8" s="1">
+        <v>200004</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:7">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1722,13 +1749,16 @@
         <v>100005</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:6">
+        <v>20</v>
+      </c>
+      <c r="G9" s="1">
+        <v>200005</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:7">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1745,13 +1775,16 @@
         <v>100006</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:6">
+        <v>22</v>
+      </c>
+      <c r="G10" s="1">
+        <v>200006</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:7">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1768,13 +1801,16 @@
         <v>100007</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:6">
+        <v>24</v>
+      </c>
+      <c r="G11" s="1">
+        <v>200007</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:7">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1791,13 +1827,16 @@
         <v>100008</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:6">
+        <v>26</v>
+      </c>
+      <c r="G12" s="1">
+        <v>200008</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:7">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1814,13 +1853,16 @@
         <v>100009</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:6">
+        <v>28</v>
+      </c>
+      <c r="G13" s="1">
+        <v>200009</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:7">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1837,13 +1879,16 @@
         <v>100010</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:6">
+        <v>30</v>
+      </c>
+      <c r="G14" s="1">
+        <v>200010</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:7">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1860,13 +1905,16 @@
         <v>100011</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:6">
+        <v>32</v>
+      </c>
+      <c r="G15" s="1">
+        <v>200011</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:7">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1883,13 +1931,16 @@
         <v>100012</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:6">
+        <v>34</v>
+      </c>
+      <c r="G16" s="1">
+        <v>200012</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:7">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1906,13 +1957,16 @@
         <v>100013</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:6">
+        <v>36</v>
+      </c>
+      <c r="G17" s="1">
+        <v>200013</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:7">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1929,13 +1983,16 @@
         <v>100014</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:6">
+        <v>38</v>
+      </c>
+      <c r="G18" s="1">
+        <v>200014</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:7">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1952,13 +2009,16 @@
         <v>100015</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:6">
+        <v>40</v>
+      </c>
+      <c r="G19" s="1">
+        <v>200015</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:7">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1975,13 +2035,16 @@
         <v>100016</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:6">
+        <v>42</v>
+      </c>
+      <c r="G20" s="1">
+        <v>200016</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:7">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1998,13 +2061,16 @@
         <v>100017</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:6">
+        <v>44</v>
+      </c>
+      <c r="G21" s="1">
+        <v>200017</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:7">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2021,13 +2087,16 @@
         <v>100018</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:6">
+        <v>46</v>
+      </c>
+      <c r="G22" s="1">
+        <v>200018</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:7">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2044,13 +2113,16 @@
         <v>100019</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:6">
+        <v>48</v>
+      </c>
+      <c r="G23" s="1">
+        <v>200019</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:7">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2067,13 +2139,16 @@
         <v>100020</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
+        <v>50</v>
+      </c>
+      <c r="G24" s="1">
+        <v>200020</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
       <c r="A25">
         <f t="shared" si="0"/>
         <v>1001</v>
@@ -2090,13 +2165,16 @@
         <v>101001</v>
       </c>
       <c r="E25" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F25" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
+        <v>52</v>
+      </c>
+      <c r="G25">
+        <v>201001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
       <c r="A26">
         <f t="shared" si="0"/>
         <v>1002</v>
@@ -2113,13 +2191,16 @@
         <v>101002</v>
       </c>
       <c r="E26" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
+        <v>54</v>
+      </c>
+      <c r="G26">
+        <v>201002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
       <c r="A27">
         <f t="shared" si="0"/>
         <v>1003</v>
@@ -2136,13 +2217,16 @@
         <v>101003</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
+        <v>56</v>
+      </c>
+      <c r="G27">
+        <v>201003</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
       <c r="A28">
         <f t="shared" si="0"/>
         <v>1004</v>
@@ -2159,13 +2243,16 @@
         <v>101004</v>
       </c>
       <c r="E28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F28" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
+        <v>58</v>
+      </c>
+      <c r="G28">
+        <v>201004</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
       <c r="A29">
         <f t="shared" si="0"/>
         <v>1005</v>
@@ -2182,13 +2269,16 @@
         <v>101005</v>
       </c>
       <c r="E29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F29" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
+        <v>60</v>
+      </c>
+      <c r="G29">
+        <v>201005</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
       <c r="A30">
         <f t="shared" si="0"/>
         <v>1006</v>
@@ -2205,13 +2295,16 @@
         <v>101006</v>
       </c>
       <c r="E30" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F30" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
+        <v>62</v>
+      </c>
+      <c r="G30">
+        <v>201006</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
       <c r="A31">
         <f t="shared" si="0"/>
         <v>1007</v>
@@ -2228,13 +2321,16 @@
         <v>101007</v>
       </c>
       <c r="E31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
+        <v>64</v>
+      </c>
+      <c r="G31">
+        <v>201007</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
       <c r="A32">
         <f t="shared" si="0"/>
         <v>1008</v>
@@ -2251,13 +2347,16 @@
         <v>101008</v>
       </c>
       <c r="E32" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F32" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
+        <v>66</v>
+      </c>
+      <c r="G32">
+        <v>201008</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7">
       <c r="A33">
         <f t="shared" si="0"/>
         <v>1009</v>
@@ -2274,13 +2373,16 @@
         <v>101009</v>
       </c>
       <c r="E33" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F33" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6">
+        <v>68</v>
+      </c>
+      <c r="G33">
+        <v>201009</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7">
       <c r="A34">
         <f t="shared" si="0"/>
         <v>1010</v>
@@ -2297,13 +2399,16 @@
         <v>101010</v>
       </c>
       <c r="E34" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F34" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
+        <v>70</v>
+      </c>
+      <c r="G34">
+        <v>201010</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7">
       <c r="A35">
         <f t="shared" si="0"/>
         <v>1011</v>
@@ -2320,13 +2425,16 @@
         <v>101011</v>
       </c>
       <c r="E35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F35" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
+        <v>72</v>
+      </c>
+      <c r="G35">
+        <v>201011</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>1012</v>
@@ -2343,13 +2451,16 @@
         <v>101012</v>
       </c>
       <c r="E36" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F36" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6">
+        <v>74</v>
+      </c>
+      <c r="G36">
+        <v>201012</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>1013</v>
@@ -2366,13 +2477,16 @@
         <v>101013</v>
       </c>
       <c r="E37" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F37" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
+        <v>76</v>
+      </c>
+      <c r="G37">
+        <v>201013</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>1014</v>
@@ -2389,13 +2503,16 @@
         <v>101014</v>
       </c>
       <c r="E38" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
+        <v>78</v>
+      </c>
+      <c r="G38">
+        <v>201014</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>1015</v>
@@ -2412,13 +2529,16 @@
         <v>101015</v>
       </c>
       <c r="E39" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
+        <v>80</v>
+      </c>
+      <c r="G39">
+        <v>201015</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>1016</v>
@@ -2435,13 +2555,16 @@
         <v>101016</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F40" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
+        <v>82</v>
+      </c>
+      <c r="G40">
+        <v>201016</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>1017</v>
@@ -2458,13 +2581,16 @@
         <v>101017</v>
       </c>
       <c r="E41" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
+        <v>84</v>
+      </c>
+      <c r="G41">
+        <v>201017</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>1018</v>
@@ -2481,13 +2607,16 @@
         <v>101018</v>
       </c>
       <c r="E42" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F42" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
+        <v>86</v>
+      </c>
+      <c r="G42">
+        <v>201018</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>1019</v>
@@ -2504,13 +2633,16 @@
         <v>101019</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F43" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
+        <v>88</v>
+      </c>
+      <c r="G43">
+        <v>201019</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>1020</v>
@@ -2527,13 +2659,16 @@
         <v>101020</v>
       </c>
       <c r="E44" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F44" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="45" s="2" customFormat="1" spans="1:6">
+        <v>90</v>
+      </c>
+      <c r="G44">
+        <v>201020</v>
+      </c>
+    </row>
+    <row r="45" s="2" customFormat="1" spans="1:7">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>2001</v>
@@ -2550,13 +2685,16 @@
         <v>102001</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="46" s="2" customFormat="1" spans="1:6">
+        <v>92</v>
+      </c>
+      <c r="G45" s="2">
+        <v>202001</v>
+      </c>
+    </row>
+    <row r="46" s="2" customFormat="1" spans="1:7">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>2002</v>
@@ -2573,13 +2711,16 @@
         <v>102002</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="47" s="2" customFormat="1" spans="1:6">
+        <v>94</v>
+      </c>
+      <c r="G46" s="2">
+        <v>202002</v>
+      </c>
+    </row>
+    <row r="47" s="2" customFormat="1" spans="1:7">
       <c r="A47" s="2">
         <f t="shared" ref="A47:A66" si="3">C47*1000+B47</f>
         <v>2003</v>
@@ -2596,13 +2737,16 @@
         <v>102003</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="48" s="2" customFormat="1" spans="1:6">
+        <v>96</v>
+      </c>
+      <c r="G47" s="2">
+        <v>202003</v>
+      </c>
+    </row>
+    <row r="48" s="2" customFormat="1" spans="1:7">
       <c r="A48" s="2">
         <f t="shared" si="3"/>
         <v>2004</v>
@@ -2619,13 +2763,16 @@
         <v>102004</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="49" s="2" customFormat="1" spans="1:6">
+        <v>98</v>
+      </c>
+      <c r="G48" s="2">
+        <v>202004</v>
+      </c>
+    </row>
+    <row r="49" s="2" customFormat="1" spans="1:7">
       <c r="A49" s="2">
         <f t="shared" si="3"/>
         <v>2005</v>
@@ -2642,13 +2789,16 @@
         <v>102005</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="50" s="2" customFormat="1" spans="1:6">
+        <v>100</v>
+      </c>
+      <c r="G49" s="2">
+        <v>202005</v>
+      </c>
+    </row>
+    <row r="50" s="2" customFormat="1" spans="1:7">
       <c r="A50" s="2">
         <f t="shared" si="3"/>
         <v>2006</v>
@@ -2665,13 +2815,16 @@
         <v>102006</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" s="2" customFormat="1" spans="1:6">
+        <v>102</v>
+      </c>
+      <c r="G50" s="2">
+        <v>202006</v>
+      </c>
+    </row>
+    <row r="51" s="2" customFormat="1" spans="1:7">
       <c r="A51" s="2">
         <f t="shared" si="3"/>
         <v>2007</v>
@@ -2688,13 +2841,16 @@
         <v>102007</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="52" s="2" customFormat="1" spans="1:6">
+        <v>104</v>
+      </c>
+      <c r="G51" s="2">
+        <v>202007</v>
+      </c>
+    </row>
+    <row r="52" s="2" customFormat="1" spans="1:7">
       <c r="A52" s="2">
         <f t="shared" si="3"/>
         <v>2008</v>
@@ -2711,13 +2867,16 @@
         <v>102008</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="53" s="2" customFormat="1" spans="1:6">
+        <v>106</v>
+      </c>
+      <c r="G52" s="2">
+        <v>202008</v>
+      </c>
+    </row>
+    <row r="53" s="2" customFormat="1" spans="1:7">
       <c r="A53" s="2">
         <f t="shared" si="3"/>
         <v>2009</v>
@@ -2734,13 +2893,16 @@
         <v>102009</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="54" s="2" customFormat="1" spans="1:6">
+        <v>108</v>
+      </c>
+      <c r="G53" s="2">
+        <v>202009</v>
+      </c>
+    </row>
+    <row r="54" s="2" customFormat="1" spans="1:7">
       <c r="A54" s="2">
         <f t="shared" si="3"/>
         <v>2010</v>
@@ -2757,13 +2919,16 @@
         <v>102010</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="55" s="2" customFormat="1" spans="1:6">
+        <v>110</v>
+      </c>
+      <c r="G54" s="2">
+        <v>202010</v>
+      </c>
+    </row>
+    <row r="55" s="2" customFormat="1" spans="1:7">
       <c r="A55" s="2">
         <f t="shared" si="3"/>
         <v>2011</v>
@@ -2780,13 +2945,16 @@
         <v>102011</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" s="2" customFormat="1" spans="1:6">
+        <v>112</v>
+      </c>
+      <c r="G55" s="2">
+        <v>202011</v>
+      </c>
+    </row>
+    <row r="56" s="2" customFormat="1" spans="1:7">
       <c r="A56" s="2">
         <f t="shared" si="3"/>
         <v>2012</v>
@@ -2803,13 +2971,16 @@
         <v>102012</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="57" s="2" customFormat="1" spans="1:6">
+        <v>114</v>
+      </c>
+      <c r="G56" s="2">
+        <v>202012</v>
+      </c>
+    </row>
+    <row r="57" s="2" customFormat="1" spans="1:7">
       <c r="A57" s="2">
         <f t="shared" si="3"/>
         <v>2013</v>
@@ -2826,13 +2997,16 @@
         <v>102013</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" s="2" customFormat="1" spans="1:6">
+        <v>116</v>
+      </c>
+      <c r="G57" s="2">
+        <v>202013</v>
+      </c>
+    </row>
+    <row r="58" s="2" customFormat="1" spans="1:7">
       <c r="A58" s="2">
         <f t="shared" si="3"/>
         <v>2014</v>
@@ -2849,13 +3023,16 @@
         <v>102014</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="59" s="2" customFormat="1" spans="1:6">
+        <v>118</v>
+      </c>
+      <c r="G58" s="2">
+        <v>202014</v>
+      </c>
+    </row>
+    <row r="59" s="2" customFormat="1" spans="1:7">
       <c r="A59" s="2">
         <f t="shared" si="3"/>
         <v>2015</v>
@@ -2872,13 +3049,16 @@
         <v>102015</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="60" s="2" customFormat="1" spans="1:6">
+        <v>120</v>
+      </c>
+      <c r="G59" s="2">
+        <v>202015</v>
+      </c>
+    </row>
+    <row r="60" s="2" customFormat="1" spans="1:7">
       <c r="A60" s="2">
         <f t="shared" si="3"/>
         <v>2016</v>
@@ -2895,13 +3075,16 @@
         <v>102016</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="61" s="2" customFormat="1" spans="1:6">
+        <v>122</v>
+      </c>
+      <c r="G60" s="2">
+        <v>202016</v>
+      </c>
+    </row>
+    <row r="61" s="2" customFormat="1" spans="1:7">
       <c r="A61" s="2">
         <f t="shared" si="3"/>
         <v>2017</v>
@@ -2918,13 +3101,16 @@
         <v>102017</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="1:6">
+        <v>124</v>
+      </c>
+      <c r="G61" s="2">
+        <v>202017</v>
+      </c>
+    </row>
+    <row r="62" s="2" customFormat="1" spans="1:7">
       <c r="A62" s="2">
         <f t="shared" si="3"/>
         <v>2018</v>
@@ -2941,13 +3127,16 @@
         <v>102018</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="63" s="2" customFormat="1" spans="1:6">
+        <v>126</v>
+      </c>
+      <c r="G62" s="2">
+        <v>202018</v>
+      </c>
+    </row>
+    <row r="63" s="2" customFormat="1" spans="1:7">
       <c r="A63" s="2">
         <f t="shared" si="3"/>
         <v>2019</v>
@@ -2964,13 +3153,16 @@
         <v>102019</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:6">
+        <v>128</v>
+      </c>
+      <c r="G63" s="2">
+        <v>202019</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" spans="1:7">
       <c r="A64" s="2">
         <f t="shared" si="3"/>
         <v>2020</v>
@@ -2987,13 +3179,16 @@
         <v>102020</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="65" s="3" customFormat="1" spans="1:6">
+        <v>130</v>
+      </c>
+      <c r="G64" s="2">
+        <v>202020</v>
+      </c>
+    </row>
+    <row r="65" s="3" customFormat="1" spans="1:7">
       <c r="A65" s="3">
         <f t="shared" si="3"/>
         <v>3001</v>
@@ -3010,13 +3205,16 @@
         <v>103001</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="66" s="3" customFormat="1" spans="1:6">
+        <v>132</v>
+      </c>
+      <c r="G65" s="3">
+        <v>203001</v>
+      </c>
+    </row>
+    <row r="66" s="3" customFormat="1" spans="1:7">
       <c r="A66" s="3">
         <f t="shared" si="3"/>
         <v>3002</v>
@@ -3033,13 +3231,16 @@
         <v>103002</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="67" s="3" customFormat="1" spans="1:6">
+        <v>134</v>
+      </c>
+      <c r="G66" s="3">
+        <v>203002</v>
+      </c>
+    </row>
+    <row r="67" s="3" customFormat="1" spans="1:7">
       <c r="A67" s="3">
         <f t="shared" ref="A67:A84" si="4">C67*1000+B67</f>
         <v>3003</v>
@@ -3056,13 +3257,16 @@
         <v>103003</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="68" s="3" customFormat="1" spans="1:6">
+        <v>136</v>
+      </c>
+      <c r="G67" s="3">
+        <v>203003</v>
+      </c>
+    </row>
+    <row r="68" s="3" customFormat="1" spans="1:7">
       <c r="A68" s="3">
         <f t="shared" si="4"/>
         <v>3004</v>
@@ -3079,13 +3283,16 @@
         <v>103004</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="69" s="3" customFormat="1" spans="1:6">
+        <v>138</v>
+      </c>
+      <c r="G68" s="3">
+        <v>203004</v>
+      </c>
+    </row>
+    <row r="69" s="3" customFormat="1" spans="1:7">
       <c r="A69" s="3">
         <f t="shared" si="4"/>
         <v>3005</v>
@@ -3102,13 +3309,16 @@
         <v>103005</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="70" s="3" customFormat="1" spans="1:6">
+        <v>140</v>
+      </c>
+      <c r="G69" s="3">
+        <v>203005</v>
+      </c>
+    </row>
+    <row r="70" s="3" customFormat="1" spans="1:7">
       <c r="A70" s="3">
         <f t="shared" si="4"/>
         <v>3006</v>
@@ -3125,13 +3335,16 @@
         <v>103006</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="71" s="3" customFormat="1" spans="1:6">
+        <v>142</v>
+      </c>
+      <c r="G70" s="3">
+        <v>203006</v>
+      </c>
+    </row>
+    <row r="71" s="3" customFormat="1" spans="1:7">
       <c r="A71" s="3">
         <f t="shared" si="4"/>
         <v>3007</v>
@@ -3148,13 +3361,16 @@
         <v>103007</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="72" s="3" customFormat="1" spans="1:6">
+        <v>144</v>
+      </c>
+      <c r="G71" s="3">
+        <v>203007</v>
+      </c>
+    </row>
+    <row r="72" s="3" customFormat="1" spans="1:7">
       <c r="A72" s="3">
         <f t="shared" si="4"/>
         <v>3008</v>
@@ -3171,13 +3387,16 @@
         <v>103008</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="73" s="3" customFormat="1" spans="1:6">
+        <v>146</v>
+      </c>
+      <c r="G72" s="3">
+        <v>203008</v>
+      </c>
+    </row>
+    <row r="73" s="3" customFormat="1" spans="1:7">
       <c r="A73" s="3">
         <f t="shared" si="4"/>
         <v>3009</v>
@@ -3194,13 +3413,16 @@
         <v>103009</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="74" s="3" customFormat="1" spans="1:6">
+        <v>148</v>
+      </c>
+      <c r="G73" s="3">
+        <v>203009</v>
+      </c>
+    </row>
+    <row r="74" s="3" customFormat="1" spans="1:7">
       <c r="A74" s="3">
         <f t="shared" si="4"/>
         <v>3010</v>
@@ -3217,13 +3439,16 @@
         <v>103010</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="75" s="3" customFormat="1" spans="1:6">
+        <v>150</v>
+      </c>
+      <c r="G74" s="3">
+        <v>203010</v>
+      </c>
+    </row>
+    <row r="75" s="3" customFormat="1" spans="1:7">
       <c r="A75" s="3">
         <f t="shared" si="4"/>
         <v>3011</v>
@@ -3240,13 +3465,16 @@
         <v>103011</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="76" s="3" customFormat="1" spans="1:6">
+        <v>152</v>
+      </c>
+      <c r="G75" s="3">
+        <v>203011</v>
+      </c>
+    </row>
+    <row r="76" s="3" customFormat="1" spans="1:7">
       <c r="A76" s="3">
         <f t="shared" si="4"/>
         <v>3012</v>
@@ -3263,13 +3491,16 @@
         <v>103012</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" s="3" customFormat="1" spans="1:6">
+        <v>154</v>
+      </c>
+      <c r="G76" s="3">
+        <v>203012</v>
+      </c>
+    </row>
+    <row r="77" s="3" customFormat="1" spans="1:7">
       <c r="A77" s="3">
         <f t="shared" si="4"/>
         <v>3013</v>
@@ -3286,13 +3517,16 @@
         <v>103013</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="78" s="3" customFormat="1" spans="1:6">
+        <v>156</v>
+      </c>
+      <c r="G77" s="3">
+        <v>203013</v>
+      </c>
+    </row>
+    <row r="78" s="3" customFormat="1" spans="1:7">
       <c r="A78" s="3">
         <f t="shared" si="4"/>
         <v>3014</v>
@@ -3309,13 +3543,16 @@
         <v>103014</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="79" s="3" customFormat="1" spans="1:6">
+        <v>158</v>
+      </c>
+      <c r="G78" s="3">
+        <v>203014</v>
+      </c>
+    </row>
+    <row r="79" s="3" customFormat="1" spans="1:7">
       <c r="A79" s="3">
         <f t="shared" si="4"/>
         <v>3015</v>
@@ -3332,13 +3569,16 @@
         <v>103015</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="80" s="3" customFormat="1" spans="1:6">
+        <v>160</v>
+      </c>
+      <c r="G79" s="3">
+        <v>203015</v>
+      </c>
+    </row>
+    <row r="80" s="3" customFormat="1" spans="1:7">
       <c r="A80" s="3">
         <f t="shared" si="4"/>
         <v>3016</v>
@@ -3355,13 +3595,16 @@
         <v>103016</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="81" s="3" customFormat="1" spans="1:6">
+        <v>162</v>
+      </c>
+      <c r="G80" s="3">
+        <v>203016</v>
+      </c>
+    </row>
+    <row r="81" s="3" customFormat="1" spans="1:7">
       <c r="A81" s="3">
         <f t="shared" si="4"/>
         <v>3017</v>
@@ -3378,13 +3621,16 @@
         <v>103017</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="82" s="3" customFormat="1" spans="1:6">
+        <v>164</v>
+      </c>
+      <c r="G81" s="3">
+        <v>203017</v>
+      </c>
+    </row>
+    <row r="82" s="3" customFormat="1" spans="1:7">
       <c r="A82" s="3">
         <f t="shared" si="4"/>
         <v>3018</v>
@@ -3401,13 +3647,16 @@
         <v>103018</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="83" s="3" customFormat="1" spans="1:6">
+        <v>166</v>
+      </c>
+      <c r="G82" s="3">
+        <v>203018</v>
+      </c>
+    </row>
+    <row r="83" s="3" customFormat="1" spans="1:7">
       <c r="A83" s="3">
         <f t="shared" si="4"/>
         <v>3019</v>
@@ -3424,13 +3673,16 @@
         <v>103019</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="84" s="3" customFormat="1" spans="1:6">
+        <v>168</v>
+      </c>
+      <c r="G83" s="3">
+        <v>203019</v>
+      </c>
+    </row>
+    <row r="84" s="3" customFormat="1" spans="1:7">
       <c r="A84" s="3">
         <f t="shared" si="4"/>
         <v>3020</v>
@@ -3447,10 +3699,13 @@
         <v>103020</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
+      </c>
+      <c r="G84" s="3">
+        <v>203020</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -50,10 +50,29 @@
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
-0：头像
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="12"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>0：头像
 1：头像边框
 2：国旗
-3：头衔/称号</t>
+3：头衔/称号
+4：筹码
+5：牌背
+6：大厅背景</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">	</t>
         </r>
       </text>
     </comment>
@@ -84,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="233">
   <si>
     <t>id</t>
   </si>
@@ -101,6 +120,9 @@
     <t>资源描述</t>
   </si>
   <si>
+    <t>获得条件</t>
+  </si>
+  <si>
     <t>int</t>
   </si>
   <si>
@@ -119,6 +141,9 @@
     <t>Dec</t>
   </si>
   <si>
+    <t>VIPLevel</t>
+  </si>
+  <si>
     <t>头像1</t>
   </si>
   <si>
@@ -597,6 +622,186 @@
   </si>
   <si>
     <t>Title_020.png</t>
+  </si>
+  <si>
+    <t>筹码1</t>
+  </si>
+  <si>
+    <t>筹码2</t>
+  </si>
+  <si>
+    <t>筹码3</t>
+  </si>
+  <si>
+    <t>筹码4</t>
+  </si>
+  <si>
+    <t>筹码5</t>
+  </si>
+  <si>
+    <t>筹码6</t>
+  </si>
+  <si>
+    <t>筹码7</t>
+  </si>
+  <si>
+    <t>筹码8</t>
+  </si>
+  <si>
+    <t>筹码9</t>
+  </si>
+  <si>
+    <t>筹码10</t>
+  </si>
+  <si>
+    <t>筹码11</t>
+  </si>
+  <si>
+    <t>筹码12</t>
+  </si>
+  <si>
+    <t>筹码13</t>
+  </si>
+  <si>
+    <t>筹码14</t>
+  </si>
+  <si>
+    <t>筹码15</t>
+  </si>
+  <si>
+    <t>筹码16</t>
+  </si>
+  <si>
+    <t>筹码17</t>
+  </si>
+  <si>
+    <t>筹码18</t>
+  </si>
+  <si>
+    <t>筹码19</t>
+  </si>
+  <si>
+    <t>筹码20</t>
+  </si>
+  <si>
+    <t>牌背1</t>
+  </si>
+  <si>
+    <t>牌背2</t>
+  </si>
+  <si>
+    <t>牌背3</t>
+  </si>
+  <si>
+    <t>牌背4</t>
+  </si>
+  <si>
+    <t>牌背5</t>
+  </si>
+  <si>
+    <t>牌背6</t>
+  </si>
+  <si>
+    <t>牌背7</t>
+  </si>
+  <si>
+    <t>牌背8</t>
+  </si>
+  <si>
+    <t>牌背9</t>
+  </si>
+  <si>
+    <t>牌背10</t>
+  </si>
+  <si>
+    <t>牌背11</t>
+  </si>
+  <si>
+    <t>牌背12</t>
+  </si>
+  <si>
+    <t>牌背13</t>
+  </si>
+  <si>
+    <t>牌背14</t>
+  </si>
+  <si>
+    <t>牌背15</t>
+  </si>
+  <si>
+    <t>牌背16</t>
+  </si>
+  <si>
+    <t>牌背17</t>
+  </si>
+  <si>
+    <t>牌背18</t>
+  </si>
+  <si>
+    <t>牌背19</t>
+  </si>
+  <si>
+    <t>牌背20</t>
+  </si>
+  <si>
+    <t>大厅背景1</t>
+  </si>
+  <si>
+    <t>大厅背景2</t>
+  </si>
+  <si>
+    <t>大厅背景3</t>
+  </si>
+  <si>
+    <t>大厅背景4</t>
+  </si>
+  <si>
+    <t>大厅背景5</t>
+  </si>
+  <si>
+    <t>大厅背景6</t>
+  </si>
+  <si>
+    <t>大厅背景7</t>
+  </si>
+  <si>
+    <t>大厅背景8</t>
+  </si>
+  <si>
+    <t>大厅背景9</t>
+  </si>
+  <si>
+    <t>大厅背景10</t>
+  </si>
+  <si>
+    <t>大厅背景11</t>
+  </si>
+  <si>
+    <t>大厅背景12</t>
+  </si>
+  <si>
+    <t>大厅背景13</t>
+  </si>
+  <si>
+    <t>大厅背景14</t>
+  </si>
+  <si>
+    <t>大厅背景15</t>
+  </si>
+  <si>
+    <t>大厅背景16</t>
+  </si>
+  <si>
+    <t>大厅背景17</t>
+  </si>
+  <si>
+    <t>大厅背景18</t>
+  </si>
+  <si>
+    <t>大厅背景19</t>
+  </si>
+  <si>
+    <t>大厅背景20</t>
   </si>
 </sst>
 </file>
@@ -609,7 +814,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -772,8 +977,13 @@
       <name val="宋体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="39">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -795,6 +1005,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1117,7 +1345,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1141,16 +1369,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1159,89 +1387,89 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1252,6 +1480,18 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1565,16 +1805,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G84"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="6"/>
+  <dimension ref="A1:H144"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
     <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="19.125" customWidth="1"/>
     <col min="7" max="7" width="12.5" customWidth="1"/>
+    <col min="8" max="8" width="12.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:7">
+    <row r="1" customFormat="1" spans="1:8">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1591,41 +1832,50 @@
       <c r="G1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" customFormat="1" spans="1:7">
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="1" spans="1:8">
       <c r="A2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B2"/>
       <c r="C2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" customFormat="1" spans="1:7">
+      <c r="H2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="1" spans="1:8">
       <c r="A3" t="s">
         <v>0</v>
       </c>
       <c r="B3"/>
       <c r="C3" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G3" t="s">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="H3" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="5" s="1" customFormat="1" spans="1:7">
@@ -1645,10 +1895,10 @@
         <v>100001</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="G5" s="1">
         <v>200001</v>
@@ -1671,10 +1921,10 @@
         <v>100002</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G6" s="1">
         <v>200002</v>
@@ -1697,10 +1947,10 @@
         <v>100003</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" s="1">
         <v>200003</v>
@@ -1723,10 +1973,10 @@
         <v>100004</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G8" s="1">
         <v>200004</v>
@@ -1749,10 +1999,10 @@
         <v>100005</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1">
         <v>200005</v>
@@ -1775,10 +2025,10 @@
         <v>100006</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G10" s="1">
         <v>200006</v>
@@ -1801,10 +2051,10 @@
         <v>100007</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G11" s="1">
         <v>200007</v>
@@ -1827,10 +2077,10 @@
         <v>100008</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G12" s="1">
         <v>200008</v>
@@ -1853,10 +2103,10 @@
         <v>100009</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G13" s="1">
         <v>200009</v>
@@ -1879,10 +2129,10 @@
         <v>100010</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G14" s="1">
         <v>200010</v>
@@ -1905,16 +2155,16 @@
         <v>100011</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G15" s="1">
         <v>200011</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:7">
+    <row r="16" s="1" customFormat="1" spans="1:8">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1931,16 +2181,19 @@
         <v>100012</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G16" s="1">
         <v>200012</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:7">
+      <c r="H16" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:8">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1957,16 +2210,19 @@
         <v>100013</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G17" s="1">
         <v>200013</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:7">
+      <c r="H17" s="1">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:8">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1983,16 +2239,19 @@
         <v>100014</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G18" s="1">
         <v>200014</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:7">
+      <c r="H18" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:8">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2009,16 +2268,19 @@
         <v>100015</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G19" s="1">
         <v>200015</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:7">
+      <c r="H19" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:8">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2035,16 +2297,19 @@
         <v>100016</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G20" s="1">
         <v>200016</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:7">
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:8">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2061,16 +2326,19 @@
         <v>100017</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G21" s="1">
         <v>200017</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:7">
+      <c r="H21" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:8">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2087,16 +2355,19 @@
         <v>100018</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G22" s="1">
         <v>200018</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:7">
+      <c r="H22" s="1">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:8">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2113,16 +2384,19 @@
         <v>100019</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G23" s="1">
         <v>200019</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:7">
+      <c r="H23" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:8">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2139,13 +2413,16 @@
         <v>100020</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G24" s="1">
         <v>200020</v>
+      </c>
+      <c r="H24" s="1">
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -2165,10 +2442,10 @@
         <v>101001</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F25" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G25">
         <v>201001</v>
@@ -2191,10 +2468,10 @@
         <v>101002</v>
       </c>
       <c r="E26" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F26" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G26">
         <v>201002</v>
@@ -2217,10 +2494,10 @@
         <v>101003</v>
       </c>
       <c r="E27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G27">
         <v>201003</v>
@@ -2243,10 +2520,10 @@
         <v>101004</v>
       </c>
       <c r="E28" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F28" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G28">
         <v>201004</v>
@@ -2269,10 +2546,10 @@
         <v>101005</v>
       </c>
       <c r="E29" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G29">
         <v>201005</v>
@@ -2295,10 +2572,10 @@
         <v>101006</v>
       </c>
       <c r="E30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G30">
         <v>201006</v>
@@ -2321,10 +2598,10 @@
         <v>101007</v>
       </c>
       <c r="E31" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G31">
         <v>201007</v>
@@ -2347,10 +2624,10 @@
         <v>101008</v>
       </c>
       <c r="E32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G32">
         <v>201008</v>
@@ -2373,10 +2650,10 @@
         <v>101009</v>
       </c>
       <c r="E33" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G33">
         <v>201009</v>
@@ -2399,10 +2676,10 @@
         <v>101010</v>
       </c>
       <c r="E34" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G34">
         <v>201010</v>
@@ -2425,16 +2702,16 @@
         <v>101011</v>
       </c>
       <c r="E35" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F35" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="G35">
         <v>201011</v>
       </c>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:8">
       <c r="A36">
         <f t="shared" si="0"/>
         <v>1012</v>
@@ -2451,16 +2728,19 @@
         <v>101012</v>
       </c>
       <c r="E36" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F36" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G36">
         <v>201012</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
       <c r="A37">
         <f t="shared" si="0"/>
         <v>1013</v>
@@ -2477,16 +2757,19 @@
         <v>101013</v>
       </c>
       <c r="E37" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F37" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G37">
         <v>201013</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38">
         <f t="shared" si="0"/>
         <v>1014</v>
@@ -2499,20 +2782,23 @@
         <v>1</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" ref="D38:D84" si="2">100000+C38*1000+B38</f>
+        <f t="shared" ref="D38:D101" si="2">100000+C38*1000+B38</f>
         <v>101014</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G38">
         <v>201014</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39">
         <f t="shared" si="0"/>
         <v>1015</v>
@@ -2529,16 +2815,19 @@
         <v>101015</v>
       </c>
       <c r="E39" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="F39" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G39">
         <v>201015</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40">
         <f t="shared" si="0"/>
         <v>1016</v>
@@ -2555,16 +2844,19 @@
         <v>101016</v>
       </c>
       <c r="E40" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F40" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="G40">
         <v>201016</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41">
         <f t="shared" si="0"/>
         <v>1017</v>
@@ -2581,16 +2873,19 @@
         <v>101017</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G41">
         <v>201017</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42">
         <f t="shared" si="0"/>
         <v>1018</v>
@@ -2607,16 +2902,19 @@
         <v>101018</v>
       </c>
       <c r="E42" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="F42" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G42">
         <v>201018</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43">
         <f t="shared" si="0"/>
         <v>1019</v>
@@ -2633,16 +2931,19 @@
         <v>101019</v>
       </c>
       <c r="E43" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F43" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G43">
         <v>201019</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" s="7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44">
         <f t="shared" si="0"/>
         <v>1020</v>
@@ -2659,13 +2960,16 @@
         <v>101020</v>
       </c>
       <c r="E44" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="F44" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="G44">
         <v>201020</v>
+      </c>
+      <c r="H44" s="7">
+        <v>9</v>
       </c>
     </row>
     <row r="45" s="2" customFormat="1" spans="1:7">
@@ -2685,10 +2989,10 @@
         <v>102001</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G45" s="2">
         <v>202001</v>
@@ -2711,10 +3015,10 @@
         <v>102002</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="G46" s="2">
         <v>202002</v>
@@ -2737,10 +3041,10 @@
         <v>102003</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G47" s="2">
         <v>202003</v>
@@ -2763,10 +3067,10 @@
         <v>102004</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G48" s="2">
         <v>202004</v>
@@ -2789,10 +3093,10 @@
         <v>102005</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G49" s="2">
         <v>202005</v>
@@ -2815,10 +3119,10 @@
         <v>102006</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G50" s="2">
         <v>202006</v>
@@ -2841,10 +3145,10 @@
         <v>102007</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G51" s="2">
         <v>202007</v>
@@ -2867,10 +3171,10 @@
         <v>102008</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="G52" s="2">
         <v>202008</v>
@@ -2893,10 +3197,10 @@
         <v>102009</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="G53" s="2">
         <v>202009</v>
@@ -2919,10 +3223,10 @@
         <v>102010</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="G54" s="2">
         <v>202010</v>
@@ -2945,10 +3249,10 @@
         <v>102011</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G55" s="2">
         <v>202011</v>
@@ -2971,10 +3275,10 @@
         <v>102012</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="G56" s="2">
         <v>202012</v>
@@ -2997,10 +3301,10 @@
         <v>102013</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G57" s="2">
         <v>202013</v>
@@ -3023,10 +3327,10 @@
         <v>102014</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G58" s="2">
         <v>202014</v>
@@ -3049,10 +3353,10 @@
         <v>102015</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="G59" s="2">
         <v>202015</v>
@@ -3075,10 +3379,10 @@
         <v>102016</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G60" s="2">
         <v>202016</v>
@@ -3101,10 +3405,10 @@
         <v>102017</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="G61" s="2">
         <v>202017</v>
@@ -3127,10 +3431,10 @@
         <v>102018</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="G62" s="2">
         <v>202018</v>
@@ -3153,10 +3457,10 @@
         <v>102019</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="G63" s="2">
         <v>202019</v>
@@ -3179,10 +3483,10 @@
         <v>102020</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G64" s="2">
         <v>202020</v>
@@ -3205,16 +3509,16 @@
         <v>103001</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="G65" s="3">
         <v>203001</v>
       </c>
     </row>
-    <row r="66" s="3" customFormat="1" spans="1:7">
+    <row r="66" s="3" customFormat="1" spans="1:8">
       <c r="A66" s="3">
         <f t="shared" si="3"/>
         <v>3002</v>
@@ -3231,18 +3535,21 @@
         <v>103002</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G66" s="3">
         <v>203002</v>
       </c>
-    </row>
-    <row r="67" s="3" customFormat="1" spans="1:7">
+      <c r="H66" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" s="3" customFormat="1" spans="1:8">
       <c r="A67" s="3">
-        <f t="shared" ref="A67:A84" si="4">C67*1000+B67</f>
+        <f t="shared" ref="A67:A130" si="4">C67*1000+B67</f>
         <v>3003</v>
       </c>
       <c r="B67" s="3">
@@ -3257,16 +3564,19 @@
         <v>103003</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="G67" s="3">
         <v>203003</v>
       </c>
-    </row>
-    <row r="68" s="3" customFormat="1" spans="1:7">
+      <c r="H67" s="3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="68" s="3" customFormat="1" spans="1:8">
       <c r="A68" s="3">
         <f t="shared" si="4"/>
         <v>3004</v>
@@ -3283,16 +3593,19 @@
         <v>103004</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="G68" s="3">
         <v>203004</v>
       </c>
-    </row>
-    <row r="69" s="3" customFormat="1" spans="1:7">
+      <c r="H68" s="3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" s="3" customFormat="1" spans="1:8">
       <c r="A69" s="3">
         <f t="shared" si="4"/>
         <v>3005</v>
@@ -3309,16 +3622,19 @@
         <v>103005</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G69" s="3">
         <v>203005</v>
       </c>
-    </row>
-    <row r="70" s="3" customFormat="1" spans="1:7">
+      <c r="H69" s="3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" s="3" customFormat="1" spans="1:8">
       <c r="A70" s="3">
         <f t="shared" si="4"/>
         <v>3006</v>
@@ -3335,16 +3651,19 @@
         <v>103006</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G70" s="3">
         <v>203006</v>
       </c>
-    </row>
-    <row r="71" s="3" customFormat="1" spans="1:7">
+      <c r="H70" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" s="3" customFormat="1" spans="1:8">
       <c r="A71" s="3">
         <f t="shared" si="4"/>
         <v>3007</v>
@@ -3361,16 +3680,19 @@
         <v>103007</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="G71" s="3">
         <v>203007</v>
       </c>
-    </row>
-    <row r="72" s="3" customFormat="1" spans="1:7">
+      <c r="H71" s="3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="72" s="3" customFormat="1" spans="1:8">
       <c r="A72" s="3">
         <f t="shared" si="4"/>
         <v>3008</v>
@@ -3387,16 +3709,19 @@
         <v>103008</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="G72" s="3">
         <v>203008</v>
       </c>
-    </row>
-    <row r="73" s="3" customFormat="1" spans="1:7">
+      <c r="H72" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" s="3" customFormat="1" spans="1:8">
       <c r="A73" s="3">
         <f t="shared" si="4"/>
         <v>3009</v>
@@ -3413,13 +3738,16 @@
         <v>103009</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G73" s="3">
         <v>203009</v>
+      </c>
+      <c r="H73" s="3">
+        <v>9</v>
       </c>
     </row>
     <row r="74" s="3" customFormat="1" spans="1:7">
@@ -3439,10 +3767,10 @@
         <v>103010</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G74" s="3">
         <v>203010</v>
@@ -3465,10 +3793,10 @@
         <v>103011</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G75" s="3">
         <v>203011</v>
@@ -3491,10 +3819,10 @@
         <v>103012</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G76" s="3">
         <v>203012</v>
@@ -3517,10 +3845,10 @@
         <v>103013</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G77" s="3">
         <v>203013</v>
@@ -3543,10 +3871,10 @@
         <v>103014</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G78" s="3">
         <v>203014</v>
@@ -3569,10 +3897,10 @@
         <v>103015</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="G79" s="3">
         <v>203015</v>
@@ -3595,10 +3923,10 @@
         <v>103016</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="G80" s="3">
         <v>203016</v>
@@ -3621,10 +3949,10 @@
         <v>103017</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G81" s="3">
         <v>203017</v>
@@ -3647,10 +3975,10 @@
         <v>103018</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="G82" s="3">
         <v>203018</v>
@@ -3673,10 +4001,10 @@
         <v>103019</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F83" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G83" s="3">
         <v>203019</v>
@@ -3699,13 +4027,1714 @@
         <v>103020</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F84" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G84" s="3">
         <v>203020</v>
+      </c>
+    </row>
+    <row r="85" s="4" customFormat="1" spans="1:7">
+      <c r="A85" s="4">
+        <f t="shared" si="4"/>
+        <v>4001</v>
+      </c>
+      <c r="B85" s="4">
+        <f>COUNTIF($C$1:C85,C85)</f>
+        <v>1</v>
+      </c>
+      <c r="C85" s="4">
+        <v>4</v>
+      </c>
+      <c r="D85" s="4">
+        <f t="shared" si="2"/>
+        <v>104001</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="G85" s="4">
+        <f>200000+A85</f>
+        <v>204001</v>
+      </c>
+    </row>
+    <row r="86" s="4" customFormat="1" spans="1:8">
+      <c r="A86" s="4">
+        <f t="shared" si="4"/>
+        <v>4002</v>
+      </c>
+      <c r="B86" s="4">
+        <f>COUNTIF($C$1:C86,C86)</f>
+        <v>2</v>
+      </c>
+      <c r="C86" s="4">
+        <v>4</v>
+      </c>
+      <c r="D86" s="4">
+        <f t="shared" si="2"/>
+        <v>104002</v>
+      </c>
+      <c r="E86" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="G86" s="4">
+        <f t="shared" ref="G86:G144" si="5">200000+A86</f>
+        <v>204002</v>
+      </c>
+      <c r="H86" s="4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="87" s="4" customFormat="1" spans="1:8">
+      <c r="A87" s="4">
+        <f t="shared" si="4"/>
+        <v>4003</v>
+      </c>
+      <c r="B87" s="4">
+        <f>COUNTIF($C$1:C87,C87)</f>
+        <v>3</v>
+      </c>
+      <c r="C87" s="4">
+        <v>4</v>
+      </c>
+      <c r="D87" s="4">
+        <f t="shared" si="2"/>
+        <v>104003</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="G87" s="4">
+        <f t="shared" si="5"/>
+        <v>204003</v>
+      </c>
+      <c r="H87" s="4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="88" s="4" customFormat="1" spans="1:8">
+      <c r="A88" s="4">
+        <f t="shared" si="4"/>
+        <v>4004</v>
+      </c>
+      <c r="B88" s="4">
+        <f>COUNTIF($C$1:C88,C88)</f>
+        <v>4</v>
+      </c>
+      <c r="C88" s="4">
+        <v>4</v>
+      </c>
+      <c r="D88" s="4">
+        <f t="shared" si="2"/>
+        <v>104004</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="5"/>
+        <v>204004</v>
+      </c>
+      <c r="H88" s="4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="89" s="4" customFormat="1" spans="1:8">
+      <c r="A89" s="4">
+        <f t="shared" si="4"/>
+        <v>4005</v>
+      </c>
+      <c r="B89" s="4">
+        <f>COUNTIF($C$1:C89,C89)</f>
+        <v>5</v>
+      </c>
+      <c r="C89" s="4">
+        <v>4</v>
+      </c>
+      <c r="D89" s="4">
+        <f t="shared" si="2"/>
+        <v>104005</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="G89" s="4">
+        <f t="shared" si="5"/>
+        <v>204005</v>
+      </c>
+      <c r="H89" s="4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" s="4" customFormat="1" spans="1:8">
+      <c r="A90" s="4">
+        <f t="shared" si="4"/>
+        <v>4006</v>
+      </c>
+      <c r="B90" s="4">
+        <f>COUNTIF($C$1:C90,C90)</f>
+        <v>6</v>
+      </c>
+      <c r="C90" s="4">
+        <v>4</v>
+      </c>
+      <c r="D90" s="4">
+        <f t="shared" si="2"/>
+        <v>104006</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="G90" s="4">
+        <f t="shared" si="5"/>
+        <v>204006</v>
+      </c>
+      <c r="H90" s="4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" s="4" customFormat="1" spans="1:8">
+      <c r="A91" s="4">
+        <f t="shared" si="4"/>
+        <v>4007</v>
+      </c>
+      <c r="B91" s="4">
+        <f>COUNTIF($C$1:C91,C91)</f>
+        <v>7</v>
+      </c>
+      <c r="C91" s="4">
+        <v>4</v>
+      </c>
+      <c r="D91" s="4">
+        <f t="shared" si="2"/>
+        <v>104007</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="G91" s="4">
+        <f t="shared" si="5"/>
+        <v>204007</v>
+      </c>
+      <c r="H91" s="4">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" s="4" customFormat="1" spans="1:8">
+      <c r="A92" s="4">
+        <f t="shared" si="4"/>
+        <v>4008</v>
+      </c>
+      <c r="B92" s="4">
+        <f>COUNTIF($C$1:C92,C92)</f>
+        <v>8</v>
+      </c>
+      <c r="C92" s="4">
+        <v>4</v>
+      </c>
+      <c r="D92" s="4">
+        <f t="shared" si="2"/>
+        <v>104008</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="G92" s="4">
+        <f t="shared" si="5"/>
+        <v>204008</v>
+      </c>
+      <c r="H92" s="4">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="93" s="4" customFormat="1" spans="1:8">
+      <c r="A93" s="4">
+        <f t="shared" si="4"/>
+        <v>4009</v>
+      </c>
+      <c r="B93" s="4">
+        <f>COUNTIF($C$1:C93,C93)</f>
+        <v>9</v>
+      </c>
+      <c r="C93" s="4">
+        <v>4</v>
+      </c>
+      <c r="D93" s="4">
+        <f t="shared" si="2"/>
+        <v>104009</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G93" s="4">
+        <f t="shared" si="5"/>
+        <v>204009</v>
+      </c>
+      <c r="H93" s="4">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="94" s="4" customFormat="1" spans="1:8">
+      <c r="A94" s="4">
+        <f t="shared" si="4"/>
+        <v>4010</v>
+      </c>
+      <c r="B94" s="4">
+        <f>COUNTIF($C$1:C94,C94)</f>
+        <v>10</v>
+      </c>
+      <c r="C94" s="4">
+        <v>4</v>
+      </c>
+      <c r="D94" s="4">
+        <f t="shared" si="2"/>
+        <v>104010</v>
+      </c>
+      <c r="E94" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="F94" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="G94" s="4">
+        <f t="shared" si="5"/>
+        <v>204010</v>
+      </c>
+      <c r="H94" s="4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="95" s="4" customFormat="1" spans="1:7">
+      <c r="A95" s="4">
+        <f t="shared" si="4"/>
+        <v>4011</v>
+      </c>
+      <c r="B95" s="4">
+        <f>COUNTIF($C$1:C95,C95)</f>
+        <v>11</v>
+      </c>
+      <c r="C95" s="4">
+        <v>4</v>
+      </c>
+      <c r="D95" s="4">
+        <f t="shared" si="2"/>
+        <v>104011</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="G95" s="4">
+        <f t="shared" si="5"/>
+        <v>204011</v>
+      </c>
+    </row>
+    <row r="96" s="4" customFormat="1" spans="1:7">
+      <c r="A96" s="4">
+        <f t="shared" si="4"/>
+        <v>4012</v>
+      </c>
+      <c r="B96" s="4">
+        <f>COUNTIF($C$1:C96,C96)</f>
+        <v>12</v>
+      </c>
+      <c r="C96" s="4">
+        <v>4</v>
+      </c>
+      <c r="D96" s="4">
+        <f t="shared" si="2"/>
+        <v>104012</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="G96" s="4">
+        <f t="shared" si="5"/>
+        <v>204012</v>
+      </c>
+    </row>
+    <row r="97" s="4" customFormat="1" spans="1:7">
+      <c r="A97" s="4">
+        <f t="shared" si="4"/>
+        <v>4013</v>
+      </c>
+      <c r="B97" s="4">
+        <f>COUNTIF($C$1:C97,C97)</f>
+        <v>13</v>
+      </c>
+      <c r="C97" s="4">
+        <v>4</v>
+      </c>
+      <c r="D97" s="4">
+        <f t="shared" si="2"/>
+        <v>104013</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G97" s="4">
+        <f t="shared" si="5"/>
+        <v>204013</v>
+      </c>
+    </row>
+    <row r="98" s="4" customFormat="1" spans="1:7">
+      <c r="A98" s="4">
+        <f t="shared" si="4"/>
+        <v>4014</v>
+      </c>
+      <c r="B98" s="4">
+        <f>COUNTIF($C$1:C98,C98)</f>
+        <v>14</v>
+      </c>
+      <c r="C98" s="4">
+        <v>4</v>
+      </c>
+      <c r="D98" s="4">
+        <f t="shared" si="2"/>
+        <v>104014</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G98" s="4">
+        <f t="shared" si="5"/>
+        <v>204014</v>
+      </c>
+    </row>
+    <row r="99" s="4" customFormat="1" spans="1:7">
+      <c r="A99" s="4">
+        <f t="shared" si="4"/>
+        <v>4015</v>
+      </c>
+      <c r="B99" s="4">
+        <f>COUNTIF($C$1:C99,C99)</f>
+        <v>15</v>
+      </c>
+      <c r="C99" s="4">
+        <v>4</v>
+      </c>
+      <c r="D99" s="4">
+        <f t="shared" si="2"/>
+        <v>104015</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="F99" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G99" s="4">
+        <f t="shared" si="5"/>
+        <v>204015</v>
+      </c>
+    </row>
+    <row r="100" s="4" customFormat="1" spans="1:7">
+      <c r="A100" s="4">
+        <f t="shared" si="4"/>
+        <v>4016</v>
+      </c>
+      <c r="B100" s="4">
+        <f>COUNTIF($C$1:C100,C100)</f>
+        <v>16</v>
+      </c>
+      <c r="C100" s="4">
+        <v>4</v>
+      </c>
+      <c r="D100" s="4">
+        <f t="shared" si="2"/>
+        <v>104016</v>
+      </c>
+      <c r="E100" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="F100" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="G100" s="4">
+        <f t="shared" si="5"/>
+        <v>204016</v>
+      </c>
+    </row>
+    <row r="101" s="4" customFormat="1" spans="1:7">
+      <c r="A101" s="4">
+        <f t="shared" si="4"/>
+        <v>4017</v>
+      </c>
+      <c r="B101" s="4">
+        <f>COUNTIF($C$1:C101,C101)</f>
+        <v>17</v>
+      </c>
+      <c r="C101" s="4">
+        <v>4</v>
+      </c>
+      <c r="D101" s="4">
+        <f t="shared" si="2"/>
+        <v>104017</v>
+      </c>
+      <c r="E101" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="F101" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="G101" s="4">
+        <f t="shared" si="5"/>
+        <v>204017</v>
+      </c>
+    </row>
+    <row r="102" s="4" customFormat="1" spans="1:7">
+      <c r="A102" s="4">
+        <f t="shared" si="4"/>
+        <v>4018</v>
+      </c>
+      <c r="B102" s="4">
+        <f>COUNTIF($C$1:C102,C102)</f>
+        <v>18</v>
+      </c>
+      <c r="C102" s="4">
+        <v>4</v>
+      </c>
+      <c r="D102" s="4">
+        <f t="shared" ref="D102:D144" si="6">100000+C102*1000+B102</f>
+        <v>104018</v>
+      </c>
+      <c r="E102" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="F102" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="G102" s="4">
+        <f t="shared" si="5"/>
+        <v>204018</v>
+      </c>
+    </row>
+    <row r="103" s="4" customFormat="1" spans="1:7">
+      <c r="A103" s="4">
+        <f t="shared" si="4"/>
+        <v>4019</v>
+      </c>
+      <c r="B103" s="4">
+        <f>COUNTIF($C$1:C103,C103)</f>
+        <v>19</v>
+      </c>
+      <c r="C103" s="4">
+        <v>4</v>
+      </c>
+      <c r="D103" s="4">
+        <f t="shared" si="6"/>
+        <v>104019</v>
+      </c>
+      <c r="E103" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="G103" s="4">
+        <f t="shared" si="5"/>
+        <v>204019</v>
+      </c>
+    </row>
+    <row r="104" s="4" customFormat="1" spans="1:7">
+      <c r="A104" s="4">
+        <f t="shared" si="4"/>
+        <v>4020</v>
+      </c>
+      <c r="B104" s="4">
+        <f>COUNTIF($C$1:C104,C104)</f>
+        <v>20</v>
+      </c>
+      <c r="C104" s="4">
+        <v>4</v>
+      </c>
+      <c r="D104" s="4">
+        <f t="shared" si="6"/>
+        <v>104020</v>
+      </c>
+      <c r="E104" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="G104" s="4">
+        <f t="shared" si="5"/>
+        <v>204020</v>
+      </c>
+    </row>
+    <row r="105" s="5" customFormat="1" spans="1:7">
+      <c r="A105" s="5">
+        <f t="shared" si="4"/>
+        <v>5001</v>
+      </c>
+      <c r="B105" s="5">
+        <f>COUNTIF($C$1:C105,C105)</f>
+        <v>1</v>
+      </c>
+      <c r="C105" s="5">
+        <v>5</v>
+      </c>
+      <c r="D105" s="5">
+        <f t="shared" si="6"/>
+        <v>105001</v>
+      </c>
+      <c r="E105" s="5" t="s">
+        <v>193</v>
+      </c>
+      <c r="F105" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G105" s="5">
+        <f t="shared" si="5"/>
+        <v>205001</v>
+      </c>
+    </row>
+    <row r="106" s="5" customFormat="1" spans="1:8">
+      <c r="A106" s="5">
+        <f t="shared" si="4"/>
+        <v>5002</v>
+      </c>
+      <c r="B106" s="5">
+        <f>COUNTIF($C$1:C106,C106)</f>
+        <v>2</v>
+      </c>
+      <c r="C106" s="5">
+        <v>5</v>
+      </c>
+      <c r="D106" s="5">
+        <f t="shared" si="6"/>
+        <v>105002</v>
+      </c>
+      <c r="E106" s="5" t="s">
+        <v>194</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G106" s="5">
+        <f t="shared" si="5"/>
+        <v>205002</v>
+      </c>
+      <c r="H106" s="5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" s="5" customFormat="1" spans="1:8">
+      <c r="A107" s="5">
+        <f t="shared" si="4"/>
+        <v>5003</v>
+      </c>
+      <c r="B107" s="5">
+        <f>COUNTIF($C$1:C107,C107)</f>
+        <v>3</v>
+      </c>
+      <c r="C107" s="5">
+        <v>5</v>
+      </c>
+      <c r="D107" s="5">
+        <f t="shared" si="6"/>
+        <v>105003</v>
+      </c>
+      <c r="E107" s="5" t="s">
+        <v>195</v>
+      </c>
+      <c r="F107" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G107" s="5">
+        <f t="shared" si="5"/>
+        <v>205003</v>
+      </c>
+      <c r="H107" s="5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" s="5" customFormat="1" spans="1:8">
+      <c r="A108" s="5">
+        <f t="shared" si="4"/>
+        <v>5004</v>
+      </c>
+      <c r="B108" s="5">
+        <f>COUNTIF($C$1:C108,C108)</f>
+        <v>4</v>
+      </c>
+      <c r="C108" s="5">
+        <v>5</v>
+      </c>
+      <c r="D108" s="5">
+        <f t="shared" si="6"/>
+        <v>105004</v>
+      </c>
+      <c r="E108" s="5" t="s">
+        <v>196</v>
+      </c>
+      <c r="F108" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G108" s="5">
+        <f t="shared" si="5"/>
+        <v>205004</v>
+      </c>
+      <c r="H108" s="5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" s="5" customFormat="1" spans="1:8">
+      <c r="A109" s="5">
+        <f t="shared" si="4"/>
+        <v>5005</v>
+      </c>
+      <c r="B109" s="5">
+        <f>COUNTIF($C$1:C109,C109)</f>
+        <v>5</v>
+      </c>
+      <c r="C109" s="5">
+        <v>5</v>
+      </c>
+      <c r="D109" s="5">
+        <f t="shared" si="6"/>
+        <v>105005</v>
+      </c>
+      <c r="E109" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="F109" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G109" s="5">
+        <f t="shared" si="5"/>
+        <v>205005</v>
+      </c>
+      <c r="H109" s="5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="110" s="5" customFormat="1" spans="1:8">
+      <c r="A110" s="5">
+        <f t="shared" si="4"/>
+        <v>5006</v>
+      </c>
+      <c r="B110" s="5">
+        <f>COUNTIF($C$1:C110,C110)</f>
+        <v>6</v>
+      </c>
+      <c r="C110" s="5">
+        <v>5</v>
+      </c>
+      <c r="D110" s="5">
+        <f t="shared" si="6"/>
+        <v>105006</v>
+      </c>
+      <c r="E110" s="5" t="s">
+        <v>198</v>
+      </c>
+      <c r="F110" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="G110" s="5">
+        <f t="shared" si="5"/>
+        <v>205006</v>
+      </c>
+      <c r="H110" s="5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="111" s="5" customFormat="1" spans="1:8">
+      <c r="A111" s="5">
+        <f t="shared" si="4"/>
+        <v>5007</v>
+      </c>
+      <c r="B111" s="5">
+        <f>COUNTIF($C$1:C111,C111)</f>
+        <v>7</v>
+      </c>
+      <c r="C111" s="5">
+        <v>5</v>
+      </c>
+      <c r="D111" s="5">
+        <f t="shared" si="6"/>
+        <v>105007</v>
+      </c>
+      <c r="E111" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="F111" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="G111" s="5">
+        <f t="shared" si="5"/>
+        <v>205007</v>
+      </c>
+      <c r="H111" s="5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="112" s="5" customFormat="1" spans="1:8">
+      <c r="A112" s="5">
+        <f t="shared" si="4"/>
+        <v>5008</v>
+      </c>
+      <c r="B112" s="5">
+        <f>COUNTIF($C$1:C112,C112)</f>
+        <v>8</v>
+      </c>
+      <c r="C112" s="5">
+        <v>5</v>
+      </c>
+      <c r="D112" s="5">
+        <f t="shared" si="6"/>
+        <v>105008</v>
+      </c>
+      <c r="E112" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="F112" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="G112" s="5">
+        <f t="shared" si="5"/>
+        <v>205008</v>
+      </c>
+      <c r="H112" s="5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="113" s="5" customFormat="1" spans="1:8">
+      <c r="A113" s="5">
+        <f t="shared" si="4"/>
+        <v>5009</v>
+      </c>
+      <c r="B113" s="5">
+        <f>COUNTIF($C$1:C113,C113)</f>
+        <v>9</v>
+      </c>
+      <c r="C113" s="5">
+        <v>5</v>
+      </c>
+      <c r="D113" s="5">
+        <f t="shared" si="6"/>
+        <v>105009</v>
+      </c>
+      <c r="E113" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="G113" s="5">
+        <f t="shared" si="5"/>
+        <v>205009</v>
+      </c>
+      <c r="H113" s="5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="114" s="5" customFormat="1" spans="1:8">
+      <c r="A114" s="5">
+        <f t="shared" si="4"/>
+        <v>5010</v>
+      </c>
+      <c r="B114" s="5">
+        <f>COUNTIF($C$1:C114,C114)</f>
+        <v>10</v>
+      </c>
+      <c r="C114" s="5">
+        <v>5</v>
+      </c>
+      <c r="D114" s="5">
+        <f t="shared" si="6"/>
+        <v>105010</v>
+      </c>
+      <c r="E114" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="G114" s="5">
+        <f t="shared" si="5"/>
+        <v>205010</v>
+      </c>
+      <c r="H114" s="5">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="115" s="5" customFormat="1" spans="1:7">
+      <c r="A115" s="5">
+        <f t="shared" si="4"/>
+        <v>5011</v>
+      </c>
+      <c r="B115" s="5">
+        <f>COUNTIF($C$1:C115,C115)</f>
+        <v>11</v>
+      </c>
+      <c r="C115" s="5">
+        <v>5</v>
+      </c>
+      <c r="D115" s="5">
+        <f t="shared" si="6"/>
+        <v>105011</v>
+      </c>
+      <c r="E115" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="G115" s="5">
+        <f t="shared" si="5"/>
+        <v>205011</v>
+      </c>
+    </row>
+    <row r="116" s="5" customFormat="1" spans="1:7">
+      <c r="A116" s="5">
+        <f t="shared" si="4"/>
+        <v>5012</v>
+      </c>
+      <c r="B116" s="5">
+        <f>COUNTIF($C$1:C116,C116)</f>
+        <v>12</v>
+      </c>
+      <c r="C116" s="5">
+        <v>5</v>
+      </c>
+      <c r="D116" s="5">
+        <f t="shared" si="6"/>
+        <v>105012</v>
+      </c>
+      <c r="E116" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="F116" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="G116" s="5">
+        <f t="shared" si="5"/>
+        <v>205012</v>
+      </c>
+    </row>
+    <row r="117" s="5" customFormat="1" spans="1:7">
+      <c r="A117" s="5">
+        <f t="shared" si="4"/>
+        <v>5013</v>
+      </c>
+      <c r="B117" s="5">
+        <f>COUNTIF($C$1:C117,C117)</f>
+        <v>13</v>
+      </c>
+      <c r="C117" s="5">
+        <v>5</v>
+      </c>
+      <c r="D117" s="5">
+        <f t="shared" si="6"/>
+        <v>105013</v>
+      </c>
+      <c r="E117" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="F117" s="5" t="s">
+        <v>158</v>
+      </c>
+      <c r="G117" s="5">
+        <f t="shared" si="5"/>
+        <v>205013</v>
+      </c>
+    </row>
+    <row r="118" s="5" customFormat="1" spans="1:7">
+      <c r="A118" s="5">
+        <f t="shared" si="4"/>
+        <v>5014</v>
+      </c>
+      <c r="B118" s="5">
+        <f>COUNTIF($C$1:C118,C118)</f>
+        <v>14</v>
+      </c>
+      <c r="C118" s="5">
+        <v>5</v>
+      </c>
+      <c r="D118" s="5">
+        <f t="shared" si="6"/>
+        <v>105014</v>
+      </c>
+      <c r="E118" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="F118" s="5" t="s">
+        <v>160</v>
+      </c>
+      <c r="G118" s="5">
+        <f t="shared" si="5"/>
+        <v>205014</v>
+      </c>
+    </row>
+    <row r="119" s="5" customFormat="1" spans="1:7">
+      <c r="A119" s="5">
+        <f t="shared" si="4"/>
+        <v>5015</v>
+      </c>
+      <c r="B119" s="5">
+        <f>COUNTIF($C$1:C119,C119)</f>
+        <v>15</v>
+      </c>
+      <c r="C119" s="5">
+        <v>5</v>
+      </c>
+      <c r="D119" s="5">
+        <f t="shared" si="6"/>
+        <v>105015</v>
+      </c>
+      <c r="E119" s="5" t="s">
+        <v>207</v>
+      </c>
+      <c r="F119" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="G119" s="5">
+        <f t="shared" si="5"/>
+        <v>205015</v>
+      </c>
+    </row>
+    <row r="120" s="5" customFormat="1" spans="1:7">
+      <c r="A120" s="5">
+        <f t="shared" si="4"/>
+        <v>5016</v>
+      </c>
+      <c r="B120" s="5">
+        <f>COUNTIF($C$1:C120,C120)</f>
+        <v>16</v>
+      </c>
+      <c r="C120" s="5">
+        <v>5</v>
+      </c>
+      <c r="D120" s="5">
+        <f t="shared" si="6"/>
+        <v>105016</v>
+      </c>
+      <c r="E120" s="5" t="s">
+        <v>208</v>
+      </c>
+      <c r="F120" s="5" t="s">
+        <v>164</v>
+      </c>
+      <c r="G120" s="5">
+        <f t="shared" si="5"/>
+        <v>205016</v>
+      </c>
+    </row>
+    <row r="121" s="5" customFormat="1" spans="1:7">
+      <c r="A121" s="5">
+        <f t="shared" si="4"/>
+        <v>5017</v>
+      </c>
+      <c r="B121" s="5">
+        <f>COUNTIF($C$1:C121,C121)</f>
+        <v>17</v>
+      </c>
+      <c r="C121" s="5">
+        <v>5</v>
+      </c>
+      <c r="D121" s="5">
+        <f t="shared" si="6"/>
+        <v>105017</v>
+      </c>
+      <c r="E121" s="5" t="s">
+        <v>209</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="G121" s="5">
+        <f t="shared" si="5"/>
+        <v>205017</v>
+      </c>
+    </row>
+    <row r="122" s="5" customFormat="1" spans="1:7">
+      <c r="A122" s="5">
+        <f t="shared" si="4"/>
+        <v>5018</v>
+      </c>
+      <c r="B122" s="5">
+        <f>COUNTIF($C$1:C122,C122)</f>
+        <v>18</v>
+      </c>
+      <c r="C122" s="5">
+        <v>5</v>
+      </c>
+      <c r="D122" s="5">
+        <f t="shared" si="6"/>
+        <v>105018</v>
+      </c>
+      <c r="E122" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F122" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="G122" s="5">
+        <f t="shared" si="5"/>
+        <v>205018</v>
+      </c>
+    </row>
+    <row r="123" s="5" customFormat="1" spans="1:7">
+      <c r="A123" s="5">
+        <f t="shared" si="4"/>
+        <v>5019</v>
+      </c>
+      <c r="B123" s="5">
+        <f>COUNTIF($C$1:C123,C123)</f>
+        <v>19</v>
+      </c>
+      <c r="C123" s="5">
+        <v>5</v>
+      </c>
+      <c r="D123" s="5">
+        <f t="shared" si="6"/>
+        <v>105019</v>
+      </c>
+      <c r="E123" s="5" t="s">
+        <v>211</v>
+      </c>
+      <c r="F123" s="5" t="s">
+        <v>170</v>
+      </c>
+      <c r="G123" s="5">
+        <f t="shared" si="5"/>
+        <v>205019</v>
+      </c>
+    </row>
+    <row r="124" s="5" customFormat="1" spans="1:7">
+      <c r="A124" s="5">
+        <f t="shared" si="4"/>
+        <v>5020</v>
+      </c>
+      <c r="B124" s="5">
+        <f>COUNTIF($C$1:C124,C124)</f>
+        <v>20</v>
+      </c>
+      <c r="C124" s="5">
+        <v>5</v>
+      </c>
+      <c r="D124" s="5">
+        <f t="shared" si="6"/>
+        <v>105020</v>
+      </c>
+      <c r="E124" s="5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F124" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="G124" s="5">
+        <f t="shared" si="5"/>
+        <v>205020</v>
+      </c>
+    </row>
+    <row r="125" s="6" customFormat="1" spans="1:7">
+      <c r="A125" s="6">
+        <f t="shared" si="4"/>
+        <v>6001</v>
+      </c>
+      <c r="B125" s="6">
+        <f>COUNTIF($C$1:C125,C125)</f>
+        <v>1</v>
+      </c>
+      <c r="C125" s="6">
+        <v>6</v>
+      </c>
+      <c r="D125" s="6">
+        <f t="shared" si="6"/>
+        <v>106001</v>
+      </c>
+      <c r="E125" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F125" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G125" s="6">
+        <f t="shared" si="5"/>
+        <v>206001</v>
+      </c>
+    </row>
+    <row r="126" s="6" customFormat="1" spans="1:8">
+      <c r="A126" s="6">
+        <f t="shared" si="4"/>
+        <v>6002</v>
+      </c>
+      <c r="B126" s="6">
+        <f>COUNTIF($C$1:C126,C126)</f>
+        <v>2</v>
+      </c>
+      <c r="C126" s="6">
+        <v>6</v>
+      </c>
+      <c r="D126" s="6">
+        <f t="shared" si="6"/>
+        <v>106002</v>
+      </c>
+      <c r="E126" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F126" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="G126" s="6">
+        <f t="shared" si="5"/>
+        <v>206002</v>
+      </c>
+      <c r="H126" s="6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="127" s="6" customFormat="1" spans="1:8">
+      <c r="A127" s="6">
+        <f t="shared" si="4"/>
+        <v>6003</v>
+      </c>
+      <c r="B127" s="6">
+        <f>COUNTIF($C$1:C127,C127)</f>
+        <v>3</v>
+      </c>
+      <c r="C127" s="6">
+        <v>6</v>
+      </c>
+      <c r="D127" s="6">
+        <f t="shared" si="6"/>
+        <v>106003</v>
+      </c>
+      <c r="E127" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="G127" s="6">
+        <f t="shared" si="5"/>
+        <v>206003</v>
+      </c>
+      <c r="H127" s="6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128" s="6" customFormat="1" spans="1:8">
+      <c r="A128" s="6">
+        <f t="shared" si="4"/>
+        <v>6004</v>
+      </c>
+      <c r="B128" s="6">
+        <f>COUNTIF($C$1:C128,C128)</f>
+        <v>4</v>
+      </c>
+      <c r="C128" s="6">
+        <v>6</v>
+      </c>
+      <c r="D128" s="6">
+        <f t="shared" si="6"/>
+        <v>106004</v>
+      </c>
+      <c r="E128" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="G128" s="6">
+        <f t="shared" si="5"/>
+        <v>206004</v>
+      </c>
+      <c r="H128" s="6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="129" s="6" customFormat="1" spans="1:8">
+      <c r="A129" s="6">
+        <f t="shared" si="4"/>
+        <v>6005</v>
+      </c>
+      <c r="B129" s="6">
+        <f>COUNTIF($C$1:C129,C129)</f>
+        <v>5</v>
+      </c>
+      <c r="C129" s="6">
+        <v>6</v>
+      </c>
+      <c r="D129" s="6">
+        <f t="shared" si="6"/>
+        <v>106005</v>
+      </c>
+      <c r="E129" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F129" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="G129" s="6">
+        <f t="shared" si="5"/>
+        <v>206005</v>
+      </c>
+      <c r="H129" s="6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="130" s="6" customFormat="1" spans="1:8">
+      <c r="A130" s="6">
+        <f t="shared" si="4"/>
+        <v>6006</v>
+      </c>
+      <c r="B130" s="6">
+        <f>COUNTIF($C$1:C130,C130)</f>
+        <v>6</v>
+      </c>
+      <c r="C130" s="6">
+        <v>6</v>
+      </c>
+      <c r="D130" s="6">
+        <f t="shared" si="6"/>
+        <v>106006</v>
+      </c>
+      <c r="E130" s="6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F130" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G130" s="6">
+        <f t="shared" si="5"/>
+        <v>206006</v>
+      </c>
+      <c r="H130" s="6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="131" s="6" customFormat="1" spans="1:8">
+      <c r="A131" s="6">
+        <f t="shared" ref="A131:A144" si="7">C131*1000+B131</f>
+        <v>6007</v>
+      </c>
+      <c r="B131" s="6">
+        <f>COUNTIF($C$1:C131,C131)</f>
+        <v>7</v>
+      </c>
+      <c r="C131" s="6">
+        <v>6</v>
+      </c>
+      <c r="D131" s="6">
+        <f t="shared" si="6"/>
+        <v>106007</v>
+      </c>
+      <c r="E131" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="F131" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="G131" s="6">
+        <f t="shared" si="5"/>
+        <v>206007</v>
+      </c>
+      <c r="H131" s="6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="132" s="6" customFormat="1" spans="1:8">
+      <c r="A132" s="6">
+        <f t="shared" si="7"/>
+        <v>6008</v>
+      </c>
+      <c r="B132" s="6">
+        <f>COUNTIF($C$1:C132,C132)</f>
+        <v>8</v>
+      </c>
+      <c r="C132" s="6">
+        <v>6</v>
+      </c>
+      <c r="D132" s="6">
+        <f t="shared" si="6"/>
+        <v>106008</v>
+      </c>
+      <c r="E132" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F132" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="G132" s="6">
+        <f t="shared" si="5"/>
+        <v>206008</v>
+      </c>
+      <c r="H132" s="6">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="133" s="6" customFormat="1" spans="1:8">
+      <c r="A133" s="6">
+        <f t="shared" si="7"/>
+        <v>6009</v>
+      </c>
+      <c r="B133" s="6">
+        <f>COUNTIF($C$1:C133,C133)</f>
+        <v>9</v>
+      </c>
+      <c r="C133" s="6">
+        <v>6</v>
+      </c>
+      <c r="D133" s="6">
+        <f t="shared" si="6"/>
+        <v>106009</v>
+      </c>
+      <c r="E133" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F133" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="G133" s="6">
+        <f t="shared" si="5"/>
+        <v>206009</v>
+      </c>
+      <c r="H133" s="6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="134" s="6" customFormat="1" spans="1:8">
+      <c r="A134" s="6">
+        <f t="shared" si="7"/>
+        <v>6010</v>
+      </c>
+      <c r="B134" s="6">
+        <f>COUNTIF($C$1:C134,C134)</f>
+        <v>10</v>
+      </c>
+      <c r="C134" s="6">
+        <v>6</v>
+      </c>
+      <c r="D134" s="6">
+        <f t="shared" si="6"/>
+        <v>106010</v>
+      </c>
+      <c r="E134" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F134" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="G134" s="6">
+        <f t="shared" si="5"/>
+        <v>206010</v>
+      </c>
+      <c r="H134" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135" s="6" customFormat="1" spans="1:7">
+      <c r="A135" s="6">
+        <f t="shared" si="7"/>
+        <v>6011</v>
+      </c>
+      <c r="B135" s="6">
+        <f>COUNTIF($C$1:C135,C135)</f>
+        <v>11</v>
+      </c>
+      <c r="C135" s="6">
+        <v>6</v>
+      </c>
+      <c r="D135" s="6">
+        <f t="shared" si="6"/>
+        <v>106011</v>
+      </c>
+      <c r="E135" s="6" t="s">
+        <v>223</v>
+      </c>
+      <c r="F135" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="G135" s="6">
+        <f t="shared" si="5"/>
+        <v>206011</v>
+      </c>
+    </row>
+    <row r="136" s="6" customFormat="1" spans="1:7">
+      <c r="A136" s="6">
+        <f t="shared" si="7"/>
+        <v>6012</v>
+      </c>
+      <c r="B136" s="6">
+        <f>COUNTIF($C$1:C136,C136)</f>
+        <v>12</v>
+      </c>
+      <c r="C136" s="6">
+        <v>6</v>
+      </c>
+      <c r="D136" s="6">
+        <f t="shared" si="6"/>
+        <v>106012</v>
+      </c>
+      <c r="E136" s="6" t="s">
+        <v>224</v>
+      </c>
+      <c r="F136" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="G136" s="6">
+        <f t="shared" si="5"/>
+        <v>206012</v>
+      </c>
+    </row>
+    <row r="137" s="6" customFormat="1" spans="1:7">
+      <c r="A137" s="6">
+        <f t="shared" si="7"/>
+        <v>6013</v>
+      </c>
+      <c r="B137" s="6">
+        <f>COUNTIF($C$1:C137,C137)</f>
+        <v>13</v>
+      </c>
+      <c r="C137" s="6">
+        <v>6</v>
+      </c>
+      <c r="D137" s="6">
+        <f t="shared" si="6"/>
+        <v>106013</v>
+      </c>
+      <c r="E137" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="F137" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="G137" s="6">
+        <f t="shared" si="5"/>
+        <v>206013</v>
+      </c>
+    </row>
+    <row r="138" s="6" customFormat="1" spans="1:7">
+      <c r="A138" s="6">
+        <f t="shared" si="7"/>
+        <v>6014</v>
+      </c>
+      <c r="B138" s="6">
+        <f>COUNTIF($C$1:C138,C138)</f>
+        <v>14</v>
+      </c>
+      <c r="C138" s="6">
+        <v>6</v>
+      </c>
+      <c r="D138" s="6">
+        <f t="shared" si="6"/>
+        <v>106014</v>
+      </c>
+      <c r="E138" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F138" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="G138" s="6">
+        <f t="shared" si="5"/>
+        <v>206014</v>
+      </c>
+    </row>
+    <row r="139" s="6" customFormat="1" spans="1:7">
+      <c r="A139" s="6">
+        <f t="shared" si="7"/>
+        <v>6015</v>
+      </c>
+      <c r="B139" s="6">
+        <f>COUNTIF($C$1:C139,C139)</f>
+        <v>15</v>
+      </c>
+      <c r="C139" s="6">
+        <v>6</v>
+      </c>
+      <c r="D139" s="6">
+        <f t="shared" si="6"/>
+        <v>106015</v>
+      </c>
+      <c r="E139" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="F139" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="G139" s="6">
+        <f t="shared" si="5"/>
+        <v>206015</v>
+      </c>
+    </row>
+    <row r="140" s="6" customFormat="1" spans="1:7">
+      <c r="A140" s="6">
+        <f t="shared" si="7"/>
+        <v>6016</v>
+      </c>
+      <c r="B140" s="6">
+        <f>COUNTIF($C$1:C140,C140)</f>
+        <v>16</v>
+      </c>
+      <c r="C140" s="6">
+        <v>6</v>
+      </c>
+      <c r="D140" s="6">
+        <f t="shared" si="6"/>
+        <v>106016</v>
+      </c>
+      <c r="E140" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="G140" s="6">
+        <f t="shared" si="5"/>
+        <v>206016</v>
+      </c>
+    </row>
+    <row r="141" s="6" customFormat="1" spans="1:7">
+      <c r="A141" s="6">
+        <f t="shared" si="7"/>
+        <v>6017</v>
+      </c>
+      <c r="B141" s="6">
+        <f>COUNTIF($C$1:C141,C141)</f>
+        <v>17</v>
+      </c>
+      <c r="C141" s="6">
+        <v>6</v>
+      </c>
+      <c r="D141" s="6">
+        <f t="shared" si="6"/>
+        <v>106017</v>
+      </c>
+      <c r="E141" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="G141" s="6">
+        <f t="shared" si="5"/>
+        <v>206017</v>
+      </c>
+    </row>
+    <row r="142" s="6" customFormat="1" spans="1:7">
+      <c r="A142" s="6">
+        <f t="shared" si="7"/>
+        <v>6018</v>
+      </c>
+      <c r="B142" s="6">
+        <f>COUNTIF($C$1:C142,C142)</f>
+        <v>18</v>
+      </c>
+      <c r="C142" s="6">
+        <v>6</v>
+      </c>
+      <c r="D142" s="6">
+        <f t="shared" si="6"/>
+        <v>106018</v>
+      </c>
+      <c r="E142" s="6" t="s">
+        <v>230</v>
+      </c>
+      <c r="F142" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="G142" s="6">
+        <f t="shared" si="5"/>
+        <v>206018</v>
+      </c>
+    </row>
+    <row r="143" s="6" customFormat="1" spans="1:7">
+      <c r="A143" s="6">
+        <f t="shared" si="7"/>
+        <v>6019</v>
+      </c>
+      <c r="B143" s="6">
+        <f>COUNTIF($C$1:C143,C143)</f>
+        <v>19</v>
+      </c>
+      <c r="C143" s="6">
+        <v>6</v>
+      </c>
+      <c r="D143" s="6">
+        <f t="shared" si="6"/>
+        <v>106019</v>
+      </c>
+      <c r="E143" s="6" t="s">
+        <v>231</v>
+      </c>
+      <c r="F143" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="G143" s="6">
+        <f t="shared" si="5"/>
+        <v>206019</v>
+      </c>
+    </row>
+    <row r="144" s="6" customFormat="1" spans="1:7">
+      <c r="A144" s="6">
+        <f t="shared" si="7"/>
+        <v>6020</v>
+      </c>
+      <c r="B144" s="6">
+        <f>COUNTIF($C$1:C144,C144)</f>
+        <v>20</v>
+      </c>
+      <c r="C144" s="6">
+        <v>6</v>
+      </c>
+      <c r="D144" s="6">
+        <f t="shared" si="6"/>
+        <v>106020</v>
+      </c>
+      <c r="E144" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="F144" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="G144" s="6">
+        <f t="shared" si="5"/>
+        <v>206020</v>
       </c>
     </row>
   </sheetData>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -841,12 +841,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1761,7 +1761,7 @@
     </row>
     <row r="5" s="1" customFormat="1" spans="1:7">
       <c r="A5" s="1">
-        <f>C5*1000+B5</f>
+        <f t="shared" ref="A5:A24" si="0">C5*1000+B5</f>
         <v>1</v>
       </c>
       <c r="B5" s="1">
@@ -1787,7 +1787,7 @@
     </row>
     <row r="6" s="1" customFormat="1" spans="1:7">
       <c r="A6" s="1">
-        <f>C6*1000+B6</f>
+        <f t="shared" si="0"/>
         <v>2</v>
       </c>
       <c r="B6" s="1">
@@ -1798,7 +1798,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" ref="D6:D37" si="0">100000+C6*1000+B6</f>
+        <f t="shared" ref="D6:D37" si="1">100000+C6*1000+B6</f>
         <v>100002</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -1813,7 +1813,7 @@
     </row>
     <row r="7" s="1" customFormat="1" spans="1:7">
       <c r="A7" s="1">
-        <f>C7*1000+B7</f>
+        <f t="shared" si="0"/>
         <v>3</v>
       </c>
       <c r="B7" s="1">
@@ -1824,7 +1824,7 @@
         <v>0</v>
       </c>
       <c r="D7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100003</v>
       </c>
       <c r="E7" s="1" t="s">
@@ -1839,7 +1839,7 @@
     </row>
     <row r="8" s="1" customFormat="1" spans="1:7">
       <c r="A8" s="1">
-        <f>C8*1000+B8</f>
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="B8" s="1">
@@ -1850,7 +1850,7 @@
         <v>0</v>
       </c>
       <c r="D8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100004</v>
       </c>
       <c r="E8" s="1" t="s">
@@ -1865,7 +1865,7 @@
     </row>
     <row r="9" s="1" customFormat="1" spans="1:7">
       <c r="A9" s="1">
-        <f>C9*1000+B9</f>
+        <f t="shared" si="0"/>
         <v>5</v>
       </c>
       <c r="B9" s="1">
@@ -1876,7 +1876,7 @@
         <v>0</v>
       </c>
       <c r="D9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100005</v>
       </c>
       <c r="E9" s="1" t="s">
@@ -1891,7 +1891,7 @@
     </row>
     <row r="10" s="1" customFormat="1" spans="1:7">
       <c r="A10" s="1">
-        <f>C10*1000+B10</f>
+        <f t="shared" si="0"/>
         <v>6</v>
       </c>
       <c r="B10" s="1">
@@ -1902,7 +1902,7 @@
         <v>0</v>
       </c>
       <c r="D10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100006</v>
       </c>
       <c r="E10" s="1" t="s">
@@ -1917,7 +1917,7 @@
     </row>
     <row r="11" s="1" customFormat="1" spans="1:7">
       <c r="A11" s="1">
-        <f>C11*1000+B11</f>
+        <f t="shared" si="0"/>
         <v>7</v>
       </c>
       <c r="B11" s="1">
@@ -1928,7 +1928,7 @@
         <v>0</v>
       </c>
       <c r="D11" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100007</v>
       </c>
       <c r="E11" s="1" t="s">
@@ -1943,7 +1943,7 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:7">
       <c r="A12" s="1">
-        <f>C12*1000+B12</f>
+        <f t="shared" si="0"/>
         <v>8</v>
       </c>
       <c r="B12" s="1">
@@ -1954,7 +1954,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100008</v>
       </c>
       <c r="E12" s="1" t="s">
@@ -1969,7 +1969,7 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:7">
       <c r="A13" s="1">
-        <f>C13*1000+B13</f>
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="B13" s="1">
@@ -1980,7 +1980,7 @@
         <v>0</v>
       </c>
       <c r="D13" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100009</v>
       </c>
       <c r="E13" s="1" t="s">
@@ -1995,7 +1995,7 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:7">
       <c r="A14" s="1">
-        <f>C14*1000+B14</f>
+        <f t="shared" si="0"/>
         <v>10</v>
       </c>
       <c r="B14" s="1">
@@ -2006,7 +2006,7 @@
         <v>0</v>
       </c>
       <c r="D14" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100010</v>
       </c>
       <c r="E14" s="1" t="s">
@@ -2021,7 +2021,7 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:7">
       <c r="A15" s="1">
-        <f>C15*1000+B15</f>
+        <f t="shared" si="0"/>
         <v>11</v>
       </c>
       <c r="B15" s="1">
@@ -2032,7 +2032,7 @@
         <v>0</v>
       </c>
       <c r="D15" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100011</v>
       </c>
       <c r="E15" s="1" t="s">
@@ -2045,9 +2045,9 @@
         <v>200011</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:8">
+    <row r="16" s="1" customFormat="1" spans="1:7">
       <c r="A16" s="1">
-        <f>C16*1000+B16</f>
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="B16" s="1">
@@ -2058,7 +2058,7 @@
         <v>0</v>
       </c>
       <c r="D16" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100012</v>
       </c>
       <c r="E16" s="1" t="s">
@@ -2070,13 +2070,10 @@
       <c r="G16" s="1">
         <v>200012</v>
       </c>
-      <c r="H16" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:7">
       <c r="A17" s="1">
-        <f>C17*1000+B17</f>
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
       <c r="B17" s="1">
@@ -2087,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100013</v>
       </c>
       <c r="E17" s="1" t="s">
@@ -2099,13 +2096,10 @@
       <c r="G17" s="1">
         <v>200013</v>
       </c>
-      <c r="H17" s="1">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:7">
       <c r="A18" s="1">
-        <f>C18*1000+B18</f>
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
       <c r="B18" s="1">
@@ -2116,7 +2110,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100014</v>
       </c>
       <c r="E18" s="1" t="s">
@@ -2128,13 +2122,10 @@
       <c r="G18" s="1">
         <v>200014</v>
       </c>
-      <c r="H18" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:7">
       <c r="A19" s="1">
-        <f>C19*1000+B19</f>
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
       <c r="B19" s="1">
@@ -2145,7 +2136,7 @@
         <v>0</v>
       </c>
       <c r="D19" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100015</v>
       </c>
       <c r="E19" s="1" t="s">
@@ -2157,13 +2148,10 @@
       <c r="G19" s="1">
         <v>200015</v>
       </c>
-      <c r="H19" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:7">
       <c r="A20" s="1">
-        <f>C20*1000+B20</f>
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
       <c r="B20" s="1">
@@ -2174,7 +2162,7 @@
         <v>0</v>
       </c>
       <c r="D20" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100016</v>
       </c>
       <c r="E20" s="1" t="s">
@@ -2186,13 +2174,10 @@
       <c r="G20" s="1">
         <v>200016</v>
       </c>
-      <c r="H20" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:7">
       <c r="A21" s="1">
-        <f>C21*1000+B21</f>
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
       <c r="B21" s="1">
@@ -2203,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="D21" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100017</v>
       </c>
       <c r="E21" s="1" t="s">
@@ -2215,13 +2200,10 @@
       <c r="G21" s="1">
         <v>200017</v>
       </c>
-      <c r="H21" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:7">
       <c r="A22" s="1">
-        <f>C22*1000+B22</f>
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
       <c r="B22" s="1">
@@ -2232,7 +2214,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100018</v>
       </c>
       <c r="E22" s="1" t="s">
@@ -2244,13 +2226,10 @@
       <c r="G22" s="1">
         <v>200018</v>
       </c>
-      <c r="H22" s="1">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:7">
       <c r="A23" s="1">
-        <f>C23*1000+B23</f>
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
       <c r="B23" s="1">
@@ -2261,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100019</v>
       </c>
       <c r="E23" s="1" t="s">
@@ -2273,13 +2252,10 @@
       <c r="G23" s="1">
         <v>200019</v>
       </c>
-      <c r="H23" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:8">
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:7">
       <c r="A24" s="1">
-        <f>C24*1000+B24</f>
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
       <c r="B24" s="1">
@@ -2290,7 +2266,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>100020</v>
       </c>
       <c r="E24" s="1" t="s">
@@ -2302,13 +2278,10 @@
       <c r="G24" s="1">
         <v>200020</v>
       </c>
-      <c r="H24" s="1">
-        <v>9</v>
-      </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:7">
       <c r="A25" s="1">
-        <f t="shared" ref="A25:A43" si="1">C25*1000+B25</f>
+        <f t="shared" ref="A25:A43" si="2">C25*1000+B25</f>
         <v>21</v>
       </c>
       <c r="B25" s="1">
@@ -2319,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" ref="D25:D43" si="2">100000+C25*1000+B25</f>
+        <f t="shared" ref="D25:D88" si="3">100000+C25*1000+B25</f>
         <v>100021</v>
       </c>
       <c r="E25" s="1" t="s">
@@ -2334,7 +2307,7 @@
     </row>
     <row r="26" s="1" customFormat="1" spans="1:7">
       <c r="A26" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>22</v>
       </c>
       <c r="B26" s="1">
@@ -2345,7 +2318,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100022</v>
       </c>
       <c r="E26" s="1" t="s">
@@ -2360,7 +2333,7 @@
     </row>
     <row r="27" s="1" customFormat="1" spans="1:7">
       <c r="A27" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>23</v>
       </c>
       <c r="B27" s="1">
@@ -2371,7 +2344,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100023</v>
       </c>
       <c r="E27" s="1" t="s">
@@ -2386,7 +2359,7 @@
     </row>
     <row r="28" s="1" customFormat="1" spans="1:7">
       <c r="A28" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>24</v>
       </c>
       <c r="B28" s="1">
@@ -2397,7 +2370,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100024</v>
       </c>
       <c r="E28" s="1" t="s">
@@ -2412,7 +2385,7 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="1:7">
       <c r="A29" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>25</v>
       </c>
       <c r="B29" s="1">
@@ -2423,7 +2396,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100025</v>
       </c>
       <c r="E29" s="1" t="s">
@@ -2438,7 +2411,7 @@
     </row>
     <row r="30" s="1" customFormat="1" spans="1:7">
       <c r="A30" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>26</v>
       </c>
       <c r="B30" s="1">
@@ -2449,7 +2422,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100026</v>
       </c>
       <c r="E30" s="1" t="s">
@@ -2464,7 +2437,7 @@
     </row>
     <row r="31" s="1" customFormat="1" spans="1:7">
       <c r="A31" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>27</v>
       </c>
       <c r="B31" s="1">
@@ -2475,7 +2448,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100027</v>
       </c>
       <c r="E31" s="1" t="s">
@@ -2490,7 +2463,7 @@
     </row>
     <row r="32" s="1" customFormat="1" spans="1:7">
       <c r="A32" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>28</v>
       </c>
       <c r="B32" s="1">
@@ -2501,7 +2474,7 @@
         <v>0</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100028</v>
       </c>
       <c r="E32" s="1" t="s">
@@ -2516,7 +2489,7 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="1:7">
       <c r="A33" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>29</v>
       </c>
       <c r="B33" s="1">
@@ -2527,7 +2500,7 @@
         <v>0</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100029</v>
       </c>
       <c r="E33" s="1" t="s">
@@ -2542,7 +2515,7 @@
     </row>
     <row r="34" s="1" customFormat="1" spans="1:7">
       <c r="A34" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>30</v>
       </c>
       <c r="B34" s="1">
@@ -2553,7 +2526,7 @@
         <v>0</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100030</v>
       </c>
       <c r="E34" s="1" t="s">
@@ -2568,7 +2541,7 @@
     </row>
     <row r="35" s="1" customFormat="1" spans="1:7">
       <c r="A35" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="B35" s="1">
@@ -2579,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100031</v>
       </c>
       <c r="E35" s="1" t="s">
@@ -2594,7 +2567,7 @@
     </row>
     <row r="36" s="1" customFormat="1" spans="1:7">
       <c r="A36" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>32</v>
       </c>
       <c r="B36" s="1">
@@ -2605,7 +2578,7 @@
         <v>0</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100032</v>
       </c>
       <c r="E36" s="1" t="s">
@@ -2620,7 +2593,7 @@
     </row>
     <row r="37" s="1" customFormat="1" spans="1:7">
       <c r="A37" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>33</v>
       </c>
       <c r="B37" s="1">
@@ -2631,7 +2604,7 @@
         <v>0</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100033</v>
       </c>
       <c r="E37" s="1" t="s">
@@ -2646,7 +2619,7 @@
     </row>
     <row r="38" s="1" customFormat="1" spans="1:7">
       <c r="A38" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>34</v>
       </c>
       <c r="B38" s="1">
@@ -2657,7 +2630,7 @@
         <v>0</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100034</v>
       </c>
       <c r="E38" s="1" t="s">
@@ -2672,7 +2645,7 @@
     </row>
     <row r="39" s="1" customFormat="1" spans="1:7">
       <c r="A39" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>35</v>
       </c>
       <c r="B39" s="1">
@@ -2683,7 +2656,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100035</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -2698,7 +2671,7 @@
     </row>
     <row r="40" s="1" customFormat="1" spans="1:7">
       <c r="A40" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>36</v>
       </c>
       <c r="B40" s="1">
@@ -2709,7 +2682,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100036</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -2724,7 +2697,7 @@
     </row>
     <row r="41" s="1" customFormat="1" spans="1:7">
       <c r="A41" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>37</v>
       </c>
       <c r="B41" s="1">
@@ -2735,7 +2708,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100037</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -2750,7 +2723,7 @@
     </row>
     <row r="42" s="1" customFormat="1" spans="1:7">
       <c r="A42" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>38</v>
       </c>
       <c r="B42" s="1">
@@ -2761,7 +2734,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100038</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -2776,7 +2749,7 @@
     </row>
     <row r="43" s="1" customFormat="1" spans="1:7">
       <c r="A43" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>39</v>
       </c>
       <c r="B43" s="1">
@@ -2787,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>100039</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -2802,7 +2775,7 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <f t="shared" ref="A44:A65" si="3">C44*1000+B44</f>
+        <f t="shared" ref="A44:A65" si="4">C44*1000+B44</f>
         <v>1001</v>
       </c>
       <c r="B44">
@@ -2813,7 +2786,7 @@
         <v>1</v>
       </c>
       <c r="D44" s="1">
-        <f>100000+C44*1000+B44</f>
+        <f t="shared" si="3"/>
         <v>101001</v>
       </c>
       <c r="E44" t="s">
@@ -2828,7 +2801,7 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1002</v>
       </c>
       <c r="B45">
@@ -2839,7 +2812,7 @@
         <v>1</v>
       </c>
       <c r="D45" s="1">
-        <f>100000+C45*1000+B45</f>
+        <f t="shared" si="3"/>
         <v>101002</v>
       </c>
       <c r="E45" t="s">
@@ -2854,7 +2827,7 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1003</v>
       </c>
       <c r="B46">
@@ -2865,7 +2838,7 @@
         <v>1</v>
       </c>
       <c r="D46" s="1">
-        <f>100000+C46*1000+B46</f>
+        <f t="shared" si="3"/>
         <v>101003</v>
       </c>
       <c r="E46" t="s">
@@ -2880,7 +2853,7 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1004</v>
       </c>
       <c r="B47">
@@ -2891,7 +2864,7 @@
         <v>1</v>
       </c>
       <c r="D47" s="1">
-        <f>100000+C47*1000+B47</f>
+        <f t="shared" si="3"/>
         <v>101004</v>
       </c>
       <c r="E47" t="s">
@@ -2906,7 +2879,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1005</v>
       </c>
       <c r="B48">
@@ -2917,7 +2890,7 @@
         <v>1</v>
       </c>
       <c r="D48" s="1">
-        <f>100000+C48*1000+B48</f>
+        <f t="shared" si="3"/>
         <v>101005</v>
       </c>
       <c r="E48" t="s">
@@ -2932,7 +2905,7 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1006</v>
       </c>
       <c r="B49">
@@ -2943,7 +2916,7 @@
         <v>1</v>
       </c>
       <c r="D49" s="1">
-        <f>100000+C49*1000+B49</f>
+        <f t="shared" si="3"/>
         <v>101006</v>
       </c>
       <c r="E49" t="s">
@@ -2958,7 +2931,7 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1007</v>
       </c>
       <c r="B50">
@@ -2969,7 +2942,7 @@
         <v>1</v>
       </c>
       <c r="D50" s="1">
-        <f>100000+C50*1000+B50</f>
+        <f t="shared" si="3"/>
         <v>101007</v>
       </c>
       <c r="E50" t="s">
@@ -2984,7 +2957,7 @@
     </row>
     <row r="51" spans="1:18">
       <c r="A51">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1008</v>
       </c>
       <c r="B51">
@@ -2995,7 +2968,7 @@
         <v>1</v>
       </c>
       <c r="D51" s="1">
-        <f>100000+C51*1000+B51</f>
+        <f t="shared" si="3"/>
         <v>101008</v>
       </c>
       <c r="E51" t="s">
@@ -3007,12 +2980,11 @@
       <c r="G51">
         <v>201008</v>
       </c>
-      <c r="H51"/>
       <c r="R51" s="1"/>
     </row>
     <row r="52" spans="1:18">
       <c r="A52">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1009</v>
       </c>
       <c r="B52">
@@ -3023,7 +2995,7 @@
         <v>1</v>
       </c>
       <c r="D52" s="1">
-        <f>100000+C52*1000+B52</f>
+        <f t="shared" si="3"/>
         <v>101009</v>
       </c>
       <c r="E52" t="s">
@@ -3035,12 +3007,11 @@
       <c r="G52">
         <v>201009</v>
       </c>
-      <c r="H52"/>
       <c r="R52" s="1"/>
     </row>
     <row r="53" spans="1:18">
       <c r="A53">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1010</v>
       </c>
       <c r="B53">
@@ -3051,7 +3022,7 @@
         <v>1</v>
       </c>
       <c r="D53" s="1">
-        <f>100000+C53*1000+B53</f>
+        <f t="shared" si="3"/>
         <v>101010</v>
       </c>
       <c r="E53" t="s">
@@ -3063,15 +3034,13 @@
       <c r="G53">
         <v>201010</v>
       </c>
-      <c r="H53" s="7">
-        <v>1</v>
-      </c>
+      <c r="H53" s="7"/>
       <c r="J53" s="1"/>
       <c r="R53" s="1"/>
     </row>
     <row r="54" spans="1:18">
       <c r="A54">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1011</v>
       </c>
       <c r="B54">
@@ -3082,7 +3051,7 @@
         <v>1</v>
       </c>
       <c r="D54" s="1">
-        <f>100000+C54*1000+B54</f>
+        <f t="shared" si="3"/>
         <v>101011</v>
       </c>
       <c r="E54" t="s">
@@ -3094,15 +3063,13 @@
       <c r="G54">
         <v>201011</v>
       </c>
-      <c r="H54" s="7">
-        <v>2</v>
-      </c>
+      <c r="H54" s="7"/>
       <c r="J54" s="1"/>
       <c r="R54" s="1"/>
     </row>
     <row r="55" spans="1:18">
       <c r="A55">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1012</v>
       </c>
       <c r="B55">
@@ -3113,7 +3080,7 @@
         <v>1</v>
       </c>
       <c r="D55" s="1">
-        <f>100000+C55*1000+B55</f>
+        <f t="shared" si="3"/>
         <v>101012</v>
       </c>
       <c r="E55" t="s">
@@ -3125,15 +3092,13 @@
       <c r="G55">
         <v>201012</v>
       </c>
-      <c r="H55" s="7">
-        <v>3</v>
-      </c>
+      <c r="H55" s="7"/>
       <c r="J55" s="1"/>
       <c r="R55" s="1"/>
     </row>
     <row r="56" spans="1:18">
       <c r="A56">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1013</v>
       </c>
       <c r="B56">
@@ -3144,7 +3109,7 @@
         <v>1</v>
       </c>
       <c r="D56" s="1">
-        <f>100000+C56*1000+B56</f>
+        <f t="shared" si="3"/>
         <v>101013</v>
       </c>
       <c r="E56" t="s">
@@ -3156,15 +3121,13 @@
       <c r="G56">
         <v>201013</v>
       </c>
-      <c r="H56" s="7">
-        <v>4</v>
-      </c>
+      <c r="H56" s="7"/>
       <c r="J56" s="1"/>
       <c r="R56" s="1"/>
     </row>
     <row r="57" spans="1:18">
       <c r="A57">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1014</v>
       </c>
       <c r="B57">
@@ -3175,7 +3138,7 @@
         <v>1</v>
       </c>
       <c r="D57" s="1">
-        <f>100000+C57*1000+B57</f>
+        <f t="shared" si="3"/>
         <v>101014</v>
       </c>
       <c r="E57" t="s">
@@ -3187,15 +3150,13 @@
       <c r="G57">
         <v>201014</v>
       </c>
-      <c r="H57" s="7">
-        <v>5</v>
-      </c>
+      <c r="H57" s="7"/>
       <c r="J57" s="1"/>
       <c r="R57" s="1"/>
     </row>
     <row r="58" spans="1:18">
       <c r="A58">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1015</v>
       </c>
       <c r="B58">
@@ -3206,7 +3167,7 @@
         <v>1</v>
       </c>
       <c r="D58" s="1">
-        <f>100000+C58*1000+B58</f>
+        <f t="shared" si="3"/>
         <v>101015</v>
       </c>
       <c r="E58" t="s">
@@ -3218,15 +3179,13 @@
       <c r="G58">
         <v>201015</v>
       </c>
-      <c r="H58" s="7">
-        <v>6</v>
-      </c>
+      <c r="H58" s="7"/>
       <c r="J58" s="1"/>
       <c r="R58" s="1"/>
     </row>
     <row r="59" spans="1:18">
       <c r="A59">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1016</v>
       </c>
       <c r="B59">
@@ -3237,7 +3196,7 @@
         <v>1</v>
       </c>
       <c r="D59" s="1">
-        <f>100000+C59*1000+B59</f>
+        <f t="shared" si="3"/>
         <v>101016</v>
       </c>
       <c r="E59" t="s">
@@ -3249,15 +3208,13 @@
       <c r="G59">
         <v>201016</v>
       </c>
-      <c r="H59" s="7">
-        <v>7</v>
-      </c>
+      <c r="H59" s="7"/>
       <c r="J59" s="1"/>
       <c r="R59" s="1"/>
     </row>
     <row r="60" spans="1:18">
       <c r="A60">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1017</v>
       </c>
       <c r="B60">
@@ -3268,7 +3225,7 @@
         <v>1</v>
       </c>
       <c r="D60" s="1">
-        <f>100000+C60*1000+B60</f>
+        <f t="shared" si="3"/>
         <v>101017</v>
       </c>
       <c r="E60" t="s">
@@ -3280,15 +3237,13 @@
       <c r="G60">
         <v>201017</v>
       </c>
-      <c r="H60" s="7">
-        <v>8</v>
-      </c>
+      <c r="H60" s="7"/>
       <c r="J60" s="1"/>
       <c r="R60" s="1"/>
     </row>
     <row r="61" spans="1:18">
       <c r="A61">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1018</v>
       </c>
       <c r="B61">
@@ -3299,7 +3254,7 @@
         <v>1</v>
       </c>
       <c r="D61" s="1">
-        <f>100000+C61*1000+B61</f>
+        <f t="shared" si="3"/>
         <v>101018</v>
       </c>
       <c r="E61" t="s">
@@ -3311,15 +3266,13 @@
       <c r="G61">
         <v>201018</v>
       </c>
-      <c r="H61" s="7">
-        <v>9</v>
-      </c>
+      <c r="H61" s="7"/>
       <c r="J61" s="1"/>
       <c r="R61" s="1"/>
     </row>
     <row r="62" s="2" customFormat="1" spans="1:18">
       <c r="A62" s="2">
-        <f>C62*1000+B62</f>
+        <f t="shared" si="4"/>
         <v>2001</v>
       </c>
       <c r="B62" s="2">
@@ -3330,7 +3283,7 @@
         <v>2</v>
       </c>
       <c r="D62" s="1">
-        <f>100000+C62*1000+B62</f>
+        <f t="shared" si="3"/>
         <v>102001</v>
       </c>
       <c r="E62" s="2" t="s">
@@ -3348,7 +3301,7 @@
     </row>
     <row r="63" s="2" customFormat="1" spans="1:18">
       <c r="A63" s="2">
-        <f>C63*1000+B63</f>
+        <f t="shared" si="4"/>
         <v>2002</v>
       </c>
       <c r="B63" s="2">
@@ -3359,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="D63" s="1">
-        <f>100000+C63*1000+B63</f>
+        <f t="shared" si="3"/>
         <v>102002</v>
       </c>
       <c r="E63" s="2" t="s">
@@ -3377,7 +3330,7 @@
     </row>
     <row r="64" s="2" customFormat="1" spans="1:18">
       <c r="A64" s="2">
-        <f t="shared" ref="A64:A83" si="4">C64*1000+B64</f>
+        <f t="shared" ref="A64:A93" si="5">C64*1000+B64</f>
         <v>2003</v>
       </c>
       <c r="B64" s="2">
@@ -3388,7 +3341,7 @@
         <v>2</v>
       </c>
       <c r="D64" s="1">
-        <f>100000+C64*1000+B64</f>
+        <f t="shared" si="3"/>
         <v>102003</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -3406,7 +3359,7 @@
     </row>
     <row r="65" s="2" customFormat="1" spans="1:18">
       <c r="A65" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2004</v>
       </c>
       <c r="B65" s="2">
@@ -3417,7 +3370,7 @@
         <v>2</v>
       </c>
       <c r="D65" s="1">
-        <f>100000+C65*1000+B65</f>
+        <f t="shared" si="3"/>
         <v>102004</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -3435,7 +3388,7 @@
     </row>
     <row r="66" s="2" customFormat="1" spans="1:18">
       <c r="A66" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2005</v>
       </c>
       <c r="B66" s="2">
@@ -3446,7 +3399,7 @@
         <v>2</v>
       </c>
       <c r="D66" s="1">
-        <f>100000+C66*1000+B66</f>
+        <f t="shared" si="3"/>
         <v>102005</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -3464,7 +3417,7 @@
     </row>
     <row r="67" s="2" customFormat="1" spans="1:18">
       <c r="A67" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2006</v>
       </c>
       <c r="B67" s="2">
@@ -3475,7 +3428,7 @@
         <v>2</v>
       </c>
       <c r="D67" s="1">
-        <f>100000+C67*1000+B67</f>
+        <f t="shared" si="3"/>
         <v>102006</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -3493,7 +3446,7 @@
     </row>
     <row r="68" s="2" customFormat="1" spans="1:18">
       <c r="A68" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2007</v>
       </c>
       <c r="B68" s="2">
@@ -3504,7 +3457,7 @@
         <v>2</v>
       </c>
       <c r="D68" s="1">
-        <f>100000+C68*1000+B68</f>
+        <f t="shared" si="3"/>
         <v>102007</v>
       </c>
       <c r="E68" s="2" t="s">
@@ -3522,7 +3475,7 @@
     </row>
     <row r="69" s="2" customFormat="1" spans="1:18">
       <c r="A69" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2008</v>
       </c>
       <c r="B69" s="2">
@@ -3533,7 +3486,7 @@
         <v>2</v>
       </c>
       <c r="D69" s="1">
-        <f>100000+C69*1000+B69</f>
+        <f t="shared" si="3"/>
         <v>102008</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -3551,7 +3504,7 @@
     </row>
     <row r="70" s="2" customFormat="1" spans="1:18">
       <c r="A70" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2009</v>
       </c>
       <c r="B70" s="2">
@@ -3562,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="D70" s="1">
-        <f>100000+C70*1000+B70</f>
+        <f t="shared" si="3"/>
         <v>102009</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -3580,7 +3533,7 @@
     </row>
     <row r="71" s="2" customFormat="1" spans="1:18">
       <c r="A71" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2010</v>
       </c>
       <c r="B71" s="2">
@@ -3591,7 +3544,7 @@
         <v>2</v>
       </c>
       <c r="D71" s="1">
-        <f>100000+C71*1000+B71</f>
+        <f t="shared" si="3"/>
         <v>102010</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -3609,7 +3562,7 @@
     </row>
     <row r="72" s="2" customFormat="1" spans="1:18">
       <c r="A72" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2011</v>
       </c>
       <c r="B72" s="2">
@@ -3620,7 +3573,7 @@
         <v>2</v>
       </c>
       <c r="D72" s="1">
-        <f>100000+C72*1000+B72</f>
+        <f t="shared" si="3"/>
         <v>102011</v>
       </c>
       <c r="E72" s="2" t="s">
@@ -3638,7 +3591,7 @@
     </row>
     <row r="73" s="2" customFormat="1" spans="1:18">
       <c r="A73" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2012</v>
       </c>
       <c r="B73" s="2">
@@ -3649,7 +3602,7 @@
         <v>2</v>
       </c>
       <c r="D73" s="1">
-        <f>100000+C73*1000+B73</f>
+        <f t="shared" si="3"/>
         <v>102012</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -3667,7 +3620,7 @@
     </row>
     <row r="74" s="2" customFormat="1" spans="1:18">
       <c r="A74" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2013</v>
       </c>
       <c r="B74" s="2">
@@ -3678,7 +3631,7 @@
         <v>2</v>
       </c>
       <c r="D74" s="1">
-        <f>100000+C74*1000+B74</f>
+        <f t="shared" si="3"/>
         <v>102013</v>
       </c>
       <c r="E74" s="2" t="s">
@@ -3696,7 +3649,7 @@
     </row>
     <row r="75" s="2" customFormat="1" spans="1:18">
       <c r="A75" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2014</v>
       </c>
       <c r="B75" s="2">
@@ -3707,7 +3660,7 @@
         <v>2</v>
       </c>
       <c r="D75" s="1">
-        <f>100000+C75*1000+B75</f>
+        <f t="shared" si="3"/>
         <v>102014</v>
       </c>
       <c r="E75" s="2" t="s">
@@ -3725,7 +3678,7 @@
     </row>
     <row r="76" s="2" customFormat="1" spans="1:18">
       <c r="A76" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2015</v>
       </c>
       <c r="B76" s="2">
@@ -3736,7 +3689,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="1">
-        <f>100000+C76*1000+B76</f>
+        <f t="shared" si="3"/>
         <v>102015</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -3754,7 +3707,7 @@
     </row>
     <row r="77" s="2" customFormat="1" spans="1:18">
       <c r="A77" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2016</v>
       </c>
       <c r="B77" s="2">
@@ -3765,7 +3718,7 @@
         <v>2</v>
       </c>
       <c r="D77" s="1">
-        <f>100000+C77*1000+B77</f>
+        <f t="shared" si="3"/>
         <v>102016</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -3783,7 +3736,7 @@
     </row>
     <row r="78" s="2" customFormat="1" spans="1:18">
       <c r="A78" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2017</v>
       </c>
       <c r="B78" s="2">
@@ -3794,7 +3747,7 @@
         <v>2</v>
       </c>
       <c r="D78" s="1">
-        <f>100000+C78*1000+B78</f>
+        <f t="shared" si="3"/>
         <v>102017</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -3812,7 +3765,7 @@
     </row>
     <row r="79" s="2" customFormat="1" spans="1:18">
       <c r="A79" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2018</v>
       </c>
       <c r="B79" s="2">
@@ -3823,7 +3776,7 @@
         <v>2</v>
       </c>
       <c r="D79" s="1">
-        <f>100000+C79*1000+B79</f>
+        <f t="shared" si="3"/>
         <v>102018</v>
       </c>
       <c r="E79" s="2" t="s">
@@ -3841,7 +3794,7 @@
     </row>
     <row r="80" s="2" customFormat="1" spans="1:18">
       <c r="A80" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2019</v>
       </c>
       <c r="B80" s="2">
@@ -3852,7 +3805,7 @@
         <v>2</v>
       </c>
       <c r="D80" s="1">
-        <f>100000+C80*1000+B80</f>
+        <f t="shared" si="3"/>
         <v>102019</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -3870,7 +3823,7 @@
     </row>
     <row r="81" s="2" customFormat="1" spans="1:18">
       <c r="A81" s="2">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2020</v>
       </c>
       <c r="B81" s="2">
@@ -3881,7 +3834,7 @@
         <v>2</v>
       </c>
       <c r="D81" s="1">
-        <f>100000+C81*1000+B81</f>
+        <f t="shared" si="3"/>
         <v>102020</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -3899,7 +3852,7 @@
     </row>
     <row r="82" s="3" customFormat="1" spans="1:10">
       <c r="A82" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3001</v>
       </c>
       <c r="B82" s="3">
@@ -3910,7 +3863,7 @@
         <v>3</v>
       </c>
       <c r="D82" s="1">
-        <f>100000+C82*1000+B82</f>
+        <f t="shared" si="3"/>
         <v>103001</v>
       </c>
       <c r="E82" s="3" t="s">
@@ -3925,11 +3878,11 @@
       <c r="H82" s="3">
         <v>3</v>
       </c>
-      <c r="J82" s="9"/>
+      <c r="J82" s="1"/>
     </row>
     <row r="83" s="3" customFormat="1" spans="1:10">
       <c r="A83" s="3">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3002</v>
       </c>
       <c r="B83" s="3">
@@ -3940,7 +3893,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="1">
-        <f>100000+C83*1000+B83</f>
+        <f t="shared" si="3"/>
         <v>103002</v>
       </c>
       <c r="E83" s="3" t="s">
@@ -3955,11 +3908,11 @@
       <c r="H83" s="3">
         <v>6</v>
       </c>
-      <c r="J83" s="9"/>
+      <c r="J83" s="1"/>
     </row>
     <row r="84" s="3" customFormat="1" spans="1:10">
       <c r="A84" s="3">
-        <f>C84*1000+B84</f>
+        <f t="shared" si="5"/>
         <v>3003</v>
       </c>
       <c r="B84" s="3">
@@ -3970,7 +3923,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="1">
-        <f>100000+C84*1000+B84</f>
+        <f t="shared" si="3"/>
         <v>103003</v>
       </c>
       <c r="E84" s="3" t="s">
@@ -3985,11 +3938,11 @@
       <c r="H84" s="3">
         <v>9</v>
       </c>
-      <c r="J84" s="9"/>
+      <c r="J84" s="1"/>
     </row>
     <row r="85" s="4" customFormat="1" spans="1:10">
       <c r="A85" s="4">
-        <f>C85*1000+B85</f>
+        <f t="shared" si="5"/>
         <v>4001</v>
       </c>
       <c r="B85" s="4">
@@ -4000,7 +3953,7 @@
         <v>4</v>
       </c>
       <c r="D85" s="4">
-        <f>100000+C85*1000+B85</f>
+        <f t="shared" si="3"/>
         <v>104001</v>
       </c>
       <c r="E85" s="4" t="s">
@@ -4010,7 +3963,7 @@
         <v>174</v>
       </c>
       <c r="G85" s="4">
-        <f>200000+A85</f>
+        <f t="shared" ref="G85:G93" si="6">200000+A85</f>
         <v>204001</v>
       </c>
       <c r="H85" s="3">
@@ -4021,7 +3974,7 @@
     </row>
     <row r="86" s="4" customFormat="1" spans="1:10">
       <c r="A86" s="4">
-        <f>C86*1000+B86</f>
+        <f t="shared" si="5"/>
         <v>4002</v>
       </c>
       <c r="B86" s="4">
@@ -4032,7 +3985,7 @@
         <v>4</v>
       </c>
       <c r="D86" s="4">
-        <f>100000+C86*1000+B86</f>
+        <f t="shared" si="3"/>
         <v>104002</v>
       </c>
       <c r="E86" s="4" t="s">
@@ -4042,7 +3995,7 @@
         <v>176</v>
       </c>
       <c r="G86" s="4">
-        <f>200000+A86</f>
+        <f t="shared" si="6"/>
         <v>204002</v>
       </c>
       <c r="H86" s="3">
@@ -4053,7 +4006,7 @@
     </row>
     <row r="87" s="4" customFormat="1" spans="1:10">
       <c r="A87" s="4">
-        <f>C87*1000+B87</f>
+        <f t="shared" si="5"/>
         <v>4003</v>
       </c>
       <c r="B87" s="4">
@@ -4064,7 +4017,7 @@
         <v>4</v>
       </c>
       <c r="D87" s="4">
-        <f>100000+C87*1000+B87</f>
+        <f t="shared" si="3"/>
         <v>104003</v>
       </c>
       <c r="E87" s="4" t="s">
@@ -4074,7 +4027,7 @@
         <v>178</v>
       </c>
       <c r="G87" s="4">
-        <f>200000+A87</f>
+        <f t="shared" si="6"/>
         <v>204003</v>
       </c>
       <c r="H87" s="3">
@@ -4085,7 +4038,7 @@
     </row>
     <row r="88" s="5" customFormat="1" spans="1:10">
       <c r="A88" s="5">
-        <f>C88*1000+B88</f>
+        <f t="shared" si="5"/>
         <v>5001</v>
       </c>
       <c r="B88" s="5">
@@ -4096,7 +4049,7 @@
         <v>5</v>
       </c>
       <c r="D88" s="5">
-        <f>100000+C88*1000+B88</f>
+        <f t="shared" si="3"/>
         <v>105001</v>
       </c>
       <c r="E88" s="5" t="s">
@@ -4106,7 +4059,7 @@
         <v>180</v>
       </c>
       <c r="G88" s="5">
-        <f>200000+A88</f>
+        <f t="shared" si="6"/>
         <v>205001</v>
       </c>
       <c r="H88" s="3">
@@ -4117,7 +4070,7 @@
     </row>
     <row r="89" s="5" customFormat="1" spans="1:10">
       <c r="A89" s="5">
-        <f>C89*1000+B89</f>
+        <f t="shared" si="5"/>
         <v>5002</v>
       </c>
       <c r="B89" s="5">
@@ -4138,7 +4091,7 @@
         <v>182</v>
       </c>
       <c r="G89" s="5">
-        <f>200000+A89</f>
+        <f t="shared" si="6"/>
         <v>205002</v>
       </c>
       <c r="H89" s="3">
@@ -4149,7 +4102,7 @@
     </row>
     <row r="90" s="5" customFormat="1" spans="1:10">
       <c r="A90" s="5">
-        <f>C90*1000+B90</f>
+        <f t="shared" si="5"/>
         <v>5003</v>
       </c>
       <c r="B90" s="5">
@@ -4170,7 +4123,7 @@
         <v>184</v>
       </c>
       <c r="G90" s="5">
-        <f>200000+A90</f>
+        <f t="shared" si="6"/>
         <v>205003</v>
       </c>
       <c r="H90" s="3">
@@ -4181,7 +4134,7 @@
     </row>
     <row r="91" s="6" customFormat="1" spans="1:10">
       <c r="A91" s="6">
-        <f>C91*1000+B91</f>
+        <f t="shared" si="5"/>
         <v>6001</v>
       </c>
       <c r="B91" s="6">
@@ -4202,7 +4155,7 @@
         <v>186</v>
       </c>
       <c r="G91" s="6">
-        <f>200000+A91</f>
+        <f t="shared" si="6"/>
         <v>206001</v>
       </c>
       <c r="H91" s="3">
@@ -4213,7 +4166,7 @@
     </row>
     <row r="92" s="6" customFormat="1" spans="1:10">
       <c r="A92" s="6">
-        <f>C92*1000+B92</f>
+        <f t="shared" si="5"/>
         <v>6002</v>
       </c>
       <c r="B92" s="6">
@@ -4234,7 +4187,7 @@
         <v>188</v>
       </c>
       <c r="G92" s="6">
-        <f>200000+A92</f>
+        <f t="shared" si="6"/>
         <v>206002</v>
       </c>
       <c r="H92" s="3">
@@ -4245,7 +4198,7 @@
     </row>
     <row r="93" s="6" customFormat="1" spans="1:10">
       <c r="A93" s="6">
-        <f>C93*1000+B93</f>
+        <f t="shared" si="5"/>
         <v>6003</v>
       </c>
       <c r="B93" s="6">
@@ -4266,7 +4219,7 @@
         <v>190</v>
       </c>
       <c r="G93" s="6">
-        <f>200000+A93</f>
+        <f t="shared" si="6"/>
         <v>206003</v>
       </c>
       <c r="H93" s="3">

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="avatar" sheetId="1" r:id="rId1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="188">
   <si>
     <t>id</t>
   </si>
@@ -630,15 +630,12 @@
     <t>VIP_pf_cm1.png</t>
   </si>
   <si>
+    <t>VIP_pf_cm2.png</t>
+  </si>
+  <si>
     <t>筹码2</t>
   </si>
   <si>
-    <t>VIP_pf_cm2.png</t>
-  </si>
-  <si>
-    <t>筹码3</t>
-  </si>
-  <si>
     <t>VIP_pf_cm3.png</t>
   </si>
   <si>
@@ -648,21 +645,21 @@
     <t>VIP_pf_pai1.png</t>
   </si>
   <si>
+    <t>VIP_pf_pai2.png</t>
+  </si>
+  <si>
     <t>牌背2</t>
   </si>
   <si>
-    <t>VIP_pf_pai2.png</t>
-  </si>
-  <si>
-    <t>牌背3</t>
-  </si>
-  <si>
     <t>VIP_pf_pai3.png</t>
   </si>
   <si>
     <t>大厅背景1</t>
   </si>
   <si>
+    <t>VIP_pf_bj0.png</t>
+  </si>
+  <si>
     <t>VIP_pf_bj1.png</t>
   </si>
   <si>
@@ -670,12 +667,6 @@
   </si>
   <si>
     <t>VIP_pf_bj2.png</t>
-  </si>
-  <si>
-    <t>大厅背景3</t>
-  </si>
-  <si>
-    <t>VIP_pf_bj3.png</t>
   </si>
 </sst>
 </file>
@@ -841,7 +832,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -852,7 +843,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1685,15 +1676,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R93"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="19.125" customWidth="1"/>
     <col min="7" max="7" width="12.5" customWidth="1"/>
-    <col min="8" max="8" width="12.125" customWidth="1"/>
-    <col min="17" max="17" width="14.375" customWidth="1"/>
+    <col min="8" max="9" width="12.125" customWidth="1"/>
+    <col min="14" max="15" width="12.625"/>
+    <col min="18" max="18" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:8">
@@ -1759,7 +1751,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A24" si="0">C5*1000+B5</f>
         <v>1</v>
@@ -1784,8 +1776,11 @@
       <c r="G5" s="1">
         <v>200001</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1810,8 +1805,11 @@
       <c r="G6" s="1">
         <v>200002</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:15">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1836,8 +1834,11 @@
       <c r="G7" s="1">
         <v>200003</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:15">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1862,8 +1863,11 @@
       <c r="G8" s="1">
         <v>200004</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:15">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1888,8 +1892,11 @@
       <c r="G9" s="1">
         <v>200005</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:15">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1914,8 +1921,11 @@
       <c r="G10" s="1">
         <v>200006</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:7">
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:15">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1940,8 +1950,11 @@
       <c r="G11" s="1">
         <v>200007</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:15">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1966,8 +1979,11 @@
       <c r="G12" s="1">
         <v>200008</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:7">
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:15">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1992,8 +2008,11 @@
       <c r="G13" s="1">
         <v>200009</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:15">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2018,8 +2037,11 @@
       <c r="G14" s="1">
         <v>200010</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:15">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2044,8 +2066,11 @@
       <c r="G15" s="1">
         <v>200011</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:7">
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:15">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2070,8 +2095,11 @@
       <c r="G16" s="1">
         <v>200012</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:7">
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:15">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2096,8 +2124,11 @@
       <c r="G17" s="1">
         <v>200013</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:7">
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:15">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2122,8 +2153,11 @@
       <c r="G18" s="1">
         <v>200014</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:7">
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:15">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2148,8 +2182,11 @@
       <c r="G19" s="1">
         <v>200015</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:7">
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:15">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2174,8 +2211,11 @@
       <c r="G20" s="1">
         <v>200016</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:7">
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:15">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2200,8 +2240,11 @@
       <c r="G21" s="1">
         <v>200017</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:7">
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:15">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2226,8 +2269,11 @@
       <c r="G22" s="1">
         <v>200018</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:7">
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:15">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2252,8 +2298,11 @@
       <c r="G23" s="1">
         <v>200019</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:7">
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:15">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2278,8 +2327,11 @@
       <c r="G24" s="1">
         <v>200020</v>
       </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:7">
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:15">
       <c r="A25" s="1">
         <f t="shared" ref="A25:A43" si="2">C25*1000+B25</f>
         <v>21</v>
@@ -2304,8 +2356,11 @@
       <c r="G25" s="1">
         <v>200021</v>
       </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:7">
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:15">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2330,8 +2385,11 @@
       <c r="G26" s="1">
         <v>200022</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:7">
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:15">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2356,8 +2414,11 @@
       <c r="G27" s="1">
         <v>200023</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:7">
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:15">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2382,8 +2443,11 @@
       <c r="G28" s="1">
         <v>200024</v>
       </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:7">
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:15">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2408,8 +2472,11 @@
       <c r="G29" s="1">
         <v>200025</v>
       </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:7">
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:15">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2434,8 +2501,11 @@
       <c r="G30" s="1">
         <v>200026</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:7">
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:15">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2460,8 +2530,11 @@
       <c r="G31" s="1">
         <v>200027</v>
       </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:7">
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:15">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2486,8 +2559,11 @@
       <c r="G32" s="1">
         <v>200028</v>
       </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:7">
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:15">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -2512,8 +2588,11 @@
       <c r="G33" s="1">
         <v>200029</v>
       </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:7">
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:15">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -2538,8 +2617,11 @@
       <c r="G34" s="1">
         <v>200030</v>
       </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:7">
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:15">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -2564,8 +2646,11 @@
       <c r="G35" s="1">
         <v>200031</v>
       </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:7">
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:15">
       <c r="A36" s="1">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -2590,8 +2675,11 @@
       <c r="G36" s="1">
         <v>200032</v>
       </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:7">
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:15">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -2616,8 +2704,11 @@
       <c r="G37" s="1">
         <v>200033</v>
       </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:7">
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:15">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -2642,8 +2733,11 @@
       <c r="G38" s="1">
         <v>200034</v>
       </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:7">
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:15">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -2668,8 +2762,11 @@
       <c r="G39" s="1">
         <v>200035</v>
       </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:7">
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:15">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -2694,8 +2791,11 @@
       <c r="G40" s="1">
         <v>200036</v>
       </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:7">
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:15">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -2720,8 +2820,11 @@
       <c r="G41" s="1">
         <v>200037</v>
       </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:7">
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:15">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -2746,8 +2849,11 @@
       <c r="G42" s="1">
         <v>200038</v>
       </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:7">
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:15">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -2772,6 +2878,9 @@
       <c r="G43" s="1">
         <v>200039</v>
       </c>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
@@ -2955,7 +3064,7 @@
         <v>201007</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:19">
       <c r="A51">
         <f t="shared" si="4"/>
         <v>1008</v>
@@ -2980,9 +3089,9 @@
       <c r="G51">
         <v>201008</v>
       </c>
-      <c r="R51" s="1"/>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="S51" s="1"/>
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52">
         <f t="shared" si="4"/>
         <v>1009</v>
@@ -3007,9 +3116,9 @@
       <c r="G52">
         <v>201009</v>
       </c>
-      <c r="R52" s="1"/>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="S52" s="1"/>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53">
         <f t="shared" si="4"/>
         <v>1010</v>
@@ -3035,10 +3144,11 @@
         <v>201010</v>
       </c>
       <c r="H53" s="7"/>
-      <c r="J53" s="1"/>
-      <c r="R53" s="1"/>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="I53" s="7"/>
+      <c r="K53" s="1"/>
+      <c r="S53" s="1"/>
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54">
         <f t="shared" si="4"/>
         <v>1011</v>
@@ -3064,10 +3174,11 @@
         <v>201011</v>
       </c>
       <c r="H54" s="7"/>
-      <c r="J54" s="1"/>
-      <c r="R54" s="1"/>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="I54" s="7"/>
+      <c r="K54" s="1"/>
+      <c r="S54" s="1"/>
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55">
         <f t="shared" si="4"/>
         <v>1012</v>
@@ -3093,10 +3204,11 @@
         <v>201012</v>
       </c>
       <c r="H55" s="7"/>
-      <c r="J55" s="1"/>
-      <c r="R55" s="1"/>
-    </row>
-    <row r="56" spans="1:18">
+      <c r="I55" s="7"/>
+      <c r="K55" s="1"/>
+      <c r="S55" s="1"/>
+    </row>
+    <row r="56" spans="1:19">
       <c r="A56">
         <f t="shared" si="4"/>
         <v>1013</v>
@@ -3122,10 +3234,11 @@
         <v>201013</v>
       </c>
       <c r="H56" s="7"/>
-      <c r="J56" s="1"/>
-      <c r="R56" s="1"/>
-    </row>
-    <row r="57" spans="1:18">
+      <c r="I56" s="7"/>
+      <c r="K56" s="1"/>
+      <c r="S56" s="1"/>
+    </row>
+    <row r="57" spans="1:19">
       <c r="A57">
         <f t="shared" si="4"/>
         <v>1014</v>
@@ -3151,10 +3264,11 @@
         <v>201014</v>
       </c>
       <c r="H57" s="7"/>
-      <c r="J57" s="1"/>
-      <c r="R57" s="1"/>
-    </row>
-    <row r="58" spans="1:18">
+      <c r="I57" s="7"/>
+      <c r="K57" s="1"/>
+      <c r="S57" s="1"/>
+    </row>
+    <row r="58" spans="1:19">
       <c r="A58">
         <f t="shared" si="4"/>
         <v>1015</v>
@@ -3180,10 +3294,11 @@
         <v>201015</v>
       </c>
       <c r="H58" s="7"/>
-      <c r="J58" s="1"/>
-      <c r="R58" s="1"/>
-    </row>
-    <row r="59" spans="1:18">
+      <c r="I58" s="7"/>
+      <c r="K58" s="1"/>
+      <c r="S58" s="1"/>
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59">
         <f t="shared" si="4"/>
         <v>1016</v>
@@ -3209,10 +3324,11 @@
         <v>201016</v>
       </c>
       <c r="H59" s="7"/>
-      <c r="J59" s="1"/>
-      <c r="R59" s="1"/>
-    </row>
-    <row r="60" spans="1:18">
+      <c r="I59" s="7"/>
+      <c r="K59" s="1"/>
+      <c r="S59" s="1"/>
+    </row>
+    <row r="60" spans="1:19">
       <c r="A60">
         <f t="shared" si="4"/>
         <v>1017</v>
@@ -3238,10 +3354,11 @@
         <v>201017</v>
       </c>
       <c r="H60" s="7"/>
-      <c r="J60" s="1"/>
-      <c r="R60" s="1"/>
-    </row>
-    <row r="61" spans="1:18">
+      <c r="I60" s="7"/>
+      <c r="K60" s="1"/>
+      <c r="S60" s="1"/>
+    </row>
+    <row r="61" spans="1:19">
       <c r="A61">
         <f t="shared" si="4"/>
         <v>1018</v>
@@ -3267,10 +3384,11 @@
         <v>201018</v>
       </c>
       <c r="H61" s="7"/>
-      <c r="J61" s="1"/>
-      <c r="R61" s="1"/>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="1:18">
+      <c r="I61" s="7"/>
+      <c r="K61" s="1"/>
+      <c r="S61" s="1"/>
+    </row>
+    <row r="62" s="2" customFormat="1" spans="1:19">
       <c r="A62" s="2">
         <f t="shared" si="4"/>
         <v>2001</v>
@@ -3283,7 +3401,7 @@
         <v>2</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D62:D93" si="5">100000+C62*1000+B62</f>
         <v>102001</v>
       </c>
       <c r="E62" s="2" t="s">
@@ -3296,10 +3414,13 @@
         <v>202001</v>
       </c>
       <c r="H62" s="2"/>
-      <c r="J62" s="8"/>
-      <c r="R62" s="1"/>
-    </row>
-    <row r="63" s="2" customFormat="1" spans="1:18">
+      <c r="K62" s="8"/>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="S62" s="1"/>
+    </row>
+    <row r="63" s="2" customFormat="1" spans="1:19">
       <c r="A63" s="2">
         <f t="shared" si="4"/>
         <v>2002</v>
@@ -3312,7 +3433,7 @@
         <v>2</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102002</v>
       </c>
       <c r="E63" s="2" t="s">
@@ -3325,12 +3446,15 @@
         <v>202002</v>
       </c>
       <c r="H63" s="2"/>
-      <c r="J63" s="8"/>
-      <c r="R63" s="1"/>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:18">
+      <c r="K63" s="8"/>
+      <c r="M63"/>
+      <c r="N63"/>
+      <c r="O63"/>
+      <c r="S63" s="1"/>
+    </row>
+    <row r="64" s="2" customFormat="1" spans="1:19">
       <c r="A64" s="2">
-        <f t="shared" ref="A64:A93" si="5">C64*1000+B64</f>
+        <f t="shared" ref="A64:A93" si="6">C64*1000+B64</f>
         <v>2003</v>
       </c>
       <c r="B64" s="2">
@@ -3341,7 +3465,7 @@
         <v>2</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102003</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -3354,12 +3478,15 @@
         <v>202003</v>
       </c>
       <c r="H64" s="2"/>
-      <c r="J64" s="8"/>
-      <c r="R64" s="1"/>
-    </row>
-    <row r="65" s="2" customFormat="1" spans="1:18">
+      <c r="K64" s="8"/>
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="O64"/>
+      <c r="S64" s="1"/>
+    </row>
+    <row r="65" s="2" customFormat="1" spans="1:19">
       <c r="A65" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2004</v>
       </c>
       <c r="B65" s="2">
@@ -3370,7 +3497,7 @@
         <v>2</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102004</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -3383,12 +3510,15 @@
         <v>202004</v>
       </c>
       <c r="H65" s="2"/>
-      <c r="J65" s="8"/>
-      <c r="R65" s="1"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:18">
+      <c r="K65" s="8"/>
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="S65" s="1"/>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="1:19">
       <c r="A66" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2005</v>
       </c>
       <c r="B66" s="2">
@@ -3399,7 +3529,7 @@
         <v>2</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102005</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -3412,12 +3542,15 @@
         <v>202005</v>
       </c>
       <c r="H66" s="2"/>
-      <c r="J66" s="8"/>
-      <c r="R66" s="1"/>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="1:18">
+      <c r="K66" s="8"/>
+      <c r="M66"/>
+      <c r="N66"/>
+      <c r="O66"/>
+      <c r="S66" s="1"/>
+    </row>
+    <row r="67" s="2" customFormat="1" spans="1:19">
       <c r="A67" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2006</v>
       </c>
       <c r="B67" s="2">
@@ -3428,7 +3561,7 @@
         <v>2</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102006</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -3441,12 +3574,15 @@
         <v>202006</v>
       </c>
       <c r="H67" s="2"/>
-      <c r="J67" s="8"/>
-      <c r="R67" s="1"/>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:18">
+      <c r="K67" s="8"/>
+      <c r="M67"/>
+      <c r="N67"/>
+      <c r="O67"/>
+      <c r="S67" s="1"/>
+    </row>
+    <row r="68" s="2" customFormat="1" spans="1:19">
       <c r="A68" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2007</v>
       </c>
       <c r="B68" s="2">
@@ -3457,7 +3593,7 @@
         <v>2</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102007</v>
       </c>
       <c r="E68" s="2" t="s">
@@ -3470,12 +3606,15 @@
         <v>202007</v>
       </c>
       <c r="H68" s="2"/>
-      <c r="J68" s="8"/>
-      <c r="R68" s="1"/>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:18">
+      <c r="K68" s="8"/>
+      <c r="M68"/>
+      <c r="N68"/>
+      <c r="O68"/>
+      <c r="S68" s="1"/>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:19">
       <c r="A69" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2008</v>
       </c>
       <c r="B69" s="2">
@@ -3486,7 +3625,7 @@
         <v>2</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102008</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -3499,12 +3638,15 @@
         <v>202008</v>
       </c>
       <c r="H69" s="2"/>
-      <c r="J69" s="8"/>
-      <c r="R69" s="1"/>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:18">
+      <c r="K69" s="8"/>
+      <c r="M69"/>
+      <c r="N69"/>
+      <c r="O69"/>
+      <c r="S69" s="1"/>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:19">
       <c r="A70" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2009</v>
       </c>
       <c r="B70" s="2">
@@ -3515,7 +3657,7 @@
         <v>2</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102009</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -3528,12 +3670,15 @@
         <v>202009</v>
       </c>
       <c r="H70" s="2"/>
-      <c r="J70" s="8"/>
-      <c r="R70" s="1"/>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:18">
+      <c r="K70" s="8"/>
+      <c r="M70"/>
+      <c r="N70"/>
+      <c r="O70"/>
+      <c r="S70" s="1"/>
+    </row>
+    <row r="71" s="2" customFormat="1" spans="1:19">
       <c r="A71" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2010</v>
       </c>
       <c r="B71" s="2">
@@ -3544,7 +3689,7 @@
         <v>2</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102010</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -3557,12 +3702,15 @@
         <v>202010</v>
       </c>
       <c r="H71" s="2"/>
-      <c r="J71" s="8"/>
-      <c r="R71" s="1"/>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:18">
+      <c r="K71" s="8"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="S71" s="1"/>
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:19">
       <c r="A72" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2011</v>
       </c>
       <c r="B72" s="2">
@@ -3573,7 +3721,7 @@
         <v>2</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102011</v>
       </c>
       <c r="E72" s="2" t="s">
@@ -3586,12 +3734,15 @@
         <v>202011</v>
       </c>
       <c r="H72" s="2"/>
-      <c r="J72" s="8"/>
-      <c r="R72" s="1"/>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:18">
+      <c r="K72" s="8"/>
+      <c r="M72"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="S72" s="1"/>
+    </row>
+    <row r="73" s="2" customFormat="1" spans="1:19">
       <c r="A73" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2012</v>
       </c>
       <c r="B73" s="2">
@@ -3602,7 +3753,7 @@
         <v>2</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102012</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -3615,12 +3766,15 @@
         <v>202012</v>
       </c>
       <c r="H73" s="2"/>
-      <c r="J73" s="8"/>
-      <c r="R73" s="1"/>
-    </row>
-    <row r="74" s="2" customFormat="1" spans="1:18">
+      <c r="K73" s="8"/>
+      <c r="M73"/>
+      <c r="N73"/>
+      <c r="O73"/>
+      <c r="S73" s="1"/>
+    </row>
+    <row r="74" s="2" customFormat="1" spans="1:19">
       <c r="A74" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2013</v>
       </c>
       <c r="B74" s="2">
@@ -3631,7 +3785,7 @@
         <v>2</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102013</v>
       </c>
       <c r="E74" s="2" t="s">
@@ -3644,12 +3798,15 @@
         <v>202013</v>
       </c>
       <c r="H74" s="2"/>
-      <c r="J74" s="8"/>
-      <c r="R74" s="1"/>
-    </row>
-    <row r="75" s="2" customFormat="1" spans="1:18">
+      <c r="K74" s="8"/>
+      <c r="M74"/>
+      <c r="N74"/>
+      <c r="O74"/>
+      <c r="S74" s="1"/>
+    </row>
+    <row r="75" s="2" customFormat="1" spans="1:19">
       <c r="A75" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2014</v>
       </c>
       <c r="B75" s="2">
@@ -3660,7 +3817,7 @@
         <v>2</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102014</v>
       </c>
       <c r="E75" s="2" t="s">
@@ -3673,12 +3830,15 @@
         <v>202014</v>
       </c>
       <c r="H75" s="2"/>
-      <c r="J75" s="8"/>
-      <c r="R75" s="1"/>
-    </row>
-    <row r="76" s="2" customFormat="1" spans="1:18">
+      <c r="K75" s="8"/>
+      <c r="M75"/>
+      <c r="N75"/>
+      <c r="O75"/>
+      <c r="S75" s="1"/>
+    </row>
+    <row r="76" s="2" customFormat="1" spans="1:19">
       <c r="A76" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2015</v>
       </c>
       <c r="B76" s="2">
@@ -3689,7 +3849,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102015</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -3702,12 +3862,15 @@
         <v>202015</v>
       </c>
       <c r="H76" s="2"/>
-      <c r="J76" s="8"/>
-      <c r="R76" s="1"/>
-    </row>
-    <row r="77" s="2" customFormat="1" spans="1:18">
+      <c r="K76" s="8"/>
+      <c r="M76"/>
+      <c r="N76"/>
+      <c r="O76"/>
+      <c r="S76" s="1"/>
+    </row>
+    <row r="77" s="2" customFormat="1" spans="1:19">
       <c r="A77" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2016</v>
       </c>
       <c r="B77" s="2">
@@ -3718,7 +3881,7 @@
         <v>2</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102016</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -3731,12 +3894,15 @@
         <v>202016</v>
       </c>
       <c r="H77" s="2"/>
-      <c r="J77" s="8"/>
-      <c r="R77" s="1"/>
-    </row>
-    <row r="78" s="2" customFormat="1" spans="1:18">
+      <c r="K77" s="8"/>
+      <c r="M77"/>
+      <c r="N77"/>
+      <c r="O77"/>
+      <c r="S77" s="1"/>
+    </row>
+    <row r="78" s="2" customFormat="1" spans="1:19">
       <c r="A78" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2017</v>
       </c>
       <c r="B78" s="2">
@@ -3747,7 +3913,7 @@
         <v>2</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102017</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -3760,12 +3926,15 @@
         <v>202017</v>
       </c>
       <c r="H78" s="2"/>
-      <c r="J78" s="8"/>
-      <c r="R78" s="1"/>
-    </row>
-    <row r="79" s="2" customFormat="1" spans="1:18">
+      <c r="K78" s="8"/>
+      <c r="M78"/>
+      <c r="N78"/>
+      <c r="O78"/>
+      <c r="S78" s="1"/>
+    </row>
+    <row r="79" s="2" customFormat="1" spans="1:19">
       <c r="A79" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2018</v>
       </c>
       <c r="B79" s="2">
@@ -3776,7 +3945,7 @@
         <v>2</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102018</v>
       </c>
       <c r="E79" s="2" t="s">
@@ -3789,12 +3958,15 @@
         <v>202018</v>
       </c>
       <c r="H79" s="2"/>
-      <c r="J79" s="8"/>
-      <c r="R79" s="1"/>
-    </row>
-    <row r="80" s="2" customFormat="1" spans="1:18">
+      <c r="K79" s="8"/>
+      <c r="M79"/>
+      <c r="N79"/>
+      <c r="O79"/>
+      <c r="S79" s="1"/>
+    </row>
+    <row r="80" s="2" customFormat="1" spans="1:19">
       <c r="A80" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2019</v>
       </c>
       <c r="B80" s="2">
@@ -3805,7 +3977,7 @@
         <v>2</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102019</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -3818,12 +3990,15 @@
         <v>202019</v>
       </c>
       <c r="H80" s="2"/>
-      <c r="J80" s="8"/>
-      <c r="R80" s="1"/>
-    </row>
-    <row r="81" s="2" customFormat="1" spans="1:18">
+      <c r="K80" s="8"/>
+      <c r="M80"/>
+      <c r="N80"/>
+      <c r="O80"/>
+      <c r="S80" s="1"/>
+    </row>
+    <row r="81" s="2" customFormat="1" spans="1:19">
       <c r="A81" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2020</v>
       </c>
       <c r="B81" s="2">
@@ -3834,7 +4009,7 @@
         <v>2</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102020</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -3847,12 +4022,15 @@
         <v>202020</v>
       </c>
       <c r="H81" s="2"/>
-      <c r="J81" s="8"/>
-      <c r="R81" s="1"/>
-    </row>
-    <row r="82" s="3" customFormat="1" spans="1:10">
+      <c r="K81" s="8"/>
+      <c r="M81"/>
+      <c r="N81"/>
+      <c r="O81"/>
+      <c r="S81" s="1"/>
+    </row>
+    <row r="82" s="3" customFormat="1" spans="1:11">
       <c r="A82" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3001</v>
       </c>
       <c r="B82" s="3">
@@ -3863,7 +4041,7 @@
         <v>3</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>103001</v>
       </c>
       <c r="E82" s="3" t="s">
@@ -3878,11 +4056,11 @@
       <c r="H82" s="3">
         <v>3</v>
       </c>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" s="3" customFormat="1" spans="1:10">
+      <c r="K82" s="1"/>
+    </row>
+    <row r="83" s="3" customFormat="1" spans="1:11">
       <c r="A83" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3002</v>
       </c>
       <c r="B83" s="3">
@@ -3893,7 +4071,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>103002</v>
       </c>
       <c r="E83" s="3" t="s">
@@ -3908,11 +4086,11 @@
       <c r="H83" s="3">
         <v>6</v>
       </c>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" s="3" customFormat="1" spans="1:10">
+      <c r="K83" s="1"/>
+    </row>
+    <row r="84" s="3" customFormat="1" spans="1:11">
       <c r="A84" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3003</v>
       </c>
       <c r="B84" s="3">
@@ -3923,7 +4101,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>103003</v>
       </c>
       <c r="E84" s="3" t="s">
@@ -3938,11 +4116,11 @@
       <c r="H84" s="3">
         <v>9</v>
       </c>
-      <c r="J84" s="1"/>
-    </row>
-    <row r="85" s="4" customFormat="1" spans="1:10">
+      <c r="K84" s="1"/>
+    </row>
+    <row r="85" s="4" customFormat="1" spans="1:11">
       <c r="A85" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4001</v>
       </c>
       <c r="B85" s="4">
@@ -3953,7 +4131,7 @@
         <v>4</v>
       </c>
       <c r="D85" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>104001</v>
       </c>
       <c r="E85" s="4" t="s">
@@ -3963,18 +4141,17 @@
         <v>174</v>
       </c>
       <c r="G85" s="4">
-        <f t="shared" ref="G85:G93" si="6">200000+A85</f>
+        <f t="shared" ref="G85:G94" si="7">200000+A85</f>
         <v>204001</v>
       </c>
-      <c r="H85" s="3">
-        <v>3</v>
-      </c>
+      <c r="H85" s="3"/>
       <c r="I85" s="3"/>
-      <c r="J85" s="9"/>
-    </row>
-    <row r="86" s="4" customFormat="1" spans="1:10">
+      <c r="J85" s="3"/>
+      <c r="K85" s="9"/>
+    </row>
+    <row r="86" s="4" customFormat="1" spans="1:11">
       <c r="A86" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4002</v>
       </c>
       <c r="B86" s="4">
@@ -3985,28 +4162,29 @@
         <v>4</v>
       </c>
       <c r="D86" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>104002</v>
       </c>
       <c r="E86" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>176</v>
-      </c>
       <c r="G86" s="4">
+        <f t="shared" si="7"/>
+        <v>204002</v>
+      </c>
+      <c r="H86" s="3">
+        <v>3</v>
+      </c>
+      <c r="I86" s="3"/>
+      <c r="J86" s="3"/>
+      <c r="K86" s="9"/>
+    </row>
+    <row r="87" s="4" customFormat="1" spans="1:11">
+      <c r="A87" s="4">
         <f t="shared" si="6"/>
-        <v>204002</v>
-      </c>
-      <c r="H86" s="3">
-        <v>6</v>
-      </c>
-      <c r="I86" s="3"/>
-      <c r="J86" s="9"/>
-    </row>
-    <row r="87" s="4" customFormat="1" spans="1:10">
-      <c r="A87" s="4">
-        <f t="shared" si="5"/>
         <v>4003</v>
       </c>
       <c r="B87" s="4">
@@ -4017,28 +4195,29 @@
         <v>4</v>
       </c>
       <c r="D87" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>104003</v>
       </c>
       <c r="E87" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F87" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="G87" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>204003</v>
       </c>
       <c r="H87" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I87" s="3"/>
-      <c r="J87" s="9"/>
-    </row>
-    <row r="88" s="5" customFormat="1" spans="1:10">
+      <c r="J87" s="3"/>
+      <c r="K87" s="9"/>
+    </row>
+    <row r="88" s="5" customFormat="1" spans="1:11">
       <c r="A88" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="A88:A95" si="8">C88*1000+B88</f>
         <v>5001</v>
       </c>
       <c r="B88" s="5">
@@ -4049,28 +4228,27 @@
         <v>5</v>
       </c>
       <c r="D88" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D88:D95" si="9">100000+C88*1000+B88</f>
         <v>105001</v>
       </c>
       <c r="E88" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F88" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="F88" s="5" t="s">
-        <v>180</v>
-      </c>
       <c r="G88" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>205001</v>
       </c>
-      <c r="H88" s="3">
-        <v>3</v>
-      </c>
+      <c r="H88" s="3"/>
       <c r="I88" s="3"/>
-      <c r="J88" s="9"/>
-    </row>
-    <row r="89" s="5" customFormat="1" spans="1:10">
+      <c r="J88" s="3"/>
+      <c r="K88" s="9"/>
+    </row>
+    <row r="89" s="5" customFormat="1" spans="1:11">
       <c r="A89" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>5002</v>
       </c>
       <c r="B89" s="5">
@@ -4081,28 +4259,29 @@
         <v>5</v>
       </c>
       <c r="D89" s="5">
-        <f>100000+C89*1000+B89</f>
+        <f t="shared" si="9"/>
         <v>105002</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="G89" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>205002</v>
       </c>
       <c r="H89" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I89" s="3"/>
-      <c r="J89" s="9"/>
-    </row>
-    <row r="90" s="5" customFormat="1" spans="1:10">
+      <c r="J89" s="3"/>
+      <c r="K89" s="9"/>
+    </row>
+    <row r="90" s="5" customFormat="1" spans="1:11">
       <c r="A90" s="5">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>5003</v>
       </c>
       <c r="B90" s="5">
@@ -4113,28 +4292,29 @@
         <v>5</v>
       </c>
       <c r="D90" s="5">
-        <f>100000+C90*1000+B90</f>
+        <f t="shared" si="9"/>
         <v>105003</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G90" s="5">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>205003</v>
       </c>
       <c r="H90" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I90" s="3"/>
-      <c r="J90" s="9"/>
-    </row>
-    <row r="91" s="6" customFormat="1" spans="1:10">
+      <c r="J90" s="3"/>
+      <c r="K90" s="9"/>
+    </row>
+    <row r="91" s="6" customFormat="1" spans="1:11">
       <c r="A91" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6001</v>
       </c>
       <c r="B91" s="6">
@@ -4145,28 +4325,27 @@
         <v>6</v>
       </c>
       <c r="D91" s="6">
-        <f>100000+C91*1000+B91</f>
+        <f t="shared" si="9"/>
         <v>106001</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F91" s="6" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="G91" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>206001</v>
       </c>
-      <c r="H91" s="3">
-        <v>3</v>
-      </c>
+      <c r="H91" s="3"/>
       <c r="I91" s="3"/>
-      <c r="J91" s="9"/>
-    </row>
-    <row r="92" s="6" customFormat="1" spans="1:10">
+      <c r="J91" s="3"/>
+      <c r="K91" s="9"/>
+    </row>
+    <row r="92" s="6" customFormat="1" spans="1:11">
       <c r="A92" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6002</v>
       </c>
       <c r="B92" s="6">
@@ -4177,28 +4356,29 @@
         <v>6</v>
       </c>
       <c r="D92" s="6">
-        <f>100000+C92*1000+B92</f>
+        <f t="shared" si="9"/>
         <v>106002</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="G92" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>206002</v>
       </c>
       <c r="H92" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I92" s="3"/>
-      <c r="J92" s="9"/>
-    </row>
-    <row r="93" s="6" customFormat="1" spans="1:10">
+      <c r="J92" s="3"/>
+      <c r="K92" s="9"/>
+    </row>
+    <row r="93" s="6" customFormat="1" spans="1:11">
       <c r="A93" s="6">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>6003</v>
       </c>
       <c r="B93" s="6">
@@ -4209,24 +4389,25 @@
         <v>6</v>
       </c>
       <c r="D93" s="6">
-        <f>100000+C93*1000+B93</f>
+        <f t="shared" si="9"/>
         <v>106003</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="G93" s="6">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>206003</v>
       </c>
       <c r="H93" s="3">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I93" s="3"/>
-      <c r="J93" s="9"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="194">
   <si>
     <t>id</t>
   </si>
@@ -627,6 +627,9 @@
     <t>筹码1</t>
   </si>
   <si>
+    <t>VIP_pf_cm0.png</t>
+  </si>
+  <si>
     <t>VIP_pf_cm1.png</t>
   </si>
   <si>
@@ -645,6 +648,9 @@
     <t>牌背1</t>
   </si>
   <si>
+    <t>VIP_pf_pai0.png</t>
+  </si>
+  <si>
     <t>VIP_pf_pai1.png</t>
   </si>
   <si>
@@ -661,6 +667,9 @@
   </si>
   <si>
     <t>大厅背景1</t>
+  </si>
+  <si>
+    <t>VIP_pf_bj0.png</t>
   </si>
   <si>
     <t>VIP_pf_bj1.png</t>
@@ -841,12 +850,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1685,15 +1694,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R93"/>
+  <dimension ref="A1:S96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="5" max="5" width="9" customWidth="1"/>
     <col min="6" max="6" width="19.125" customWidth="1"/>
     <col min="7" max="7" width="12.5" customWidth="1"/>
-    <col min="8" max="8" width="12.125" customWidth="1"/>
-    <col min="17" max="17" width="14.375" customWidth="1"/>
+    <col min="8" max="9" width="12.125" customWidth="1"/>
+    <col min="14" max="15" width="12.625"/>
+    <col min="18" max="18" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="1" spans="1:8">
@@ -1759,7 +1769,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:7">
+    <row r="5" s="1" customFormat="1" spans="1:15">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A24" si="0">C5*1000+B5</f>
         <v>1</v>
@@ -1784,8 +1794,11 @@
       <c r="G5" s="1">
         <v>200001</v>
       </c>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:7">
+      <c r="M5"/>
+      <c r="N5"/>
+      <c r="O5"/>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:15">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1810,8 +1823,11 @@
       <c r="G6" s="1">
         <v>200002</v>
       </c>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:7">
+      <c r="M6"/>
+      <c r="N6"/>
+      <c r="O6"/>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:15">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1836,8 +1852,11 @@
       <c r="G7" s="1">
         <v>200003</v>
       </c>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:7">
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:15">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1862,8 +1881,11 @@
       <c r="G8" s="1">
         <v>200004</v>
       </c>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:7">
+      <c r="M8"/>
+      <c r="N8"/>
+      <c r="O8"/>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:15">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1888,8 +1910,11 @@
       <c r="G9" s="1">
         <v>200005</v>
       </c>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:7">
+      <c r="M9"/>
+      <c r="N9"/>
+      <c r="O9"/>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:15">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1914,8 +1939,11 @@
       <c r="G10" s="1">
         <v>200006</v>
       </c>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:7">
+      <c r="M10"/>
+      <c r="N10"/>
+      <c r="O10"/>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:15">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1940,8 +1968,11 @@
       <c r="G11" s="1">
         <v>200007</v>
       </c>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:7">
+      <c r="M11"/>
+      <c r="N11"/>
+      <c r="O11"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:15">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1966,8 +1997,11 @@
       <c r="G12" s="1">
         <v>200008</v>
       </c>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:7">
+      <c r="M12"/>
+      <c r="N12"/>
+      <c r="O12"/>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:15">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1992,8 +2026,11 @@
       <c r="G13" s="1">
         <v>200009</v>
       </c>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:7">
+      <c r="M13"/>
+      <c r="N13"/>
+      <c r="O13"/>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:15">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2018,8 +2055,11 @@
       <c r="G14" s="1">
         <v>200010</v>
       </c>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:7">
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:15">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2044,8 +2084,11 @@
       <c r="G15" s="1">
         <v>200011</v>
       </c>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:7">
+      <c r="M15"/>
+      <c r="N15"/>
+      <c r="O15"/>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:15">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2070,8 +2113,11 @@
       <c r="G16" s="1">
         <v>200012</v>
       </c>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:7">
+      <c r="M16"/>
+      <c r="N16"/>
+      <c r="O16"/>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:15">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2096,8 +2142,11 @@
       <c r="G17" s="1">
         <v>200013</v>
       </c>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:7">
+      <c r="M17"/>
+      <c r="N17"/>
+      <c r="O17"/>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:15">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2122,8 +2171,11 @@
       <c r="G18" s="1">
         <v>200014</v>
       </c>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:7">
+      <c r="M18"/>
+      <c r="N18"/>
+      <c r="O18"/>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:15">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2148,8 +2200,11 @@
       <c r="G19" s="1">
         <v>200015</v>
       </c>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:7">
+      <c r="M19"/>
+      <c r="N19"/>
+      <c r="O19"/>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:15">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2174,8 +2229,11 @@
       <c r="G20" s="1">
         <v>200016</v>
       </c>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:7">
+      <c r="M20"/>
+      <c r="N20"/>
+      <c r="O20"/>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:15">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2200,8 +2258,11 @@
       <c r="G21" s="1">
         <v>200017</v>
       </c>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:7">
+      <c r="M21"/>
+      <c r="N21"/>
+      <c r="O21"/>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:15">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2226,8 +2287,11 @@
       <c r="G22" s="1">
         <v>200018</v>
       </c>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:7">
+      <c r="M22"/>
+      <c r="N22"/>
+      <c r="O22"/>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:15">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2252,8 +2316,11 @@
       <c r="G23" s="1">
         <v>200019</v>
       </c>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:7">
+      <c r="M23"/>
+      <c r="N23"/>
+      <c r="O23"/>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:15">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2278,8 +2345,11 @@
       <c r="G24" s="1">
         <v>200020</v>
       </c>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:7">
+      <c r="M24"/>
+      <c r="N24"/>
+      <c r="O24"/>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:15">
       <c r="A25" s="1">
         <f t="shared" ref="A25:A43" si="2">C25*1000+B25</f>
         <v>21</v>
@@ -2304,8 +2374,11 @@
       <c r="G25" s="1">
         <v>200021</v>
       </c>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:7">
+      <c r="M25"/>
+      <c r="N25"/>
+      <c r="O25"/>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:15">
       <c r="A26" s="1">
         <f t="shared" si="2"/>
         <v>22</v>
@@ -2330,8 +2403,11 @@
       <c r="G26" s="1">
         <v>200022</v>
       </c>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:7">
+      <c r="M26"/>
+      <c r="N26"/>
+      <c r="O26"/>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:15">
       <c r="A27" s="1">
         <f t="shared" si="2"/>
         <v>23</v>
@@ -2356,8 +2432,11 @@
       <c r="G27" s="1">
         <v>200023</v>
       </c>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:7">
+      <c r="M27"/>
+      <c r="N27"/>
+      <c r="O27"/>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:15">
       <c r="A28" s="1">
         <f t="shared" si="2"/>
         <v>24</v>
@@ -2382,8 +2461,11 @@
       <c r="G28" s="1">
         <v>200024</v>
       </c>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:7">
+      <c r="M28"/>
+      <c r="N28"/>
+      <c r="O28"/>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:15">
       <c r="A29" s="1">
         <f t="shared" si="2"/>
         <v>25</v>
@@ -2408,8 +2490,11 @@
       <c r="G29" s="1">
         <v>200025</v>
       </c>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:7">
+      <c r="M29"/>
+      <c r="N29"/>
+      <c r="O29"/>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:15">
       <c r="A30" s="1">
         <f t="shared" si="2"/>
         <v>26</v>
@@ -2434,8 +2519,11 @@
       <c r="G30" s="1">
         <v>200026</v>
       </c>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:7">
+      <c r="M30"/>
+      <c r="N30"/>
+      <c r="O30"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:15">
       <c r="A31" s="1">
         <f t="shared" si="2"/>
         <v>27</v>
@@ -2460,8 +2548,11 @@
       <c r="G31" s="1">
         <v>200027</v>
       </c>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:7">
+      <c r="M31"/>
+      <c r="N31"/>
+      <c r="O31"/>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:15">
       <c r="A32" s="1">
         <f t="shared" si="2"/>
         <v>28</v>
@@ -2486,8 +2577,11 @@
       <c r="G32" s="1">
         <v>200028</v>
       </c>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:7">
+      <c r="M32"/>
+      <c r="N32"/>
+      <c r="O32"/>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:15">
       <c r="A33" s="1">
         <f t="shared" si="2"/>
         <v>29</v>
@@ -2512,8 +2606,11 @@
       <c r="G33" s="1">
         <v>200029</v>
       </c>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:7">
+      <c r="M33"/>
+      <c r="N33"/>
+      <c r="O33"/>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:15">
       <c r="A34" s="1">
         <f t="shared" si="2"/>
         <v>30</v>
@@ -2538,8 +2635,11 @@
       <c r="G34" s="1">
         <v>200030</v>
       </c>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:7">
+      <c r="M34"/>
+      <c r="N34"/>
+      <c r="O34"/>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:15">
       <c r="A35" s="1">
         <f t="shared" si="2"/>
         <v>31</v>
@@ -2564,8 +2664,11 @@
       <c r="G35" s="1">
         <v>200031</v>
       </c>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:7">
+      <c r="M35"/>
+      <c r="N35"/>
+      <c r="O35"/>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:15">
       <c r="A36" s="1">
         <f t="shared" si="2"/>
         <v>32</v>
@@ -2590,8 +2693,11 @@
       <c r="G36" s="1">
         <v>200032</v>
       </c>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:7">
+      <c r="M36"/>
+      <c r="N36"/>
+      <c r="O36"/>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:15">
       <c r="A37" s="1">
         <f t="shared" si="2"/>
         <v>33</v>
@@ -2616,8 +2722,11 @@
       <c r="G37" s="1">
         <v>200033</v>
       </c>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:7">
+      <c r="M37"/>
+      <c r="N37"/>
+      <c r="O37"/>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:15">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -2642,8 +2751,11 @@
       <c r="G38" s="1">
         <v>200034</v>
       </c>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:7">
+      <c r="M38"/>
+      <c r="N38"/>
+      <c r="O38"/>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:15">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -2668,8 +2780,11 @@
       <c r="G39" s="1">
         <v>200035</v>
       </c>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:7">
+      <c r="M39"/>
+      <c r="N39"/>
+      <c r="O39"/>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:15">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -2694,8 +2809,11 @@
       <c r="G40" s="1">
         <v>200036</v>
       </c>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:7">
+      <c r="M40"/>
+      <c r="N40"/>
+      <c r="O40"/>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:15">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -2720,8 +2838,11 @@
       <c r="G41" s="1">
         <v>200037</v>
       </c>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:7">
+      <c r="M41"/>
+      <c r="N41"/>
+      <c r="O41"/>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:15">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -2746,8 +2867,11 @@
       <c r="G42" s="1">
         <v>200038</v>
       </c>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:7">
+      <c r="M42"/>
+      <c r="N42"/>
+      <c r="O42"/>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:15">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -2772,6 +2896,9 @@
       <c r="G43" s="1">
         <v>200039</v>
       </c>
+      <c r="M43"/>
+      <c r="N43"/>
+      <c r="O43"/>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
@@ -2955,7 +3082,7 @@
         <v>201007</v>
       </c>
     </row>
-    <row r="51" spans="1:18">
+    <row r="51" spans="1:19">
       <c r="A51">
         <f t="shared" si="4"/>
         <v>1008</v>
@@ -2980,9 +3107,9 @@
       <c r="G51">
         <v>201008</v>
       </c>
-      <c r="R51" s="1"/>
-    </row>
-    <row r="52" spans="1:18">
+      <c r="S51" s="1"/>
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52">
         <f t="shared" si="4"/>
         <v>1009</v>
@@ -3007,9 +3134,9 @@
       <c r="G52">
         <v>201009</v>
       </c>
-      <c r="R52" s="1"/>
-    </row>
-    <row r="53" spans="1:18">
+      <c r="S52" s="1"/>
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53">
         <f t="shared" si="4"/>
         <v>1010</v>
@@ -3035,10 +3162,11 @@
         <v>201010</v>
       </c>
       <c r="H53" s="7"/>
-      <c r="J53" s="1"/>
-      <c r="R53" s="1"/>
-    </row>
-    <row r="54" spans="1:18">
+      <c r="I53" s="7"/>
+      <c r="K53" s="1"/>
+      <c r="S53" s="1"/>
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54">
         <f t="shared" si="4"/>
         <v>1011</v>
@@ -3064,10 +3192,11 @@
         <v>201011</v>
       </c>
       <c r="H54" s="7"/>
-      <c r="J54" s="1"/>
-      <c r="R54" s="1"/>
-    </row>
-    <row r="55" spans="1:18">
+      <c r="I54" s="7"/>
+      <c r="K54" s="1"/>
+      <c r="S54" s="1"/>
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55">
         <f t="shared" si="4"/>
         <v>1012</v>
@@ -3093,10 +3222,11 @@
         <v>201012</v>
       </c>
       <c r="H55" s="7"/>
-      <c r="J55" s="1"/>
-      <c r="R55" s="1"/>
-    </row>
-    <row r="56" spans="1:18">
+      <c r="I55" s="7"/>
+      <c r="K55" s="1"/>
+      <c r="S55" s="1"/>
+    </row>
+    <row r="56" spans="1:19">
       <c r="A56">
         <f t="shared" si="4"/>
         <v>1013</v>
@@ -3122,10 +3252,11 @@
         <v>201013</v>
       </c>
       <c r="H56" s="7"/>
-      <c r="J56" s="1"/>
-      <c r="R56" s="1"/>
-    </row>
-    <row r="57" spans="1:18">
+      <c r="I56" s="7"/>
+      <c r="K56" s="1"/>
+      <c r="S56" s="1"/>
+    </row>
+    <row r="57" spans="1:19">
       <c r="A57">
         <f t="shared" si="4"/>
         <v>1014</v>
@@ -3151,10 +3282,11 @@
         <v>201014</v>
       </c>
       <c r="H57" s="7"/>
-      <c r="J57" s="1"/>
-      <c r="R57" s="1"/>
-    </row>
-    <row r="58" spans="1:18">
+      <c r="I57" s="7"/>
+      <c r="K57" s="1"/>
+      <c r="S57" s="1"/>
+    </row>
+    <row r="58" spans="1:19">
       <c r="A58">
         <f t="shared" si="4"/>
         <v>1015</v>
@@ -3180,10 +3312,11 @@
         <v>201015</v>
       </c>
       <c r="H58" s="7"/>
-      <c r="J58" s="1"/>
-      <c r="R58" s="1"/>
-    </row>
-    <row r="59" spans="1:18">
+      <c r="I58" s="7"/>
+      <c r="K58" s="1"/>
+      <c r="S58" s="1"/>
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59">
         <f t="shared" si="4"/>
         <v>1016</v>
@@ -3209,10 +3342,11 @@
         <v>201016</v>
       </c>
       <c r="H59" s="7"/>
-      <c r="J59" s="1"/>
-      <c r="R59" s="1"/>
-    </row>
-    <row r="60" spans="1:18">
+      <c r="I59" s="7"/>
+      <c r="K59" s="1"/>
+      <c r="S59" s="1"/>
+    </row>
+    <row r="60" spans="1:19">
       <c r="A60">
         <f t="shared" si="4"/>
         <v>1017</v>
@@ -3238,10 +3372,11 @@
         <v>201017</v>
       </c>
       <c r="H60" s="7"/>
-      <c r="J60" s="1"/>
-      <c r="R60" s="1"/>
-    </row>
-    <row r="61" spans="1:18">
+      <c r="I60" s="7"/>
+      <c r="K60" s="1"/>
+      <c r="S60" s="1"/>
+    </row>
+    <row r="61" spans="1:19">
       <c r="A61">
         <f t="shared" si="4"/>
         <v>1018</v>
@@ -3267,12 +3402,13 @@
         <v>201018</v>
       </c>
       <c r="H61" s="7"/>
-      <c r="J61" s="1"/>
-      <c r="R61" s="1"/>
-    </row>
-    <row r="62" s="2" customFormat="1" spans="1:18">
+      <c r="I61" s="7"/>
+      <c r="K61" s="1"/>
+      <c r="S61" s="1"/>
+    </row>
+    <row r="62" s="2" customFormat="1" spans="1:19">
       <c r="A62" s="2">
-        <f t="shared" si="4"/>
+        <f>C62*1000+B62</f>
         <v>2001</v>
       </c>
       <c r="B62" s="2">
@@ -3283,7 +3419,7 @@
         <v>2</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D62:D93" si="5">100000+C62*1000+B62</f>
         <v>102001</v>
       </c>
       <c r="E62" s="2" t="s">
@@ -3296,12 +3432,15 @@
         <v>202001</v>
       </c>
       <c r="H62" s="2"/>
-      <c r="J62" s="8"/>
-      <c r="R62" s="1"/>
-    </row>
-    <row r="63" s="2" customFormat="1" spans="1:18">
+      <c r="K62" s="8"/>
+      <c r="M62"/>
+      <c r="N62"/>
+      <c r="O62"/>
+      <c r="S62" s="1"/>
+    </row>
+    <row r="63" s="2" customFormat="1" spans="1:19">
       <c r="A63" s="2">
-        <f t="shared" si="4"/>
+        <f>C63*1000+B63</f>
         <v>2002</v>
       </c>
       <c r="B63" s="2">
@@ -3312,7 +3451,7 @@
         <v>2</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102002</v>
       </c>
       <c r="E63" s="2" t="s">
@@ -3325,12 +3464,15 @@
         <v>202002</v>
       </c>
       <c r="H63" s="2"/>
-      <c r="J63" s="8"/>
-      <c r="R63" s="1"/>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:18">
+      <c r="K63" s="8"/>
+      <c r="M63"/>
+      <c r="N63"/>
+      <c r="O63"/>
+      <c r="S63" s="1"/>
+    </row>
+    <row r="64" s="2" customFormat="1" spans="1:19">
       <c r="A64" s="2">
-        <f t="shared" ref="A64:A93" si="5">C64*1000+B64</f>
+        <f t="shared" ref="A64:A93" si="6">C64*1000+B64</f>
         <v>2003</v>
       </c>
       <c r="B64" s="2">
@@ -3341,7 +3483,7 @@
         <v>2</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102003</v>
       </c>
       <c r="E64" s="2" t="s">
@@ -3354,12 +3496,15 @@
         <v>202003</v>
       </c>
       <c r="H64" s="2"/>
-      <c r="J64" s="8"/>
-      <c r="R64" s="1"/>
-    </row>
-    <row r="65" s="2" customFormat="1" spans="1:18">
+      <c r="K64" s="8"/>
+      <c r="M64"/>
+      <c r="N64"/>
+      <c r="O64"/>
+      <c r="S64" s="1"/>
+    </row>
+    <row r="65" s="2" customFormat="1" spans="1:19">
       <c r="A65" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2004</v>
       </c>
       <c r="B65" s="2">
@@ -3370,7 +3515,7 @@
         <v>2</v>
       </c>
       <c r="D65" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102004</v>
       </c>
       <c r="E65" s="2" t="s">
@@ -3383,12 +3528,15 @@
         <v>202004</v>
       </c>
       <c r="H65" s="2"/>
-      <c r="J65" s="8"/>
-      <c r="R65" s="1"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:18">
+      <c r="K65" s="8"/>
+      <c r="M65"/>
+      <c r="N65"/>
+      <c r="O65"/>
+      <c r="S65" s="1"/>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="1:19">
       <c r="A66" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2005</v>
       </c>
       <c r="B66" s="2">
@@ -3399,7 +3547,7 @@
         <v>2</v>
       </c>
       <c r="D66" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102005</v>
       </c>
       <c r="E66" s="2" t="s">
@@ -3412,12 +3560,15 @@
         <v>202005</v>
       </c>
       <c r="H66" s="2"/>
-      <c r="J66" s="8"/>
-      <c r="R66" s="1"/>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="1:18">
+      <c r="K66" s="8"/>
+      <c r="M66"/>
+      <c r="N66"/>
+      <c r="O66"/>
+      <c r="S66" s="1"/>
+    </row>
+    <row r="67" s="2" customFormat="1" spans="1:19">
       <c r="A67" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2006</v>
       </c>
       <c r="B67" s="2">
@@ -3428,7 +3579,7 @@
         <v>2</v>
       </c>
       <c r="D67" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102006</v>
       </c>
       <c r="E67" s="2" t="s">
@@ -3441,12 +3592,15 @@
         <v>202006</v>
       </c>
       <c r="H67" s="2"/>
-      <c r="J67" s="8"/>
-      <c r="R67" s="1"/>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:18">
+      <c r="K67" s="8"/>
+      <c r="M67"/>
+      <c r="N67"/>
+      <c r="O67"/>
+      <c r="S67" s="1"/>
+    </row>
+    <row r="68" s="2" customFormat="1" spans="1:19">
       <c r="A68" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2007</v>
       </c>
       <c r="B68" s="2">
@@ -3457,7 +3611,7 @@
         <v>2</v>
       </c>
       <c r="D68" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102007</v>
       </c>
       <c r="E68" s="2" t="s">
@@ -3470,12 +3624,15 @@
         <v>202007</v>
       </c>
       <c r="H68" s="2"/>
-      <c r="J68" s="8"/>
-      <c r="R68" s="1"/>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:18">
+      <c r="K68" s="8"/>
+      <c r="M68"/>
+      <c r="N68"/>
+      <c r="O68"/>
+      <c r="S68" s="1"/>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:19">
       <c r="A69" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2008</v>
       </c>
       <c r="B69" s="2">
@@ -3486,7 +3643,7 @@
         <v>2</v>
       </c>
       <c r="D69" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102008</v>
       </c>
       <c r="E69" s="2" t="s">
@@ -3499,12 +3656,15 @@
         <v>202008</v>
       </c>
       <c r="H69" s="2"/>
-      <c r="J69" s="8"/>
-      <c r="R69" s="1"/>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:18">
+      <c r="K69" s="8"/>
+      <c r="M69"/>
+      <c r="N69"/>
+      <c r="O69"/>
+      <c r="S69" s="1"/>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:19">
       <c r="A70" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2009</v>
       </c>
       <c r="B70" s="2">
@@ -3515,7 +3675,7 @@
         <v>2</v>
       </c>
       <c r="D70" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102009</v>
       </c>
       <c r="E70" s="2" t="s">
@@ -3528,12 +3688,15 @@
         <v>202009</v>
       </c>
       <c r="H70" s="2"/>
-      <c r="J70" s="8"/>
-      <c r="R70" s="1"/>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:18">
+      <c r="K70" s="8"/>
+      <c r="M70"/>
+      <c r="N70"/>
+      <c r="O70"/>
+      <c r="S70" s="1"/>
+    </row>
+    <row r="71" s="2" customFormat="1" spans="1:19">
       <c r="A71" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2010</v>
       </c>
       <c r="B71" s="2">
@@ -3544,7 +3707,7 @@
         <v>2</v>
       </c>
       <c r="D71" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102010</v>
       </c>
       <c r="E71" s="2" t="s">
@@ -3557,12 +3720,15 @@
         <v>202010</v>
       </c>
       <c r="H71" s="2"/>
-      <c r="J71" s="8"/>
-      <c r="R71" s="1"/>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:18">
+      <c r="K71" s="8"/>
+      <c r="M71"/>
+      <c r="N71"/>
+      <c r="O71"/>
+      <c r="S71" s="1"/>
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:19">
       <c r="A72" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2011</v>
       </c>
       <c r="B72" s="2">
@@ -3573,7 +3739,7 @@
         <v>2</v>
       </c>
       <c r="D72" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102011</v>
       </c>
       <c r="E72" s="2" t="s">
@@ -3586,12 +3752,15 @@
         <v>202011</v>
       </c>
       <c r="H72" s="2"/>
-      <c r="J72" s="8"/>
-      <c r="R72" s="1"/>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:18">
+      <c r="K72" s="8"/>
+      <c r="M72"/>
+      <c r="N72"/>
+      <c r="O72"/>
+      <c r="S72" s="1"/>
+    </row>
+    <row r="73" s="2" customFormat="1" spans="1:19">
       <c r="A73" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2012</v>
       </c>
       <c r="B73" s="2">
@@ -3602,7 +3771,7 @@
         <v>2</v>
       </c>
       <c r="D73" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102012</v>
       </c>
       <c r="E73" s="2" t="s">
@@ -3615,12 +3784,15 @@
         <v>202012</v>
       </c>
       <c r="H73" s="2"/>
-      <c r="J73" s="8"/>
-      <c r="R73" s="1"/>
-    </row>
-    <row r="74" s="2" customFormat="1" spans="1:18">
+      <c r="K73" s="8"/>
+      <c r="M73"/>
+      <c r="N73"/>
+      <c r="O73"/>
+      <c r="S73" s="1"/>
+    </row>
+    <row r="74" s="2" customFormat="1" spans="1:19">
       <c r="A74" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2013</v>
       </c>
       <c r="B74" s="2">
@@ -3631,7 +3803,7 @@
         <v>2</v>
       </c>
       <c r="D74" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102013</v>
       </c>
       <c r="E74" s="2" t="s">
@@ -3644,12 +3816,15 @@
         <v>202013</v>
       </c>
       <c r="H74" s="2"/>
-      <c r="J74" s="8"/>
-      <c r="R74" s="1"/>
-    </row>
-    <row r="75" s="2" customFormat="1" spans="1:18">
+      <c r="K74" s="8"/>
+      <c r="M74"/>
+      <c r="N74"/>
+      <c r="O74"/>
+      <c r="S74" s="1"/>
+    </row>
+    <row r="75" s="2" customFormat="1" spans="1:19">
       <c r="A75" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2014</v>
       </c>
       <c r="B75" s="2">
@@ -3660,7 +3835,7 @@
         <v>2</v>
       </c>
       <c r="D75" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102014</v>
       </c>
       <c r="E75" s="2" t="s">
@@ -3673,12 +3848,15 @@
         <v>202014</v>
       </c>
       <c r="H75" s="2"/>
-      <c r="J75" s="8"/>
-      <c r="R75" s="1"/>
-    </row>
-    <row r="76" s="2" customFormat="1" spans="1:18">
+      <c r="K75" s="8"/>
+      <c r="M75"/>
+      <c r="N75"/>
+      <c r="O75"/>
+      <c r="S75" s="1"/>
+    </row>
+    <row r="76" s="2" customFormat="1" spans="1:19">
       <c r="A76" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2015</v>
       </c>
       <c r="B76" s="2">
@@ -3689,7 +3867,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102015</v>
       </c>
       <c r="E76" s="2" t="s">
@@ -3702,12 +3880,15 @@
         <v>202015</v>
       </c>
       <c r="H76" s="2"/>
-      <c r="J76" s="8"/>
-      <c r="R76" s="1"/>
-    </row>
-    <row r="77" s="2" customFormat="1" spans="1:18">
+      <c r="K76" s="8"/>
+      <c r="M76"/>
+      <c r="N76"/>
+      <c r="O76"/>
+      <c r="S76" s="1"/>
+    </row>
+    <row r="77" s="2" customFormat="1" spans="1:19">
       <c r="A77" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2016</v>
       </c>
       <c r="B77" s="2">
@@ -3718,7 +3899,7 @@
         <v>2</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102016</v>
       </c>
       <c r="E77" s="2" t="s">
@@ -3731,12 +3912,15 @@
         <v>202016</v>
       </c>
       <c r="H77" s="2"/>
-      <c r="J77" s="8"/>
-      <c r="R77" s="1"/>
-    </row>
-    <row r="78" s="2" customFormat="1" spans="1:18">
+      <c r="K77" s="8"/>
+      <c r="M77"/>
+      <c r="N77"/>
+      <c r="O77"/>
+      <c r="S77" s="1"/>
+    </row>
+    <row r="78" s="2" customFormat="1" spans="1:19">
       <c r="A78" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2017</v>
       </c>
       <c r="B78" s="2">
@@ -3747,7 +3931,7 @@
         <v>2</v>
       </c>
       <c r="D78" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102017</v>
       </c>
       <c r="E78" s="2" t="s">
@@ -3760,12 +3944,15 @@
         <v>202017</v>
       </c>
       <c r="H78" s="2"/>
-      <c r="J78" s="8"/>
-      <c r="R78" s="1"/>
-    </row>
-    <row r="79" s="2" customFormat="1" spans="1:18">
+      <c r="K78" s="8"/>
+      <c r="M78"/>
+      <c r="N78"/>
+      <c r="O78"/>
+      <c r="S78" s="1"/>
+    </row>
+    <row r="79" s="2" customFormat="1" spans="1:19">
       <c r="A79" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2018</v>
       </c>
       <c r="B79" s="2">
@@ -3776,7 +3963,7 @@
         <v>2</v>
       </c>
       <c r="D79" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102018</v>
       </c>
       <c r="E79" s="2" t="s">
@@ -3789,12 +3976,15 @@
         <v>202018</v>
       </c>
       <c r="H79" s="2"/>
-      <c r="J79" s="8"/>
-      <c r="R79" s="1"/>
-    </row>
-    <row r="80" s="2" customFormat="1" spans="1:18">
+      <c r="K79" s="8"/>
+      <c r="M79"/>
+      <c r="N79"/>
+      <c r="O79"/>
+      <c r="S79" s="1"/>
+    </row>
+    <row r="80" s="2" customFormat="1" spans="1:19">
       <c r="A80" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2019</v>
       </c>
       <c r="B80" s="2">
@@ -3805,7 +3995,7 @@
         <v>2</v>
       </c>
       <c r="D80" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102019</v>
       </c>
       <c r="E80" s="2" t="s">
@@ -3818,12 +4008,15 @@
         <v>202019</v>
       </c>
       <c r="H80" s="2"/>
-      <c r="J80" s="8"/>
-      <c r="R80" s="1"/>
-    </row>
-    <row r="81" s="2" customFormat="1" spans="1:18">
+      <c r="K80" s="8"/>
+      <c r="M80"/>
+      <c r="N80"/>
+      <c r="O80"/>
+      <c r="S80" s="1"/>
+    </row>
+    <row r="81" s="2" customFormat="1" spans="1:19">
       <c r="A81" s="2">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2020</v>
       </c>
       <c r="B81" s="2">
@@ -3834,7 +4027,7 @@
         <v>2</v>
       </c>
       <c r="D81" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>102020</v>
       </c>
       <c r="E81" s="2" t="s">
@@ -3847,12 +4040,15 @@
         <v>202020</v>
       </c>
       <c r="H81" s="2"/>
-      <c r="J81" s="8"/>
-      <c r="R81" s="1"/>
-    </row>
-    <row r="82" s="3" customFormat="1" spans="1:10">
+      <c r="K81" s="8"/>
+      <c r="M81"/>
+      <c r="N81"/>
+      <c r="O81"/>
+      <c r="S81" s="1"/>
+    </row>
+    <row r="82" s="3" customFormat="1" spans="1:11">
       <c r="A82" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3001</v>
       </c>
       <c r="B82" s="3">
@@ -3863,7 +4059,7 @@
         <v>3</v>
       </c>
       <c r="D82" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>103001</v>
       </c>
       <c r="E82" s="3" t="s">
@@ -3878,11 +4074,11 @@
       <c r="H82" s="3">
         <v>3</v>
       </c>
-      <c r="J82" s="1"/>
-    </row>
-    <row r="83" s="3" customFormat="1" spans="1:10">
+      <c r="K82" s="1"/>
+    </row>
+    <row r="83" s="3" customFormat="1" spans="1:11">
       <c r="A83" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3002</v>
       </c>
       <c r="B83" s="3">
@@ -3893,7 +4089,7 @@
         <v>3</v>
       </c>
       <c r="D83" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>103002</v>
       </c>
       <c r="E83" s="3" t="s">
@@ -3908,11 +4104,11 @@
       <c r="H83" s="3">
         <v>6</v>
       </c>
-      <c r="J83" s="1"/>
-    </row>
-    <row r="84" s="3" customFormat="1" spans="1:10">
+      <c r="K83" s="1"/>
+    </row>
+    <row r="84" s="3" customFormat="1" spans="1:11">
       <c r="A84" s="3">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3003</v>
       </c>
       <c r="B84" s="3">
@@ -3923,7 +4119,7 @@
         <v>3</v>
       </c>
       <c r="D84" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>103003</v>
       </c>
       <c r="E84" s="3" t="s">
@@ -3938,11 +4134,11 @@
       <c r="H84" s="3">
         <v>9</v>
       </c>
-      <c r="J84" s="1"/>
-    </row>
-    <row r="85" s="4" customFormat="1" spans="1:10">
+      <c r="K84" s="1"/>
+    </row>
+    <row r="85" s="4" customFormat="1" spans="1:11">
       <c r="A85" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4001</v>
       </c>
       <c r="B85" s="4">
@@ -3953,7 +4149,7 @@
         <v>4</v>
       </c>
       <c r="D85" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="5"/>
         <v>104001</v>
       </c>
       <c r="E85" s="4" t="s">
@@ -3963,18 +4159,17 @@
         <v>174</v>
       </c>
       <c r="G85" s="4">
-        <f t="shared" ref="G85:G93" si="6">200000+A85</f>
+        <f>200000+A85</f>
         <v>204001</v>
       </c>
-      <c r="H85" s="3">
-        <v>3</v>
-      </c>
+      <c r="H85" s="3"/>
       <c r="I85" s="3"/>
-      <c r="J85" s="9"/>
-    </row>
-    <row r="86" s="4" customFormat="1" spans="1:10">
+      <c r="J85" s="3"/>
+      <c r="K85" s="9"/>
+    </row>
+    <row r="86" s="4" customFormat="1" spans="1:11">
       <c r="A86" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" ref="A86:A89" si="7">C86*1000+B86</f>
         <v>4002</v>
       </c>
       <c r="B86" s="4">
@@ -3985,28 +4180,29 @@
         <v>4</v>
       </c>
       <c r="D86" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D86:D89" si="8">100000+C86*1000+B86</f>
         <v>104002</v>
       </c>
       <c r="E86" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="F86" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F86" s="4" t="s">
-        <v>176</v>
-      </c>
       <c r="G86" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="G86:G89" si="9">200000+A86</f>
         <v>204002</v>
       </c>
       <c r="H86" s="3">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I86" s="3"/>
-      <c r="J86" s="9"/>
-    </row>
-    <row r="87" s="4" customFormat="1" spans="1:10">
+      <c r="J86" s="3"/>
+      <c r="K86" s="9"/>
+    </row>
+    <row r="87" s="4" customFormat="1" spans="1:11">
       <c r="A87" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="7"/>
         <v>4003</v>
       </c>
       <c r="B87" s="4">
@@ -4017,216 +4213,318 @@
         <v>4</v>
       </c>
       <c r="D87" s="4">
-        <f t="shared" si="3"/>
+        <f t="shared" si="8"/>
         <v>104003</v>
       </c>
       <c r="E87" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="G87" s="4">
+        <f t="shared" si="9"/>
+        <v>204003</v>
+      </c>
+      <c r="H87" s="3">
+        <v>6</v>
+      </c>
+      <c r="I87" s="3"/>
+      <c r="J87" s="3"/>
+      <c r="K87" s="9"/>
+    </row>
+    <row r="88" s="4" customFormat="1" spans="1:11">
+      <c r="A88" s="4">
+        <f t="shared" si="7"/>
+        <v>4004</v>
+      </c>
+      <c r="B88" s="4">
+        <f>COUNTIF($C$1:C88,C88)</f>
+        <v>4</v>
+      </c>
+      <c r="C88" s="4">
+        <v>4</v>
+      </c>
+      <c r="D88" s="4">
+        <f t="shared" si="8"/>
+        <v>104004</v>
+      </c>
+      <c r="E88" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="G87" s="4">
-        <f t="shared" si="6"/>
-        <v>204003</v>
-      </c>
-      <c r="H87" s="3">
+      <c r="F88" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="9"/>
+        <v>204004</v>
+      </c>
+      <c r="H88" s="3">
         <v>9</v>
       </c>
-      <c r="I87" s="3"/>
-      <c r="J87" s="9"/>
-    </row>
-    <row r="88" s="5" customFormat="1" spans="1:10">
-      <c r="A88" s="5">
-        <f t="shared" si="5"/>
+      <c r="I88" s="3"/>
+      <c r="J88" s="3"/>
+      <c r="K88" s="9"/>
+    </row>
+    <row r="89" s="5" customFormat="1" spans="1:11">
+      <c r="A89" s="5">
+        <f t="shared" si="7"/>
         <v>5001</v>
-      </c>
-      <c r="B88" s="5">
-        <f>COUNTIF($C$1:C88,C88)</f>
-        <v>1</v>
-      </c>
-      <c r="C88" s="5">
-        <v>5</v>
-      </c>
-      <c r="D88" s="5">
-        <f t="shared" si="3"/>
-        <v>105001</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="F88" s="5" t="s">
-        <v>180</v>
-      </c>
-      <c r="G88" s="5">
-        <f t="shared" si="6"/>
-        <v>205001</v>
-      </c>
-      <c r="H88" s="3">
-        <v>3</v>
-      </c>
-      <c r="I88" s="3"/>
-      <c r="J88" s="9"/>
-    </row>
-    <row r="89" s="5" customFormat="1" spans="1:10">
-      <c r="A89" s="5">
-        <f t="shared" si="5"/>
-        <v>5002</v>
       </c>
       <c r="B89" s="5">
         <f>COUNTIF($C$1:C89,C89)</f>
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C89" s="5">
         <v>5</v>
       </c>
       <c r="D89" s="5">
-        <f>100000+C89*1000+B89</f>
-        <v>105002</v>
+        <f t="shared" si="8"/>
+        <v>105001</v>
       </c>
       <c r="E89" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="F89" s="5" t="s">
-        <v>182</v>
-      </c>
       <c r="G89" s="5">
-        <f t="shared" si="6"/>
-        <v>205002</v>
-      </c>
-      <c r="H89" s="3">
-        <v>6</v>
-      </c>
+        <f t="shared" si="9"/>
+        <v>205001</v>
+      </c>
+      <c r="H89" s="3"/>
       <c r="I89" s="3"/>
-      <c r="J89" s="9"/>
-    </row>
-    <row r="90" s="5" customFormat="1" spans="1:10">
+      <c r="J89" s="3"/>
+      <c r="K89" s="9"/>
+    </row>
+    <row r="90" s="5" customFormat="1" spans="1:11">
       <c r="A90" s="5">
-        <f t="shared" si="5"/>
-        <v>5003</v>
+        <f>C90*1000+B90</f>
+        <v>5002</v>
       </c>
       <c r="B90" s="5">
         <f>COUNTIF($C$1:C90,C90)</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C90" s="5">
         <v>5</v>
       </c>
       <c r="D90" s="5">
         <f>100000+C90*1000+B90</f>
+        <v>105002</v>
+      </c>
+      <c r="E90" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="F90" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="G90" s="5">
+        <f t="shared" ref="G90:G95" si="10">200000+A90</f>
+        <v>205002</v>
+      </c>
+      <c r="H90" s="3">
+        <v>3</v>
+      </c>
+      <c r="I90" s="3"/>
+      <c r="J90" s="3"/>
+      <c r="K90" s="9"/>
+    </row>
+    <row r="91" s="5" customFormat="1" spans="1:11">
+      <c r="A91" s="5">
+        <f>C91*1000+B91</f>
+        <v>5003</v>
+      </c>
+      <c r="B91" s="5">
+        <f>COUNTIF($C$1:C91,C91)</f>
+        <v>3</v>
+      </c>
+      <c r="C91" s="5">
+        <v>5</v>
+      </c>
+      <c r="D91" s="5">
+        <f>100000+C91*1000+B91</f>
         <v>105003</v>
       </c>
-      <c r="E90" s="5" t="s">
+      <c r="E91" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F90" s="5" t="s">
+      <c r="F91" s="5" t="s">
         <v>184</v>
       </c>
-      <c r="G90" s="5">
-        <f t="shared" si="6"/>
+      <c r="G91" s="5">
+        <f t="shared" si="10"/>
         <v>205003</v>
       </c>
-      <c r="H90" s="3">
+      <c r="H91" s="3">
+        <v>6</v>
+      </c>
+      <c r="I91" s="3"/>
+      <c r="J91" s="3"/>
+      <c r="K91" s="9"/>
+    </row>
+    <row r="92" s="5" customFormat="1" spans="1:11">
+      <c r="A92" s="5">
+        <f>C92*1000+B92</f>
+        <v>5004</v>
+      </c>
+      <c r="B92" s="5">
+        <f>COUNTIF($C$1:C92,C92)</f>
+        <v>4</v>
+      </c>
+      <c r="C92" s="5">
+        <v>5</v>
+      </c>
+      <c r="D92" s="5">
+        <f>100000+C92*1000+B92</f>
+        <v>105004</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="G92" s="5">
+        <f t="shared" si="10"/>
+        <v>205004</v>
+      </c>
+      <c r="H92" s="3">
         <v>9</v>
       </c>
-      <c r="I90" s="3"/>
-      <c r="J90" s="9"/>
-    </row>
-    <row r="91" s="6" customFormat="1" spans="1:10">
-      <c r="A91" s="6">
-        <f t="shared" si="5"/>
+      <c r="I92" s="3"/>
+      <c r="J92" s="3"/>
+      <c r="K92" s="9"/>
+    </row>
+    <row r="93" s="6" customFormat="1" spans="1:11">
+      <c r="A93" s="6">
+        <f>C93*1000+B93</f>
         <v>6001</v>
-      </c>
-      <c r="B91" s="6">
-        <f>COUNTIF($C$1:C91,C91)</f>
-        <v>1</v>
-      </c>
-      <c r="C91" s="6">
-        <v>6</v>
-      </c>
-      <c r="D91" s="6">
-        <f>100000+C91*1000+B91</f>
-        <v>106001</v>
-      </c>
-      <c r="E91" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="G91" s="6">
-        <f t="shared" si="6"/>
-        <v>206001</v>
-      </c>
-      <c r="H91" s="3">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3"/>
-      <c r="J91" s="9"/>
-    </row>
-    <row r="92" s="6" customFormat="1" spans="1:10">
-      <c r="A92" s="6">
-        <f t="shared" si="5"/>
-        <v>6002</v>
-      </c>
-      <c r="B92" s="6">
-        <f>COUNTIF($C$1:C92,C92)</f>
-        <v>2</v>
-      </c>
-      <c r="C92" s="6">
-        <v>6</v>
-      </c>
-      <c r="D92" s="6">
-        <f>100000+C92*1000+B92</f>
-        <v>106002</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="G92" s="6">
-        <f t="shared" si="6"/>
-        <v>206002</v>
-      </c>
-      <c r="H92" s="3">
-        <v>6</v>
-      </c>
-      <c r="I92" s="3"/>
-      <c r="J92" s="9"/>
-    </row>
-    <row r="93" s="6" customFormat="1" spans="1:10">
-      <c r="A93" s="6">
-        <f t="shared" si="5"/>
-        <v>6003</v>
       </c>
       <c r="B93" s="6">
         <f>COUNTIF($C$1:C93,C93)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" s="6">
         <v>6</v>
       </c>
       <c r="D93" s="6">
         <f>100000+C93*1000+B93</f>
+        <v>106001</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G93" s="6">
+        <f t="shared" si="10"/>
+        <v>206001</v>
+      </c>
+      <c r="H93" s="3"/>
+      <c r="I93" s="3"/>
+      <c r="J93" s="3"/>
+      <c r="K93" s="9"/>
+    </row>
+    <row r="94" s="6" customFormat="1" spans="1:11">
+      <c r="A94" s="6">
+        <f>C94*1000+B94</f>
+        <v>6002</v>
+      </c>
+      <c r="B94" s="6">
+        <f>COUNTIF($C$1:C94,C94)</f>
+        <v>2</v>
+      </c>
+      <c r="C94" s="6">
+        <v>6</v>
+      </c>
+      <c r="D94" s="6">
+        <f>100000+C94*1000+B94</f>
+        <v>106002</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="G94" s="6">
+        <f>200000+A94</f>
+        <v>206002</v>
+      </c>
+      <c r="H94" s="3">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="9"/>
+    </row>
+    <row r="95" s="6" customFormat="1" spans="1:11">
+      <c r="A95" s="6">
+        <f>C95*1000+B95</f>
+        <v>6003</v>
+      </c>
+      <c r="B95" s="6">
+        <f>COUNTIF($C$1:C95,C95)</f>
+        <v>3</v>
+      </c>
+      <c r="C95" s="6">
+        <v>6</v>
+      </c>
+      <c r="D95" s="6">
+        <f>100000+C95*1000+B95</f>
         <v>106003</v>
       </c>
-      <c r="E93" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F93" s="6" t="s">
+      <c r="E95" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="G93" s="6">
-        <f t="shared" si="6"/>
+      <c r="F95" s="6" t="s">
+        <v>191</v>
+      </c>
+      <c r="G95" s="6">
+        <f>200000+A95</f>
         <v>206003</v>
       </c>
-      <c r="H93" s="3">
+      <c r="H95" s="3">
+        <v>6</v>
+      </c>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="9"/>
+    </row>
+    <row r="96" s="6" customFormat="1" spans="1:11">
+      <c r="A96" s="6">
+        <f>C96*1000+B96</f>
+        <v>6004</v>
+      </c>
+      <c r="B96" s="6">
+        <f>COUNTIF($C$1:C96,C96)</f>
+        <v>4</v>
+      </c>
+      <c r="C96" s="6">
+        <v>6</v>
+      </c>
+      <c r="D96" s="6">
+        <f>100000+C96*1000+B96</f>
+        <v>106004</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>192</v>
+      </c>
+      <c r="F96" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="G96" s="6">
+        <f>200000+A96</f>
+        <v>206004</v>
+      </c>
+      <c r="H96" s="3">
         <v>9</v>
       </c>
-      <c r="I93" s="3"/>
-      <c r="J93" s="9"/>
+      <c r="I96" s="3"/>
+      <c r="J96" s="3"/>
+      <c r="K96" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="avatar" sheetId="1" r:id="rId1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="188">
   <si>
     <t>id</t>
   </si>
@@ -627,42 +627,30 @@
     <t>筹码1</t>
   </si>
   <si>
-    <t>VIP_pf_cm0.png</t>
-  </si>
-  <si>
     <t>VIP_pf_cm1.png</t>
   </si>
   <si>
+    <t>VIP_pf_cm2.png</t>
+  </si>
+  <si>
     <t>筹码2</t>
   </si>
   <si>
-    <t>VIP_pf_cm2.png</t>
-  </si>
-  <si>
-    <t>筹码3</t>
-  </si>
-  <si>
     <t>VIP_pf_cm3.png</t>
   </si>
   <si>
     <t>牌背1</t>
   </si>
   <si>
-    <t>VIP_pf_pai0.png</t>
-  </si>
-  <si>
     <t>VIP_pf_pai1.png</t>
   </si>
   <si>
+    <t>VIP_pf_pai2.png</t>
+  </si>
+  <si>
     <t>牌背2</t>
   </si>
   <si>
-    <t>VIP_pf_pai2.png</t>
-  </si>
-  <si>
-    <t>牌背3</t>
-  </si>
-  <si>
     <t>VIP_pf_pai3.png</t>
   </si>
   <si>
@@ -679,12 +667,6 @@
   </si>
   <si>
     <t>VIP_pf_bj2.png</t>
-  </si>
-  <si>
-    <t>大厅背景3</t>
-  </si>
-  <si>
-    <t>VIP_pf_bj3.png</t>
   </si>
 </sst>
 </file>
@@ -850,6 +832,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -857,11 +844,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1694,7 +1676,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S96"/>
+  <dimension ref="A1:S93"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="12.25" customWidth="1"/>
@@ -3408,7 +3390,7 @@
     </row>
     <row r="62" s="2" customFormat="1" spans="1:19">
       <c r="A62" s="2">
-        <f>C62*1000+B62</f>
+        <f t="shared" si="4"/>
         <v>2001</v>
       </c>
       <c r="B62" s="2">
@@ -3440,7 +3422,7 @@
     </row>
     <row r="63" s="2" customFormat="1" spans="1:19">
       <c r="A63" s="2">
-        <f>C63*1000+B63</f>
+        <f t="shared" si="4"/>
         <v>2002</v>
       </c>
       <c r="B63" s="2">
@@ -4159,7 +4141,7 @@
         <v>174</v>
       </c>
       <c r="G85" s="4">
-        <f>200000+A85</f>
+        <f t="shared" ref="G85:G94" si="7">200000+A85</f>
         <v>204001</v>
       </c>
       <c r="H85" s="3"/>
@@ -4169,7 +4151,7 @@
     </row>
     <row r="86" s="4" customFormat="1" spans="1:11">
       <c r="A86" s="4">
-        <f t="shared" ref="A86:A89" si="7">C86*1000+B86</f>
+        <f t="shared" si="6"/>
         <v>4002</v>
       </c>
       <c r="B86" s="4">
@@ -4180,7 +4162,7 @@
         <v>4</v>
       </c>
       <c r="D86" s="4">
-        <f t="shared" ref="D86:D89" si="8">100000+C86*1000+B86</f>
+        <f t="shared" si="5"/>
         <v>104002</v>
       </c>
       <c r="E86" s="4" t="s">
@@ -4190,7 +4172,7 @@
         <v>175</v>
       </c>
       <c r="G86" s="4">
-        <f t="shared" ref="G86:G89" si="9">200000+A86</f>
+        <f t="shared" si="7"/>
         <v>204002</v>
       </c>
       <c r="H86" s="3">
@@ -4202,7 +4184,7 @@
     </row>
     <row r="87" s="4" customFormat="1" spans="1:11">
       <c r="A87" s="4">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>4003</v>
       </c>
       <c r="B87" s="4">
@@ -4213,7 +4195,7 @@
         <v>4</v>
       </c>
       <c r="D87" s="4">
-        <f t="shared" si="8"/>
+        <f t="shared" si="5"/>
         <v>104003</v>
       </c>
       <c r="E87" s="4" t="s">
@@ -4223,7 +4205,7 @@
         <v>177</v>
       </c>
       <c r="G87" s="4">
-        <f t="shared" si="9"/>
+        <f t="shared" si="7"/>
         <v>204003</v>
       </c>
       <c r="H87" s="3">
@@ -4233,164 +4215,162 @@
       <c r="J87" s="3"/>
       <c r="K87" s="9"/>
     </row>
-    <row r="88" s="4" customFormat="1" spans="1:11">
-      <c r="A88" s="4">
+    <row r="88" s="5" customFormat="1" spans="1:11">
+      <c r="A88" s="5">
+        <f t="shared" ref="A88:A95" si="8">C88*1000+B88</f>
+        <v>5001</v>
+      </c>
+      <c r="B88" s="5">
+        <f>COUNTIF($C$1:C88,C88)</f>
+        <v>1</v>
+      </c>
+      <c r="C88" s="5">
+        <v>5</v>
+      </c>
+      <c r="D88" s="5">
+        <f t="shared" ref="D88:D95" si="9">100000+C88*1000+B88</f>
+        <v>105001</v>
+      </c>
+      <c r="E88" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F88" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="G88" s="5">
         <f t="shared" si="7"/>
-        <v>4004</v>
-      </c>
-      <c r="B88" s="4">
-        <f>COUNTIF($C$1:C88,C88)</f>
-        <v>4</v>
-      </c>
-      <c r="C88" s="4">
-        <v>4</v>
-      </c>
-      <c r="D88" s="4">
-        <f t="shared" si="8"/>
-        <v>104004</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G88" s="4">
-        <f t="shared" si="9"/>
-        <v>204004</v>
-      </c>
-      <c r="H88" s="3">
-        <v>9</v>
-      </c>
+        <v>205001</v>
+      </c>
+      <c r="H88" s="3"/>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="9"/>
     </row>
     <row r="89" s="5" customFormat="1" spans="1:11">
       <c r="A89" s="5">
-        <f t="shared" si="7"/>
-        <v>5001</v>
+        <f t="shared" si="8"/>
+        <v>5002</v>
       </c>
       <c r="B89" s="5">
         <f>COUNTIF($C$1:C89,C89)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C89" s="5">
         <v>5</v>
       </c>
       <c r="D89" s="5">
-        <f t="shared" si="8"/>
-        <v>105001</v>
+        <f t="shared" si="9"/>
+        <v>105002</v>
       </c>
       <c r="E89" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="F89" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="F89" s="5" t="s">
-        <v>181</v>
-      </c>
       <c r="G89" s="5">
-        <f t="shared" si="9"/>
-        <v>205001</v>
-      </c>
-      <c r="H89" s="3"/>
+        <f t="shared" si="7"/>
+        <v>205002</v>
+      </c>
+      <c r="H89" s="3">
+        <v>3</v>
+      </c>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
       <c r="K89" s="9"/>
     </row>
     <row r="90" s="5" customFormat="1" spans="1:11">
       <c r="A90" s="5">
-        <f>C90*1000+B90</f>
-        <v>5002</v>
+        <f t="shared" si="8"/>
+        <v>5003</v>
       </c>
       <c r="B90" s="5">
         <f>COUNTIF($C$1:C90,C90)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C90" s="5">
         <v>5</v>
       </c>
       <c r="D90" s="5">
-        <f>100000+C90*1000+B90</f>
-        <v>105002</v>
+        <f t="shared" si="9"/>
+        <v>105003</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>182</v>
       </c>
       <c r="G90" s="5">
-        <f t="shared" ref="G90:G95" si="10">200000+A90</f>
-        <v>205002</v>
+        <f t="shared" si="7"/>
+        <v>205003</v>
       </c>
       <c r="H90" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="9"/>
     </row>
-    <row r="91" s="5" customFormat="1" spans="1:11">
-      <c r="A91" s="5">
-        <f>C91*1000+B91</f>
-        <v>5003</v>
-      </c>
-      <c r="B91" s="5">
+    <row r="91" s="6" customFormat="1" spans="1:11">
+      <c r="A91" s="6">
+        <f t="shared" si="8"/>
+        <v>6001</v>
+      </c>
+      <c r="B91" s="6">
         <f>COUNTIF($C$1:C91,C91)</f>
-        <v>3</v>
-      </c>
-      <c r="C91" s="5">
-        <v>5</v>
-      </c>
-      <c r="D91" s="5">
-        <f>100000+C91*1000+B91</f>
-        <v>105003</v>
-      </c>
-      <c r="E91" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C91" s="6">
+        <v>6</v>
+      </c>
+      <c r="D91" s="6">
+        <f t="shared" si="9"/>
+        <v>106001</v>
+      </c>
+      <c r="E91" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="F91" s="5" t="s">
+      <c r="F91" s="6" t="s">
         <v>184</v>
       </c>
-      <c r="G91" s="5">
-        <f t="shared" si="10"/>
-        <v>205003</v>
-      </c>
-      <c r="H91" s="3">
-        <v>6</v>
-      </c>
+      <c r="G91" s="6">
+        <f t="shared" si="7"/>
+        <v>206001</v>
+      </c>
+      <c r="H91" s="3"/>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="9"/>
     </row>
-    <row r="92" s="5" customFormat="1" spans="1:11">
-      <c r="A92" s="5">
-        <f>C92*1000+B92</f>
-        <v>5004</v>
-      </c>
-      <c r="B92" s="5">
+    <row r="92" s="6" customFormat="1" spans="1:11">
+      <c r="A92" s="6">
+        <f t="shared" si="8"/>
+        <v>6002</v>
+      </c>
+      <c r="B92" s="6">
         <f>COUNTIF($C$1:C92,C92)</f>
-        <v>4</v>
-      </c>
-      <c r="C92" s="5">
-        <v>5</v>
-      </c>
-      <c r="D92" s="5">
-        <f>100000+C92*1000+B92</f>
-        <v>105004</v>
-      </c>
-      <c r="E92" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C92" s="6">
+        <v>6</v>
+      </c>
+      <c r="D92" s="6">
+        <f t="shared" si="9"/>
+        <v>106002</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="F92" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F92" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="G92" s="5">
-        <f t="shared" si="10"/>
-        <v>205004</v>
+      <c r="G92" s="6">
+        <f t="shared" si="7"/>
+        <v>206002</v>
       </c>
       <c r="H92" s="3">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
@@ -4398,133 +4378,36 @@
     </row>
     <row r="93" s="6" customFormat="1" spans="1:11">
       <c r="A93" s="6">
-        <f>C93*1000+B93</f>
-        <v>6001</v>
+        <f t="shared" si="8"/>
+        <v>6003</v>
       </c>
       <c r="B93" s="6">
         <f>COUNTIF($C$1:C93,C93)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C93" s="6">
         <v>6</v>
       </c>
       <c r="D93" s="6">
-        <f>100000+C93*1000+B93</f>
-        <v>106001</v>
+        <f t="shared" si="9"/>
+        <v>106003</v>
       </c>
       <c r="E93" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F93" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="F93" s="6" t="s">
-        <v>188</v>
-      </c>
       <c r="G93" s="6">
-        <f t="shared" si="10"/>
-        <v>206001</v>
-      </c>
-      <c r="H93" s="3"/>
+        <f t="shared" si="7"/>
+        <v>206003</v>
+      </c>
+      <c r="H93" s="3">
+        <v>6</v>
+      </c>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="9"/>
-    </row>
-    <row r="94" s="6" customFormat="1" spans="1:11">
-      <c r="A94" s="6">
-        <f>C94*1000+B94</f>
-        <v>6002</v>
-      </c>
-      <c r="B94" s="6">
-        <f>COUNTIF($C$1:C94,C94)</f>
-        <v>2</v>
-      </c>
-      <c r="C94" s="6">
-        <v>6</v>
-      </c>
-      <c r="D94" s="6">
-        <f>100000+C94*1000+B94</f>
-        <v>106002</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="G94" s="6">
-        <f>200000+A94</f>
-        <v>206002</v>
-      </c>
-      <c r="H94" s="3">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="9"/>
-    </row>
-    <row r="95" s="6" customFormat="1" spans="1:11">
-      <c r="A95" s="6">
-        <f>C95*1000+B95</f>
-        <v>6003</v>
-      </c>
-      <c r="B95" s="6">
-        <f>COUNTIF($C$1:C95,C95)</f>
-        <v>3</v>
-      </c>
-      <c r="C95" s="6">
-        <v>6</v>
-      </c>
-      <c r="D95" s="6">
-        <f>100000+C95*1000+B95</f>
-        <v>106003</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="G95" s="6">
-        <f>200000+A95</f>
-        <v>206003</v>
-      </c>
-      <c r="H95" s="3">
-        <v>6</v>
-      </c>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="9"/>
-    </row>
-    <row r="96" s="6" customFormat="1" spans="1:11">
-      <c r="A96" s="6">
-        <f>C96*1000+B96</f>
-        <v>6004</v>
-      </c>
-      <c r="B96" s="6">
-        <f>COUNTIF($C$1:C96,C96)</f>
-        <v>4</v>
-      </c>
-      <c r="C96" s="6">
-        <v>6</v>
-      </c>
-      <c r="D96" s="6">
-        <f>100000+C96*1000+B96</f>
-        <v>106004</v>
-      </c>
-      <c r="E96" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="F96" s="6" t="s">
-        <v>193</v>
-      </c>
-      <c r="G96" s="6">
-        <f>200000+A96</f>
-        <v>206004</v>
-      </c>
-      <c r="H96" s="3">
-        <v>9</v>
-      </c>
-      <c r="I96" s="3"/>
-      <c r="J96" s="3"/>
-      <c r="K96" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="avatar" sheetId="1" r:id="rId1"/>
@@ -103,7 +103,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="191">
   <si>
     <t>id</t>
   </si>
@@ -484,6 +484,15 @@
   </si>
   <si>
     <t>frame_018.png</t>
+  </si>
+  <si>
+    <t>头像框-特权卡专属</t>
+  </si>
+  <si>
+    <t>frame_801.png</t>
+  </si>
+  <si>
+    <t>头像框-首充专属</t>
   </si>
   <si>
     <t>国旗1</t>
@@ -832,11 +841,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -844,6 +848,11 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1676,11 +1685,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S93"/>
+  <dimension ref="A1:S95"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="3" max="3" width="12.25" customWidth="1"/>
-    <col min="5" max="5" width="9" customWidth="1"/>
+    <col min="5" max="5" width="18.25" customWidth="1"/>
     <col min="6" max="6" width="19.125" customWidth="1"/>
     <col min="7" max="7" width="12.5" customWidth="1"/>
     <col min="8" max="9" width="12.125" customWidth="1"/>
@@ -3388,94 +3397,88 @@
       <c r="K61" s="1"/>
       <c r="S61" s="1"/>
     </row>
-    <row r="62" s="2" customFormat="1" spans="1:19">
-      <c r="A62" s="2">
-        <f t="shared" si="4"/>
-        <v>2001</v>
-      </c>
-      <c r="B62" s="2">
-        <f>COUNTIF($C$1:C62,C62)</f>
+    <row r="62" customFormat="1" spans="1:19">
+      <c r="A62">
+        <f>C62*1000+B62</f>
+        <v>1801</v>
+      </c>
+      <c r="B62">
+        <v>801</v>
+      </c>
+      <c r="C62">
         <v>1</v>
       </c>
-      <c r="C62" s="2">
-        <v>2</v>
-      </c>
       <c r="D62" s="1">
-        <f t="shared" ref="D62:D93" si="5">100000+C62*1000+B62</f>
-        <v>102001</v>
-      </c>
-      <c r="E62" s="2" t="s">
+        <f>100000+C62*1000+B62</f>
+        <v>101801</v>
+      </c>
+      <c r="E62" t="s">
         <v>127</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" t="s">
         <v>128</v>
       </c>
-      <c r="G62" s="2">
-        <v>202001</v>
-      </c>
-      <c r="H62" s="2"/>
-      <c r="K62" s="8"/>
-      <c r="M62"/>
-      <c r="N62"/>
-      <c r="O62"/>
+      <c r="G62">
+        <v>201801</v>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="7"/>
+      <c r="K62" s="1"/>
       <c r="S62" s="1"/>
     </row>
-    <row r="63" s="2" customFormat="1" spans="1:19">
-      <c r="A63" s="2">
-        <f t="shared" si="4"/>
-        <v>2002</v>
-      </c>
-      <c r="B63" s="2">
-        <f>COUNTIF($C$1:C63,C63)</f>
-        <v>2</v>
-      </c>
-      <c r="C63" s="2">
-        <v>2</v>
+    <row r="63" customFormat="1" spans="1:19">
+      <c r="A63">
+        <f>C63*1000+B63</f>
+        <v>1802</v>
+      </c>
+      <c r="B63">
+        <v>802</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
       </c>
       <c r="D63" s="1">
-        <f t="shared" si="5"/>
-        <v>102002</v>
-      </c>
-      <c r="E63" s="2" t="s">
+        <f>100000+C63*1000+B63</f>
+        <v>101802</v>
+      </c>
+      <c r="E63" t="s">
         <v>129</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="G63" s="2">
-        <v>202002</v>
-      </c>
-      <c r="H63" s="2"/>
-      <c r="K63" s="8"/>
-      <c r="M63"/>
-      <c r="N63"/>
-      <c r="O63"/>
+      <c r="F63" t="s">
+        <v>126</v>
+      </c>
+      <c r="G63">
+        <v>201802</v>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="7"/>
+      <c r="K63" s="1"/>
       <c r="S63" s="1"/>
     </row>
     <row r="64" s="2" customFormat="1" spans="1:19">
       <c r="A64" s="2">
-        <f t="shared" ref="A64:A93" si="6">C64*1000+B64</f>
-        <v>2003</v>
+        <f>C64*1000+B64</f>
+        <v>2001</v>
       </c>
       <c r="B64" s="2">
         <f>COUNTIF($C$1:C64,C64)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" s="2">
         <v>2</v>
       </c>
       <c r="D64" s="1">
-        <f t="shared" si="5"/>
-        <v>102003</v>
+        <f t="shared" ref="D64:D95" si="5">100000+C64*1000+B64</f>
+        <v>102001</v>
       </c>
       <c r="E64" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F64" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>132</v>
-      </c>
       <c r="G64" s="2">
-        <v>202003</v>
+        <v>202001</v>
       </c>
       <c r="H64" s="2"/>
       <c r="K64" s="8"/>
@@ -3486,28 +3489,28 @@
     </row>
     <row r="65" s="2" customFormat="1" spans="1:19">
       <c r="A65" s="2">
-        <f t="shared" si="6"/>
-        <v>2004</v>
+        <f>C65*1000+B65</f>
+        <v>2002</v>
       </c>
       <c r="B65" s="2">
         <f>COUNTIF($C$1:C65,C65)</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C65" s="2">
         <v>2</v>
       </c>
       <c r="D65" s="1">
         <f t="shared" si="5"/>
-        <v>102004</v>
+        <v>102002</v>
       </c>
       <c r="E65" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F65" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>134</v>
-      </c>
       <c r="G65" s="2">
-        <v>202004</v>
+        <v>202002</v>
       </c>
       <c r="H65" s="2"/>
       <c r="K65" s="8"/>
@@ -3518,28 +3521,28 @@
     </row>
     <row r="66" s="2" customFormat="1" spans="1:19">
       <c r="A66" s="2">
-        <f t="shared" si="6"/>
-        <v>2005</v>
+        <f t="shared" ref="A66:A95" si="6">C66*1000+B66</f>
+        <v>2003</v>
       </c>
       <c r="B66" s="2">
         <f>COUNTIF($C$1:C66,C66)</f>
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="C66" s="2">
         <v>2</v>
       </c>
       <c r="D66" s="1">
         <f t="shared" si="5"/>
-        <v>102005</v>
+        <v>102003</v>
       </c>
       <c r="E66" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F66" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="G66" s="2">
-        <v>202005</v>
+        <v>202003</v>
       </c>
       <c r="H66" s="2"/>
       <c r="K66" s="8"/>
@@ -3551,27 +3554,27 @@
     <row r="67" s="2" customFormat="1" spans="1:19">
       <c r="A67" s="2">
         <f t="shared" si="6"/>
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="B67" s="2">
         <f>COUNTIF($C$1:C67,C67)</f>
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C67" s="2">
         <v>2</v>
       </c>
       <c r="D67" s="1">
         <f t="shared" si="5"/>
-        <v>102006</v>
+        <v>102004</v>
       </c>
       <c r="E67" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="F67" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>138</v>
-      </c>
       <c r="G67" s="2">
-        <v>202006</v>
+        <v>202004</v>
       </c>
       <c r="H67" s="2"/>
       <c r="K67" s="8"/>
@@ -3583,27 +3586,27 @@
     <row r="68" s="2" customFormat="1" spans="1:19">
       <c r="A68" s="2">
         <f t="shared" si="6"/>
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="B68" s="2">
         <f>COUNTIF($C$1:C68,C68)</f>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C68" s="2">
         <v>2</v>
       </c>
       <c r="D68" s="1">
         <f t="shared" si="5"/>
-        <v>102007</v>
+        <v>102005</v>
       </c>
       <c r="E68" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F68" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>140</v>
-      </c>
       <c r="G68" s="2">
-        <v>202007</v>
+        <v>202005</v>
       </c>
       <c r="H68" s="2"/>
       <c r="K68" s="8"/>
@@ -3615,27 +3618,27 @@
     <row r="69" s="2" customFormat="1" spans="1:19">
       <c r="A69" s="2">
         <f t="shared" si="6"/>
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="B69" s="2">
         <f>COUNTIF($C$1:C69,C69)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C69" s="2">
         <v>2</v>
       </c>
       <c r="D69" s="1">
         <f t="shared" si="5"/>
-        <v>102008</v>
+        <v>102006</v>
       </c>
       <c r="E69" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>142</v>
-      </c>
       <c r="G69" s="2">
-        <v>202008</v>
+        <v>202006</v>
       </c>
       <c r="H69" s="2"/>
       <c r="K69" s="8"/>
@@ -3647,27 +3650,27 @@
     <row r="70" s="2" customFormat="1" spans="1:19">
       <c r="A70" s="2">
         <f t="shared" si="6"/>
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="B70" s="2">
         <f>COUNTIF($C$1:C70,C70)</f>
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C70" s="2">
         <v>2</v>
       </c>
       <c r="D70" s="1">
         <f t="shared" si="5"/>
-        <v>102009</v>
+        <v>102007</v>
       </c>
       <c r="E70" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F70" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>144</v>
-      </c>
       <c r="G70" s="2">
-        <v>202009</v>
+        <v>202007</v>
       </c>
       <c r="H70" s="2"/>
       <c r="K70" s="8"/>
@@ -3679,27 +3682,27 @@
     <row r="71" s="2" customFormat="1" spans="1:19">
       <c r="A71" s="2">
         <f t="shared" si="6"/>
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="B71" s="2">
         <f>COUNTIF($C$1:C71,C71)</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C71" s="2">
         <v>2</v>
       </c>
       <c r="D71" s="1">
         <f t="shared" si="5"/>
-        <v>102010</v>
+        <v>102008</v>
       </c>
       <c r="E71" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F71" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="F71" s="2" t="s">
-        <v>146</v>
-      </c>
       <c r="G71" s="2">
-        <v>202010</v>
+        <v>202008</v>
       </c>
       <c r="H71" s="2"/>
       <c r="K71" s="8"/>
@@ -3711,27 +3714,27 @@
     <row r="72" s="2" customFormat="1" spans="1:19">
       <c r="A72" s="2">
         <f t="shared" si="6"/>
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="B72" s="2">
         <f>COUNTIF($C$1:C72,C72)</f>
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C72" s="2">
         <v>2</v>
       </c>
       <c r="D72" s="1">
         <f t="shared" si="5"/>
-        <v>102011</v>
+        <v>102009</v>
       </c>
       <c r="E72" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F72" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F72" s="2" t="s">
-        <v>148</v>
-      </c>
       <c r="G72" s="2">
-        <v>202011</v>
+        <v>202009</v>
       </c>
       <c r="H72" s="2"/>
       <c r="K72" s="8"/>
@@ -3743,27 +3746,27 @@
     <row r="73" s="2" customFormat="1" spans="1:19">
       <c r="A73" s="2">
         <f t="shared" si="6"/>
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="B73" s="2">
         <f>COUNTIF($C$1:C73,C73)</f>
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C73" s="2">
         <v>2</v>
       </c>
       <c r="D73" s="1">
         <f t="shared" si="5"/>
-        <v>102012</v>
+        <v>102010</v>
       </c>
       <c r="E73" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>150</v>
-      </c>
       <c r="G73" s="2">
-        <v>202012</v>
+        <v>202010</v>
       </c>
       <c r="H73" s="2"/>
       <c r="K73" s="8"/>
@@ -3775,27 +3778,27 @@
     <row r="74" s="2" customFormat="1" spans="1:19">
       <c r="A74" s="2">
         <f t="shared" si="6"/>
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="B74" s="2">
         <f>COUNTIF($C$1:C74,C74)</f>
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C74" s="2">
         <v>2</v>
       </c>
       <c r="D74" s="1">
         <f t="shared" si="5"/>
-        <v>102013</v>
+        <v>102011</v>
       </c>
       <c r="E74" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F74" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="F74" s="2" t="s">
-        <v>152</v>
-      </c>
       <c r="G74" s="2">
-        <v>202013</v>
+        <v>202011</v>
       </c>
       <c r="H74" s="2"/>
       <c r="K74" s="8"/>
@@ -3807,27 +3810,27 @@
     <row r="75" s="2" customFormat="1" spans="1:19">
       <c r="A75" s="2">
         <f t="shared" si="6"/>
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="B75" s="2">
         <f>COUNTIF($C$1:C75,C75)</f>
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C75" s="2">
         <v>2</v>
       </c>
       <c r="D75" s="1">
         <f t="shared" si="5"/>
-        <v>102014</v>
+        <v>102012</v>
       </c>
       <c r="E75" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F75" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F75" s="2" t="s">
-        <v>154</v>
-      </c>
       <c r="G75" s="2">
-        <v>202014</v>
+        <v>202012</v>
       </c>
       <c r="H75" s="2"/>
       <c r="K75" s="8"/>
@@ -3839,27 +3842,27 @@
     <row r="76" s="2" customFormat="1" spans="1:19">
       <c r="A76" s="2">
         <f t="shared" si="6"/>
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="B76" s="2">
         <f>COUNTIF($C$1:C76,C76)</f>
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C76" s="2">
         <v>2</v>
       </c>
       <c r="D76" s="1">
         <f t="shared" si="5"/>
-        <v>102015</v>
+        <v>102013</v>
       </c>
       <c r="E76" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F76" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="G76" s="2">
-        <v>202015</v>
+        <v>202013</v>
       </c>
       <c r="H76" s="2"/>
       <c r="K76" s="8"/>
@@ -3871,27 +3874,27 @@
     <row r="77" s="2" customFormat="1" spans="1:19">
       <c r="A77" s="2">
         <f t="shared" si="6"/>
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="B77" s="2">
         <f>COUNTIF($C$1:C77,C77)</f>
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C77" s="2">
         <v>2</v>
       </c>
       <c r="D77" s="1">
         <f t="shared" si="5"/>
-        <v>102016</v>
+        <v>102014</v>
       </c>
       <c r="E77" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F77" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>158</v>
-      </c>
       <c r="G77" s="2">
-        <v>202016</v>
+        <v>202014</v>
       </c>
       <c r="H77" s="2"/>
       <c r="K77" s="8"/>
@@ -3903,27 +3906,27 @@
     <row r="78" s="2" customFormat="1" spans="1:19">
       <c r="A78" s="2">
         <f t="shared" si="6"/>
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="B78" s="2">
         <f>COUNTIF($C$1:C78,C78)</f>
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C78" s="2">
         <v>2</v>
       </c>
       <c r="D78" s="1">
         <f t="shared" si="5"/>
-        <v>102017</v>
+        <v>102015</v>
       </c>
       <c r="E78" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F78" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>160</v>
-      </c>
       <c r="G78" s="2">
-        <v>202017</v>
+        <v>202015</v>
       </c>
       <c r="H78" s="2"/>
       <c r="K78" s="8"/>
@@ -3935,27 +3938,27 @@
     <row r="79" s="2" customFormat="1" spans="1:19">
       <c r="A79" s="2">
         <f t="shared" si="6"/>
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="B79" s="2">
         <f>COUNTIF($C$1:C79,C79)</f>
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C79" s="2">
         <v>2</v>
       </c>
       <c r="D79" s="1">
         <f t="shared" si="5"/>
-        <v>102018</v>
+        <v>102016</v>
       </c>
       <c r="E79" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F79" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>162</v>
-      </c>
       <c r="G79" s="2">
-        <v>202018</v>
+        <v>202016</v>
       </c>
       <c r="H79" s="2"/>
       <c r="K79" s="8"/>
@@ -3967,27 +3970,27 @@
     <row r="80" s="2" customFormat="1" spans="1:19">
       <c r="A80" s="2">
         <f t="shared" si="6"/>
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="B80" s="2">
         <f>COUNTIF($C$1:C80,C80)</f>
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C80" s="2">
         <v>2</v>
       </c>
       <c r="D80" s="1">
         <f t="shared" si="5"/>
-        <v>102019</v>
+        <v>102017</v>
       </c>
       <c r="E80" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F80" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="G80" s="2">
-        <v>202019</v>
+        <v>202017</v>
       </c>
       <c r="H80" s="2"/>
       <c r="K80" s="8"/>
@@ -3999,27 +4002,27 @@
     <row r="81" s="2" customFormat="1" spans="1:19">
       <c r="A81" s="2">
         <f t="shared" si="6"/>
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="B81" s="2">
         <f>COUNTIF($C$1:C81,C81)</f>
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C81" s="2">
         <v>2</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="5"/>
-        <v>102020</v>
+        <v>102018</v>
       </c>
       <c r="E81" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F81" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F81" s="2" t="s">
-        <v>166</v>
-      </c>
       <c r="G81" s="2">
-        <v>202020</v>
+        <v>202018</v>
       </c>
       <c r="H81" s="2"/>
       <c r="K81" s="8"/>
@@ -4028,175 +4031,175 @@
       <c r="O81"/>
       <c r="S81" s="1"/>
     </row>
-    <row r="82" s="3" customFormat="1" spans="1:11">
-      <c r="A82" s="3">
+    <row r="82" s="2" customFormat="1" spans="1:19">
+      <c r="A82" s="2">
         <f t="shared" si="6"/>
-        <v>3001</v>
-      </c>
-      <c r="B82" s="3">
+        <v>2019</v>
+      </c>
+      <c r="B82" s="2">
         <f>COUNTIF($C$1:C82,C82)</f>
-        <v>1</v>
-      </c>
-      <c r="C82" s="3">
-        <v>3</v>
+        <v>19</v>
+      </c>
+      <c r="C82" s="2">
+        <v>2</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" si="5"/>
-        <v>103001</v>
-      </c>
-      <c r="E82" s="3" t="s">
+        <v>102019</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="F82" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F82" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="G82" s="3">
-        <v>203001</v>
-      </c>
-      <c r="H82" s="3">
-        <v>3</v>
-      </c>
-      <c r="K82" s="1"/>
-    </row>
-    <row r="83" s="3" customFormat="1" spans="1:11">
-      <c r="A83" s="3">
+      <c r="G82" s="2">
+        <v>202019</v>
+      </c>
+      <c r="H82" s="2"/>
+      <c r="K82" s="8"/>
+      <c r="M82"/>
+      <c r="N82"/>
+      <c r="O82"/>
+      <c r="S82" s="1"/>
+    </row>
+    <row r="83" s="2" customFormat="1" spans="1:19">
+      <c r="A83" s="2">
         <f t="shared" si="6"/>
-        <v>3002</v>
-      </c>
-      <c r="B83" s="3">
+        <v>2020</v>
+      </c>
+      <c r="B83" s="2">
         <f>COUNTIF($C$1:C83,C83)</f>
+        <v>20</v>
+      </c>
+      <c r="C83" s="2">
         <v>2</v>
-      </c>
-      <c r="C83" s="3">
-        <v>3</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="5"/>
-        <v>103002</v>
-      </c>
-      <c r="E83" s="3" t="s">
+        <v>102020</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F83" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="F83" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="G83" s="3">
-        <v>203002</v>
-      </c>
-      <c r="H83" s="3">
-        <v>6</v>
-      </c>
-      <c r="K83" s="1"/>
+      <c r="G83" s="2">
+        <v>202020</v>
+      </c>
+      <c r="H83" s="2"/>
+      <c r="K83" s="8"/>
+      <c r="M83"/>
+      <c r="N83"/>
+      <c r="O83"/>
+      <c r="S83" s="1"/>
     </row>
     <row r="84" s="3" customFormat="1" spans="1:11">
       <c r="A84" s="3">
         <f t="shared" si="6"/>
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="B84" s="3">
         <f>COUNTIF($C$1:C84,C84)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C84" s="3">
         <v>3</v>
       </c>
       <c r="D84" s="1">
         <f t="shared" si="5"/>
+        <v>103001</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="G84" s="3">
+        <v>203001</v>
+      </c>
+      <c r="H84" s="3">
+        <v>3</v>
+      </c>
+      <c r="K84" s="1"/>
+    </row>
+    <row r="85" s="3" customFormat="1" spans="1:11">
+      <c r="A85" s="3">
+        <f t="shared" si="6"/>
+        <v>3002</v>
+      </c>
+      <c r="B85" s="3">
+        <f>COUNTIF($C$1:C85,C85)</f>
+        <v>2</v>
+      </c>
+      <c r="C85" s="3">
+        <v>3</v>
+      </c>
+      <c r="D85" s="1">
+        <f t="shared" si="5"/>
+        <v>103002</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="G85" s="3">
+        <v>203002</v>
+      </c>
+      <c r="H85" s="3">
+        <v>6</v>
+      </c>
+      <c r="K85" s="1"/>
+    </row>
+    <row r="86" s="3" customFormat="1" spans="1:11">
+      <c r="A86" s="3">
+        <f t="shared" si="6"/>
+        <v>3003</v>
+      </c>
+      <c r="B86" s="3">
+        <f>COUNTIF($C$1:C86,C86)</f>
+        <v>3</v>
+      </c>
+      <c r="C86" s="3">
+        <v>3</v>
+      </c>
+      <c r="D86" s="1">
+        <f t="shared" si="5"/>
         <v>103003</v>
       </c>
-      <c r="E84" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="G84" s="3">
+      <c r="E86" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G86" s="3">
         <v>203003</v>
       </c>
-      <c r="H84" s="3">
+      <c r="H86" s="3">
         <v>9</v>
       </c>
-      <c r="K84" s="1"/>
-    </row>
-    <row r="85" s="4" customFormat="1" spans="1:11">
-      <c r="A85" s="4">
-        <f t="shared" si="6"/>
-        <v>4001</v>
-      </c>
-      <c r="B85" s="4">
-        <f>COUNTIF($C$1:C85,C85)</f>
-        <v>1</v>
-      </c>
-      <c r="C85" s="4">
-        <v>4</v>
-      </c>
-      <c r="D85" s="4">
-        <f t="shared" si="5"/>
-        <v>104001</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="G85" s="4">
-        <f t="shared" ref="G85:G94" si="7">200000+A85</f>
-        <v>204001</v>
-      </c>
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-      <c r="J85" s="3"/>
-      <c r="K85" s="9"/>
-    </row>
-    <row r="86" s="4" customFormat="1" spans="1:11">
-      <c r="A86" s="4">
-        <f t="shared" si="6"/>
-        <v>4002</v>
-      </c>
-      <c r="B86" s="4">
-        <f>COUNTIF($C$1:C86,C86)</f>
-        <v>2</v>
-      </c>
-      <c r="C86" s="4">
-        <v>4</v>
-      </c>
-      <c r="D86" s="4">
-        <f t="shared" si="5"/>
-        <v>104002</v>
-      </c>
-      <c r="E86" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="F86" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="G86" s="4">
-        <f t="shared" si="7"/>
-        <v>204002</v>
-      </c>
-      <c r="H86" s="3">
-        <v>3</v>
-      </c>
-      <c r="I86" s="3"/>
-      <c r="J86" s="3"/>
-      <c r="K86" s="9"/>
+      <c r="K86" s="1"/>
     </row>
     <row r="87" s="4" customFormat="1" spans="1:11">
       <c r="A87" s="4">
         <f t="shared" si="6"/>
-        <v>4003</v>
+        <v>4001</v>
       </c>
       <c r="B87" s="4">
         <f>COUNTIF($C$1:C87,C87)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C87" s="4">
         <v>4</v>
       </c>
       <c r="D87" s="4">
         <f t="shared" si="5"/>
-        <v>104003</v>
+        <v>104001</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>176</v>
@@ -4205,75 +4208,75 @@
         <v>177</v>
       </c>
       <c r="G87" s="4">
-        <f t="shared" si="7"/>
-        <v>204003</v>
-      </c>
-      <c r="H87" s="3">
-        <v>6</v>
-      </c>
+        <f t="shared" ref="G87:G96" si="7">200000+A87</f>
+        <v>204001</v>
+      </c>
+      <c r="H87" s="3"/>
       <c r="I87" s="3"/>
       <c r="J87" s="3"/>
       <c r="K87" s="9"/>
     </row>
-    <row r="88" s="5" customFormat="1" spans="1:11">
-      <c r="A88" s="5">
-        <f t="shared" ref="A88:A95" si="8">C88*1000+B88</f>
-        <v>5001</v>
-      </c>
-      <c r="B88" s="5">
+    <row r="88" s="4" customFormat="1" spans="1:11">
+      <c r="A88" s="4">
+        <f t="shared" si="6"/>
+        <v>4002</v>
+      </c>
+      <c r="B88" s="4">
         <f>COUNTIF($C$1:C88,C88)</f>
-        <v>1</v>
-      </c>
-      <c r="C88" s="5">
-        <v>5</v>
-      </c>
-      <c r="D88" s="5">
-        <f t="shared" ref="D88:D95" si="9">100000+C88*1000+B88</f>
-        <v>105001</v>
-      </c>
-      <c r="E88" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C88" s="4">
+        <v>4</v>
+      </c>
+      <c r="D88" s="4">
+        <f t="shared" si="5"/>
+        <v>104002</v>
+      </c>
+      <c r="E88" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F88" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="F88" s="5" t="s">
-        <v>179</v>
-      </c>
-      <c r="G88" s="5">
+      <c r="G88" s="4">
         <f t="shared" si="7"/>
-        <v>205001</v>
-      </c>
-      <c r="H88" s="3"/>
+        <v>204002</v>
+      </c>
+      <c r="H88" s="3">
+        <v>3</v>
+      </c>
       <c r="I88" s="3"/>
       <c r="J88" s="3"/>
       <c r="K88" s="9"/>
     </row>
-    <row r="89" s="5" customFormat="1" spans="1:11">
-      <c r="A89" s="5">
-        <f t="shared" si="8"/>
-        <v>5002</v>
-      </c>
-      <c r="B89" s="5">
+    <row r="89" s="4" customFormat="1" spans="1:11">
+      <c r="A89" s="4">
+        <f t="shared" si="6"/>
+        <v>4003</v>
+      </c>
+      <c r="B89" s="4">
         <f>COUNTIF($C$1:C89,C89)</f>
-        <v>2</v>
-      </c>
-      <c r="C89" s="5">
-        <v>5</v>
-      </c>
-      <c r="D89" s="5">
-        <f t="shared" si="9"/>
-        <v>105002</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>178</v>
-      </c>
-      <c r="F89" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C89" s="4">
+        <v>4</v>
+      </c>
+      <c r="D89" s="4">
+        <f t="shared" si="5"/>
+        <v>104003</v>
+      </c>
+      <c r="E89" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="F89" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="G89" s="5">
+      <c r="G89" s="4">
         <f t="shared" si="7"/>
-        <v>205002</v>
+        <v>204003</v>
       </c>
       <c r="H89" s="3">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
@@ -4281,19 +4284,19 @@
     </row>
     <row r="90" s="5" customFormat="1" spans="1:11">
       <c r="A90" s="5">
-        <f t="shared" si="8"/>
-        <v>5003</v>
+        <f t="shared" ref="A90:A97" si="8">C90*1000+B90</f>
+        <v>5001</v>
       </c>
       <c r="B90" s="5">
         <f>COUNTIF($C$1:C90,C90)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C90" s="5">
         <v>5</v>
       </c>
       <c r="D90" s="5">
-        <f t="shared" si="9"/>
-        <v>105003</v>
+        <f t="shared" ref="D90:D97" si="9">100000+C90*1000+B90</f>
+        <v>105001</v>
       </c>
       <c r="E90" s="5" t="s">
         <v>181</v>
@@ -4303,74 +4306,74 @@
       </c>
       <c r="G90" s="5">
         <f t="shared" si="7"/>
-        <v>205003</v>
-      </c>
-      <c r="H90" s="3">
-        <v>6</v>
-      </c>
+        <v>205001</v>
+      </c>
+      <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
       <c r="K90" s="9"/>
     </row>
-    <row r="91" s="6" customFormat="1" spans="1:11">
-      <c r="A91" s="6">
+    <row r="91" s="5" customFormat="1" spans="1:11">
+      <c r="A91" s="5">
         <f t="shared" si="8"/>
-        <v>6001</v>
-      </c>
-      <c r="B91" s="6">
+        <v>5002</v>
+      </c>
+      <c r="B91" s="5">
         <f>COUNTIF($C$1:C91,C91)</f>
-        <v>1</v>
-      </c>
-      <c r="C91" s="6">
-        <v>6</v>
-      </c>
-      <c r="D91" s="6">
+        <v>2</v>
+      </c>
+      <c r="C91" s="5">
+        <v>5</v>
+      </c>
+      <c r="D91" s="5">
         <f t="shared" si="9"/>
-        <v>106001</v>
-      </c>
-      <c r="E91" s="6" t="s">
+        <v>105002</v>
+      </c>
+      <c r="E91" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="F91" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="F91" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="G91" s="6">
+      <c r="G91" s="5">
         <f t="shared" si="7"/>
-        <v>206001</v>
-      </c>
-      <c r="H91" s="3"/>
+        <v>205002</v>
+      </c>
+      <c r="H91" s="3">
+        <v>3</v>
+      </c>
       <c r="I91" s="3"/>
       <c r="J91" s="3"/>
       <c r="K91" s="9"/>
     </row>
-    <row r="92" s="6" customFormat="1" spans="1:11">
-      <c r="A92" s="6">
+    <row r="92" s="5" customFormat="1" spans="1:11">
+      <c r="A92" s="5">
         <f t="shared" si="8"/>
-        <v>6002</v>
-      </c>
-      <c r="B92" s="6">
+        <v>5003</v>
+      </c>
+      <c r="B92" s="5">
         <f>COUNTIF($C$1:C92,C92)</f>
-        <v>2</v>
-      </c>
-      <c r="C92" s="6">
+        <v>3</v>
+      </c>
+      <c r="C92" s="5">
+        <v>5</v>
+      </c>
+      <c r="D92" s="5">
+        <f t="shared" si="9"/>
+        <v>105003</v>
+      </c>
+      <c r="E92" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="F92" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="G92" s="5">
+        <f t="shared" si="7"/>
+        <v>205003</v>
+      </c>
+      <c r="H92" s="3">
         <v>6</v>
-      </c>
-      <c r="D92" s="6">
-        <f t="shared" si="9"/>
-        <v>106002</v>
-      </c>
-      <c r="E92" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="F92" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="G92" s="6">
-        <f t="shared" si="7"/>
-        <v>206002</v>
-      </c>
-      <c r="H92" s="3">
-        <v>3</v>
       </c>
       <c r="I92" s="3"/>
       <c r="J92" s="3"/>
@@ -4379,18 +4382,18 @@
     <row r="93" s="6" customFormat="1" spans="1:11">
       <c r="A93" s="6">
         <f t="shared" si="8"/>
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="B93" s="6">
         <f>COUNTIF($C$1:C93,C93)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C93" s="6">
         <v>6</v>
       </c>
       <c r="D93" s="6">
         <f t="shared" si="9"/>
-        <v>106003</v>
+        <v>106001</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>186</v>
@@ -4400,14 +4403,78 @@
       </c>
       <c r="G93" s="6">
         <f t="shared" si="7"/>
-        <v>206003</v>
-      </c>
-      <c r="H93" s="3">
-        <v>6</v>
-      </c>
+        <v>206001</v>
+      </c>
+      <c r="H93" s="3"/>
       <c r="I93" s="3"/>
       <c r="J93" s="3"/>
       <c r="K93" s="9"/>
+    </row>
+    <row r="94" s="6" customFormat="1" spans="1:11">
+      <c r="A94" s="6">
+        <f t="shared" si="8"/>
+        <v>6002</v>
+      </c>
+      <c r="B94" s="6">
+        <f>COUNTIF($C$1:C94,C94)</f>
+        <v>2</v>
+      </c>
+      <c r="C94" s="6">
+        <v>6</v>
+      </c>
+      <c r="D94" s="6">
+        <f t="shared" si="9"/>
+        <v>106002</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="G94" s="6">
+        <f t="shared" si="7"/>
+        <v>206002</v>
+      </c>
+      <c r="H94" s="3">
+        <v>3</v>
+      </c>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="9"/>
+    </row>
+    <row r="95" s="6" customFormat="1" spans="1:11">
+      <c r="A95" s="6">
+        <f t="shared" si="8"/>
+        <v>6003</v>
+      </c>
+      <c r="B95" s="6">
+        <f>COUNTIF($C$1:C95,C95)</f>
+        <v>3</v>
+      </c>
+      <c r="C95" s="6">
+        <v>6</v>
+      </c>
+      <c r="D95" s="6">
+        <f t="shared" si="9"/>
+        <v>106003</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="G95" s="6">
+        <f t="shared" si="7"/>
+        <v>206003</v>
+      </c>
+      <c r="H95" s="3">
+        <v>6</v>
+      </c>
+      <c r="I95" s="3"/>
+      <c r="J95" s="3"/>
+      <c r="K95" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -98,12 +98,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="I1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+参数：货币ID_货币数量_赠送头像或头像框的ID</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="237">
   <si>
     <t>id</t>
   </si>
@@ -120,7 +142,16 @@
     <t>资源描述</t>
   </si>
   <si>
-    <t>客户端展示获得VIP条件</t>
+    <t>等级</t>
+  </si>
+  <si>
+    <t>货币购买</t>
+  </si>
+  <si>
+    <t>VIP条件</t>
+  </si>
+  <si>
+    <t>多语言ID</t>
   </si>
   <si>
     <t>int</t>
@@ -129,6 +160,9 @@
     <t>string</t>
   </si>
   <si>
+    <t>list&lt;int&gt;{_}</t>
+  </si>
+  <si>
     <t>resourceType</t>
   </si>
   <si>
@@ -141,7 +175,16 @@
     <t>Dec</t>
   </si>
   <si>
-    <t>VIPLevel</t>
+    <t>playerLv</t>
+  </si>
+  <si>
+    <t>buyItem</t>
+  </si>
+  <si>
+    <t>vipLevel</t>
+  </si>
+  <si>
+    <t>languageId</t>
   </si>
   <si>
     <t>头像1</t>
@@ -153,183 +196,183 @@
     <t>头像2</t>
   </si>
   <si>
+    <t>picture_017.png</t>
+  </si>
+  <si>
+    <t>头像3</t>
+  </si>
+  <si>
     <t>picture_002.png</t>
   </si>
   <si>
-    <t>头像3</t>
+    <t>头像4</t>
+  </si>
+  <si>
+    <t>picture_018.png</t>
+  </si>
+  <si>
+    <t>头像5</t>
   </si>
   <si>
     <t>picture_003.png</t>
   </si>
   <si>
-    <t>头像4</t>
+    <t>头像6</t>
+  </si>
+  <si>
+    <t>picture_019.png</t>
+  </si>
+  <si>
+    <t>头像7</t>
   </si>
   <si>
     <t>picture_004.png</t>
   </si>
   <si>
-    <t>头像5</t>
+    <t>头像8</t>
+  </si>
+  <si>
+    <t>picture_020.png</t>
+  </si>
+  <si>
+    <t>头像9</t>
   </si>
   <si>
     <t>picture_005.png</t>
   </si>
   <si>
-    <t>头像6</t>
+    <t>头像10</t>
+  </si>
+  <si>
+    <t>picture_021.png</t>
+  </si>
+  <si>
+    <t>头像11</t>
   </si>
   <si>
     <t>picture_006.png</t>
   </si>
   <si>
-    <t>头像7</t>
+    <t>头像12</t>
+  </si>
+  <si>
+    <t>picture_022.png</t>
+  </si>
+  <si>
+    <t>头像13</t>
   </si>
   <si>
     <t>picture_007.png</t>
   </si>
   <si>
-    <t>头像8</t>
+    <t>头像14</t>
+  </si>
+  <si>
+    <t>picture_023.png</t>
+  </si>
+  <si>
+    <t>头像15</t>
   </si>
   <si>
     <t>picture_008.png</t>
   </si>
   <si>
-    <t>头像9</t>
+    <t>头像16</t>
+  </si>
+  <si>
+    <t>picture_024.png</t>
+  </si>
+  <si>
+    <t>头像17</t>
   </si>
   <si>
     <t>picture_009.png</t>
   </si>
   <si>
-    <t>头像10</t>
+    <t>头像18</t>
+  </si>
+  <si>
+    <t>picture_025.png</t>
+  </si>
+  <si>
+    <t>头像19</t>
   </si>
   <si>
     <t>picture_010.png</t>
   </si>
   <si>
-    <t>头像11</t>
+    <t>头像20</t>
+  </si>
+  <si>
+    <t>picture_026.png</t>
+  </si>
+  <si>
+    <t>头像21</t>
   </si>
   <si>
     <t>picture_011.png</t>
   </si>
   <si>
-    <t>头像12</t>
+    <t>头像22</t>
+  </si>
+  <si>
+    <t>picture_027.png</t>
+  </si>
+  <si>
+    <t>头像23</t>
   </si>
   <si>
     <t>picture_012.png</t>
   </si>
   <si>
-    <t>头像13</t>
+    <t>头像24</t>
+  </si>
+  <si>
+    <t>picture_028.png</t>
+  </si>
+  <si>
+    <t>头像25</t>
   </si>
   <si>
     <t>picture_013.png</t>
   </si>
   <si>
-    <t>头像14</t>
+    <t>头像26</t>
+  </si>
+  <si>
+    <t>picture_029.png</t>
+  </si>
+  <si>
+    <t>头像27</t>
   </si>
   <si>
     <t>picture_014.png</t>
   </si>
   <si>
-    <t>头像15</t>
+    <t>头像28</t>
+  </si>
+  <si>
+    <t>picture_030.png</t>
+  </si>
+  <si>
+    <t>头像29</t>
   </si>
   <si>
     <t>picture_015.png</t>
   </si>
   <si>
-    <t>头像16</t>
+    <t>头像30</t>
+  </si>
+  <si>
+    <t>picture_031.png</t>
+  </si>
+  <si>
+    <t>头像31</t>
   </si>
   <si>
     <t>picture_016.png</t>
   </si>
   <si>
-    <t>头像17</t>
-  </si>
-  <si>
-    <t>picture_017.png</t>
-  </si>
-  <si>
-    <t>头像18</t>
-  </si>
-  <si>
-    <t>picture_018.png</t>
-  </si>
-  <si>
-    <t>头像19</t>
-  </si>
-  <si>
-    <t>picture_019.png</t>
-  </si>
-  <si>
-    <t>头像20</t>
-  </si>
-  <si>
-    <t>picture_020.png</t>
-  </si>
-  <si>
-    <t>头像21</t>
-  </si>
-  <si>
-    <t>picture_021.png</t>
-  </si>
-  <si>
-    <t>头像22</t>
-  </si>
-  <si>
-    <t>picture_022.png</t>
-  </si>
-  <si>
-    <t>头像23</t>
-  </si>
-  <si>
-    <t>picture_023.png</t>
-  </si>
-  <si>
-    <t>头像24</t>
-  </si>
-  <si>
-    <t>picture_024.png</t>
-  </si>
-  <si>
-    <t>头像25</t>
-  </si>
-  <si>
-    <t>picture_025.png</t>
-  </si>
-  <si>
-    <t>头像26</t>
-  </si>
-  <si>
-    <t>picture_026.png</t>
-  </si>
-  <si>
-    <t>头像27</t>
-  </si>
-  <si>
-    <t>picture_027.png</t>
-  </si>
-  <si>
-    <t>头像28</t>
-  </si>
-  <si>
-    <t>picture_028.png</t>
-  </si>
-  <si>
-    <t>头像29</t>
-  </si>
-  <si>
-    <t>picture_029.png</t>
-  </si>
-  <si>
-    <t>头像30</t>
-  </si>
-  <si>
-    <t>picture_030.png</t>
-  </si>
-  <si>
-    <t>头像31</t>
-  </si>
-  <si>
-    <t>picture_031.png</t>
-  </si>
-  <si>
     <t>头像32</t>
   </si>
   <si>
@@ -378,6 +421,84 @@
     <t>picture_039.png</t>
   </si>
   <si>
+    <t>头像40</t>
+  </si>
+  <si>
+    <t>1980000_1500_1008</t>
+  </si>
+  <si>
+    <t>头像41</t>
+  </si>
+  <si>
+    <t>1980000_1500_1009</t>
+  </si>
+  <si>
+    <t>头像42</t>
+  </si>
+  <si>
+    <t>1980000_1500_1010</t>
+  </si>
+  <si>
+    <t>头像43</t>
+  </si>
+  <si>
+    <t>1980000_1500_1011</t>
+  </si>
+  <si>
+    <t>头像44</t>
+  </si>
+  <si>
+    <t>1980000_1500_1012</t>
+  </si>
+  <si>
+    <t>头像45</t>
+  </si>
+  <si>
+    <t>1980000_1500_1013</t>
+  </si>
+  <si>
+    <t>头像46</t>
+  </si>
+  <si>
+    <t>1980000_1500_1014</t>
+  </si>
+  <si>
+    <t>头像47</t>
+  </si>
+  <si>
+    <t>1980000_1500_1015</t>
+  </si>
+  <si>
+    <t>头像48</t>
+  </si>
+  <si>
+    <t>1980000_1500_1016</t>
+  </si>
+  <si>
+    <t>头像49</t>
+  </si>
+  <si>
+    <t>1980000_1500_1017</t>
+  </si>
+  <si>
+    <t>头像50</t>
+  </si>
+  <si>
+    <t>1980000_1500_1018</t>
+  </si>
+  <si>
+    <t>头像51</t>
+  </si>
+  <si>
+    <t>1980000_1500_1019</t>
+  </si>
+  <si>
+    <t>头像52</t>
+  </si>
+  <si>
+    <t>1980000_1500_1020</t>
+  </si>
+  <si>
     <t>头像框1</t>
   </si>
   <si>
@@ -408,91 +529,130 @@
     <t>frame_005.png</t>
   </si>
   <si>
+    <t>头像框-每日奖金</t>
+  </si>
+  <si>
+    <t>frame_801.png</t>
+  </si>
+  <si>
+    <t>头像框-首充专属</t>
+  </si>
+  <si>
+    <t>frame_018.png</t>
+  </si>
+  <si>
     <t>头像框6</t>
   </si>
   <si>
     <t>frame_006.png</t>
   </si>
   <si>
+    <t>1980000_1500_40</t>
+  </si>
+  <si>
     <t>头像框7</t>
   </si>
   <si>
     <t>frame_007.png</t>
   </si>
   <si>
+    <t>1980000_1500_41</t>
+  </si>
+  <si>
     <t>头像框8</t>
   </si>
   <si>
     <t>frame_008.png</t>
   </si>
   <si>
+    <t>1980000_1500_42</t>
+  </si>
+  <si>
     <t>头像框9</t>
   </si>
   <si>
     <t>frame_009.png</t>
   </si>
   <si>
+    <t>1980000_1500_43</t>
+  </si>
+  <si>
     <t>头像框10</t>
   </si>
   <si>
     <t>frame_010.png</t>
   </si>
   <si>
+    <t>1980000_1500_44</t>
+  </si>
+  <si>
     <t>头像框11</t>
   </si>
   <si>
     <t>frame_011.png</t>
   </si>
   <si>
+    <t>1980000_1500_45</t>
+  </si>
+  <si>
     <t>头像框12</t>
   </si>
   <si>
     <t>frame_012.png</t>
   </si>
   <si>
+    <t>1980000_1500_46</t>
+  </si>
+  <si>
     <t>头像框13</t>
   </si>
   <si>
     <t>frame_013.png</t>
   </si>
   <si>
+    <t>1980000_1500_47</t>
+  </si>
+  <si>
     <t>头像框14</t>
   </si>
   <si>
     <t>frame_014.png</t>
   </si>
   <si>
+    <t>1980000_1500_48</t>
+  </si>
+  <si>
     <t>头像框15</t>
   </si>
   <si>
     <t>frame_015.png</t>
   </si>
   <si>
+    <t>1980000_1500_49</t>
+  </si>
+  <si>
     <t>头像框16</t>
   </si>
   <si>
     <t>frame_016.png</t>
   </si>
   <si>
+    <t>1980000_1500_50</t>
+  </si>
+  <si>
     <t>头像框17</t>
   </si>
   <si>
     <t>frame_017.png</t>
   </si>
   <si>
+    <t>1980000_1500_51</t>
+  </si>
+  <si>
     <t>头像框18</t>
   </si>
   <si>
-    <t>frame_018.png</t>
-  </si>
-  <si>
-    <t>头像框-特权卡专属</t>
-  </si>
-  <si>
-    <t>frame_801.png</t>
-  </si>
-  <si>
-    <t>头像框-首充专属</t>
+    <t>1980000_1500_52</t>
   </si>
   <si>
     <t>国旗1</t>
@@ -688,13 +848,25 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="5" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <u/>
@@ -841,12 +1013,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -857,48 +1029,12 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="39">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1213,165 +1349,147 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1685,84 +1803,119 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S95"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <dimension ref="A1:K108"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
-    <col min="5" max="5" width="18.25" customWidth="1"/>
-    <col min="6" max="6" width="19.125" customWidth="1"/>
-    <col min="7" max="7" width="12.5" customWidth="1"/>
-    <col min="8" max="9" width="12.125" customWidth="1"/>
-    <col min="14" max="15" width="12.625"/>
-    <col min="18" max="18" width="14.375" customWidth="1"/>
+    <col min="1" max="2" width="9" style="1"/>
+    <col min="3" max="3" width="12.25" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="18.25" style="1" customWidth="1"/>
+    <col min="6" max="6" width="19.125" style="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5" style="1" customWidth="1"/>
+    <col min="8" max="8" width="9" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
+    <col min="10" max="10" width="8.875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9" style="1"/>
+    <col min="14" max="15" width="12.625" style="1"/>
+    <col min="16" max="17" width="9" style="1"/>
+    <col min="18" max="18" width="14.375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="1" spans="1:8">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1"/>
-      <c r="C1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:11">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" customFormat="1" spans="1:8">
-      <c r="A2" t="s">
+      <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2"/>
-      <c r="C2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="J1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G2" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3" customFormat="1" spans="1:8">
-      <c r="A3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B3"/>
-      <c r="C3" t="s">
+      <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F3" t="s">
+      <c r="B2" s="1"/>
+      <c r="C2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="H3" t="s">
+      <c r="J2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:11">
+      <c r="A3" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B3" s="1"/>
+      <c r="C3" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:15">
+      <c r="D3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:11">
       <c r="A5" s="1">
-        <f t="shared" ref="A5:A24" si="0">C5*1000+B5</f>
+        <f t="shared" ref="A5:A36" si="0">C5*1000+B5</f>
         <v>1</v>
       </c>
       <c r="B5" s="1">
@@ -1777,19 +1930,16 @@
         <v>100001</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="G5" s="1">
         <v>200001</v>
       </c>
-      <c r="M5"/>
-      <c r="N5"/>
-      <c r="O5"/>
-    </row>
-    <row r="6" s="1" customFormat="1" spans="1:15">
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:11">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1802,23 +1952,20 @@
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" ref="D6:D37" si="1">100000+C6*1000+B6</f>
+        <f t="shared" ref="D6:D38" si="1">100000+C6*1000+B6</f>
         <v>100002</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="G6" s="1">
-        <v>200002</v>
-      </c>
-      <c r="M6"/>
-      <c r="N6"/>
-      <c r="O6"/>
-    </row>
-    <row r="7" s="1" customFormat="1" spans="1:15">
+        <v>200017</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:11">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1835,19 +1982,19 @@
         <v>100003</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1">
-        <v>200003</v>
-      </c>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
-    </row>
-    <row r="8" s="1" customFormat="1" spans="1:15">
+        <v>200002</v>
+      </c>
+      <c r="H7" s="1">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:11">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1864,19 +2011,19 @@
         <v>100004</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="F8" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="1">
+        <v>200018</v>
+      </c>
+      <c r="H8" s="1">
         <v>20</v>
       </c>
-      <c r="G8" s="1">
-        <v>200004</v>
-      </c>
-      <c r="M8"/>
-      <c r="N8"/>
-      <c r="O8"/>
-    </row>
-    <row r="9" s="1" customFormat="1" spans="1:15">
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:11">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1893,19 +2040,19 @@
         <v>100005</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="G9" s="1">
-        <v>200005</v>
-      </c>
-      <c r="M9"/>
-      <c r="N9"/>
-      <c r="O9"/>
-    </row>
-    <row r="10" s="1" customFormat="1" spans="1:15">
+        <v>200003</v>
+      </c>
+      <c r="H9" s="1">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:11">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1922,19 +2069,19 @@
         <v>100006</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="G10" s="1">
-        <v>200006</v>
-      </c>
-      <c r="M10"/>
-      <c r="N10"/>
-      <c r="O10"/>
-    </row>
-    <row r="11" s="1" customFormat="1" spans="1:15">
+        <v>200019</v>
+      </c>
+      <c r="H10" s="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:11">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1951,19 +2098,19 @@
         <v>100007</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="G11" s="1">
-        <v>200007</v>
-      </c>
-      <c r="M11"/>
-      <c r="N11"/>
-      <c r="O11"/>
-    </row>
-    <row r="12" s="1" customFormat="1" spans="1:15">
+        <v>200004</v>
+      </c>
+      <c r="H11" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:11">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1980,19 +2127,19 @@
         <v>100008</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G12" s="1">
-        <v>200008</v>
-      </c>
-      <c r="M12"/>
-      <c r="N12"/>
-      <c r="O12"/>
-    </row>
-    <row r="13" s="1" customFormat="1" spans="1:15">
+        <v>200020</v>
+      </c>
+      <c r="H12" s="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:11">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2009,19 +2156,19 @@
         <v>100009</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="G13" s="1">
-        <v>200009</v>
-      </c>
-      <c r="M13"/>
-      <c r="N13"/>
-      <c r="O13"/>
-    </row>
-    <row r="14" s="1" customFormat="1" spans="1:15">
+        <v>200005</v>
+      </c>
+      <c r="H13" s="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:11">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2038,19 +2185,19 @@
         <v>100010</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="G14" s="1">
-        <v>200010</v>
-      </c>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14"/>
-    </row>
-    <row r="15" s="1" customFormat="1" spans="1:15">
+        <v>200021</v>
+      </c>
+      <c r="H14" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:11">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2067,19 +2214,19 @@
         <v>100011</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G15" s="1">
-        <v>200011</v>
-      </c>
-      <c r="M15"/>
-      <c r="N15"/>
-      <c r="O15"/>
-    </row>
-    <row r="16" s="1" customFormat="1" spans="1:15">
+        <v>200006</v>
+      </c>
+      <c r="H15" s="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:11">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2096,19 +2243,19 @@
         <v>100012</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>36</v>
+        <v>43</v>
       </c>
       <c r="G16" s="1">
-        <v>200012</v>
-      </c>
-      <c r="M16"/>
-      <c r="N16"/>
-      <c r="O16"/>
-    </row>
-    <row r="17" s="1" customFormat="1" spans="1:15">
+        <v>200022</v>
+      </c>
+      <c r="H16" s="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:8">
       <c r="A17" s="1">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2125,19 +2272,19 @@
         <v>100013</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>38</v>
+        <v>45</v>
       </c>
       <c r="G17" s="1">
-        <v>200013</v>
-      </c>
-      <c r="M17"/>
-      <c r="N17"/>
-      <c r="O17"/>
-    </row>
-    <row r="18" s="1" customFormat="1" spans="1:15">
+        <v>200007</v>
+      </c>
+      <c r="H17" s="1">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:8">
       <c r="A18" s="1">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2154,19 +2301,19 @@
         <v>100014</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="G18" s="1">
-        <v>200014</v>
-      </c>
-      <c r="M18"/>
-      <c r="N18"/>
-      <c r="O18"/>
-    </row>
-    <row r="19" s="1" customFormat="1" spans="1:15">
+        <v>200023</v>
+      </c>
+      <c r="H18" s="1">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:8">
       <c r="A19" s="1">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2183,19 +2330,19 @@
         <v>100015</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="G19" s="1">
-        <v>200015</v>
-      </c>
-      <c r="M19"/>
-      <c r="N19"/>
-      <c r="O19"/>
-    </row>
-    <row r="20" s="1" customFormat="1" spans="1:15">
+        <v>200008</v>
+      </c>
+      <c r="H19" s="1">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:8">
       <c r="A20" s="1">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2212,19 +2359,19 @@
         <v>100016</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G20" s="1">
-        <v>200016</v>
-      </c>
-      <c r="M20"/>
-      <c r="N20"/>
-      <c r="O20"/>
-    </row>
-    <row r="21" s="1" customFormat="1" spans="1:15">
+        <v>200024</v>
+      </c>
+      <c r="H20" s="1">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:8">
       <c r="A21" s="1">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2241,19 +2388,19 @@
         <v>100017</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="G21" s="1">
-        <v>200017</v>
-      </c>
-      <c r="M21"/>
-      <c r="N21"/>
-      <c r="O21"/>
-    </row>
-    <row r="22" s="1" customFormat="1" spans="1:15">
+        <v>200009</v>
+      </c>
+      <c r="H21" s="1">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:8">
       <c r="A22" s="1">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2270,19 +2417,19 @@
         <v>100018</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="G22" s="1">
-        <v>200018</v>
-      </c>
-      <c r="M22"/>
-      <c r="N22"/>
-      <c r="O22"/>
-    </row>
-    <row r="23" s="1" customFormat="1" spans="1:15">
+        <v>200025</v>
+      </c>
+      <c r="H22" s="1">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:8">
       <c r="A23" s="1">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2299,19 +2446,19 @@
         <v>100019</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="G23" s="1">
-        <v>200019</v>
-      </c>
-      <c r="M23"/>
-      <c r="N23"/>
-      <c r="O23"/>
-    </row>
-    <row r="24" s="1" customFormat="1" spans="1:15">
+        <v>200010</v>
+      </c>
+      <c r="H23" s="1">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:8">
       <c r="A24" s="1">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2328,21 +2475,21 @@
         <v>100020</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="G24" s="1">
-        <v>200020</v>
-      </c>
-      <c r="M24"/>
-      <c r="N24"/>
-      <c r="O24"/>
-    </row>
-    <row r="25" s="1" customFormat="1" spans="1:15">
+        <v>200026</v>
+      </c>
+      <c r="H24" s="1">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:8">
       <c r="A25" s="1">
-        <f t="shared" ref="A25:A43" si="2">C25*1000+B25</f>
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
       <c r="B25" s="1">
@@ -2353,25 +2500,25 @@
         <v>0</v>
       </c>
       <c r="D25" s="1">
-        <f t="shared" ref="D25:D88" si="3">100000+C25*1000+B25</f>
+        <f t="shared" si="1"/>
         <v>100021</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G25" s="1">
-        <v>200021</v>
-      </c>
-      <c r="M25"/>
-      <c r="N25"/>
-      <c r="O25"/>
-    </row>
-    <row r="26" s="1" customFormat="1" spans="1:15">
+        <v>200011</v>
+      </c>
+      <c r="H25" s="1">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:8">
       <c r="A26" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
       <c r="B26" s="1">
@@ -2382,25 +2529,25 @@
         <v>0</v>
       </c>
       <c r="D26" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100022</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G26" s="1">
-        <v>200022</v>
-      </c>
-      <c r="M26"/>
-      <c r="N26"/>
-      <c r="O26"/>
-    </row>
-    <row r="27" s="1" customFormat="1" spans="1:15">
+        <v>200027</v>
+      </c>
+      <c r="H26" s="1">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:8">
       <c r="A27" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
       <c r="B27" s="1">
@@ -2411,25 +2558,25 @@
         <v>0</v>
       </c>
       <c r="D27" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100023</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G27" s="1">
-        <v>200023</v>
-      </c>
-      <c r="M27"/>
-      <c r="N27"/>
-      <c r="O27"/>
-    </row>
-    <row r="28" s="1" customFormat="1" spans="1:15">
+        <v>200012</v>
+      </c>
+      <c r="H27" s="1">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:8">
       <c r="A28" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
       <c r="B28" s="1">
@@ -2440,25 +2587,25 @@
         <v>0</v>
       </c>
       <c r="D28" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100024</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="G28" s="1">
-        <v>200024</v>
-      </c>
-      <c r="M28"/>
-      <c r="N28"/>
-      <c r="O28"/>
-    </row>
-    <row r="29" s="1" customFormat="1" spans="1:15">
+        <v>200028</v>
+      </c>
+      <c r="H28" s="1">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:8">
       <c r="A29" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
       <c r="B29" s="1">
@@ -2469,25 +2616,25 @@
         <v>0</v>
       </c>
       <c r="D29" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100025</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="G29" s="1">
-        <v>200025</v>
-      </c>
-      <c r="M29"/>
-      <c r="N29"/>
-      <c r="O29"/>
-    </row>
-    <row r="30" s="1" customFormat="1" spans="1:15">
+        <v>200013</v>
+      </c>
+      <c r="H29" s="1">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="30" s="1" customFormat="1" spans="1:8">
       <c r="A30" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
       <c r="B30" s="1">
@@ -2498,25 +2645,25 @@
         <v>0</v>
       </c>
       <c r="D30" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100026</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G30" s="1">
-        <v>200026</v>
-      </c>
-      <c r="M30"/>
-      <c r="N30"/>
-      <c r="O30"/>
-    </row>
-    <row r="31" s="1" customFormat="1" spans="1:15">
+        <v>200029</v>
+      </c>
+      <c r="H30" s="1">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:8">
       <c r="A31" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
       <c r="B31" s="1">
@@ -2527,25 +2674,25 @@
         <v>0</v>
       </c>
       <c r="D31" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100027</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="G31" s="1">
-        <v>200027</v>
-      </c>
-      <c r="M31"/>
-      <c r="N31"/>
-      <c r="O31"/>
-    </row>
-    <row r="32" s="1" customFormat="1" spans="1:15">
+        <v>200014</v>
+      </c>
+      <c r="H31" s="1">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:8">
       <c r="A32" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
       <c r="B32" s="1">
@@ -2556,25 +2703,25 @@
         <v>0</v>
       </c>
       <c r="D32" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100028</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G32" s="1">
-        <v>200028</v>
-      </c>
-      <c r="M32"/>
-      <c r="N32"/>
-      <c r="O32"/>
-    </row>
-    <row r="33" s="1" customFormat="1" spans="1:15">
+        <v>200030</v>
+      </c>
+      <c r="H32" s="1">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:11">
       <c r="A33" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B33" s="1">
@@ -2585,25 +2732,25 @@
         <v>0</v>
       </c>
       <c r="D33" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100029</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="G33" s="1">
-        <v>200029</v>
-      </c>
-      <c r="M33"/>
-      <c r="N33"/>
-      <c r="O33"/>
-    </row>
-    <row r="34" s="1" customFormat="1" spans="1:15">
+        <v>200015</v>
+      </c>
+      <c r="H33" s="1">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:11">
       <c r="A34" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B34" s="1">
@@ -2614,25 +2761,25 @@
         <v>0</v>
       </c>
       <c r="D34" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100030</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G34" s="1">
-        <v>200030</v>
-      </c>
-      <c r="M34"/>
-      <c r="N34"/>
-      <c r="O34"/>
-    </row>
-    <row r="35" s="1" customFormat="1" spans="1:15">
+        <v>200031</v>
+      </c>
+      <c r="H34" s="1">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:11">
       <c r="A35" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B35" s="1">
@@ -2643,25 +2790,25 @@
         <v>0</v>
       </c>
       <c r="D35" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100031</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="G35" s="1">
-        <v>200031</v>
-      </c>
-      <c r="M35"/>
-      <c r="N35"/>
-      <c r="O35"/>
-    </row>
-    <row r="36" s="1" customFormat="1" spans="1:15">
+        <v>200016</v>
+      </c>
+      <c r="H35" s="1">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:11">
       <c r="A36" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B36" s="1">
@@ -2672,25 +2819,25 @@
         <v>0</v>
       </c>
       <c r="D36" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100032</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="G36" s="1">
         <v>200032</v>
       </c>
-      <c r="M36"/>
-      <c r="N36"/>
-      <c r="O36"/>
-    </row>
-    <row r="37" s="1" customFormat="1" spans="1:15">
+      <c r="H36" s="1">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:11">
       <c r="A37" s="1">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="A37:A61" si="2">C37*1000+B37</f>
         <v>33</v>
       </c>
       <c r="B37" s="1">
@@ -2701,23 +2848,23 @@
         <v>0</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100033</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G37" s="1">
         <v>200033</v>
       </c>
-      <c r="M37"/>
-      <c r="N37"/>
-      <c r="O37"/>
-    </row>
-    <row r="38" s="1" customFormat="1" spans="1:15">
+      <c r="H37" s="1">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:11">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -2730,23 +2877,23 @@
         <v>0</v>
       </c>
       <c r="D38" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100034</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="G38" s="1">
         <v>200034</v>
       </c>
-      <c r="M38"/>
-      <c r="N38"/>
-      <c r="O38"/>
-    </row>
-    <row r="39" s="1" customFormat="1" spans="1:15">
+      <c r="H38" s="1">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:11">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -2759,23 +2906,23 @@
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D39:D63" si="3">100000+C39*1000+B39</f>
         <v>100035</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="G39" s="1">
         <v>200035</v>
       </c>
-      <c r="M39"/>
-      <c r="N39"/>
-      <c r="O39"/>
-    </row>
-    <row r="40" s="1" customFormat="1" spans="1:15">
+      <c r="H39" s="1">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:11">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -2792,19 +2939,19 @@
         <v>100036</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="G40" s="1">
         <v>200036</v>
       </c>
-      <c r="M40"/>
-      <c r="N40"/>
-      <c r="O40"/>
-    </row>
-    <row r="41" s="1" customFormat="1" spans="1:15">
+      <c r="H40" s="1">
+        <v>850</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:11">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -2821,19 +2968,19 @@
         <v>100037</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G41" s="1">
         <v>200037</v>
       </c>
-      <c r="M41"/>
-      <c r="N41"/>
-      <c r="O41"/>
-    </row>
-    <row r="42" s="1" customFormat="1" spans="1:15">
+      <c r="H41" s="1">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:11">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -2850,19 +2997,19 @@
         <v>100038</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="G42" s="1">
         <v>200038</v>
       </c>
-      <c r="M42"/>
-      <c r="N42"/>
-      <c r="O42"/>
-    </row>
-    <row r="43" s="1" customFormat="1" spans="1:15">
+      <c r="H42" s="1">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:11">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -2879,1602 +3026,1922 @@
         <v>100039</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G43" s="1">
         <v>200039</v>
       </c>
-      <c r="M43"/>
-      <c r="N43"/>
-      <c r="O43"/>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44">
-        <f t="shared" ref="A44:A65" si="4">C44*1000+B44</f>
+      <c r="H43" s="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:11">
+      <c r="A44" s="2">
+        <f t="shared" si="2"/>
+        <v>40</v>
+      </c>
+      <c r="B44" s="2">
+        <f>COUNTIF($C$1:C44,C44)</f>
+        <v>40</v>
+      </c>
+      <c r="C44" s="2">
+        <v>0</v>
+      </c>
+      <c r="D44" s="2">
+        <f t="shared" si="3"/>
+        <v>100040</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="G44" s="2">
+        <v>200014</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2"/>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:11">
+      <c r="A45" s="2">
+        <f t="shared" si="2"/>
+        <v>41</v>
+      </c>
+      <c r="B45" s="2">
+        <f>COUNTIF($C$1:C45,C45)</f>
+        <v>41</v>
+      </c>
+      <c r="C45" s="2">
+        <v>0</v>
+      </c>
+      <c r="D45" s="2">
+        <f t="shared" si="3"/>
+        <v>100041</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G45" s="2">
+        <v>200030</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:11">
+      <c r="A46" s="2">
+        <f t="shared" si="2"/>
+        <v>42</v>
+      </c>
+      <c r="B46" s="2">
+        <f>COUNTIF($C$1:C46,C46)</f>
+        <v>42</v>
+      </c>
+      <c r="C46" s="2">
+        <v>0</v>
+      </c>
+      <c r="D46" s="2">
+        <f t="shared" si="3"/>
+        <v>100042</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G46" s="2">
+        <v>200015</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:11">
+      <c r="A47" s="2">
+        <f t="shared" si="2"/>
+        <v>43</v>
+      </c>
+      <c r="B47" s="2">
+        <f>COUNTIF($C$1:C47,C47)</f>
+        <v>43</v>
+      </c>
+      <c r="C47" s="2">
+        <v>0</v>
+      </c>
+      <c r="D47" s="2">
+        <f t="shared" si="3"/>
+        <v>100043</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G47" s="2">
+        <v>200031</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:11">
+      <c r="A48" s="2">
+        <f t="shared" si="2"/>
+        <v>44</v>
+      </c>
+      <c r="B48" s="2">
+        <f>COUNTIF($C$1:C48,C48)</f>
+        <v>44</v>
+      </c>
+      <c r="C48" s="2">
+        <v>0</v>
+      </c>
+      <c r="D48" s="2">
+        <f t="shared" si="3"/>
+        <v>100044</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="G48" s="2">
+        <v>200016</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:11">
+      <c r="A49" s="2">
+        <f t="shared" si="2"/>
+        <v>45</v>
+      </c>
+      <c r="B49" s="2">
+        <f>COUNTIF($C$1:C49,C49)</f>
+        <v>45</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2">
+        <f t="shared" si="3"/>
+        <v>100045</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G49" s="2">
+        <v>200032</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:11">
+      <c r="A50" s="2">
+        <f t="shared" si="2"/>
+        <v>46</v>
+      </c>
+      <c r="B50" s="2">
+        <f>COUNTIF($C$1:C50,C50)</f>
+        <v>46</v>
+      </c>
+      <c r="C50" s="2">
+        <v>0</v>
+      </c>
+      <c r="D50" s="2">
+        <f t="shared" si="3"/>
+        <v>100046</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="G50" s="2">
+        <v>200033</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:11">
+      <c r="A51" s="2">
+        <f t="shared" si="2"/>
+        <v>47</v>
+      </c>
+      <c r="B51" s="2">
+        <f>COUNTIF($C$1:C51,C51)</f>
+        <v>47</v>
+      </c>
+      <c r="C51" s="2">
+        <v>0</v>
+      </c>
+      <c r="D51" s="2">
+        <f t="shared" si="3"/>
+        <v>100047</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="G51" s="2">
+        <v>200034</v>
+      </c>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:11">
+      <c r="A52" s="2">
+        <f t="shared" si="2"/>
+        <v>48</v>
+      </c>
+      <c r="B52" s="2">
+        <f>COUNTIF($C$1:C52,C52)</f>
+        <v>48</v>
+      </c>
+      <c r="C52" s="2">
+        <v>0</v>
+      </c>
+      <c r="D52" s="2">
+        <f t="shared" si="3"/>
+        <v>100048</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="G52" s="2">
+        <v>200035</v>
+      </c>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+    </row>
+    <row r="53" s="1" customFormat="1" spans="1:11">
+      <c r="A53" s="2">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="B53" s="2">
+        <f>COUNTIF($C$1:C53,C53)</f>
+        <v>49</v>
+      </c>
+      <c r="C53" s="2">
+        <v>0</v>
+      </c>
+      <c r="D53" s="2">
+        <f t="shared" si="3"/>
+        <v>100049</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="G53" s="2">
+        <v>200036</v>
+      </c>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:11">
+      <c r="A54" s="2">
+        <f t="shared" si="2"/>
+        <v>50</v>
+      </c>
+      <c r="B54" s="2">
+        <f>COUNTIF($C$1:C54,C54)</f>
+        <v>50</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0</v>
+      </c>
+      <c r="D54" s="2">
+        <f t="shared" si="3"/>
+        <v>100050</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G54" s="2">
+        <v>200037</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:11">
+      <c r="A55" s="2">
+        <f t="shared" si="2"/>
+        <v>51</v>
+      </c>
+      <c r="B55" s="2">
+        <f>COUNTIF($C$1:C55,C55)</f>
+        <v>51</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2">
+        <f t="shared" si="3"/>
+        <v>100051</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G55" s="2">
+        <v>200038</v>
+      </c>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:11">
+      <c r="A56" s="2">
+        <f t="shared" si="2"/>
+        <v>52</v>
+      </c>
+      <c r="B56" s="2">
+        <f>COUNTIF($C$1:C56,C56)</f>
+        <v>52</v>
+      </c>
+      <c r="C56" s="2">
+        <v>0</v>
+      </c>
+      <c r="D56" s="2">
+        <f t="shared" si="3"/>
+        <v>100052</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="G56" s="2">
+        <v>200039</v>
+      </c>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+    </row>
+    <row r="57" spans="1:11">
+      <c r="A57" s="1">
+        <f>C57*1000+B57</f>
         <v>1001</v>
       </c>
-      <c r="B44">
-        <f>COUNTIF($C$1:C44,C44)</f>
+      <c r="B57" s="1">
+        <f>COUNTIF($C$1:C57,C57)</f>
         <v>1</v>
       </c>
-      <c r="C44">
+      <c r="C57" s="1">
         <v>1</v>
       </c>
-      <c r="D44" s="1">
+      <c r="D57" s="1">
         <f t="shared" si="3"/>
         <v>101001</v>
       </c>
-      <c r="E44" t="s">
-        <v>91</v>
-      </c>
-      <c r="F44" t="s">
-        <v>92</v>
-      </c>
-      <c r="G44">
+      <c r="E57" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="F57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="G57" s="1">
         <v>201001</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45">
-        <f t="shared" si="4"/>
+    <row r="58" spans="1:11">
+      <c r="A58" s="1">
+        <f t="shared" si="2"/>
         <v>1002</v>
       </c>
-      <c r="B45">
-        <f>COUNTIF($C$1:C45,C45)</f>
+      <c r="B58" s="1">
+        <f>COUNTIF($C$1:C58,C58)</f>
         <v>2</v>
       </c>
-      <c r="C45">
+      <c r="C58" s="1">
         <v>1</v>
       </c>
-      <c r="D45" s="1">
+      <c r="D58" s="1">
         <f t="shared" si="3"/>
         <v>101002</v>
       </c>
-      <c r="E45" t="s">
-        <v>93</v>
-      </c>
-      <c r="F45" t="s">
-        <v>94</v>
-      </c>
-      <c r="G45">
+      <c r="E58" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="G58" s="1">
         <v>201002</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46">
-        <f t="shared" si="4"/>
+      <c r="H58" s="1">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
+      <c r="A59" s="1">
+        <f t="shared" si="2"/>
         <v>1003</v>
       </c>
-      <c r="B46">
-        <f>COUNTIF($C$1:C46,C46)</f>
+      <c r="B59" s="1">
+        <f>COUNTIF($C$1:C59,C59)</f>
         <v>3</v>
       </c>
-      <c r="C46">
+      <c r="C59" s="1">
         <v>1</v>
       </c>
-      <c r="D46" s="1">
+      <c r="D59" s="1">
         <f t="shared" si="3"/>
         <v>101003</v>
       </c>
-      <c r="E46" t="s">
-        <v>95</v>
-      </c>
-      <c r="F46" t="s">
-        <v>96</v>
-      </c>
-      <c r="G46">
+      <c r="E59" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="G59" s="1">
         <v>201003</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47">
-        <f t="shared" si="4"/>
+      <c r="J59" s="1">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
+      <c r="A60" s="1">
+        <f t="shared" si="2"/>
         <v>1004</v>
       </c>
-      <c r="B47">
-        <f>COUNTIF($C$1:C47,C47)</f>
+      <c r="B60" s="1">
+        <f>COUNTIF($C$1:C60,C60)</f>
         <v>4</v>
       </c>
-      <c r="C47">
+      <c r="C60" s="1">
         <v>1</v>
       </c>
-      <c r="D47" s="1">
+      <c r="D60" s="1">
         <f t="shared" si="3"/>
         <v>101004</v>
       </c>
-      <c r="E47" t="s">
-        <v>97</v>
-      </c>
-      <c r="F47" t="s">
-        <v>98</v>
-      </c>
-      <c r="G47">
+      <c r="E60" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="F60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G60" s="1">
         <v>201004</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48">
-        <f t="shared" si="4"/>
+      <c r="J60" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
+      <c r="A61" s="1">
+        <f t="shared" ref="A61:A63" si="4">C61*1000+B61</f>
         <v>1005</v>
       </c>
-      <c r="B48">
-        <f>COUNTIF($C$1:C48,C48)</f>
+      <c r="B61" s="1">
+        <f>COUNTIF($C$1:C61,C61)</f>
         <v>5</v>
       </c>
-      <c r="C48">
+      <c r="C61" s="1">
         <v>1</v>
       </c>
-      <c r="D48" s="1">
+      <c r="D61" s="1">
         <f t="shared" si="3"/>
         <v>101005</v>
       </c>
-      <c r="E48" t="s">
-        <v>99</v>
-      </c>
-      <c r="F48" t="s">
-        <v>100</v>
-      </c>
-      <c r="G48">
+      <c r="E61" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="F61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="G61" s="1">
         <v>201005</v>
       </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49">
+      <c r="J61" s="1">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="62" s="1" customFormat="1" spans="1:11">
+      <c r="A62" s="1">
         <f t="shared" si="4"/>
         <v>1006</v>
       </c>
-      <c r="B49">
-        <f>COUNTIF($C$1:C49,C49)</f>
+      <c r="B62" s="1">
+        <f>COUNTIF($C$1:C62,C62)</f>
         <v>6</v>
       </c>
-      <c r="C49">
+      <c r="C62" s="1">
         <v>1</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D62" s="1">
         <f t="shared" si="3"/>
         <v>101006</v>
       </c>
-      <c r="E49" t="s">
-        <v>101</v>
-      </c>
-      <c r="F49" t="s">
-        <v>102</v>
-      </c>
-      <c r="G49">
-        <v>201006</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50">
+      <c r="E62" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="G62" s="1">
+        <v>201801</v>
+      </c>
+      <c r="K62" s="1">
+        <v>56008</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="1:11">
+      <c r="A63" s="1">
         <f t="shared" si="4"/>
         <v>1007</v>
       </c>
-      <c r="B50">
-        <f>COUNTIF($C$1:C50,C50)</f>
+      <c r="B63" s="1">
+        <f>COUNTIF($C$1:C63,C63)</f>
         <v>7</v>
       </c>
-      <c r="C50">
+      <c r="C63" s="1">
         <v>1</v>
       </c>
-      <c r="D50" s="1">
+      <c r="D63" s="1">
         <f t="shared" si="3"/>
         <v>101007</v>
       </c>
-      <c r="E50" t="s">
-        <v>103</v>
-      </c>
-      <c r="F50" t="s">
-        <v>104</v>
-      </c>
-      <c r="G50">
-        <v>201007</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19">
-      <c r="A51">
-        <f t="shared" si="4"/>
+      <c r="E63" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="G63" s="1">
+        <v>201802</v>
+      </c>
+      <c r="K63" s="1">
+        <v>57011</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" spans="1:11">
+      <c r="A64" s="2">
+        <f t="shared" ref="A64:A76" si="5">C64*1000+B64</f>
         <v>1008</v>
-      </c>
-      <c r="B51">
-        <f>COUNTIF($C$1:C51,C51)</f>
-        <v>8</v>
-      </c>
-      <c r="C51">
-        <v>1</v>
-      </c>
-      <c r="D51" s="1">
-        <f t="shared" si="3"/>
-        <v>101008</v>
-      </c>
-      <c r="E51" t="s">
-        <v>105</v>
-      </c>
-      <c r="F51" t="s">
-        <v>106</v>
-      </c>
-      <c r="G51">
-        <v>201008</v>
-      </c>
-      <c r="S51" s="1"/>
-    </row>
-    <row r="52" spans="1:19">
-      <c r="A52">
-        <f t="shared" si="4"/>
-        <v>1009</v>
-      </c>
-      <c r="B52">
-        <f>COUNTIF($C$1:C52,C52)</f>
-        <v>9</v>
-      </c>
-      <c r="C52">
-        <v>1</v>
-      </c>
-      <c r="D52" s="1">
-        <f t="shared" si="3"/>
-        <v>101009</v>
-      </c>
-      <c r="E52" t="s">
-        <v>107</v>
-      </c>
-      <c r="F52" t="s">
-        <v>108</v>
-      </c>
-      <c r="G52">
-        <v>201009</v>
-      </c>
-      <c r="S52" s="1"/>
-    </row>
-    <row r="53" spans="1:19">
-      <c r="A53">
-        <f t="shared" si="4"/>
-        <v>1010</v>
-      </c>
-      <c r="B53">
-        <f>COUNTIF($C$1:C53,C53)</f>
-        <v>10</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" s="1">
-        <f t="shared" si="3"/>
-        <v>101010</v>
-      </c>
-      <c r="E53" t="s">
-        <v>109</v>
-      </c>
-      <c r="F53" t="s">
-        <v>110</v>
-      </c>
-      <c r="G53">
-        <v>201010</v>
-      </c>
-      <c r="H53" s="7"/>
-      <c r="I53" s="7"/>
-      <c r="K53" s="1"/>
-      <c r="S53" s="1"/>
-    </row>
-    <row r="54" spans="1:19">
-      <c r="A54">
-        <f t="shared" si="4"/>
-        <v>1011</v>
-      </c>
-      <c r="B54">
-        <f>COUNTIF($C$1:C54,C54)</f>
-        <v>11</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54" s="1">
-        <f t="shared" si="3"/>
-        <v>101011</v>
-      </c>
-      <c r="E54" t="s">
-        <v>111</v>
-      </c>
-      <c r="F54" t="s">
-        <v>112</v>
-      </c>
-      <c r="G54">
-        <v>201011</v>
-      </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="7"/>
-      <c r="K54" s="1"/>
-      <c r="S54" s="1"/>
-    </row>
-    <row r="55" spans="1:19">
-      <c r="A55">
-        <f t="shared" si="4"/>
-        <v>1012</v>
-      </c>
-      <c r="B55">
-        <f>COUNTIF($C$1:C55,C55)</f>
-        <v>12</v>
-      </c>
-      <c r="C55">
-        <v>1</v>
-      </c>
-      <c r="D55" s="1">
-        <f t="shared" si="3"/>
-        <v>101012</v>
-      </c>
-      <c r="E55" t="s">
-        <v>113</v>
-      </c>
-      <c r="F55" t="s">
-        <v>114</v>
-      </c>
-      <c r="G55">
-        <v>201012</v>
-      </c>
-      <c r="H55" s="7"/>
-      <c r="I55" s="7"/>
-      <c r="K55" s="1"/>
-      <c r="S55" s="1"/>
-    </row>
-    <row r="56" spans="1:19">
-      <c r="A56">
-        <f t="shared" si="4"/>
-        <v>1013</v>
-      </c>
-      <c r="B56">
-        <f>COUNTIF($C$1:C56,C56)</f>
-        <v>13</v>
-      </c>
-      <c r="C56">
-        <v>1</v>
-      </c>
-      <c r="D56" s="1">
-        <f t="shared" si="3"/>
-        <v>101013</v>
-      </c>
-      <c r="E56" t="s">
-        <v>115</v>
-      </c>
-      <c r="F56" t="s">
-        <v>116</v>
-      </c>
-      <c r="G56">
-        <v>201013</v>
-      </c>
-      <c r="H56" s="7"/>
-      <c r="I56" s="7"/>
-      <c r="K56" s="1"/>
-      <c r="S56" s="1"/>
-    </row>
-    <row r="57" spans="1:19">
-      <c r="A57">
-        <f t="shared" si="4"/>
-        <v>1014</v>
-      </c>
-      <c r="B57">
-        <f>COUNTIF($C$1:C57,C57)</f>
-        <v>14</v>
-      </c>
-      <c r="C57">
-        <v>1</v>
-      </c>
-      <c r="D57" s="1">
-        <f t="shared" si="3"/>
-        <v>101014</v>
-      </c>
-      <c r="E57" t="s">
-        <v>117</v>
-      </c>
-      <c r="F57" t="s">
-        <v>118</v>
-      </c>
-      <c r="G57">
-        <v>201014</v>
-      </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="7"/>
-      <c r="K57" s="1"/>
-      <c r="S57" s="1"/>
-    </row>
-    <row r="58" spans="1:19">
-      <c r="A58">
-        <f t="shared" si="4"/>
-        <v>1015</v>
-      </c>
-      <c r="B58">
-        <f>COUNTIF($C$1:C58,C58)</f>
-        <v>15</v>
-      </c>
-      <c r="C58">
-        <v>1</v>
-      </c>
-      <c r="D58" s="1">
-        <f t="shared" si="3"/>
-        <v>101015</v>
-      </c>
-      <c r="E58" t="s">
-        <v>119</v>
-      </c>
-      <c r="F58" t="s">
-        <v>120</v>
-      </c>
-      <c r="G58">
-        <v>201015</v>
-      </c>
-      <c r="H58" s="7"/>
-      <c r="I58" s="7"/>
-      <c r="K58" s="1"/>
-      <c r="S58" s="1"/>
-    </row>
-    <row r="59" spans="1:19">
-      <c r="A59">
-        <f t="shared" si="4"/>
-        <v>1016</v>
-      </c>
-      <c r="B59">
-        <f>COUNTIF($C$1:C59,C59)</f>
-        <v>16</v>
-      </c>
-      <c r="C59">
-        <v>1</v>
-      </c>
-      <c r="D59" s="1">
-        <f t="shared" si="3"/>
-        <v>101016</v>
-      </c>
-      <c r="E59" t="s">
-        <v>121</v>
-      </c>
-      <c r="F59" t="s">
-        <v>122</v>
-      </c>
-      <c r="G59">
-        <v>201016</v>
-      </c>
-      <c r="H59" s="7"/>
-      <c r="I59" s="7"/>
-      <c r="K59" s="1"/>
-      <c r="S59" s="1"/>
-    </row>
-    <row r="60" spans="1:19">
-      <c r="A60">
-        <f t="shared" si="4"/>
-        <v>1017</v>
-      </c>
-      <c r="B60">
-        <f>COUNTIF($C$1:C60,C60)</f>
-        <v>17</v>
-      </c>
-      <c r="C60">
-        <v>1</v>
-      </c>
-      <c r="D60" s="1">
-        <f t="shared" si="3"/>
-        <v>101017</v>
-      </c>
-      <c r="E60" t="s">
-        <v>123</v>
-      </c>
-      <c r="F60" t="s">
-        <v>124</v>
-      </c>
-      <c r="G60">
-        <v>201017</v>
-      </c>
-      <c r="H60" s="7"/>
-      <c r="I60" s="7"/>
-      <c r="K60" s="1"/>
-      <c r="S60" s="1"/>
-    </row>
-    <row r="61" spans="1:19">
-      <c r="A61">
-        <f t="shared" si="4"/>
-        <v>1018</v>
-      </c>
-      <c r="B61">
-        <f>COUNTIF($C$1:C61,C61)</f>
-        <v>18</v>
-      </c>
-      <c r="C61">
-        <v>1</v>
-      </c>
-      <c r="D61" s="1">
-        <f t="shared" si="3"/>
-        <v>101018</v>
-      </c>
-      <c r="E61" t="s">
-        <v>125</v>
-      </c>
-      <c r="F61" t="s">
-        <v>126</v>
-      </c>
-      <c r="G61">
-        <v>201018</v>
-      </c>
-      <c r="H61" s="7"/>
-      <c r="I61" s="7"/>
-      <c r="K61" s="1"/>
-      <c r="S61" s="1"/>
-    </row>
-    <row r="62" customFormat="1" spans="1:19">
-      <c r="A62">
-        <f>C62*1000+B62</f>
-        <v>1801</v>
-      </c>
-      <c r="B62">
-        <v>801</v>
-      </c>
-      <c r="C62">
-        <v>1</v>
-      </c>
-      <c r="D62" s="1">
-        <f>100000+C62*1000+B62</f>
-        <v>101801</v>
-      </c>
-      <c r="E62" t="s">
-        <v>127</v>
-      </c>
-      <c r="F62" t="s">
-        <v>128</v>
-      </c>
-      <c r="G62">
-        <v>201801</v>
-      </c>
-      <c r="H62" s="7"/>
-      <c r="I62" s="7"/>
-      <c r="K62" s="1"/>
-      <c r="S62" s="1"/>
-    </row>
-    <row r="63" customFormat="1" spans="1:19">
-      <c r="A63">
-        <f>C63*1000+B63</f>
-        <v>1802</v>
-      </c>
-      <c r="B63">
-        <v>802</v>
-      </c>
-      <c r="C63">
-        <v>1</v>
-      </c>
-      <c r="D63" s="1">
-        <f>100000+C63*1000+B63</f>
-        <v>101802</v>
-      </c>
-      <c r="E63" t="s">
-        <v>129</v>
-      </c>
-      <c r="F63" t="s">
-        <v>126</v>
-      </c>
-      <c r="G63">
-        <v>201802</v>
-      </c>
-      <c r="H63" s="7"/>
-      <c r="I63" s="7"/>
-      <c r="K63" s="1"/>
-      <c r="S63" s="1"/>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:19">
-      <c r="A64" s="2">
-        <f>C64*1000+B64</f>
-        <v>2001</v>
       </c>
       <c r="B64" s="2">
         <f>COUNTIF($C$1:C64,C64)</f>
+        <v>8</v>
+      </c>
+      <c r="C64" s="2">
         <v>1</v>
       </c>
-      <c r="C64" s="2">
-        <v>2</v>
-      </c>
-      <c r="D64" s="1">
-        <f t="shared" ref="D64:D95" si="5">100000+C64*1000+B64</f>
-        <v>102001</v>
+      <c r="D64" s="2">
+        <f>100000+C64*1000+B64</f>
+        <v>101008</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="G64" s="2">
-        <v>202001</v>
+        <v>201006</v>
       </c>
       <c r="H64" s="2"/>
-      <c r="K64" s="8"/>
-      <c r="M64"/>
-      <c r="N64"/>
-      <c r="O64"/>
-      <c r="S64" s="1"/>
-    </row>
-    <row r="65" s="2" customFormat="1" spans="1:19">
+      <c r="I64" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" spans="1:11">
       <c r="A65" s="2">
-        <f>C65*1000+B65</f>
-        <v>2002</v>
+        <f t="shared" si="5"/>
+        <v>1009</v>
       </c>
       <c r="B65" s="2">
         <f>COUNTIF($C$1:C65,C65)</f>
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="C65" s="2">
-        <v>2</v>
-      </c>
-      <c r="D65" s="1">
+        <v>1</v>
+      </c>
+      <c r="D65" s="2">
+        <f>100000+C65*1000+B65</f>
+        <v>101009</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G65" s="2">
+        <v>201007</v>
+      </c>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="1:11">
+      <c r="A66" s="2">
         <f t="shared" si="5"/>
-        <v>102002</v>
-      </c>
-      <c r="E65" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="F65" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="G65" s="2">
-        <v>202002</v>
-      </c>
-      <c r="H65" s="2"/>
-      <c r="K65" s="8"/>
-      <c r="M65"/>
-      <c r="N65"/>
-      <c r="O65"/>
-      <c r="S65" s="1"/>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:19">
-      <c r="A66" s="2">
-        <f t="shared" ref="A66:A95" si="6">C66*1000+B66</f>
-        <v>2003</v>
+        <v>1010</v>
       </c>
       <c r="B66" s="2">
         <f>COUNTIF($C$1:C66,C66)</f>
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="C66" s="2">
-        <v>2</v>
-      </c>
-      <c r="D66" s="1">
+        <v>1</v>
+      </c>
+      <c r="D66" s="2">
+        <f>100000+C66*1000+B66</f>
+        <v>101010</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="G66" s="2">
+        <v>201008</v>
+      </c>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" spans="1:11">
+      <c r="A67" s="2">
         <f t="shared" si="5"/>
-        <v>102003</v>
-      </c>
-      <c r="E66" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F66" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="G66" s="2">
-        <v>202003</v>
-      </c>
-      <c r="H66" s="2"/>
-      <c r="K66" s="8"/>
-      <c r="M66"/>
-      <c r="N66"/>
-      <c r="O66"/>
-      <c r="S66" s="1"/>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="1:19">
-      <c r="A67" s="2">
-        <f t="shared" si="6"/>
-        <v>2004</v>
+        <v>1011</v>
       </c>
       <c r="B67" s="2">
         <f>COUNTIF($C$1:C67,C67)</f>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="C67" s="2">
-        <v>2</v>
-      </c>
-      <c r="D67" s="1">
+        <v>1</v>
+      </c>
+      <c r="D67" s="2">
+        <f>100000+C67*1000+B67</f>
+        <v>101011</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G67" s="2">
+        <v>201009</v>
+      </c>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" spans="1:11">
+      <c r="A68" s="2">
         <f t="shared" si="5"/>
-        <v>102004</v>
-      </c>
-      <c r="E67" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="F67" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G67" s="2">
-        <v>202004</v>
-      </c>
-      <c r="H67" s="2"/>
-      <c r="K67" s="8"/>
-      <c r="M67"/>
-      <c r="N67"/>
-      <c r="O67"/>
-      <c r="S67" s="1"/>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:19">
-      <c r="A68" s="2">
-        <f t="shared" si="6"/>
-        <v>2005</v>
+        <v>1012</v>
       </c>
       <c r="B68" s="2">
         <f>COUNTIF($C$1:C68,C68)</f>
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C68" s="2">
-        <v>2</v>
-      </c>
-      <c r="D68" s="1">
+        <v>1</v>
+      </c>
+      <c r="D68" s="2">
+        <f>100000+C68*1000+B68</f>
+        <v>101012</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="G68" s="2">
+        <v>201010</v>
+      </c>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:11">
+      <c r="A69" s="2">
         <f t="shared" si="5"/>
-        <v>102005</v>
-      </c>
-      <c r="E68" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F68" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="G68" s="2">
-        <v>202005</v>
-      </c>
-      <c r="H68" s="2"/>
-      <c r="K68" s="8"/>
-      <c r="M68"/>
-      <c r="N68"/>
-      <c r="O68"/>
-      <c r="S68" s="1"/>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:19">
-      <c r="A69" s="2">
-        <f t="shared" si="6"/>
-        <v>2006</v>
+        <v>1013</v>
       </c>
       <c r="B69" s="2">
         <f>COUNTIF($C$1:C69,C69)</f>
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C69" s="2">
-        <v>2</v>
-      </c>
-      <c r="D69" s="1">
+        <v>1</v>
+      </c>
+      <c r="D69" s="2">
+        <f>100000+C69*1000+B69</f>
+        <v>101013</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="G69" s="2">
+        <v>201011</v>
+      </c>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:11">
+      <c r="A70" s="2">
         <f t="shared" si="5"/>
-        <v>102006</v>
-      </c>
-      <c r="E69" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="G69" s="2">
-        <v>202006</v>
-      </c>
-      <c r="H69" s="2"/>
-      <c r="K69" s="8"/>
-      <c r="M69"/>
-      <c r="N69"/>
-      <c r="O69"/>
-      <c r="S69" s="1"/>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:19">
-      <c r="A70" s="2">
-        <f t="shared" si="6"/>
-        <v>2007</v>
+        <v>1014</v>
       </c>
       <c r="B70" s="2">
         <f>COUNTIF($C$1:C70,C70)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C70" s="2">
-        <v>2</v>
-      </c>
-      <c r="D70" s="1">
+        <v>1</v>
+      </c>
+      <c r="D70" s="2">
+        <f>100000+C70*1000+B70</f>
+        <v>101014</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="G70" s="2">
+        <v>201012</v>
+      </c>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" spans="1:11">
+      <c r="A71" s="2">
         <f t="shared" si="5"/>
-        <v>102007</v>
-      </c>
-      <c r="E70" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="F70" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G70" s="2">
-        <v>202007</v>
-      </c>
-      <c r="H70" s="2"/>
-      <c r="K70" s="8"/>
-      <c r="M70"/>
-      <c r="N70"/>
-      <c r="O70"/>
-      <c r="S70" s="1"/>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:19">
-      <c r="A71" s="2">
-        <f t="shared" si="6"/>
-        <v>2008</v>
+        <v>1015</v>
       </c>
       <c r="B71" s="2">
         <f>COUNTIF($C$1:C71,C71)</f>
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="C71" s="2">
-        <v>2</v>
-      </c>
-      <c r="D71" s="1">
+        <v>1</v>
+      </c>
+      <c r="D71" s="2">
+        <f>100000+C71*1000+B71</f>
+        <v>101015</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="G71" s="2">
+        <v>201013</v>
+      </c>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:11">
+      <c r="A72" s="2">
         <f t="shared" si="5"/>
-        <v>102008</v>
-      </c>
-      <c r="E71" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G71" s="2">
-        <v>202008</v>
-      </c>
-      <c r="H71" s="2"/>
-      <c r="K71" s="8"/>
-      <c r="M71"/>
-      <c r="N71"/>
-      <c r="O71"/>
-      <c r="S71" s="1"/>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:19">
-      <c r="A72" s="2">
-        <f t="shared" si="6"/>
-        <v>2009</v>
+        <v>1016</v>
       </c>
       <c r="B72" s="2">
         <f>COUNTIF($C$1:C72,C72)</f>
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C72" s="2">
-        <v>2</v>
-      </c>
-      <c r="D72" s="1">
+        <v>1</v>
+      </c>
+      <c r="D72" s="2">
+        <f>100000+C72*1000+B72</f>
+        <v>101016</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="G72" s="2">
+        <v>201014</v>
+      </c>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" spans="1:11">
+      <c r="A73" s="2">
         <f t="shared" si="5"/>
-        <v>102009</v>
-      </c>
-      <c r="E72" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F72" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="G72" s="2">
-        <v>202009</v>
-      </c>
-      <c r="H72" s="2"/>
-      <c r="K72" s="8"/>
-      <c r="M72"/>
-      <c r="N72"/>
-      <c r="O72"/>
-      <c r="S72" s="1"/>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:19">
-      <c r="A73" s="2">
-        <f t="shared" si="6"/>
-        <v>2010</v>
+        <v>1017</v>
       </c>
       <c r="B73" s="2">
         <f>COUNTIF($C$1:C73,C73)</f>
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="C73" s="2">
-        <v>2</v>
-      </c>
-      <c r="D73" s="1">
+        <v>1</v>
+      </c>
+      <c r="D73" s="2">
+        <f>100000+C73*1000+B73</f>
+        <v>101017</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="G73" s="2">
+        <v>201015</v>
+      </c>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" spans="1:11">
+      <c r="A74" s="2">
         <f t="shared" si="5"/>
-        <v>102010</v>
-      </c>
-      <c r="E73" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="F73" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="G73" s="2">
-        <v>202010</v>
-      </c>
-      <c r="H73" s="2"/>
-      <c r="K73" s="8"/>
-      <c r="M73"/>
-      <c r="N73"/>
-      <c r="O73"/>
-      <c r="S73" s="1"/>
-    </row>
-    <row r="74" s="2" customFormat="1" spans="1:19">
-      <c r="A74" s="2">
-        <f t="shared" si="6"/>
-        <v>2011</v>
+        <v>1018</v>
       </c>
       <c r="B74" s="2">
         <f>COUNTIF($C$1:C74,C74)</f>
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C74" s="2">
-        <v>2</v>
-      </c>
-      <c r="D74" s="1">
+        <v>1</v>
+      </c>
+      <c r="D74" s="2">
+        <f>100000+C74*1000+B74</f>
+        <v>101018</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="G74" s="2">
+        <v>201016</v>
+      </c>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" spans="1:11">
+      <c r="A75" s="2">
         <f t="shared" si="5"/>
-        <v>102011</v>
-      </c>
-      <c r="E74" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="G74" s="2">
-        <v>202011</v>
-      </c>
-      <c r="H74" s="2"/>
-      <c r="K74" s="8"/>
-      <c r="M74"/>
-      <c r="N74"/>
-      <c r="O74"/>
-      <c r="S74" s="1"/>
-    </row>
-    <row r="75" s="2" customFormat="1" spans="1:19">
-      <c r="A75" s="2">
-        <f t="shared" si="6"/>
-        <v>2012</v>
+        <v>1019</v>
       </c>
       <c r="B75" s="2">
         <f>COUNTIF($C$1:C75,C75)</f>
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="C75" s="2">
-        <v>2</v>
-      </c>
-      <c r="D75" s="1">
+        <v>1</v>
+      </c>
+      <c r="D75" s="2">
+        <f>100000+C75*1000+B75</f>
+        <v>101019</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="G75" s="2">
+        <v>201017</v>
+      </c>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" spans="1:11">
+      <c r="A76" s="2">
         <f t="shared" si="5"/>
-        <v>102012</v>
-      </c>
-      <c r="E75" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="F75" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="G75" s="2">
-        <v>202012</v>
-      </c>
-      <c r="H75" s="2"/>
-      <c r="K75" s="8"/>
-      <c r="M75"/>
-      <c r="N75"/>
-      <c r="O75"/>
-      <c r="S75" s="1"/>
-    </row>
-    <row r="76" s="2" customFormat="1" spans="1:19">
-      <c r="A76" s="2">
-        <f t="shared" si="6"/>
-        <v>2013</v>
+        <v>1020</v>
       </c>
       <c r="B76" s="2">
         <f>COUNTIF($C$1:C76,C76)</f>
+        <v>20</v>
+      </c>
+      <c r="C76" s="2">
+        <v>1</v>
+      </c>
+      <c r="D76" s="2">
+        <f>100000+C76*1000+B76</f>
+        <v>101020</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="G76" s="2">
+        <v>201018</v>
+      </c>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:11">
+      <c r="A77" s="1">
+        <f>C77*1000+B77</f>
+        <v>2001</v>
+      </c>
+      <c r="B77" s="1">
+        <f>COUNTIF($C$1:C77,C77)</f>
+        <v>1</v>
+      </c>
+      <c r="C77" s="1">
+        <v>2</v>
+      </c>
+      <c r="D77" s="1">
+        <f t="shared" ref="D77:D108" si="6">100000+C77*1000+B77</f>
+        <v>102001</v>
+      </c>
+      <c r="E77" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F77" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G77" s="1">
+        <v>202001</v>
+      </c>
+      <c r="K77" s="3"/>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:11">
+      <c r="A78" s="1">
+        <f>C78*1000+B78</f>
+        <v>2002</v>
+      </c>
+      <c r="B78" s="1">
+        <f>COUNTIF($C$1:C78,C78)</f>
+        <v>2</v>
+      </c>
+      <c r="C78" s="1">
+        <v>2</v>
+      </c>
+      <c r="D78" s="1">
+        <f t="shared" si="6"/>
+        <v>102002</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>178</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="G78" s="1">
+        <v>202002</v>
+      </c>
+      <c r="K78" s="3"/>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="1:11">
+      <c r="A79" s="1">
+        <f t="shared" ref="A79:A108" si="7">C79*1000+B79</f>
+        <v>2003</v>
+      </c>
+      <c r="B79" s="1">
+        <f>COUNTIF($C$1:C79,C79)</f>
+        <v>3</v>
+      </c>
+      <c r="C79" s="1">
+        <v>2</v>
+      </c>
+      <c r="D79" s="1">
+        <f t="shared" si="6"/>
+        <v>102003</v>
+      </c>
+      <c r="E79" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="F79" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="G79" s="1">
+        <v>202003</v>
+      </c>
+      <c r="K79" s="3"/>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="1:11">
+      <c r="A80" s="1">
+        <f t="shared" si="7"/>
+        <v>2004</v>
+      </c>
+      <c r="B80" s="1">
+        <f>COUNTIF($C$1:C80,C80)</f>
+        <v>4</v>
+      </c>
+      <c r="C80" s="1">
+        <v>2</v>
+      </c>
+      <c r="D80" s="1">
+        <f t="shared" si="6"/>
+        <v>102004</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="G80" s="1">
+        <v>202004</v>
+      </c>
+      <c r="K80" s="3"/>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="1:11">
+      <c r="A81" s="1">
+        <f t="shared" si="7"/>
+        <v>2005</v>
+      </c>
+      <c r="B81" s="1">
+        <f>COUNTIF($C$1:C81,C81)</f>
+        <v>5</v>
+      </c>
+      <c r="C81" s="1">
+        <v>2</v>
+      </c>
+      <c r="D81" s="1">
+        <f t="shared" si="6"/>
+        <v>102005</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F81" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G81" s="1">
+        <v>202005</v>
+      </c>
+      <c r="K81" s="3"/>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="1:11">
+      <c r="A82" s="1">
+        <f t="shared" si="7"/>
+        <v>2006</v>
+      </c>
+      <c r="B82" s="1">
+        <f>COUNTIF($C$1:C82,C82)</f>
+        <v>6</v>
+      </c>
+      <c r="C82" s="1">
+        <v>2</v>
+      </c>
+      <c r="D82" s="1">
+        <f t="shared" si="6"/>
+        <v>102006</v>
+      </c>
+      <c r="E82" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="F82" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="G82" s="1">
+        <v>202006</v>
+      </c>
+      <c r="K82" s="3"/>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="1:11">
+      <c r="A83" s="1">
+        <f t="shared" si="7"/>
+        <v>2007</v>
+      </c>
+      <c r="B83" s="1">
+        <f>COUNTIF($C$1:C83,C83)</f>
+        <v>7</v>
+      </c>
+      <c r="C83" s="1">
+        <v>2</v>
+      </c>
+      <c r="D83" s="1">
+        <f t="shared" si="6"/>
+        <v>102007</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="G83" s="1">
+        <v>202007</v>
+      </c>
+      <c r="K83" s="3"/>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="1:11">
+      <c r="A84" s="1">
+        <f t="shared" si="7"/>
+        <v>2008</v>
+      </c>
+      <c r="B84" s="1">
+        <f>COUNTIF($C$1:C84,C84)</f>
+        <v>8</v>
+      </c>
+      <c r="C84" s="1">
+        <v>2</v>
+      </c>
+      <c r="D84" s="1">
+        <f t="shared" si="6"/>
+        <v>102008</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G84" s="1">
+        <v>202008</v>
+      </c>
+      <c r="K84" s="3"/>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="1:11">
+      <c r="A85" s="1">
+        <f t="shared" si="7"/>
+        <v>2009</v>
+      </c>
+      <c r="B85" s="1">
+        <f>COUNTIF($C$1:C85,C85)</f>
+        <v>9</v>
+      </c>
+      <c r="C85" s="1">
+        <v>2</v>
+      </c>
+      <c r="D85" s="1">
+        <f t="shared" si="6"/>
+        <v>102009</v>
+      </c>
+      <c r="E85" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="F85" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="G85" s="1">
+        <v>202009</v>
+      </c>
+      <c r="K85" s="3"/>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="1:11">
+      <c r="A86" s="1">
+        <f t="shared" si="7"/>
+        <v>2010</v>
+      </c>
+      <c r="B86" s="1">
+        <f>COUNTIF($C$1:C86,C86)</f>
+        <v>10</v>
+      </c>
+      <c r="C86" s="1">
+        <v>2</v>
+      </c>
+      <c r="D86" s="1">
+        <f t="shared" si="6"/>
+        <v>102010</v>
+      </c>
+      <c r="E86" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="F86" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G86" s="1">
+        <v>202010</v>
+      </c>
+      <c r="K86" s="3"/>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="1:11">
+      <c r="A87" s="1">
+        <f t="shared" si="7"/>
+        <v>2011</v>
+      </c>
+      <c r="B87" s="1">
+        <f>COUNTIF($C$1:C87,C87)</f>
+        <v>11</v>
+      </c>
+      <c r="C87" s="1">
+        <v>2</v>
+      </c>
+      <c r="D87" s="1">
+        <f t="shared" si="6"/>
+        <v>102011</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F87" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="G87" s="1">
+        <v>202011</v>
+      </c>
+      <c r="K87" s="3"/>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="1:11">
+      <c r="A88" s="1">
+        <f t="shared" si="7"/>
+        <v>2012</v>
+      </c>
+      <c r="B88" s="1">
+        <f>COUNTIF($C$1:C88,C88)</f>
+        <v>12</v>
+      </c>
+      <c r="C88" s="1">
+        <v>2</v>
+      </c>
+      <c r="D88" s="1">
+        <f t="shared" si="6"/>
+        <v>102012</v>
+      </c>
+      <c r="E88" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="F88" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="G88" s="1">
+        <v>202012</v>
+      </c>
+      <c r="K88" s="3"/>
+    </row>
+    <row r="89" s="1" customFormat="1" spans="1:11">
+      <c r="A89" s="1">
+        <f t="shared" si="7"/>
+        <v>2013</v>
+      </c>
+      <c r="B89" s="1">
+        <f>COUNTIF($C$1:C89,C89)</f>
         <v>13</v>
       </c>
-      <c r="C76" s="2">
+      <c r="C89" s="1">
         <v>2</v>
       </c>
-      <c r="D76" s="1">
-        <f t="shared" si="5"/>
+      <c r="D89" s="1">
+        <f t="shared" si="6"/>
         <v>102013</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="G76" s="2">
+      <c r="E89" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="F89" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="G89" s="1">
         <v>202013</v>
       </c>
-      <c r="H76" s="2"/>
-      <c r="K76" s="8"/>
-      <c r="M76"/>
-      <c r="N76"/>
-      <c r="O76"/>
-      <c r="S76" s="1"/>
-    </row>
-    <row r="77" s="2" customFormat="1" spans="1:19">
-      <c r="A77" s="2">
+      <c r="K89" s="3"/>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="1:11">
+      <c r="A90" s="1">
+        <f t="shared" si="7"/>
+        <v>2014</v>
+      </c>
+      <c r="B90" s="1">
+        <f>COUNTIF($C$1:C90,C90)</f>
+        <v>14</v>
+      </c>
+      <c r="C90" s="1">
+        <v>2</v>
+      </c>
+      <c r="D90" s="1">
         <f t="shared" si="6"/>
-        <v>2014</v>
-      </c>
-      <c r="B77" s="2">
-        <f>COUNTIF($C$1:C77,C77)</f>
-        <v>14</v>
-      </c>
-      <c r="C77" s="2">
+        <v>102014</v>
+      </c>
+      <c r="E90" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="F90" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="G90" s="1">
+        <v>202014</v>
+      </c>
+      <c r="K90" s="3"/>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="1:11">
+      <c r="A91" s="1">
+        <f t="shared" si="7"/>
+        <v>2015</v>
+      </c>
+      <c r="B91" s="1">
+        <f>COUNTIF($C$1:C91,C91)</f>
+        <v>15</v>
+      </c>
+      <c r="C91" s="1">
         <v>2</v>
       </c>
-      <c r="D77" s="1">
-        <f t="shared" si="5"/>
-        <v>102014</v>
-      </c>
-      <c r="E77" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="F77" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="G77" s="2">
-        <v>202014</v>
-      </c>
-      <c r="H77" s="2"/>
-      <c r="K77" s="8"/>
-      <c r="M77"/>
-      <c r="N77"/>
-      <c r="O77"/>
-      <c r="S77" s="1"/>
-    </row>
-    <row r="78" s="2" customFormat="1" spans="1:19">
-      <c r="A78" s="2">
+      <c r="D91" s="1">
         <f t="shared" si="6"/>
-        <v>2015</v>
-      </c>
-      <c r="B78" s="2">
-        <f>COUNTIF($C$1:C78,C78)</f>
-        <v>15</v>
-      </c>
-      <c r="C78" s="2">
+        <v>102015</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F91" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G91" s="1">
+        <v>202015</v>
+      </c>
+      <c r="K91" s="3"/>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="1:11">
+      <c r="A92" s="1">
+        <f t="shared" si="7"/>
+        <v>2016</v>
+      </c>
+      <c r="B92" s="1">
+        <f>COUNTIF($C$1:C92,C92)</f>
+        <v>16</v>
+      </c>
+      <c r="C92" s="1">
         <v>2</v>
       </c>
-      <c r="D78" s="1">
-        <f t="shared" si="5"/>
-        <v>102015</v>
-      </c>
-      <c r="E78" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="F78" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G78" s="2">
-        <v>202015</v>
-      </c>
-      <c r="H78" s="2"/>
-      <c r="K78" s="8"/>
-      <c r="M78"/>
-      <c r="N78"/>
-      <c r="O78"/>
-      <c r="S78" s="1"/>
-    </row>
-    <row r="79" s="2" customFormat="1" spans="1:19">
-      <c r="A79" s="2">
+      <c r="D92" s="1">
         <f t="shared" si="6"/>
-        <v>2016</v>
-      </c>
-      <c r="B79" s="2">
-        <f>COUNTIF($C$1:C79,C79)</f>
-        <v>16</v>
-      </c>
-      <c r="C79" s="2">
+        <v>102016</v>
+      </c>
+      <c r="E92" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="F92" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="G92" s="1">
+        <v>202016</v>
+      </c>
+      <c r="K92" s="3"/>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="1:11">
+      <c r="A93" s="1">
+        <f t="shared" si="7"/>
+        <v>2017</v>
+      </c>
+      <c r="B93" s="1">
+        <f>COUNTIF($C$1:C93,C93)</f>
+        <v>17</v>
+      </c>
+      <c r="C93" s="1">
         <v>2</v>
       </c>
-      <c r="D79" s="1">
-        <f t="shared" si="5"/>
-        <v>102016</v>
-      </c>
-      <c r="E79" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F79" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="G79" s="2">
-        <v>202016</v>
-      </c>
-      <c r="H79" s="2"/>
-      <c r="K79" s="8"/>
-      <c r="M79"/>
-      <c r="N79"/>
-      <c r="O79"/>
-      <c r="S79" s="1"/>
-    </row>
-    <row r="80" s="2" customFormat="1" spans="1:19">
-      <c r="A80" s="2">
+      <c r="D93" s="1">
         <f t="shared" si="6"/>
-        <v>2017</v>
-      </c>
-      <c r="B80" s="2">
-        <f>COUNTIF($C$1:C80,C80)</f>
-        <v>17</v>
-      </c>
-      <c r="C80" s="2">
+        <v>102017</v>
+      </c>
+      <c r="E93" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="F93" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="G93" s="1">
+        <v>202017</v>
+      </c>
+      <c r="K93" s="3"/>
+    </row>
+    <row r="94" s="1" customFormat="1" spans="1:11">
+      <c r="A94" s="1">
+        <f t="shared" si="7"/>
+        <v>2018</v>
+      </c>
+      <c r="B94" s="1">
+        <f>COUNTIF($C$1:C94,C94)</f>
+        <v>18</v>
+      </c>
+      <c r="C94" s="1">
         <v>2</v>
       </c>
-      <c r="D80" s="1">
-        <f t="shared" si="5"/>
-        <v>102017</v>
-      </c>
-      <c r="E80" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="F80" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="G80" s="2">
-        <v>202017</v>
-      </c>
-      <c r="H80" s="2"/>
-      <c r="K80" s="8"/>
-      <c r="M80"/>
-      <c r="N80"/>
-      <c r="O80"/>
-      <c r="S80" s="1"/>
-    </row>
-    <row r="81" s="2" customFormat="1" spans="1:19">
-      <c r="A81" s="2">
+      <c r="D94" s="1">
         <f t="shared" si="6"/>
-        <v>2018</v>
-      </c>
-      <c r="B81" s="2">
-        <f>COUNTIF($C$1:C81,C81)</f>
-        <v>18</v>
-      </c>
-      <c r="C81" s="2">
+        <v>102018</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="F94" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="G94" s="1">
+        <v>202018</v>
+      </c>
+      <c r="K94" s="3"/>
+    </row>
+    <row r="95" s="1" customFormat="1" spans="1:11">
+      <c r="A95" s="1">
+        <f t="shared" si="7"/>
+        <v>2019</v>
+      </c>
+      <c r="B95" s="1">
+        <f>COUNTIF($C$1:C95,C95)</f>
+        <v>19</v>
+      </c>
+      <c r="C95" s="1">
         <v>2</v>
       </c>
-      <c r="D81" s="1">
-        <f t="shared" si="5"/>
-        <v>102018</v>
-      </c>
-      <c r="E81" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="G81" s="2">
-        <v>202018</v>
-      </c>
-      <c r="H81" s="2"/>
-      <c r="K81" s="8"/>
-      <c r="M81"/>
-      <c r="N81"/>
-      <c r="O81"/>
-      <c r="S81" s="1"/>
-    </row>
-    <row r="82" s="2" customFormat="1" spans="1:19">
-      <c r="A82" s="2">
+      <c r="D95" s="1">
         <f t="shared" si="6"/>
-        <v>2019</v>
-      </c>
-      <c r="B82" s="2">
-        <f>COUNTIF($C$1:C82,C82)</f>
-        <v>19</v>
-      </c>
-      <c r="C82" s="2">
+        <v>102019</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="F95" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="G95" s="1">
+        <v>202019</v>
+      </c>
+      <c r="K95" s="3"/>
+    </row>
+    <row r="96" s="1" customFormat="1" spans="1:11">
+      <c r="A96" s="1">
+        <f t="shared" si="7"/>
+        <v>2020</v>
+      </c>
+      <c r="B96" s="1">
+        <f>COUNTIF($C$1:C96,C96)</f>
+        <v>20</v>
+      </c>
+      <c r="C96" s="1">
         <v>2</v>
       </c>
-      <c r="D82" s="1">
-        <f t="shared" si="5"/>
-        <v>102019</v>
-      </c>
-      <c r="E82" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="F82" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G82" s="2">
-        <v>202019</v>
-      </c>
-      <c r="H82" s="2"/>
-      <c r="K82" s="8"/>
-      <c r="M82"/>
-      <c r="N82"/>
-      <c r="O82"/>
-      <c r="S82" s="1"/>
-    </row>
-    <row r="83" s="2" customFormat="1" spans="1:19">
-      <c r="A83" s="2">
+      <c r="D96" s="1">
         <f t="shared" si="6"/>
-        <v>2020</v>
-      </c>
-      <c r="B83" s="2">
-        <f>COUNTIF($C$1:C83,C83)</f>
-        <v>20</v>
-      </c>
-      <c r="C83" s="2">
+        <v>102020</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="F96" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="G96" s="1">
+        <v>202020</v>
+      </c>
+      <c r="K96" s="3"/>
+    </row>
+    <row r="97" s="1" customFormat="1" spans="1:11">
+      <c r="A97" s="1">
+        <f t="shared" si="7"/>
+        <v>3001</v>
+      </c>
+      <c r="B97" s="1">
+        <f>COUNTIF($C$1:C97,C97)</f>
+        <v>1</v>
+      </c>
+      <c r="C97" s="1">
+        <v>3</v>
+      </c>
+      <c r="D97" s="1">
+        <f t="shared" si="6"/>
+        <v>103001</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F97" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="G97" s="1">
+        <v>203001</v>
+      </c>
+      <c r="H97" s="1"/>
+      <c r="I97" s="1"/>
+      <c r="J97" s="1">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="98" s="1" customFormat="1" spans="1:11">
+      <c r="A98" s="1">
+        <f t="shared" si="7"/>
+        <v>3002</v>
+      </c>
+      <c r="B98" s="1">
+        <f>COUNTIF($C$1:C98,C98)</f>
         <v>2</v>
       </c>
-      <c r="D83" s="1">
-        <f t="shared" si="5"/>
-        <v>102020</v>
-      </c>
-      <c r="E83" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="F83" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="G83" s="2">
-        <v>202020</v>
-      </c>
-      <c r="H83" s="2"/>
-      <c r="K83" s="8"/>
-      <c r="M83"/>
-      <c r="N83"/>
-      <c r="O83"/>
-      <c r="S83" s="1"/>
-    </row>
-    <row r="84" s="3" customFormat="1" spans="1:11">
-      <c r="A84" s="3">
+      <c r="C98" s="1">
+        <v>3</v>
+      </c>
+      <c r="D98" s="1">
         <f t="shared" si="6"/>
-        <v>3001</v>
-      </c>
-      <c r="B84" s="3">
-        <f>COUNTIF($C$1:C84,C84)</f>
+        <v>103002</v>
+      </c>
+      <c r="E98" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="F98" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="G98" s="1">
+        <v>203002</v>
+      </c>
+      <c r="J98" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" s="1" customFormat="1" spans="1:11">
+      <c r="A99" s="1">
+        <f t="shared" si="7"/>
+        <v>3003</v>
+      </c>
+      <c r="B99" s="1">
+        <f>COUNTIF($C$1:C99,C99)</f>
+        <v>3</v>
+      </c>
+      <c r="C99" s="1">
+        <v>3</v>
+      </c>
+      <c r="D99" s="1">
+        <f t="shared" si="6"/>
+        <v>103003</v>
+      </c>
+      <c r="E99" s="1" t="s">
+        <v>220</v>
+      </c>
+      <c r="F99" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="G99" s="1">
+        <v>203003</v>
+      </c>
+      <c r="J99" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="100" s="1" customFormat="1" spans="1:11">
+      <c r="A100" s="1">
+        <f t="shared" si="7"/>
+        <v>4001</v>
+      </c>
+      <c r="B100" s="1">
+        <f>COUNTIF($C$1:C100,C100)</f>
         <v>1</v>
       </c>
-      <c r="C84" s="3">
+      <c r="C100" s="1">
+        <v>4</v>
+      </c>
+      <c r="D100" s="1">
+        <f t="shared" si="6"/>
+        <v>104001</v>
+      </c>
+      <c r="E100" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F100" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G100" s="1">
+        <f t="shared" ref="G100:G109" si="8">200000+A100</f>
+        <v>204001</v>
+      </c>
+      <c r="K100" s="3"/>
+    </row>
+    <row r="101" s="1" customFormat="1" spans="1:11">
+      <c r="A101" s="1">
+        <f t="shared" si="7"/>
+        <v>4002</v>
+      </c>
+      <c r="B101" s="1">
+        <f>COUNTIF($C$1:C101,C101)</f>
+        <v>2</v>
+      </c>
+      <c r="C101" s="1">
+        <v>4</v>
+      </c>
+      <c r="D101" s="1">
+        <f t="shared" si="6"/>
+        <v>104002</v>
+      </c>
+      <c r="E101" s="1" t="s">
+        <v>222</v>
+      </c>
+      <c r="F101" s="1" t="s">
+        <v>224</v>
+      </c>
+      <c r="G101" s="1">
+        <f t="shared" si="8"/>
+        <v>204002</v>
+      </c>
+      <c r="J101" s="1">
+        <v>6</v>
+      </c>
+      <c r="K101" s="3"/>
+    </row>
+    <row r="102" s="1" customFormat="1" spans="1:11">
+      <c r="A102" s="1">
+        <f t="shared" si="7"/>
+        <v>4003</v>
+      </c>
+      <c r="B102" s="1">
+        <f>COUNTIF($C$1:C102,C102)</f>
         <v>3</v>
       </c>
-      <c r="D84" s="1">
-        <f t="shared" si="5"/>
-        <v>103001</v>
-      </c>
-      <c r="E84" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="G84" s="3">
-        <v>203001</v>
-      </c>
-      <c r="H84" s="3">
+      <c r="C102" s="1">
+        <v>4</v>
+      </c>
+      <c r="D102" s="1">
+        <f t="shared" si="6"/>
+        <v>104003</v>
+      </c>
+      <c r="E102" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="F102" s="1" t="s">
+        <v>226</v>
+      </c>
+      <c r="G102" s="1">
+        <f t="shared" si="8"/>
+        <v>204003</v>
+      </c>
+      <c r="J102" s="1">
+        <v>9</v>
+      </c>
+      <c r="K102" s="3"/>
+    </row>
+    <row r="103" s="1" customFormat="1" spans="1:11">
+      <c r="A103" s="1">
+        <f t="shared" ref="A103:A110" si="9">C103*1000+B103</f>
+        <v>5001</v>
+      </c>
+      <c r="B103" s="1">
+        <f>COUNTIF($C$1:C103,C103)</f>
+        <v>1</v>
+      </c>
+      <c r="C103" s="1">
+        <v>5</v>
+      </c>
+      <c r="D103" s="1">
+        <f t="shared" ref="D103:D110" si="10">100000+C103*1000+B103</f>
+        <v>105001</v>
+      </c>
+      <c r="E103" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F103" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G103" s="1">
+        <f t="shared" si="8"/>
+        <v>205001</v>
+      </c>
+      <c r="K103" s="3"/>
+    </row>
+    <row r="104" s="1" customFormat="1" spans="1:11">
+      <c r="A104" s="1">
+        <f t="shared" si="9"/>
+        <v>5002</v>
+      </c>
+      <c r="B104" s="1">
+        <f>COUNTIF($C$1:C104,C104)</f>
+        <v>2</v>
+      </c>
+      <c r="C104" s="1">
+        <v>5</v>
+      </c>
+      <c r="D104" s="1">
+        <f t="shared" si="10"/>
+        <v>105002</v>
+      </c>
+      <c r="E104" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F104" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G104" s="1">
+        <f t="shared" si="8"/>
+        <v>205002</v>
+      </c>
+      <c r="J104" s="1">
+        <v>6</v>
+      </c>
+      <c r="K104" s="3"/>
+    </row>
+    <row r="105" s="1" customFormat="1" spans="1:11">
+      <c r="A105" s="1">
+        <f t="shared" si="9"/>
+        <v>5003</v>
+      </c>
+      <c r="B105" s="1">
+        <f>COUNTIF($C$1:C105,C105)</f>
         <v>3</v>
       </c>
-      <c r="K84" s="1"/>
-    </row>
-    <row r="85" s="3" customFormat="1" spans="1:11">
-      <c r="A85" s="3">
-        <f t="shared" si="6"/>
-        <v>3002</v>
-      </c>
-      <c r="B85" s="3">
-        <f>COUNTIF($C$1:C85,C85)</f>
+      <c r="C105" s="1">
+        <v>5</v>
+      </c>
+      <c r="D105" s="1">
+        <f t="shared" si="10"/>
+        <v>105003</v>
+      </c>
+      <c r="E105" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F105" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G105" s="1">
+        <f t="shared" si="8"/>
+        <v>205003</v>
+      </c>
+      <c r="J105" s="1">
+        <v>9</v>
+      </c>
+      <c r="K105" s="3"/>
+    </row>
+    <row r="106" s="1" customFormat="1" spans="1:11">
+      <c r="A106" s="1">
+        <f t="shared" si="9"/>
+        <v>6001</v>
+      </c>
+      <c r="B106" s="1">
+        <f>COUNTIF($C$1:C106,C106)</f>
+        <v>1</v>
+      </c>
+      <c r="C106" s="1">
+        <v>6</v>
+      </c>
+      <c r="D106" s="1">
+        <f t="shared" si="10"/>
+        <v>106001</v>
+      </c>
+      <c r="E106" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F106" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="G106" s="1">
+        <f t="shared" si="8"/>
+        <v>206001</v>
+      </c>
+      <c r="K106" s="3"/>
+    </row>
+    <row r="107" s="1" customFormat="1" spans="1:11">
+      <c r="A107" s="1">
+        <f t="shared" si="9"/>
+        <v>6002</v>
+      </c>
+      <c r="B107" s="1">
+        <f>COUNTIF($C$1:C107,C107)</f>
         <v>2</v>
       </c>
-      <c r="C85" s="3">
+      <c r="C107" s="1">
+        <v>6</v>
+      </c>
+      <c r="D107" s="1">
+        <f t="shared" si="10"/>
+        <v>106002</v>
+      </c>
+      <c r="E107" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="F107" s="1" t="s">
+        <v>234</v>
+      </c>
+      <c r="G107" s="1">
+        <f t="shared" si="8"/>
+        <v>206002</v>
+      </c>
+      <c r="J107" s="1">
+        <v>6</v>
+      </c>
+      <c r="K107" s="3"/>
+    </row>
+    <row r="108" s="1" customFormat="1" spans="1:11">
+      <c r="A108" s="1">
+        <f t="shared" si="9"/>
+        <v>6003</v>
+      </c>
+      <c r="B108" s="1">
+        <f>COUNTIF($C$1:C108,C108)</f>
         <v>3</v>
       </c>
-      <c r="D85" s="1">
-        <f t="shared" si="5"/>
-        <v>103002</v>
-      </c>
-      <c r="E85" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="G85" s="3">
-        <v>203002</v>
-      </c>
-      <c r="H85" s="3">
+      <c r="C108" s="1">
         <v>6</v>
       </c>
-      <c r="K85" s="1"/>
-    </row>
-    <row r="86" s="3" customFormat="1" spans="1:11">
-      <c r="A86" s="3">
-        <f t="shared" si="6"/>
-        <v>3003</v>
-      </c>
-      <c r="B86" s="3">
-        <f>COUNTIF($C$1:C86,C86)</f>
-        <v>3</v>
-      </c>
-      <c r="C86" s="3">
-        <v>3</v>
-      </c>
-      <c r="D86" s="1">
-        <f t="shared" si="5"/>
-        <v>103003</v>
-      </c>
-      <c r="E86" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G86" s="3">
-        <v>203003</v>
-      </c>
-      <c r="H86" s="3">
+      <c r="D108" s="1">
+        <f t="shared" si="10"/>
+        <v>106003</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="G108" s="1">
+        <f t="shared" si="8"/>
+        <v>206003</v>
+      </c>
+      <c r="J108" s="1">
         <v>9</v>
       </c>
-      <c r="K86" s="1"/>
-    </row>
-    <row r="87" s="4" customFormat="1" spans="1:11">
-      <c r="A87" s="4">
-        <f t="shared" si="6"/>
-        <v>4001</v>
-      </c>
-      <c r="B87" s="4">
-        <f>COUNTIF($C$1:C87,C87)</f>
-        <v>1</v>
-      </c>
-      <c r="C87" s="4">
-        <v>4</v>
-      </c>
-      <c r="D87" s="4">
-        <f t="shared" si="5"/>
-        <v>104001</v>
-      </c>
-      <c r="E87" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="G87" s="4">
-        <f t="shared" ref="G87:G96" si="7">200000+A87</f>
-        <v>204001</v>
-      </c>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-      <c r="J87" s="3"/>
-      <c r="K87" s="9"/>
-    </row>
-    <row r="88" s="4" customFormat="1" spans="1:11">
-      <c r="A88" s="4">
-        <f t="shared" si="6"/>
-        <v>4002</v>
-      </c>
-      <c r="B88" s="4">
-        <f>COUNTIF($C$1:C88,C88)</f>
-        <v>2</v>
-      </c>
-      <c r="C88" s="4">
-        <v>4</v>
-      </c>
-      <c r="D88" s="4">
-        <f t="shared" si="5"/>
-        <v>104002</v>
-      </c>
-      <c r="E88" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="F88" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G88" s="4">
-        <f t="shared" si="7"/>
-        <v>204002</v>
-      </c>
-      <c r="H88" s="3">
-        <v>3</v>
-      </c>
-      <c r="I88" s="3"/>
-      <c r="J88" s="3"/>
-      <c r="K88" s="9"/>
-    </row>
-    <row r="89" s="4" customFormat="1" spans="1:11">
-      <c r="A89" s="4">
-        <f t="shared" si="6"/>
-        <v>4003</v>
-      </c>
-      <c r="B89" s="4">
-        <f>COUNTIF($C$1:C89,C89)</f>
-        <v>3</v>
-      </c>
-      <c r="C89" s="4">
-        <v>4</v>
-      </c>
-      <c r="D89" s="4">
-        <f t="shared" si="5"/>
-        <v>104003</v>
-      </c>
-      <c r="E89" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="F89" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G89" s="4">
-        <f t="shared" si="7"/>
-        <v>204003</v>
-      </c>
-      <c r="H89" s="3">
-        <v>6</v>
-      </c>
-      <c r="I89" s="3"/>
-      <c r="J89" s="3"/>
-      <c r="K89" s="9"/>
-    </row>
-    <row r="90" s="5" customFormat="1" spans="1:11">
-      <c r="A90" s="5">
-        <f t="shared" ref="A90:A97" si="8">C90*1000+B90</f>
-        <v>5001</v>
-      </c>
-      <c r="B90" s="5">
-        <f>COUNTIF($C$1:C90,C90)</f>
-        <v>1</v>
-      </c>
-      <c r="C90" s="5">
-        <v>5</v>
-      </c>
-      <c r="D90" s="5">
-        <f t="shared" ref="D90:D97" si="9">100000+C90*1000+B90</f>
-        <v>105001</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="F90" s="5" t="s">
-        <v>182</v>
-      </c>
-      <c r="G90" s="5">
-        <f t="shared" si="7"/>
-        <v>205001</v>
-      </c>
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-      <c r="J90" s="3"/>
-      <c r="K90" s="9"/>
-    </row>
-    <row r="91" s="5" customFormat="1" spans="1:11">
-      <c r="A91" s="5">
-        <f t="shared" si="8"/>
-        <v>5002</v>
-      </c>
-      <c r="B91" s="5">
-        <f>COUNTIF($C$1:C91,C91)</f>
-        <v>2</v>
-      </c>
-      <c r="C91" s="5">
-        <v>5</v>
-      </c>
-      <c r="D91" s="5">
-        <f t="shared" si="9"/>
-        <v>105002</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>181</v>
-      </c>
-      <c r="F91" s="5" t="s">
-        <v>183</v>
-      </c>
-      <c r="G91" s="5">
-        <f t="shared" si="7"/>
-        <v>205002</v>
-      </c>
-      <c r="H91" s="3">
-        <v>3</v>
-      </c>
-      <c r="I91" s="3"/>
-      <c r="J91" s="3"/>
-      <c r="K91" s="9"/>
-    </row>
-    <row r="92" s="5" customFormat="1" spans="1:11">
-      <c r="A92" s="5">
-        <f t="shared" si="8"/>
-        <v>5003</v>
-      </c>
-      <c r="B92" s="5">
-        <f>COUNTIF($C$1:C92,C92)</f>
-        <v>3</v>
-      </c>
-      <c r="C92" s="5">
-        <v>5</v>
-      </c>
-      <c r="D92" s="5">
-        <f t="shared" si="9"/>
-        <v>105003</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>184</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>185</v>
-      </c>
-      <c r="G92" s="5">
-        <f t="shared" si="7"/>
-        <v>205003</v>
-      </c>
-      <c r="H92" s="3">
-        <v>6</v>
-      </c>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="9"/>
-    </row>
-    <row r="93" s="6" customFormat="1" spans="1:11">
-      <c r="A93" s="6">
-        <f t="shared" si="8"/>
-        <v>6001</v>
-      </c>
-      <c r="B93" s="6">
-        <f>COUNTIF($C$1:C93,C93)</f>
-        <v>1</v>
-      </c>
-      <c r="C93" s="6">
-        <v>6</v>
-      </c>
-      <c r="D93" s="6">
-        <f t="shared" si="9"/>
-        <v>106001</v>
-      </c>
-      <c r="E93" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F93" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="G93" s="6">
-        <f t="shared" si="7"/>
-        <v>206001</v>
-      </c>
-      <c r="H93" s="3"/>
-      <c r="I93" s="3"/>
-      <c r="J93" s="3"/>
-      <c r="K93" s="9"/>
-    </row>
-    <row r="94" s="6" customFormat="1" spans="1:11">
-      <c r="A94" s="6">
-        <f t="shared" si="8"/>
-        <v>6002</v>
-      </c>
-      <c r="B94" s="6">
-        <f>COUNTIF($C$1:C94,C94)</f>
-        <v>2</v>
-      </c>
-      <c r="C94" s="6">
-        <v>6</v>
-      </c>
-      <c r="D94" s="6">
-        <f t="shared" si="9"/>
-        <v>106002</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>188</v>
-      </c>
-      <c r="G94" s="6">
-        <f t="shared" si="7"/>
-        <v>206002</v>
-      </c>
-      <c r="H94" s="3">
-        <v>3</v>
-      </c>
-      <c r="I94" s="3"/>
-      <c r="J94" s="3"/>
-      <c r="K94" s="9"/>
-    </row>
-    <row r="95" s="6" customFormat="1" spans="1:11">
-      <c r="A95" s="6">
-        <f t="shared" si="8"/>
-        <v>6003</v>
-      </c>
-      <c r="B95" s="6">
-        <f>COUNTIF($C$1:C95,C95)</f>
-        <v>3</v>
-      </c>
-      <c r="C95" s="6">
-        <v>6</v>
-      </c>
-      <c r="D95" s="6">
-        <f t="shared" si="9"/>
-        <v>106003</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="G95" s="6">
-        <f t="shared" si="7"/>
-        <v>206003</v>
-      </c>
-      <c r="H95" s="3">
-        <v>6</v>
-      </c>
-      <c r="I95" s="3"/>
-      <c r="J95" s="3"/>
-      <c r="K95" s="9"/>
+      <c r="K108" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -120,12 +120,34 @@
         </r>
       </text>
     </comment>
+    <comment ref="K1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+当前道具获取途径是“前往获取”时，点击按钮跳到配置中的UI界面</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="237">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="228">
   <si>
     <t>id</t>
   </si>
@@ -151,7 +173,10 @@
     <t>VIP条件</t>
   </si>
   <si>
-    <t>多语言ID</t>
+    <t>跳转路径</t>
+  </si>
+  <si>
+    <t>#备注</t>
   </si>
   <si>
     <t>int</t>
@@ -184,7 +209,7 @@
     <t>vipLevel</t>
   </si>
   <si>
-    <t>languageId</t>
+    <t>jump</t>
   </si>
   <si>
     <t>头像1</t>
@@ -424,79 +449,82 @@
     <t>头像40</t>
   </si>
   <si>
-    <t>1980000_1500_1008</t>
+    <t>HeadDia_001.png</t>
+  </si>
+  <si>
+    <t>1980000_1500</t>
   </si>
   <si>
     <t>头像41</t>
   </si>
   <si>
-    <t>1980000_1500_1009</t>
+    <t>HeadDia_002.png</t>
   </si>
   <si>
     <t>头像42</t>
   </si>
   <si>
-    <t>1980000_1500_1010</t>
+    <t>HeadDia_003.png</t>
   </si>
   <si>
     <t>头像43</t>
   </si>
   <si>
-    <t>1980000_1500_1011</t>
+    <t>HeadDia_004.png</t>
   </si>
   <si>
     <t>头像44</t>
   </si>
   <si>
-    <t>1980000_1500_1012</t>
+    <t>HeadDia_005.png</t>
   </si>
   <si>
     <t>头像45</t>
   </si>
   <si>
-    <t>1980000_1500_1013</t>
+    <t>HeadDia_006.png</t>
   </si>
   <si>
     <t>头像46</t>
   </si>
   <si>
-    <t>1980000_1500_1014</t>
+    <t>HeadDia_007.png</t>
   </si>
   <si>
     <t>头像47</t>
   </si>
   <si>
-    <t>1980000_1500_1015</t>
+    <t>HeadDia_008.png</t>
   </si>
   <si>
     <t>头像48</t>
   </si>
   <si>
-    <t>1980000_1500_1016</t>
+    <t>HeadDia_009.png</t>
   </si>
   <si>
     <t>头像49</t>
   </si>
   <si>
-    <t>1980000_1500_1017</t>
+    <t>HeadDia_010.png</t>
   </si>
   <si>
     <t>头像50</t>
   </si>
   <si>
-    <t>1980000_1500_1018</t>
+    <t>HeadDia_011.png</t>
   </si>
   <si>
     <t>头像51</t>
   </si>
   <si>
-    <t>1980000_1500_1019</t>
+    <t>HeadDia_012.png</t>
   </si>
   <si>
     <t>头像52</t>
   </si>
   <si>
-    <t>1980000_1500_1020</t>
+    <t>HeadDia_013.png</t>
   </si>
   <si>
     <t>头像框1</t>
@@ -535,124 +563,91 @@
     <t>frame_801.png</t>
   </si>
   <si>
+    <t>UIDailyBonus</t>
+  </si>
+  <si>
     <t>头像框-首充专属</t>
   </si>
   <si>
     <t>frame_018.png</t>
   </si>
   <si>
+    <t>首充界面是什么？？</t>
+  </si>
+  <si>
     <t>头像框6</t>
   </si>
   <si>
     <t>frame_006.png</t>
   </si>
   <si>
-    <t>1980000_1500_40</t>
-  </si>
-  <si>
     <t>头像框7</t>
   </si>
   <si>
     <t>frame_007.png</t>
   </si>
   <si>
-    <t>1980000_1500_41</t>
-  </si>
-  <si>
     <t>头像框8</t>
   </si>
   <si>
     <t>frame_008.png</t>
   </si>
   <si>
-    <t>1980000_1500_42</t>
-  </si>
-  <si>
     <t>头像框9</t>
   </si>
   <si>
     <t>frame_009.png</t>
   </si>
   <si>
-    <t>1980000_1500_43</t>
-  </si>
-  <si>
     <t>头像框10</t>
   </si>
   <si>
     <t>frame_010.png</t>
   </si>
   <si>
-    <t>1980000_1500_44</t>
-  </si>
-  <si>
     <t>头像框11</t>
   </si>
   <si>
     <t>frame_011.png</t>
   </si>
   <si>
-    <t>1980000_1500_45</t>
-  </si>
-  <si>
     <t>头像框12</t>
   </si>
   <si>
     <t>frame_012.png</t>
   </si>
   <si>
-    <t>1980000_1500_46</t>
-  </si>
-  <si>
     <t>头像框13</t>
   </si>
   <si>
     <t>frame_013.png</t>
   </si>
   <si>
-    <t>1980000_1500_47</t>
-  </si>
-  <si>
     <t>头像框14</t>
   </si>
   <si>
     <t>frame_014.png</t>
   </si>
   <si>
-    <t>1980000_1500_48</t>
-  </si>
-  <si>
     <t>头像框15</t>
   </si>
   <si>
     <t>frame_015.png</t>
   </si>
   <si>
-    <t>1980000_1500_49</t>
-  </si>
-  <si>
     <t>头像框16</t>
   </si>
   <si>
     <t>frame_016.png</t>
   </si>
   <si>
-    <t>1980000_1500_50</t>
-  </si>
-  <si>
     <t>头像框17</t>
   </si>
   <si>
     <t>frame_017.png</t>
   </si>
   <si>
-    <t>1980000_1500_51</t>
-  </si>
-  <si>
     <t>头像框18</t>
-  </si>
-  <si>
-    <t>1980000_1500_52</t>
   </si>
   <si>
     <t>国旗1</t>
@@ -1013,12 +1008,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1479,7 +1474,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1487,9 +1482,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1803,7 +1795,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K108"/>
+  <dimension ref="A1:L108"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1815,15 +1807,15 @@
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="11.5" style="1" customWidth="1"/>
-    <col min="12" max="13" width="9" style="1"/>
-    <col min="14" max="15" width="12.625" style="1"/>
-    <col min="16" max="17" width="9" style="1"/>
-    <col min="18" max="18" width="14.375" style="1" customWidth="1"/>
-    <col min="19" max="16384" width="9" style="1"/>
+    <col min="11" max="11" width="14.7" style="1" customWidth="1"/>
+    <col min="12" max="12" width="21.4666666666667" style="1" customWidth="1"/>
+    <col min="13" max="14" width="12.625" style="1"/>
+    <col min="15" max="16" width="9" style="1"/>
+    <col min="17" max="17" width="14.375" style="1" customWidth="1"/>
+    <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:11">
+    <row r="1" s="1" customFormat="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1852,68 +1844,71 @@
       <c r="K1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" s="1" customFormat="1" spans="1:11">
+      <c r="L1" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:12">
       <c r="A2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="H2" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I2" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:12">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="1"/>
       <c r="C3" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" s="1" customFormat="1" spans="1:11">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:12">
       <c r="A5" s="1">
         <f t="shared" ref="A5:A36" si="0">C5*1000+B5</f>
         <v>1</v>
@@ -1930,16 +1925,16 @@
         <v>100001</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G5" s="1">
         <v>200001</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:11">
+    <row r="6" s="1" customFormat="1" spans="1:12">
       <c r="A6" s="1">
         <f t="shared" si="0"/>
         <v>2</v>
@@ -1956,16 +1951,16 @@
         <v>100002</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G6" s="1">
         <v>200017</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:11">
+    <row r="7" s="1" customFormat="1" spans="1:12">
       <c r="A7" s="1">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1982,10 +1977,10 @@
         <v>100003</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G7" s="1">
         <v>200002</v>
@@ -1994,7 +1989,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:11">
+    <row r="8" s="1" customFormat="1" spans="1:12">
       <c r="A8" s="1">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2011,10 +2006,10 @@
         <v>100004</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1">
         <v>200018</v>
@@ -2023,7 +2018,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:11">
+    <row r="9" s="1" customFormat="1" spans="1:12">
       <c r="A9" s="1">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2040,10 +2035,10 @@
         <v>100005</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G9" s="1">
         <v>200003</v>
@@ -2052,7 +2047,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:11">
+    <row r="10" s="1" customFormat="1" spans="1:12">
       <c r="A10" s="1">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2069,10 +2064,10 @@
         <v>100006</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G10" s="1">
         <v>200019</v>
@@ -2081,7 +2076,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:11">
+    <row r="11" s="1" customFormat="1" spans="1:12">
       <c r="A11" s="1">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2098,10 +2093,10 @@
         <v>100007</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G11" s="1">
         <v>200004</v>
@@ -2110,7 +2105,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:11">
+    <row r="12" s="1" customFormat="1" spans="1:12">
       <c r="A12" s="1">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2127,10 +2122,10 @@
         <v>100008</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" s="1">
         <v>200020</v>
@@ -2139,7 +2134,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:11">
+    <row r="13" s="1" customFormat="1" spans="1:12">
       <c r="A13" s="1">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2156,10 +2151,10 @@
         <v>100009</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G13" s="1">
         <v>200005</v>
@@ -2168,7 +2163,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:11">
+    <row r="14" s="1" customFormat="1" spans="1:12">
       <c r="A14" s="1">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2185,10 +2180,10 @@
         <v>100010</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G14" s="1">
         <v>200021</v>
@@ -2197,7 +2192,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:11">
+    <row r="15" s="1" customFormat="1" spans="1:12">
       <c r="A15" s="1">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2214,10 +2209,10 @@
         <v>100011</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G15" s="1">
         <v>200006</v>
@@ -2226,7 +2221,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:11">
+    <row r="16" s="1" customFormat="1" spans="1:12">
       <c r="A16" s="1">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2243,10 +2238,10 @@
         <v>100012</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G16" s="1">
         <v>200022</v>
@@ -2272,10 +2267,10 @@
         <v>100013</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G17" s="1">
         <v>200007</v>
@@ -2301,10 +2296,10 @@
         <v>100014</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G18" s="1">
         <v>200023</v>
@@ -2330,10 +2325,10 @@
         <v>100015</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G19" s="1">
         <v>200008</v>
@@ -2359,10 +2354,10 @@
         <v>100016</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G20" s="1">
         <v>200024</v>
@@ -2388,10 +2383,10 @@
         <v>100017</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G21" s="1">
         <v>200009</v>
@@ -2417,10 +2412,10 @@
         <v>100018</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G22" s="1">
         <v>200025</v>
@@ -2446,10 +2441,10 @@
         <v>100019</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G23" s="1">
         <v>200010</v>
@@ -2475,10 +2470,10 @@
         <v>100020</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G24" s="1">
         <v>200026</v>
@@ -2504,10 +2499,10 @@
         <v>100021</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G25" s="1">
         <v>200011</v>
@@ -2533,10 +2528,10 @@
         <v>100022</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G26" s="1">
         <v>200027</v>
@@ -2562,10 +2557,10 @@
         <v>100023</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G27" s="1">
         <v>200012</v>
@@ -2591,10 +2586,10 @@
         <v>100024</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G28" s="1">
         <v>200028</v>
@@ -2620,10 +2615,10 @@
         <v>100025</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G29" s="1">
         <v>200013</v>
@@ -2649,10 +2644,10 @@
         <v>100026</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G30" s="1">
         <v>200029</v>
@@ -2678,10 +2673,10 @@
         <v>100027</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G31" s="1">
         <v>200014</v>
@@ -2707,10 +2702,10 @@
         <v>100028</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G32" s="1">
         <v>200030</v>
@@ -2719,7 +2714,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="33" s="1" customFormat="1" spans="1:11">
+    <row r="33" s="1" customFormat="1" spans="1:10">
       <c r="A33" s="1">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2736,10 +2731,10 @@
         <v>100029</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G33" s="1">
         <v>200015</v>
@@ -2748,7 +2743,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="34" s="1" customFormat="1" spans="1:11">
+    <row r="34" s="1" customFormat="1" spans="1:10">
       <c r="A34" s="1">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2765,10 +2760,10 @@
         <v>100030</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G34" s="1">
         <v>200031</v>
@@ -2777,7 +2772,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="35" s="1" customFormat="1" spans="1:11">
+    <row r="35" s="1" customFormat="1" spans="1:10">
       <c r="A35" s="1">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2794,10 +2789,10 @@
         <v>100031</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G35" s="1">
         <v>200016</v>
@@ -2806,7 +2801,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="36" s="1" customFormat="1" spans="1:11">
+    <row r="36" s="1" customFormat="1" spans="1:10">
       <c r="A36" s="1">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2823,10 +2818,10 @@
         <v>100032</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="G36" s="1">
         <v>200032</v>
@@ -2835,7 +2830,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="37" s="1" customFormat="1" spans="1:11">
+    <row r="37" s="1" customFormat="1" spans="1:10">
       <c r="A37" s="1">
         <f t="shared" ref="A37:A61" si="2">C37*1000+B37</f>
         <v>33</v>
@@ -2852,10 +2847,10 @@
         <v>100033</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G37" s="1">
         <v>200033</v>
@@ -2864,7 +2859,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="38" s="1" customFormat="1" spans="1:11">
+    <row r="38" s="1" customFormat="1" spans="1:10">
       <c r="A38" s="1">
         <f t="shared" si="2"/>
         <v>34</v>
@@ -2881,10 +2876,10 @@
         <v>100034</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G38" s="1">
         <v>200034</v>
@@ -2893,7 +2888,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="39" s="1" customFormat="1" spans="1:11">
+    <row r="39" s="1" customFormat="1" spans="1:10">
       <c r="A39" s="1">
         <f t="shared" si="2"/>
         <v>35</v>
@@ -2906,14 +2901,14 @@
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" ref="D39:D63" si="3">100000+C39*1000+B39</f>
+        <f t="shared" ref="D39:D76" si="3">100000+C39*1000+B39</f>
         <v>100035</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G39" s="1">
         <v>200035</v>
@@ -2922,7 +2917,7 @@
         <v>800</v>
       </c>
     </row>
-    <row r="40" s="1" customFormat="1" spans="1:11">
+    <row r="40" s="1" customFormat="1" spans="1:10">
       <c r="A40" s="1">
         <f t="shared" si="2"/>
         <v>36</v>
@@ -2939,10 +2934,10 @@
         <v>100036</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="G40" s="1">
         <v>200036</v>
@@ -2951,7 +2946,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="41" s="1" customFormat="1" spans="1:11">
+    <row r="41" s="1" customFormat="1" spans="1:10">
       <c r="A41" s="1">
         <f t="shared" si="2"/>
         <v>37</v>
@@ -2968,10 +2963,10 @@
         <v>100037</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G41" s="1">
         <v>200037</v>
@@ -2980,7 +2975,7 @@
         <v>900</v>
       </c>
     </row>
-    <row r="42" s="1" customFormat="1" spans="1:11">
+    <row r="42" s="1" customFormat="1" spans="1:10">
       <c r="A42" s="1">
         <f t="shared" si="2"/>
         <v>38</v>
@@ -2997,10 +2992,10 @@
         <v>100038</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G42" s="1">
         <v>200038</v>
@@ -3009,7 +3004,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="43" s="1" customFormat="1" spans="1:11">
+    <row r="43" s="1" customFormat="1" spans="1:10">
       <c r="A43" s="1">
         <f t="shared" si="2"/>
         <v>39</v>
@@ -3026,10 +3021,10 @@
         <v>100039</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G43" s="1">
         <v>200039</v>
@@ -3038,7 +3033,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="44" s="1" customFormat="1" spans="1:11">
+    <row r="44" s="1" customFormat="1" spans="1:10">
       <c r="A44" s="2">
         <f t="shared" si="2"/>
         <v>40</v>
@@ -3055,22 +3050,21 @@
         <v>100040</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="G44" s="2">
         <v>200014</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J44" s="2"/>
-      <c r="K44" s="2"/>
-    </row>
-    <row r="45" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:10">
       <c r="A45" s="2">
         <f t="shared" si="2"/>
         <v>41</v>
@@ -3087,10 +3081,10 @@
         <v>100041</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="G45" s="2">
         <v>200030</v>
@@ -3100,9 +3094,8 @@
         <v>101</v>
       </c>
       <c r="J45" s="2"/>
-      <c r="K45" s="2"/>
-    </row>
-    <row r="46" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="46" s="1" customFormat="1" spans="1:10">
       <c r="A46" s="2">
         <f t="shared" si="2"/>
         <v>42</v>
@@ -3119,22 +3112,21 @@
         <v>100042</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>77</v>
+        <v>105</v>
       </c>
       <c r="G46" s="2">
         <v>200015</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="J46" s="2"/>
-      <c r="K46" s="2"/>
-    </row>
-    <row r="47" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="47" s="1" customFormat="1" spans="1:10">
       <c r="A47" s="2">
         <f t="shared" si="2"/>
         <v>43</v>
@@ -3151,22 +3143,21 @@
         <v>100043</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>79</v>
+        <v>107</v>
       </c>
       <c r="G47" s="2">
         <v>200031</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="J47" s="2"/>
-      <c r="K47" s="2"/>
-    </row>
-    <row r="48" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="48" s="1" customFormat="1" spans="1:10">
       <c r="A48" s="2">
         <f t="shared" si="2"/>
         <v>44</v>
@@ -3183,22 +3174,21 @@
         <v>100044</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>81</v>
+        <v>109</v>
       </c>
       <c r="G48" s="2">
         <v>200016</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="J48" s="2"/>
-      <c r="K48" s="2"/>
-    </row>
-    <row r="49" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="49" s="1" customFormat="1" spans="1:12">
       <c r="A49" s="2">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -3215,22 +3205,21 @@
         <v>100045</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="G49" s="2">
         <v>200032</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J49" s="2"/>
-      <c r="K49" s="2"/>
-    </row>
-    <row r="50" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="50" s="1" customFormat="1" spans="1:12">
       <c r="A50" s="2">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -3247,22 +3236,21 @@
         <v>100046</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>85</v>
+        <v>113</v>
       </c>
       <c r="G50" s="2">
         <v>200033</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="J50" s="2"/>
-      <c r="K50" s="2"/>
-    </row>
-    <row r="51" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="51" s="1" customFormat="1" spans="1:12">
       <c r="A51" s="2">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -3279,22 +3267,21 @@
         <v>100047</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>87</v>
+        <v>115</v>
       </c>
       <c r="G51" s="2">
         <v>200034</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="J51" s="2"/>
-      <c r="K51" s="2"/>
-    </row>
-    <row r="52" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="52" s="1" customFormat="1" spans="1:12">
       <c r="A52" s="2">
         <f t="shared" si="2"/>
         <v>48</v>
@@ -3311,22 +3298,21 @@
         <v>100048</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="G52" s="2">
         <v>200035</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
-        <v>115</v>
+        <v>101</v>
       </c>
       <c r="J52" s="2"/>
-      <c r="K52" s="2"/>
-    </row>
-    <row r="53" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="53" s="1" customFormat="1" spans="1:12">
       <c r="A53" s="2">
         <f t="shared" si="2"/>
         <v>49</v>
@@ -3343,22 +3329,21 @@
         <v>100049</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>91</v>
+        <v>119</v>
       </c>
       <c r="G53" s="2">
         <v>200036</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
       <c r="J53" s="2"/>
-      <c r="K53" s="2"/>
-    </row>
-    <row r="54" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="54" s="1" customFormat="1" spans="1:12">
       <c r="A54" s="2">
         <f t="shared" si="2"/>
         <v>50</v>
@@ -3375,22 +3360,21 @@
         <v>100050</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="G54" s="2">
         <v>200037</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
-        <v>119</v>
+        <v>101</v>
       </c>
       <c r="J54" s="2"/>
-      <c r="K54" s="2"/>
-    </row>
-    <row r="55" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="55" s="1" customFormat="1" spans="1:12">
       <c r="A55" s="2">
         <f t="shared" si="2"/>
         <v>51</v>
@@ -3407,22 +3391,21 @@
         <v>100051</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>95</v>
+        <v>123</v>
       </c>
       <c r="G55" s="2">
         <v>200038</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
-        <v>121</v>
+        <v>101</v>
       </c>
       <c r="J55" s="2"/>
-      <c r="K55" s="2"/>
-    </row>
-    <row r="56" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="56" s="1" customFormat="1" spans="1:12">
       <c r="A56" s="2">
         <f t="shared" si="2"/>
         <v>52</v>
@@ -3439,24 +3422,23 @@
         <v>100052</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>97</v>
+        <v>125</v>
       </c>
       <c r="G56" s="2">
         <v>200039</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">
-        <v>123</v>
+        <v>101</v>
       </c>
       <c r="J56" s="2"/>
-      <c r="K56" s="2"/>
-    </row>
-    <row r="57" spans="1:11">
+    </row>
+    <row r="57" spans="1:12">
       <c r="A57" s="1">
-        <f>C57*1000+B57</f>
+        <f t="shared" si="2"/>
         <v>1001</v>
       </c>
       <c r="B57" s="1">
@@ -3471,16 +3453,16 @@
         <v>101001</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G57" s="1">
         <v>201001</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:12">
       <c r="A58" s="1">
         <f t="shared" si="2"/>
         <v>1002</v>
@@ -3497,10 +3479,10 @@
         <v>101002</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="G58" s="1">
         <v>201002</v>
@@ -3509,7 +3491,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:12">
       <c r="A59" s="1">
         <f t="shared" si="2"/>
         <v>1003</v>
@@ -3526,10 +3508,10 @@
         <v>101003</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G59" s="1">
         <v>201003</v>
@@ -3538,7 +3520,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:12">
       <c r="A60" s="1">
         <f t="shared" si="2"/>
         <v>1004</v>
@@ -3555,10 +3537,10 @@
         <v>101004</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G60" s="1">
         <v>201004</v>
@@ -3567,7 +3549,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:11">
+    <row r="61" spans="1:12">
       <c r="A61" s="1">
         <f t="shared" ref="A61:A63" si="4">C61*1000+B61</f>
         <v>1005</v>
@@ -3584,10 +3566,10 @@
         <v>101005</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="G61" s="1">
         <v>201005</v>
@@ -3596,7 +3578,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="1:11">
+    <row r="62" s="1" customFormat="1" spans="1:12">
       <c r="A62" s="1">
         <f t="shared" si="4"/>
         <v>1006</v>
@@ -3613,19 +3595,19 @@
         <v>101006</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="G62" s="1">
         <v>201801</v>
       </c>
-      <c r="K62" s="1">
-        <v>56008</v>
-      </c>
-    </row>
-    <row r="63" s="1" customFormat="1" spans="1:11">
+      <c r="K62" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="63" s="1" customFormat="1" spans="1:12">
       <c r="A63" s="1">
         <f t="shared" si="4"/>
         <v>1007</v>
@@ -3642,21 +3624,24 @@
         <v>101007</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G63" s="1">
         <v>201802</v>
       </c>
-      <c r="K63" s="1">
-        <v>57011</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:11">
+      <c r="K63" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="L63" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" spans="1:12">
       <c r="A64" s="2">
-        <f t="shared" ref="A64:A76" si="5">C64*1000+B64</f>
+        <f t="shared" ref="A64:A78" si="5">C64*1000+B64</f>
         <v>1008</v>
       </c>
       <c r="B64" s="2">
@@ -3667,24 +3652,24 @@
         <v>1</v>
       </c>
       <c r="D64" s="2">
-        <f>100000+C64*1000+B64</f>
+        <f t="shared" si="3"/>
         <v>101008</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G64" s="2">
         <v>201006</v>
       </c>
       <c r="H64" s="2"/>
       <c r="I64" s="2" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="65" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="65" s="2" customFormat="1" spans="1:9">
       <c r="A65" s="2">
         <f t="shared" si="5"/>
         <v>1009</v>
@@ -3697,24 +3682,24 @@
         <v>1</v>
       </c>
       <c r="D65" s="2">
-        <f>100000+C65*1000+B65</f>
+        <f t="shared" si="3"/>
         <v>101009</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="G65" s="2">
         <v>201007</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="66" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="66" s="2" customFormat="1" spans="1:9">
       <c r="A66" s="2">
         <f t="shared" si="5"/>
         <v>1010</v>
@@ -3727,24 +3712,24 @@
         <v>1</v>
       </c>
       <c r="D66" s="2">
-        <f>100000+C66*1000+B66</f>
+        <f t="shared" si="3"/>
         <v>101010</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G66" s="2">
         <v>201008</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="67" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="67" s="2" customFormat="1" spans="1:9">
       <c r="A67" s="2">
         <f t="shared" si="5"/>
         <v>1011</v>
@@ -3757,24 +3742,24 @@
         <v>1</v>
       </c>
       <c r="D67" s="2">
-        <f>100000+C67*1000+B67</f>
+        <f t="shared" si="3"/>
         <v>101011</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G67" s="2">
         <v>201009</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="68" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="68" s="2" customFormat="1" spans="1:9">
       <c r="A68" s="2">
         <f t="shared" si="5"/>
         <v>1012</v>
@@ -3787,7 +3772,7 @@
         <v>1</v>
       </c>
       <c r="D68" s="2">
-        <f>100000+C68*1000+B68</f>
+        <f t="shared" si="3"/>
         <v>101012</v>
       </c>
       <c r="E68" s="2" t="s">
@@ -3801,10 +3786,10 @@
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="69" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="69" s="2" customFormat="1" spans="1:9">
       <c r="A69" s="2">
         <f t="shared" si="5"/>
         <v>1013</v>
@@ -3817,24 +3802,24 @@
         <v>1</v>
       </c>
       <c r="D69" s="2">
-        <f>100000+C69*1000+B69</f>
+        <f t="shared" si="3"/>
         <v>101013</v>
       </c>
       <c r="E69" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F69" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="F69" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="G69" s="2">
         <v>201011</v>
       </c>
       <c r="H69" s="2"/>
       <c r="I69" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="70" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="70" s="2" customFormat="1" spans="1:9">
       <c r="A70" s="2">
         <f t="shared" si="5"/>
         <v>1014</v>
@@ -3847,24 +3832,24 @@
         <v>1</v>
       </c>
       <c r="D70" s="2">
-        <f>100000+C70*1000+B70</f>
+        <f t="shared" si="3"/>
         <v>101014</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="G70" s="2">
         <v>201012</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="71" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="71" s="2" customFormat="1" spans="1:9">
       <c r="A71" s="2">
         <f t="shared" si="5"/>
         <v>1015</v>
@@ -3877,24 +3862,24 @@
         <v>1</v>
       </c>
       <c r="D71" s="2">
-        <f>100000+C71*1000+B71</f>
+        <f t="shared" si="3"/>
         <v>101015</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="G71" s="2">
         <v>201013</v>
       </c>
       <c r="H71" s="2"/>
       <c r="I71" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="72" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="72" s="2" customFormat="1" spans="1:9">
       <c r="A72" s="2">
         <f t="shared" si="5"/>
         <v>1016</v>
@@ -3907,24 +3892,24 @@
         <v>1</v>
       </c>
       <c r="D72" s="2">
-        <f>100000+C72*1000+B72</f>
+        <f t="shared" si="3"/>
         <v>101016</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="G72" s="2">
         <v>201014</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="73" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="73" s="2" customFormat="1" spans="1:9">
       <c r="A73" s="2">
         <f t="shared" si="5"/>
         <v>1017</v>
@@ -3937,24 +3922,24 @@
         <v>1</v>
       </c>
       <c r="D73" s="2">
-        <f>100000+C73*1000+B73</f>
+        <f t="shared" si="3"/>
         <v>101017</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G73" s="2">
         <v>201015</v>
       </c>
       <c r="H73" s="2"/>
       <c r="I73" s="2" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="74" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="74" s="2" customFormat="1" spans="1:9">
       <c r="A74" s="2">
         <f t="shared" si="5"/>
         <v>1018</v>
@@ -3967,24 +3952,24 @@
         <v>1</v>
       </c>
       <c r="D74" s="2">
-        <f>100000+C74*1000+B74</f>
+        <f t="shared" si="3"/>
         <v>101018</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="G74" s="2">
         <v>201016</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="75" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="75" s="2" customFormat="1" spans="1:9">
       <c r="A75" s="2">
         <f t="shared" si="5"/>
         <v>1019</v>
@@ -3997,24 +3982,24 @@
         <v>1</v>
       </c>
       <c r="D75" s="2">
-        <f>100000+C75*1000+B75</f>
+        <f t="shared" si="3"/>
         <v>101019</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="G75" s="2">
         <v>201017</v>
       </c>
       <c r="H75" s="2"/>
       <c r="I75" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="76" s="2" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="76" s="2" customFormat="1" spans="1:9">
       <c r="A76" s="2">
         <f t="shared" si="5"/>
         <v>1020</v>
@@ -4027,26 +4012,26 @@
         <v>1</v>
       </c>
       <c r="D76" s="2">
-        <f>100000+C76*1000+B76</f>
+        <f t="shared" si="3"/>
         <v>101020</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="G76" s="2">
         <v>201018</v>
       </c>
       <c r="H76" s="2"/>
       <c r="I76" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="1:11">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:9">
       <c r="A77" s="1">
-        <f>C77*1000+B77</f>
+        <f t="shared" si="5"/>
         <v>2001</v>
       </c>
       <c r="B77" s="1">
@@ -4061,19 +4046,18 @@
         <v>102001</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>177</v>
+        <v>168</v>
       </c>
       <c r="G77" s="1">
         <v>202001</v>
       </c>
-      <c r="K77" s="3"/>
-    </row>
-    <row r="78" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:9">
       <c r="A78" s="1">
-        <f>C78*1000+B78</f>
+        <f t="shared" si="5"/>
         <v>2002</v>
       </c>
       <c r="B78" s="1">
@@ -4088,17 +4072,16 @@
         <v>102002</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="G78" s="1">
         <v>202002</v>
       </c>
-      <c r="K78" s="3"/>
-    </row>
-    <row r="79" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="79" s="1" customFormat="1" spans="1:9">
       <c r="A79" s="1">
         <f t="shared" ref="A79:A108" si="7">C79*1000+B79</f>
         <v>2003</v>
@@ -4115,17 +4098,16 @@
         <v>102003</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="G79" s="1">
         <v>202003</v>
       </c>
-      <c r="K79" s="3"/>
-    </row>
-    <row r="80" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="80" s="1" customFormat="1" spans="1:9">
       <c r="A80" s="1">
         <f t="shared" si="7"/>
         <v>2004</v>
@@ -4142,17 +4124,16 @@
         <v>102004</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="G80" s="1">
         <v>202004</v>
       </c>
-      <c r="K80" s="3"/>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="81" s="1" customFormat="1" spans="1:7">
       <c r="A81" s="1">
         <f t="shared" si="7"/>
         <v>2005</v>
@@ -4169,17 +4150,16 @@
         <v>102005</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="G81" s="1">
         <v>202005</v>
       </c>
-      <c r="K81" s="3"/>
-    </row>
-    <row r="82" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="82" s="1" customFormat="1" spans="1:7">
       <c r="A82" s="1">
         <f t="shared" si="7"/>
         <v>2006</v>
@@ -4196,17 +4176,16 @@
         <v>102006</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="G82" s="1">
         <v>202006</v>
       </c>
-      <c r="K82" s="3"/>
-    </row>
-    <row r="83" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="83" s="1" customFormat="1" spans="1:7">
       <c r="A83" s="1">
         <f t="shared" si="7"/>
         <v>2007</v>
@@ -4223,17 +4202,16 @@
         <v>102007</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="G83" s="1">
         <v>202007</v>
       </c>
-      <c r="K83" s="3"/>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="84" s="1" customFormat="1" spans="1:7">
       <c r="A84" s="1">
         <f t="shared" si="7"/>
         <v>2008</v>
@@ -4250,17 +4228,16 @@
         <v>102008</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="G84" s="1">
         <v>202008</v>
       </c>
-      <c r="K84" s="3"/>
-    </row>
-    <row r="85" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="85" s="1" customFormat="1" spans="1:7">
       <c r="A85" s="1">
         <f t="shared" si="7"/>
         <v>2009</v>
@@ -4277,17 +4254,16 @@
         <v>102009</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="G85" s="1">
         <v>202009</v>
       </c>
-      <c r="K85" s="3"/>
-    </row>
-    <row r="86" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="86" s="1" customFormat="1" spans="1:7">
       <c r="A86" s="1">
         <f t="shared" si="7"/>
         <v>2010</v>
@@ -4304,17 +4280,16 @@
         <v>102010</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="G86" s="1">
         <v>202010</v>
       </c>
-      <c r="K86" s="3"/>
-    </row>
-    <row r="87" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="87" s="1" customFormat="1" spans="1:7">
       <c r="A87" s="1">
         <f t="shared" si="7"/>
         <v>2011</v>
@@ -4331,17 +4306,16 @@
         <v>102011</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="G87" s="1">
         <v>202011</v>
       </c>
-      <c r="K87" s="3"/>
-    </row>
-    <row r="88" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="88" s="1" customFormat="1" spans="1:7">
       <c r="A88" s="1">
         <f t="shared" si="7"/>
         <v>2012</v>
@@ -4358,17 +4332,16 @@
         <v>102012</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="G88" s="1">
         <v>202012</v>
       </c>
-      <c r="K88" s="3"/>
-    </row>
-    <row r="89" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="89" s="1" customFormat="1" spans="1:7">
       <c r="A89" s="1">
         <f t="shared" si="7"/>
         <v>2013</v>
@@ -4385,17 +4358,16 @@
         <v>102013</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="G89" s="1">
         <v>202013</v>
       </c>
-      <c r="K89" s="3"/>
-    </row>
-    <row r="90" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="90" s="1" customFormat="1" spans="1:7">
       <c r="A90" s="1">
         <f t="shared" si="7"/>
         <v>2014</v>
@@ -4412,17 +4384,16 @@
         <v>102014</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="G90" s="1">
         <v>202014</v>
       </c>
-      <c r="K90" s="3"/>
-    </row>
-    <row r="91" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="91" s="1" customFormat="1" spans="1:7">
       <c r="A91" s="1">
         <f t="shared" si="7"/>
         <v>2015</v>
@@ -4439,17 +4410,16 @@
         <v>102015</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="G91" s="1">
         <v>202015</v>
       </c>
-      <c r="K91" s="3"/>
-    </row>
-    <row r="92" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="92" s="1" customFormat="1" spans="1:7">
       <c r="A92" s="1">
         <f t="shared" si="7"/>
         <v>2016</v>
@@ -4466,17 +4436,16 @@
         <v>102016</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="G92" s="1">
         <v>202016</v>
       </c>
-      <c r="K92" s="3"/>
-    </row>
-    <row r="93" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="93" s="1" customFormat="1" spans="1:7">
       <c r="A93" s="1">
         <f t="shared" si="7"/>
         <v>2017</v>
@@ -4493,17 +4462,16 @@
         <v>102017</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="G93" s="1">
         <v>202017</v>
       </c>
-      <c r="K93" s="3"/>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="94" s="1" customFormat="1" spans="1:7">
       <c r="A94" s="1">
         <f t="shared" si="7"/>
         <v>2018</v>
@@ -4520,17 +4488,16 @@
         <v>102018</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="G94" s="1">
         <v>202018</v>
       </c>
-      <c r="K94" s="3"/>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="95" s="1" customFormat="1" spans="1:7">
       <c r="A95" s="1">
         <f t="shared" si="7"/>
         <v>2019</v>
@@ -4547,17 +4514,16 @@
         <v>102019</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="G95" s="1">
         <v>202019</v>
       </c>
-      <c r="K95" s="3"/>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="96" s="1" customFormat="1" spans="1:7">
       <c r="A96" s="1">
         <f t="shared" si="7"/>
         <v>2020</v>
@@ -4574,17 +4540,16 @@
         <v>102020</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="G96" s="1">
         <v>202020</v>
       </c>
-      <c r="K96" s="3"/>
-    </row>
-    <row r="97" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="97" s="1" customFormat="1" spans="1:10">
       <c r="A97" s="1">
         <f t="shared" si="7"/>
         <v>3001</v>
@@ -4601,10 +4566,10 @@
         <v>103001</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="G97" s="1">
         <v>203001</v>
@@ -4615,7 +4580,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="98" s="1" customFormat="1" spans="1:11">
+    <row r="98" s="1" customFormat="1" spans="1:10">
       <c r="A98" s="1">
         <f t="shared" si="7"/>
         <v>3002</v>
@@ -4632,10 +4597,10 @@
         <v>103002</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G98" s="1">
         <v>203002</v>
@@ -4644,7 +4609,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="99" s="1" customFormat="1" spans="1:11">
+    <row r="99" s="1" customFormat="1" spans="1:10">
       <c r="A99" s="1">
         <f t="shared" si="7"/>
         <v>3003</v>
@@ -4661,10 +4626,10 @@
         <v>103003</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="G99" s="1">
         <v>203003</v>
@@ -4673,7 +4638,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="100" s="1" customFormat="1" spans="1:11">
+    <row r="100" s="1" customFormat="1" spans="1:10">
       <c r="A100" s="1">
         <f t="shared" si="7"/>
         <v>4001</v>
@@ -4690,18 +4655,17 @@
         <v>104001</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="G100" s="1">
         <f t="shared" ref="G100:G109" si="8">200000+A100</f>
         <v>204001</v>
       </c>
-      <c r="K100" s="3"/>
-    </row>
-    <row r="101" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="101" s="1" customFormat="1" spans="1:10">
       <c r="A101" s="1">
         <f t="shared" si="7"/>
         <v>4002</v>
@@ -4718,10 +4682,10 @@
         <v>104002</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G101" s="1">
         <f t="shared" si="8"/>
@@ -4730,9 +4694,8 @@
       <c r="J101" s="1">
         <v>6</v>
       </c>
-      <c r="K101" s="3"/>
-    </row>
-    <row r="102" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="102" s="1" customFormat="1" spans="1:10">
       <c r="A102" s="1">
         <f t="shared" si="7"/>
         <v>4003</v>
@@ -4749,10 +4712,10 @@
         <v>104003</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="G102" s="1">
         <f t="shared" si="8"/>
@@ -4761,9 +4724,8 @@
       <c r="J102" s="1">
         <v>9</v>
       </c>
-      <c r="K102" s="3"/>
-    </row>
-    <row r="103" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="103" s="1" customFormat="1" spans="1:10">
       <c r="A103" s="1">
         <f t="shared" ref="A103:A110" si="9">C103*1000+B103</f>
         <v>5001</v>
@@ -4780,18 +4742,17 @@
         <v>105001</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="G103" s="1">
         <f t="shared" si="8"/>
         <v>205001</v>
       </c>
-      <c r="K103" s="3"/>
-    </row>
-    <row r="104" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="104" s="1" customFormat="1" spans="1:10">
       <c r="A104" s="1">
         <f t="shared" si="9"/>
         <v>5002</v>
@@ -4808,10 +4769,10 @@
         <v>105002</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="G104" s="1">
         <f t="shared" si="8"/>
@@ -4820,9 +4781,8 @@
       <c r="J104" s="1">
         <v>6</v>
       </c>
-      <c r="K104" s="3"/>
-    </row>
-    <row r="105" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="105" s="1" customFormat="1" spans="1:10">
       <c r="A105" s="1">
         <f t="shared" si="9"/>
         <v>5003</v>
@@ -4839,10 +4799,10 @@
         <v>105003</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="G105" s="1">
         <f t="shared" si="8"/>
@@ -4851,9 +4811,8 @@
       <c r="J105" s="1">
         <v>9</v>
       </c>
-      <c r="K105" s="3"/>
-    </row>
-    <row r="106" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="106" s="1" customFormat="1" spans="1:10">
       <c r="A106" s="1">
         <f t="shared" si="9"/>
         <v>6001</v>
@@ -4870,18 +4829,17 @@
         <v>106001</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="G106" s="1">
         <f t="shared" si="8"/>
         <v>206001</v>
       </c>
-      <c r="K106" s="3"/>
-    </row>
-    <row r="107" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="107" s="1" customFormat="1" spans="1:10">
       <c r="A107" s="1">
         <f t="shared" si="9"/>
         <v>6002</v>
@@ -4898,10 +4856,10 @@
         <v>106002</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="G107" s="1">
         <f t="shared" si="8"/>
@@ -4910,9 +4868,8 @@
       <c r="J107" s="1">
         <v>6</v>
       </c>
-      <c r="K107" s="3"/>
-    </row>
-    <row r="108" s="1" customFormat="1" spans="1:11">
+    </row>
+    <row r="108" s="1" customFormat="1" spans="1:10">
       <c r="A108" s="1">
         <f t="shared" si="9"/>
         <v>6003</v>
@@ -4929,10 +4886,10 @@
         <v>106003</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="G108" s="1">
         <f t="shared" si="8"/>
@@ -4941,7 +4898,6 @@
       <c r="J108" s="1">
         <v>9</v>
       </c>
-      <c r="K108" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -142,12 +142,61 @@
         </r>
       </text>
     </comment>
+    <comment ref="K62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+参数1-》类型：1 表示活动(ActivityConfig.xlsx)、2表示功能(GameFunction.xlsx)
+参数2-》类型1 读取 type字段；2类型读取 id 字段 
+参数3-》跳转对象名称，客户端功能界面名称</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="K63" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+参数1-》类型：1 表示活动(ActivityConfig.xlsx)、2表示功能(GameFunction.xlsx)
+参数2-》类型1 读取 type字段；2类型读取 id 字段 
+参数3-》跳转对象名称，客户端功能界面名称
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="229">
   <si>
     <t>id</t>
   </si>
@@ -563,13 +612,16 @@
     <t>frame_801.png</t>
   </si>
   <si>
-    <t>UIDailyBonus</t>
+    <t>1_3_UIDailyBonus</t>
   </si>
   <si>
     <t>头像框-首充专属</t>
   </si>
   <si>
     <t>frame_018.png</t>
+  </si>
+  <si>
+    <t>2_101_UIDailyBonus</t>
   </si>
   <si>
     <t>首充界面是什么？？</t>
@@ -1807,7 +1859,7 @@
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
     <col min="10" max="10" width="8.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7" style="1" customWidth="1"/>
+    <col min="11" max="11" width="18.225" style="1" customWidth="1"/>
     <col min="12" max="12" width="21.4666666666667" style="1" customWidth="1"/>
     <col min="13" max="14" width="12.625" style="1"/>
     <col min="15" max="16" width="9" style="1"/>
@@ -3633,10 +3685,10 @@
         <v>201802</v>
       </c>
       <c r="K63" s="1" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L63" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="64" s="2" customFormat="1" spans="1:12">
@@ -3656,10 +3708,10 @@
         <v>101008</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G64" s="2">
         <v>201006</v>
@@ -3686,10 +3738,10 @@
         <v>101009</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G65" s="2">
         <v>201007</v>
@@ -3716,10 +3768,10 @@
         <v>101010</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G66" s="2">
         <v>201008</v>
@@ -3746,10 +3798,10 @@
         <v>101011</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G67" s="2">
         <v>201009</v>
@@ -3776,10 +3828,10 @@
         <v>101012</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G68" s="2">
         <v>201010</v>
@@ -3806,10 +3858,10 @@
         <v>101013</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G69" s="2">
         <v>201011</v>
@@ -3836,10 +3888,10 @@
         <v>101014</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G70" s="2">
         <v>201012</v>
@@ -3866,10 +3918,10 @@
         <v>101015</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G71" s="2">
         <v>201013</v>
@@ -3896,10 +3948,10 @@
         <v>101016</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G72" s="2">
         <v>201014</v>
@@ -3926,10 +3978,10 @@
         <v>101017</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G73" s="2">
         <v>201015</v>
@@ -3956,10 +4008,10 @@
         <v>101018</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G74" s="2">
         <v>201016</v>
@@ -3986,10 +4038,10 @@
         <v>101019</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G75" s="2">
         <v>201017</v>
@@ -4016,7 +4068,7 @@
         <v>101020</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>140</v>
@@ -4046,10 +4098,10 @@
         <v>102001</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G77" s="1">
         <v>202001</v>
@@ -4072,10 +4124,10 @@
         <v>102002</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G78" s="1">
         <v>202002</v>
@@ -4098,10 +4150,10 @@
         <v>102003</v>
       </c>
       <c r="E79" s="1" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="G79" s="1">
         <v>202003</v>
@@ -4124,10 +4176,10 @@
         <v>102004</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="G80" s="1">
         <v>202004</v>
@@ -4150,10 +4202,10 @@
         <v>102005</v>
       </c>
       <c r="E81" s="1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F81" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G81" s="1">
         <v>202005</v>
@@ -4176,10 +4228,10 @@
         <v>102006</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F82" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="G82" s="1">
         <v>202006</v>
@@ -4202,10 +4254,10 @@
         <v>102007</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F83" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="G83" s="1">
         <v>202007</v>
@@ -4228,10 +4280,10 @@
         <v>102008</v>
       </c>
       <c r="E84" s="1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F84" s="1" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G84" s="1">
         <v>202008</v>
@@ -4254,10 +4306,10 @@
         <v>102009</v>
       </c>
       <c r="E85" s="1" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="G85" s="1">
         <v>202009</v>
@@ -4280,10 +4332,10 @@
         <v>102010</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G86" s="1">
         <v>202010</v>
@@ -4306,10 +4358,10 @@
         <v>102011</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F87" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="G87" s="1">
         <v>202011</v>
@@ -4332,10 +4384,10 @@
         <v>102012</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G88" s="1">
         <v>202012</v>
@@ -4358,10 +4410,10 @@
         <v>102013</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="G89" s="1">
         <v>202013</v>
@@ -4384,10 +4436,10 @@
         <v>102014</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G90" s="1">
         <v>202014</v>
@@ -4410,10 +4462,10 @@
         <v>102015</v>
       </c>
       <c r="E91" s="1" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G91" s="1">
         <v>202015</v>
@@ -4436,10 +4488,10 @@
         <v>102016</v>
       </c>
       <c r="E92" s="1" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G92" s="1">
         <v>202016</v>
@@ -4462,10 +4514,10 @@
         <v>102017</v>
       </c>
       <c r="E93" s="1" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G93" s="1">
         <v>202017</v>
@@ -4488,10 +4540,10 @@
         <v>102018</v>
       </c>
       <c r="E94" s="1" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G94" s="1">
         <v>202018</v>
@@ -4514,10 +4566,10 @@
         <v>102019</v>
       </c>
       <c r="E95" s="1" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G95" s="1">
         <v>202019</v>
@@ -4540,10 +4592,10 @@
         <v>102020</v>
       </c>
       <c r="E96" s="1" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="G96" s="1">
         <v>202020</v>
@@ -4566,10 +4618,10 @@
         <v>103001</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="G97" s="1">
         <v>203001</v>
@@ -4597,10 +4649,10 @@
         <v>103002</v>
       </c>
       <c r="E98" s="1" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G98" s="1">
         <v>203002</v>
@@ -4626,10 +4678,10 @@
         <v>103003</v>
       </c>
       <c r="E99" s="1" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G99" s="1">
         <v>203003</v>
@@ -4655,10 +4707,10 @@
         <v>104001</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G100" s="1">
         <f t="shared" ref="G100:G109" si="8">200000+A100</f>
@@ -4682,10 +4734,10 @@
         <v>104002</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G101" s="1">
         <f t="shared" si="8"/>
@@ -4712,10 +4764,10 @@
         <v>104003</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G102" s="1">
         <f t="shared" si="8"/>
@@ -4742,10 +4794,10 @@
         <v>105001</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G103" s="1">
         <f t="shared" si="8"/>
@@ -4769,10 +4821,10 @@
         <v>105002</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G104" s="1">
         <f t="shared" si="8"/>
@@ -4799,10 +4851,10 @@
         <v>105003</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G105" s="1">
         <f t="shared" si="8"/>
@@ -4829,10 +4881,10 @@
         <v>106001</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G106" s="1">
         <f t="shared" si="8"/>
@@ -4856,10 +4908,10 @@
         <v>106002</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G107" s="1">
         <f t="shared" si="8"/>
@@ -4886,10 +4938,10 @@
         <v>106003</v>
       </c>
       <c r="E108" s="1" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G108" s="1">
         <f t="shared" si="8"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -142,7 +142,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K62" authorId="0">
+    <comment ref="K61" authorId="0">
       <text>
         <r>
           <rPr>
@@ -166,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K63" authorId="0">
+    <comment ref="K62" authorId="0">
       <text>
         <r>
           <rPr>
@@ -196,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="226">
   <si>
     <t>id</t>
   </si>
@@ -213,13 +213,13 @@
     <t>资源描述</t>
   </si>
   <si>
-    <t>等级</t>
+    <t>角色等级</t>
   </si>
   <si>
     <t>货币购买</t>
   </si>
   <si>
-    <t>VIP条件</t>
+    <t>VIP条件(仅显示用)</t>
   </si>
   <si>
     <t>跳转路径</t>
@@ -501,7 +501,7 @@
     <t>HeadDia_001.png</t>
   </si>
   <si>
-    <t>1980000_1500</t>
+    <t>1980000_1800</t>
   </si>
   <si>
     <t>头像41</t>
@@ -552,9 +552,6 @@
     <t>HeadDia_009.png</t>
   </si>
   <si>
-    <t>头像49</t>
-  </si>
-  <si>
     <t>HeadDia_010.png</t>
   </si>
   <si>
@@ -600,33 +597,30 @@
     <t>frame_004.png</t>
   </si>
   <si>
+    <t>头像框-每日奖金</t>
+  </si>
+  <si>
+    <t>frame_801.png</t>
+  </si>
+  <si>
+    <t>1_2_UIDailyBonus</t>
+  </si>
+  <si>
+    <t>头像框-首充专属</t>
+  </si>
+  <si>
+    <t>frame_018.png</t>
+  </si>
+  <si>
+    <t>1_11_UIFirstRecharge</t>
+  </si>
+  <si>
     <t>头像框5</t>
   </si>
   <si>
     <t>frame_005.png</t>
   </si>
   <si>
-    <t>头像框-每日奖金</t>
-  </si>
-  <si>
-    <t>frame_801.png</t>
-  </si>
-  <si>
-    <t>1_3_UIDailyBonus</t>
-  </si>
-  <si>
-    <t>头像框-首充专属</t>
-  </si>
-  <si>
-    <t>frame_018.png</t>
-  </si>
-  <si>
-    <t>2_101_UIDailyBonus</t>
-  </si>
-  <si>
-    <t>首充界面是什么？？</t>
-  </si>
-  <si>
     <t>头像框6</t>
   </si>
   <si>
@@ -697,9 +691,6 @@
   </si>
   <si>
     <t>frame_017.png</t>
-  </si>
-  <si>
-    <t>头像框18</t>
   </si>
   <si>
     <t>国旗1</t>
@@ -1060,12 +1051,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1588,6 +1579,15 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1847,7 +1847,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L108"/>
+  <dimension ref="A1:L107"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -1858,8 +1858,8 @@
     <col min="7" max="7" width="12.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1" customWidth="1"/>
     <col min="9" max="9" width="20.875" style="1" customWidth="1"/>
-    <col min="10" max="10" width="8.875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="18.225" style="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5" style="1" customWidth="1"/>
+    <col min="11" max="11" width="24.4083333333333" style="1" customWidth="1"/>
     <col min="12" max="12" width="21.4666666666667" style="1" customWidth="1"/>
     <col min="13" max="14" width="12.625" style="1"/>
     <col min="15" max="16" width="9" style="1"/>
@@ -1985,6 +1985,9 @@
       <c r="G5" s="1">
         <v>200001</v>
       </c>
+      <c r="H5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" s="1" customFormat="1" spans="1:12">
       <c r="A6" s="1">
@@ -1999,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="D6" s="1">
-        <f t="shared" ref="D6:D38" si="1">100000+C6*1000+B6</f>
+        <f t="shared" ref="D6:D47" si="1">100000+C6*1000+B6</f>
         <v>100002</v>
       </c>
       <c r="E6" s="1" t="s">
@@ -2010,6 +2013,9 @@
       </c>
       <c r="G6" s="1">
         <v>200017</v>
+      </c>
+      <c r="H6" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="7" s="1" customFormat="1" spans="1:12">
@@ -2884,7 +2890,7 @@
     </row>
     <row r="37" s="1" customFormat="1" spans="1:10">
       <c r="A37" s="1">
-        <f t="shared" ref="A37:A61" si="2">C37*1000+B37</f>
+        <f t="shared" ref="A37:A63" si="2">C37*1000+B37</f>
         <v>33</v>
       </c>
       <c r="B37" s="1">
@@ -2953,7 +2959,7 @@
         <v>0</v>
       </c>
       <c r="D39" s="1">
-        <f t="shared" ref="D39:D76" si="3">100000+C39*1000+B39</f>
+        <f t="shared" si="1"/>
         <v>100035</v>
       </c>
       <c r="E39" s="1" t="s">
@@ -2982,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="D40" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100036</v>
       </c>
       <c r="E40" s="1" t="s">
@@ -3011,7 +3017,7 @@
         <v>0</v>
       </c>
       <c r="D41" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100037</v>
       </c>
       <c r="E41" s="1" t="s">
@@ -3040,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="D42" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100038</v>
       </c>
       <c r="E42" s="1" t="s">
@@ -3069,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="D43" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100039</v>
       </c>
       <c r="E43" s="1" t="s">
@@ -3098,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="D44" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100040</v>
       </c>
       <c r="E44" s="2" t="s">
@@ -3129,7 +3135,7 @@
         <v>0</v>
       </c>
       <c r="D45" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100041</v>
       </c>
       <c r="E45" s="2" t="s">
@@ -3160,7 +3166,7 @@
         <v>0</v>
       </c>
       <c r="D46" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100042</v>
       </c>
       <c r="E46" s="2" t="s">
@@ -3191,7 +3197,7 @@
         <v>0</v>
       </c>
       <c r="D47" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="1"/>
         <v>100043</v>
       </c>
       <c r="E47" s="2" t="s">
@@ -3222,7 +3228,7 @@
         <v>0</v>
       </c>
       <c r="D48" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D48:D53" si="3">100000+C48*1000+B48</f>
         <v>100044</v>
       </c>
       <c r="E48" s="2" t="s">
@@ -3240,7 +3246,7 @@
       </c>
       <c r="J48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1" spans="1:12">
+    <row r="49" s="1" customFormat="1" spans="1:11">
       <c r="A49" s="2">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -3271,7 +3277,7 @@
       </c>
       <c r="J49" s="2"/>
     </row>
-    <row r="50" s="1" customFormat="1" spans="1:12">
+    <row r="50" s="1" customFormat="1" spans="1:11">
       <c r="A50" s="2">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -3302,7 +3308,7 @@
       </c>
       <c r="J50" s="2"/>
     </row>
-    <row r="51" s="1" customFormat="1" spans="1:12">
+    <row r="51" s="1" customFormat="1" spans="1:11">
       <c r="A51" s="2">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -3333,7 +3339,7 @@
       </c>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" s="1" customFormat="1" spans="1:12">
+    <row r="52" s="1" customFormat="1" spans="1:11">
       <c r="A52" s="2">
         <f t="shared" si="2"/>
         <v>48</v>
@@ -3364,7 +3370,7 @@
       </c>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" s="1" customFormat="1" spans="1:12">
+    <row r="53" s="1" customFormat="1" spans="1:11">
       <c r="A53" s="2">
         <f t="shared" si="2"/>
         <v>49</v>
@@ -3381,10 +3387,10 @@
         <v>100049</v>
       </c>
       <c r="E53" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F53" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="F53" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="G53" s="2">
         <v>200036</v>
@@ -3395,7 +3401,7 @@
       </c>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" s="1" customFormat="1" spans="1:12">
+    <row r="54" s="1" customFormat="1" spans="1:11">
       <c r="A54" s="2">
         <f t="shared" si="2"/>
         <v>50</v>
@@ -3408,14 +3414,14 @@
         <v>0</v>
       </c>
       <c r="D54" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" ref="D54:D76" si="4">100000+C54*1000+B54</f>
         <v>100050</v>
       </c>
       <c r="E54" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F54" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="F54" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="G54" s="2">
         <v>200037</v>
@@ -3426,7 +3432,7 @@
       </c>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" s="1" customFormat="1" spans="1:12">
+    <row r="55" s="1" customFormat="1" spans="1:11">
       <c r="A55" s="2">
         <f t="shared" si="2"/>
         <v>51</v>
@@ -3439,14 +3445,14 @@
         <v>0</v>
       </c>
       <c r="D55" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>100051</v>
       </c>
       <c r="E55" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F55" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="F55" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="G55" s="2">
         <v>200038</v>
@@ -3457,7 +3463,7 @@
       </c>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" s="1" customFormat="1" spans="1:12">
+    <row r="56" s="1" customFormat="1" spans="1:11">
       <c r="A56" s="2">
         <f t="shared" si="2"/>
         <v>52</v>
@@ -3470,14 +3476,14 @@
         <v>0</v>
       </c>
       <c r="D56" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>100052</v>
       </c>
       <c r="E56" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F56" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="G56" s="2">
         <v>200039</v>
@@ -3488,7 +3494,7 @@
       </c>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="1:12">
+    <row r="57" spans="1:11">
       <c r="A57" s="1">
         <f t="shared" si="2"/>
         <v>1001</v>
@@ -3501,20 +3507,23 @@
         <v>1</v>
       </c>
       <c r="D57" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101001</v>
       </c>
       <c r="E57" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="F57" s="1" t="s">
         <v>126</v>
-      </c>
-      <c r="F57" s="1" t="s">
-        <v>127</v>
       </c>
       <c r="G57" s="1">
         <v>201001</v>
       </c>
-    </row>
-    <row r="58" spans="1:12">
+      <c r="H57" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" s="1">
         <f t="shared" si="2"/>
         <v>1002</v>
@@ -3527,14 +3536,14 @@
         <v>1</v>
       </c>
       <c r="D58" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101002</v>
       </c>
       <c r="E58" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="F58" s="1" t="s">
         <v>128</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>129</v>
       </c>
       <c r="G58" s="1">
         <v>201002</v>
@@ -3543,7 +3552,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:12">
+    <row r="59" spans="1:11">
       <c r="A59" s="1">
         <f t="shared" si="2"/>
         <v>1003</v>
@@ -3556,23 +3565,23 @@
         <v>1</v>
       </c>
       <c r="D59" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101003</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>130</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>131</v>
       </c>
       <c r="G59" s="1">
         <v>201003</v>
       </c>
-      <c r="J59" s="1">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12">
+      <c r="H59" s="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" s="1">
         <f t="shared" si="2"/>
         <v>1004</v>
@@ -3585,25 +3594,25 @@
         <v>1</v>
       </c>
       <c r="D60" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101004</v>
       </c>
       <c r="E60" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F60" s="1" t="s">
         <v>132</v>
-      </c>
-      <c r="F60" s="1" t="s">
-        <v>133</v>
       </c>
       <c r="G60" s="1">
         <v>201004</v>
       </c>
-      <c r="J60" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12">
+      <c r="H60" s="1">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="61" s="1" customFormat="1" spans="1:11">
       <c r="A61" s="1">
-        <f t="shared" ref="A61:A63" si="4">C61*1000+B61</f>
+        <f t="shared" si="2"/>
         <v>1005</v>
       </c>
       <c r="B61" s="1">
@@ -3614,25 +3623,25 @@
         <v>1</v>
       </c>
       <c r="D61" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101005</v>
       </c>
       <c r="E61" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>134</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="G61" s="1">
+        <v>201801</v>
+      </c>
+      <c r="K61" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="G61" s="1">
-        <v>201005</v>
-      </c>
-      <c r="J61" s="1">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="62" s="1" customFormat="1" spans="1:12">
+    </row>
+    <row r="62" s="1" customFormat="1" spans="1:11">
       <c r="A62" s="1">
-        <f t="shared" si="4"/>
+        <f t="shared" si="2"/>
         <v>1006</v>
       </c>
       <c r="B62" s="1">
@@ -3643,7 +3652,7 @@
         <v>1</v>
       </c>
       <c r="D62" s="1">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101006</v>
       </c>
       <c r="E62" s="1" t="s">
@@ -3653,45 +3662,43 @@
         <v>137</v>
       </c>
       <c r="G62" s="1">
-        <v>201801</v>
+        <v>201802</v>
       </c>
       <c r="K62" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="63" s="1" customFormat="1" spans="1:12">
-      <c r="A63" s="1">
-        <f t="shared" si="4"/>
+    <row r="63" spans="1:11">
+      <c r="A63" s="2">
+        <f t="shared" si="2"/>
         <v>1007</v>
       </c>
-      <c r="B63" s="1">
+      <c r="B63" s="2">
         <f>COUNTIF($C$1:C63,C63)</f>
         <v>7</v>
       </c>
-      <c r="C63" s="1">
+      <c r="C63" s="2">
         <v>1</v>
       </c>
-      <c r="D63" s="1">
-        <f t="shared" si="3"/>
+      <c r="D63" s="2">
+        <f t="shared" si="4"/>
         <v>101007</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G63" s="1">
-        <v>201802</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="L63" s="1" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="64" s="2" customFormat="1" spans="1:12">
+      <c r="G63" s="2">
+        <v>201005</v>
+      </c>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="64" s="2" customFormat="1" spans="1:11">
       <c r="A64" s="2">
         <f t="shared" ref="A64:A78" si="5">C64*1000+B64</f>
         <v>1008</v>
@@ -3704,14 +3711,14 @@
         <v>1</v>
       </c>
       <c r="D64" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101008</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G64" s="2">
         <v>201006</v>
@@ -3734,14 +3741,14 @@
         <v>1</v>
       </c>
       <c r="D65" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101009</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="G65" s="2">
         <v>201007</v>
@@ -3764,14 +3771,14 @@
         <v>1</v>
       </c>
       <c r="D66" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101010</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="G66" s="2">
         <v>201008</v>
@@ -3794,14 +3801,14 @@
         <v>1</v>
       </c>
       <c r="D67" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101011</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="G67" s="2">
         <v>201009</v>
@@ -3824,14 +3831,14 @@
         <v>1</v>
       </c>
       <c r="D68" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101012</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G68" s="2">
         <v>201010</v>
@@ -3854,14 +3861,14 @@
         <v>1</v>
       </c>
       <c r="D69" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101013</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G69" s="2">
         <v>201011</v>
@@ -3884,14 +3891,14 @@
         <v>1</v>
       </c>
       <c r="D70" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101014</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G70" s="2">
         <v>201012</v>
@@ -3914,14 +3921,14 @@
         <v>1</v>
       </c>
       <c r="D71" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101015</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G71" s="2">
         <v>201013</v>
@@ -3944,14 +3951,14 @@
         <v>1</v>
       </c>
       <c r="D72" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101016</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G72" s="2">
         <v>201014</v>
@@ -3974,14 +3981,14 @@
         <v>1</v>
       </c>
       <c r="D73" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101017</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G73" s="2">
         <v>201015</v>
@@ -4004,14 +4011,14 @@
         <v>1</v>
       </c>
       <c r="D74" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101018</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G74" s="2">
         <v>201016</v>
@@ -4034,14 +4041,14 @@
         <v>1</v>
       </c>
       <c r="D75" s="2">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>101019</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G75" s="2">
         <v>201017</v>
@@ -4051,907 +4058,883 @@
         <v>101</v>
       </c>
     </row>
-    <row r="76" s="2" customFormat="1" spans="1:9">
-      <c r="A76" s="2">
+    <row r="76" s="1" customFormat="1" spans="1:9">
+      <c r="A76" s="1">
         <f t="shared" si="5"/>
-        <v>1020</v>
-      </c>
-      <c r="B76" s="2">
+        <v>2001</v>
+      </c>
+      <c r="B76" s="1">
         <f>COUNTIF($C$1:C76,C76)</f>
-        <v>20</v>
-      </c>
-      <c r="C76" s="2">
         <v>1</v>
       </c>
-      <c r="D76" s="2">
-        <f t="shared" si="3"/>
-        <v>101020</v>
-      </c>
-      <c r="E76" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F76" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="G76" s="2">
-        <v>201018</v>
-      </c>
-      <c r="H76" s="2"/>
-      <c r="I76" s="2" t="s">
-        <v>101</v>
+      <c r="C76" s="1">
+        <v>2</v>
+      </c>
+      <c r="D76" s="1">
+        <f t="shared" ref="D76:D107" si="6">100000+C76*1000+B76</f>
+        <v>102001</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F76" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G76" s="1">
+        <v>202001</v>
       </c>
     </row>
     <row r="77" s="1" customFormat="1" spans="1:9">
       <c r="A77" s="1">
         <f t="shared" si="5"/>
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="B77" s="1">
         <f>COUNTIF($C$1:C77,C77)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C77" s="1">
         <v>2</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" ref="D77:D108" si="6">100000+C77*1000+B77</f>
-        <v>102001</v>
+        <f t="shared" si="6"/>
+        <v>102002</v>
       </c>
       <c r="E77" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="F77" s="1" t="s">
         <v>168</v>
       </c>
-      <c r="F77" s="1" t="s">
-        <v>169</v>
-      </c>
       <c r="G77" s="1">
-        <v>202001</v>
+        <v>202002</v>
       </c>
     </row>
     <row r="78" s="1" customFormat="1" spans="1:9">
       <c r="A78" s="1">
-        <f t="shared" si="5"/>
-        <v>2002</v>
+        <f t="shared" ref="A78:A107" si="7">C78*1000+B78</f>
+        <v>2003</v>
       </c>
       <c r="B78" s="1">
         <f>COUNTIF($C$1:C78,C78)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C78" s="1">
         <v>2</v>
       </c>
       <c r="D78" s="1">
         <f t="shared" si="6"/>
-        <v>102002</v>
+        <v>102003</v>
       </c>
       <c r="E78" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F78" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="F78" s="1" t="s">
-        <v>171</v>
-      </c>
       <c r="G78" s="1">
-        <v>202002</v>
+        <v>202003</v>
       </c>
     </row>
     <row r="79" s="1" customFormat="1" spans="1:9">
       <c r="A79" s="1">
-        <f t="shared" ref="A79:A108" si="7">C79*1000+B79</f>
-        <v>2003</v>
+        <f t="shared" si="7"/>
+        <v>2004</v>
       </c>
       <c r="B79" s="1">
         <f>COUNTIF($C$1:C79,C79)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C79" s="1">
         <v>2</v>
       </c>
       <c r="D79" s="1">
         <f t="shared" si="6"/>
-        <v>102003</v>
+        <v>102004</v>
       </c>
       <c r="E79" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="F79" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="F79" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="G79" s="1">
-        <v>202003</v>
+        <v>202004</v>
       </c>
     </row>
     <row r="80" s="1" customFormat="1" spans="1:9">
       <c r="A80" s="1">
         <f t="shared" si="7"/>
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="B80" s="1">
         <f>COUNTIF($C$1:C80,C80)</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C80" s="1">
         <v>2</v>
       </c>
       <c r="D80" s="1">
         <f t="shared" si="6"/>
-        <v>102004</v>
+        <v>102005</v>
       </c>
       <c r="E80" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F80" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="F80" s="1" t="s">
-        <v>175</v>
-      </c>
       <c r="G80" s="1">
-        <v>202004</v>
-      </c>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="1:7">
+        <v>202005</v>
+      </c>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="1:10">
       <c r="A81" s="1">
         <f t="shared" si="7"/>
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="B81" s="1">
         <f>COUNTIF($C$1:C81,C81)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C81" s="1">
         <v>2</v>
       </c>
       <c r="D81" s="1">
         <f t="shared" si="6"/>
-        <v>102005</v>
+        <v>102006</v>
       </c>
       <c r="E81" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="F81" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="F81" s="1" t="s">
-        <v>177</v>
-      </c>
       <c r="G81" s="1">
-        <v>202005</v>
-      </c>
-    </row>
-    <row r="82" s="1" customFormat="1" spans="1:7">
+        <v>202006</v>
+      </c>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="1:10">
       <c r="A82" s="1">
         <f t="shared" si="7"/>
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="B82" s="1">
         <f>COUNTIF($C$1:C82,C82)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C82" s="1">
         <v>2</v>
       </c>
       <c r="D82" s="1">
         <f t="shared" si="6"/>
-        <v>102006</v>
+        <v>102007</v>
       </c>
       <c r="E82" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F82" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F82" s="1" t="s">
-        <v>179</v>
-      </c>
       <c r="G82" s="1">
-        <v>202006</v>
-      </c>
-    </row>
-    <row r="83" s="1" customFormat="1" spans="1:7">
+        <v>202007</v>
+      </c>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="1:10">
       <c r="A83" s="1">
         <f t="shared" si="7"/>
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="B83" s="1">
         <f>COUNTIF($C$1:C83,C83)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C83" s="1">
         <v>2</v>
       </c>
       <c r="D83" s="1">
         <f t="shared" si="6"/>
-        <v>102007</v>
+        <v>102008</v>
       </c>
       <c r="E83" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="F83" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="F83" s="1" t="s">
-        <v>181</v>
-      </c>
       <c r="G83" s="1">
-        <v>202007</v>
-      </c>
-    </row>
-    <row r="84" s="1" customFormat="1" spans="1:7">
+        <v>202008</v>
+      </c>
+    </row>
+    <row r="84" s="1" customFormat="1" spans="1:10">
       <c r="A84" s="1">
         <f t="shared" si="7"/>
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="B84" s="1">
         <f>COUNTIF($C$1:C84,C84)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C84" s="1">
         <v>2</v>
       </c>
       <c r="D84" s="1">
         <f t="shared" si="6"/>
-        <v>102008</v>
+        <v>102009</v>
       </c>
       <c r="E84" s="1" t="s">
+        <v>181</v>
+      </c>
+      <c r="F84" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="F84" s="1" t="s">
-        <v>183</v>
-      </c>
       <c r="G84" s="1">
-        <v>202008</v>
-      </c>
-    </row>
-    <row r="85" s="1" customFormat="1" spans="1:7">
+        <v>202009</v>
+      </c>
+    </row>
+    <row r="85" s="1" customFormat="1" spans="1:10">
       <c r="A85" s="1">
         <f t="shared" si="7"/>
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="B85" s="1">
         <f>COUNTIF($C$1:C85,C85)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C85" s="1">
         <v>2</v>
       </c>
       <c r="D85" s="1">
         <f t="shared" si="6"/>
-        <v>102009</v>
+        <v>102010</v>
       </c>
       <c r="E85" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="F85" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="F85" s="1" t="s">
-        <v>185</v>
-      </c>
       <c r="G85" s="1">
-        <v>202009</v>
-      </c>
-    </row>
-    <row r="86" s="1" customFormat="1" spans="1:7">
+        <v>202010</v>
+      </c>
+    </row>
+    <row r="86" s="1" customFormat="1" spans="1:10">
       <c r="A86" s="1">
         <f t="shared" si="7"/>
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="B86" s="1">
         <f>COUNTIF($C$1:C86,C86)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C86" s="1">
         <v>2</v>
       </c>
       <c r="D86" s="1">
         <f t="shared" si="6"/>
-        <v>102010</v>
+        <v>102011</v>
       </c>
       <c r="E86" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="F86" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F86" s="1" t="s">
-        <v>187</v>
-      </c>
       <c r="G86" s="1">
-        <v>202010</v>
-      </c>
-    </row>
-    <row r="87" s="1" customFormat="1" spans="1:7">
+        <v>202011</v>
+      </c>
+    </row>
+    <row r="87" s="1" customFormat="1" spans="1:10">
       <c r="A87" s="1">
         <f t="shared" si="7"/>
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="B87" s="1">
         <f>COUNTIF($C$1:C87,C87)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C87" s="1">
         <v>2</v>
       </c>
       <c r="D87" s="1">
         <f t="shared" si="6"/>
-        <v>102011</v>
+        <v>102012</v>
       </c>
       <c r="E87" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F87" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F87" s="1" t="s">
-        <v>189</v>
-      </c>
       <c r="G87" s="1">
-        <v>202011</v>
-      </c>
-    </row>
-    <row r="88" s="1" customFormat="1" spans="1:7">
+        <v>202012</v>
+      </c>
+    </row>
+    <row r="88" s="1" customFormat="1" spans="1:10">
       <c r="A88" s="1">
         <f t="shared" si="7"/>
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="B88" s="1">
         <f>COUNTIF($C$1:C88,C88)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C88" s="1">
         <v>2</v>
       </c>
       <c r="D88" s="1">
         <f t="shared" si="6"/>
-        <v>102012</v>
+        <v>102013</v>
       </c>
       <c r="E88" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="F88" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F88" s="1" t="s">
-        <v>191</v>
-      </c>
       <c r="G88" s="1">
-        <v>202012</v>
-      </c>
-    </row>
-    <row r="89" s="1" customFormat="1" spans="1:7">
+        <v>202013</v>
+      </c>
+    </row>
+    <row r="89" s="1" customFormat="1" spans="1:10">
       <c r="A89" s="1">
         <f t="shared" si="7"/>
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="B89" s="1">
         <f>COUNTIF($C$1:C89,C89)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C89" s="1">
         <v>2</v>
       </c>
       <c r="D89" s="1">
         <f t="shared" si="6"/>
-        <v>102013</v>
+        <v>102014</v>
       </c>
       <c r="E89" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F89" s="1" t="s">
         <v>192</v>
       </c>
-      <c r="F89" s="1" t="s">
-        <v>193</v>
-      </c>
       <c r="G89" s="1">
-        <v>202013</v>
-      </c>
-    </row>
-    <row r="90" s="1" customFormat="1" spans="1:7">
+        <v>202014</v>
+      </c>
+    </row>
+    <row r="90" s="1" customFormat="1" spans="1:10">
       <c r="A90" s="1">
         <f t="shared" si="7"/>
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="B90" s="1">
         <f>COUNTIF($C$1:C90,C90)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C90" s="1">
         <v>2</v>
       </c>
       <c r="D90" s="1">
         <f t="shared" si="6"/>
-        <v>102014</v>
+        <v>102015</v>
       </c>
       <c r="E90" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="F90" s="1" t="s">
         <v>194</v>
       </c>
-      <c r="F90" s="1" t="s">
-        <v>195</v>
-      </c>
       <c r="G90" s="1">
-        <v>202014</v>
-      </c>
-    </row>
-    <row r="91" s="1" customFormat="1" spans="1:7">
+        <v>202015</v>
+      </c>
+    </row>
+    <row r="91" s="1" customFormat="1" spans="1:10">
       <c r="A91" s="1">
         <f t="shared" si="7"/>
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="B91" s="1">
         <f>COUNTIF($C$1:C91,C91)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C91" s="1">
         <v>2</v>
       </c>
       <c r="D91" s="1">
         <f t="shared" si="6"/>
-        <v>102015</v>
+        <v>102016</v>
       </c>
       <c r="E91" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="F91" s="1" t="s">
         <v>196</v>
       </c>
-      <c r="F91" s="1" t="s">
-        <v>197</v>
-      </c>
       <c r="G91" s="1">
-        <v>202015</v>
-      </c>
-    </row>
-    <row r="92" s="1" customFormat="1" spans="1:7">
+        <v>202016</v>
+      </c>
+    </row>
+    <row r="92" s="1" customFormat="1" spans="1:10">
       <c r="A92" s="1">
         <f t="shared" si="7"/>
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="B92" s="1">
         <f>COUNTIF($C$1:C92,C92)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C92" s="1">
         <v>2</v>
       </c>
       <c r="D92" s="1">
         <f t="shared" si="6"/>
-        <v>102016</v>
+        <v>102017</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="F92" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="F92" s="1" t="s">
-        <v>199</v>
-      </c>
       <c r="G92" s="1">
-        <v>202016</v>
-      </c>
-    </row>
-    <row r="93" s="1" customFormat="1" spans="1:7">
+        <v>202017</v>
+      </c>
+    </row>
+    <row r="93" s="1" customFormat="1" spans="1:10">
       <c r="A93" s="1">
         <f t="shared" si="7"/>
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="B93" s="1">
         <f>COUNTIF($C$1:C93,C93)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C93" s="1">
         <v>2</v>
       </c>
       <c r="D93" s="1">
         <f t="shared" si="6"/>
-        <v>102017</v>
+        <v>102018</v>
       </c>
       <c r="E93" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="F93" s="1" t="s">
         <v>200</v>
       </c>
-      <c r="F93" s="1" t="s">
-        <v>201</v>
-      </c>
       <c r="G93" s="1">
-        <v>202017</v>
-      </c>
-    </row>
-    <row r="94" s="1" customFormat="1" spans="1:7">
+        <v>202018</v>
+      </c>
+    </row>
+    <row r="94" s="1" customFormat="1" spans="1:10">
       <c r="A94" s="1">
         <f t="shared" si="7"/>
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="B94" s="1">
         <f>COUNTIF($C$1:C94,C94)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C94" s="1">
         <v>2</v>
       </c>
       <c r="D94" s="1">
         <f t="shared" si="6"/>
-        <v>102018</v>
+        <v>102019</v>
       </c>
       <c r="E94" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="F94" s="1" t="s">
         <v>202</v>
       </c>
-      <c r="F94" s="1" t="s">
-        <v>203</v>
-      </c>
       <c r="G94" s="1">
-        <v>202018</v>
-      </c>
-    </row>
-    <row r="95" s="1" customFormat="1" spans="1:7">
+        <v>202019</v>
+      </c>
+    </row>
+    <row r="95" s="1" customFormat="1" spans="1:10">
       <c r="A95" s="1">
         <f t="shared" si="7"/>
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="B95" s="1">
         <f>COUNTIF($C$1:C95,C95)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C95" s="1">
         <v>2</v>
       </c>
       <c r="D95" s="1">
         <f t="shared" si="6"/>
-        <v>102019</v>
+        <v>102020</v>
       </c>
       <c r="E95" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="F95" s="1" t="s">
         <v>204</v>
       </c>
-      <c r="F95" s="1" t="s">
-        <v>205</v>
-      </c>
       <c r="G95" s="1">
-        <v>202019</v>
-      </c>
-    </row>
-    <row r="96" s="1" customFormat="1" spans="1:7">
+        <v>202020</v>
+      </c>
+    </row>
+    <row r="96" s="1" customFormat="1" spans="1:10">
       <c r="A96" s="1">
         <f t="shared" si="7"/>
-        <v>2020</v>
+        <v>3001</v>
       </c>
       <c r="B96" s="1">
         <f>COUNTIF($C$1:C96,C96)</f>
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C96" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D96" s="1">
         <f t="shared" si="6"/>
-        <v>102020</v>
+        <v>103001</v>
       </c>
       <c r="E96" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="F96" s="1" t="s">
         <v>206</v>
       </c>
-      <c r="F96" s="1" t="s">
-        <v>207</v>
-      </c>
       <c r="G96" s="1">
-        <v>202020</v>
+        <v>203001</v>
+      </c>
+      <c r="H96" s="1"/>
+      <c r="I96" s="1"/>
+      <c r="J96" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="1:10">
       <c r="A97" s="1">
         <f t="shared" si="7"/>
-        <v>3001</v>
+        <v>3002</v>
       </c>
       <c r="B97" s="1">
         <f>COUNTIF($C$1:C97,C97)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C97" s="1">
         <v>3</v>
       </c>
       <c r="D97" s="1">
         <f t="shared" si="6"/>
-        <v>103001</v>
+        <v>103002</v>
       </c>
       <c r="E97" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="F97" s="1" t="s">
         <v>208</v>
       </c>
-      <c r="F97" s="1" t="s">
-        <v>209</v>
-      </c>
       <c r="G97" s="1">
-        <v>203001</v>
-      </c>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
+        <v>203002</v>
+      </c>
       <c r="J97" s="1">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="1:10">
       <c r="A98" s="1">
         <f t="shared" si="7"/>
-        <v>3002</v>
+        <v>3003</v>
       </c>
       <c r="B98" s="1">
         <f>COUNTIF($C$1:C98,C98)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C98" s="1">
         <v>3</v>
       </c>
       <c r="D98" s="1">
         <f t="shared" si="6"/>
-        <v>103002</v>
+        <v>103003</v>
       </c>
       <c r="E98" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="F98" s="1" t="s">
         <v>210</v>
       </c>
-      <c r="F98" s="1" t="s">
-        <v>211</v>
-      </c>
       <c r="G98" s="1">
-        <v>203002</v>
+        <v>203003</v>
       </c>
       <c r="J98" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="1:10">
       <c r="A99" s="1">
         <f t="shared" si="7"/>
-        <v>3003</v>
+        <v>4001</v>
       </c>
       <c r="B99" s="1">
         <f>COUNTIF($C$1:C99,C99)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C99" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D99" s="1">
         <f t="shared" si="6"/>
-        <v>103003</v>
+        <v>104001</v>
       </c>
       <c r="E99" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F99" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="F99" s="1" t="s">
-        <v>213</v>
-      </c>
       <c r="G99" s="1">
-        <v>203003</v>
-      </c>
-      <c r="J99" s="1">
-        <v>9</v>
+        <f t="shared" ref="G99:G108" si="8">200000+A99</f>
+        <v>204001</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="1:10">
       <c r="A100" s="1">
         <f t="shared" si="7"/>
-        <v>4001</v>
+        <v>4002</v>
       </c>
       <c r="B100" s="1">
         <f>COUNTIF($C$1:C100,C100)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C100" s="1">
         <v>4</v>
       </c>
       <c r="D100" s="1">
         <f t="shared" si="6"/>
-        <v>104001</v>
+        <v>104002</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="G100" s="1">
-        <f t="shared" ref="G100:G109" si="8">200000+A100</f>
-        <v>204001</v>
+        <f t="shared" si="8"/>
+        <v>204002</v>
+      </c>
+      <c r="J100" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="101" s="1" customFormat="1" spans="1:10">
       <c r="A101" s="1">
         <f t="shared" si="7"/>
-        <v>4002</v>
+        <v>4003</v>
       </c>
       <c r="B101" s="1">
         <f>COUNTIF($C$1:C101,C101)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C101" s="1">
         <v>4</v>
       </c>
       <c r="D101" s="1">
         <f t="shared" si="6"/>
-        <v>104002</v>
+        <v>104003</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>214</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="G101" s="1">
         <f t="shared" si="8"/>
-        <v>204002</v>
+        <v>204003</v>
       </c>
       <c r="J101" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="102" s="1" customFormat="1" spans="1:10">
       <c r="A102" s="1">
-        <f t="shared" si="7"/>
-        <v>4003</v>
+        <f t="shared" ref="A102:A109" si="9">C102*1000+B102</f>
+        <v>5001</v>
       </c>
       <c r="B102" s="1">
         <f>COUNTIF($C$1:C102,C102)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" si="6"/>
-        <v>104003</v>
+        <f t="shared" ref="D102:D109" si="10">100000+C102*1000+B102</f>
+        <v>105001</v>
       </c>
       <c r="E102" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="F102" s="1" t="s">
         <v>217</v>
-      </c>
-      <c r="F102" s="1" t="s">
-        <v>218</v>
       </c>
       <c r="G102" s="1">
         <f t="shared" si="8"/>
-        <v>204003</v>
-      </c>
-      <c r="J102" s="1">
-        <v>9</v>
+        <v>205001</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="1:10">
       <c r="A103" s="1">
-        <f t="shared" ref="A103:A110" si="9">C103*1000+B103</f>
-        <v>5001</v>
+        <f t="shared" si="9"/>
+        <v>5002</v>
       </c>
       <c r="B103" s="1">
         <f>COUNTIF($C$1:C103,C103)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C103" s="1">
         <v>5</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" ref="D103:D110" si="10">100000+C103*1000+B103</f>
-        <v>105001</v>
+        <f t="shared" si="10"/>
+        <v>105002</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G103" s="1">
         <f t="shared" si="8"/>
-        <v>205001</v>
+        <v>205002</v>
+      </c>
+      <c r="J103" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="1:10">
       <c r="A104" s="1">
         <f t="shared" si="9"/>
-        <v>5002</v>
+        <v>5003</v>
       </c>
       <c r="B104" s="1">
         <f>COUNTIF($C$1:C104,C104)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C104" s="1">
         <v>5</v>
       </c>
       <c r="D104" s="1">
         <f t="shared" si="10"/>
-        <v>105002</v>
+        <v>105003</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>219</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="G104" s="1">
         <f t="shared" si="8"/>
-        <v>205002</v>
+        <v>205003</v>
       </c>
       <c r="J104" s="1">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="1:10">
       <c r="A105" s="1">
         <f t="shared" si="9"/>
-        <v>5003</v>
+        <v>6001</v>
       </c>
       <c r="B105" s="1">
         <f>COUNTIF($C$1:C105,C105)</f>
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C105" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D105" s="1">
         <f t="shared" si="10"/>
-        <v>105003</v>
+        <v>106001</v>
       </c>
       <c r="E105" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>222</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>223</v>
       </c>
       <c r="G105" s="1">
         <f t="shared" si="8"/>
-        <v>205003</v>
-      </c>
-      <c r="J105" s="1">
-        <v>9</v>
+        <v>206001</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="1:10">
       <c r="A106" s="1">
         <f t="shared" si="9"/>
-        <v>6001</v>
+        <v>6002</v>
       </c>
       <c r="B106" s="1">
         <f>COUNTIF($C$1:C106,C106)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C106" s="1">
         <v>6</v>
       </c>
       <c r="D106" s="1">
         <f t="shared" si="10"/>
-        <v>106001</v>
+        <v>106002</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="G106" s="1">
         <f t="shared" si="8"/>
-        <v>206001</v>
+        <v>206002</v>
+      </c>
+      <c r="J106" s="1">
+        <v>6</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="1:10">
       <c r="A107" s="1">
         <f t="shared" si="9"/>
-        <v>6002</v>
+        <v>6003</v>
       </c>
       <c r="B107" s="1">
         <f>COUNTIF($C$1:C107,C107)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C107" s="1">
         <v>6</v>
       </c>
       <c r="D107" s="1">
         <f t="shared" si="10"/>
-        <v>106002</v>
+        <v>106003</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>224</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G107" s="1">
         <f t="shared" si="8"/>
-        <v>206002</v>
+        <v>206003</v>
       </c>
       <c r="J107" s="1">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="108" s="1" customFormat="1" spans="1:10">
-      <c r="A108" s="1">
-        <f t="shared" si="9"/>
-        <v>6003</v>
-      </c>
-      <c r="B108" s="1">
-        <f>COUNTIF($C$1:C108,C108)</f>
-        <v>3</v>
-      </c>
-      <c r="C108" s="1">
-        <v>6</v>
-      </c>
-      <c r="D108" s="1">
-        <f t="shared" si="10"/>
-        <v>106003</v>
-      </c>
-      <c r="E108" s="1" t="s">
-        <v>227</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>228</v>
-      </c>
-      <c r="G108" s="1">
-        <f t="shared" si="8"/>
-        <v>206003</v>
-      </c>
-      <c r="J108" s="1">
         <v>9</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="F53">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F1:F52 F54:F1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -3578,7 +3578,7 @@
         <v>201003</v>
       </c>
       <c r="H59" s="1">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3607,7 +3607,7 @@
         <v>201004</v>
       </c>
       <c r="H60" s="1">
-        <v>150</v>
+        <v>200</v>
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:11">

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -1051,12 +1051,12 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -142,6 +142,28 @@
         </r>
       </text>
     </comment>
+    <comment ref="A61" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+这个ID不能动，道具表中有使用</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="K61" authorId="0">
       <text>
         <r>
@@ -163,6 +185,29 @@
 参数1-》类型：1 表示活动(ActivityConfig.xlsx)、2表示功能(GameFunction.xlsx)
 参数2-》类型1 读取 type字段；2类型读取 id 字段 
 参数3-》跳转对象名称，客户端功能界面名称</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="A62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+这个ID不能动，道具表中有使用
+</t>
         </r>
       </text>
     </comment>
@@ -1067,12 +1112,18 @@
       <charset val="134"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -1393,7 +1444,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -1417,16 +1468,16 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1435,89 +1486,89 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1525,6 +1576,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3611,7 +3665,7 @@
       </c>
     </row>
     <row r="61" s="1" customFormat="1" spans="1:11">
-      <c r="A61" s="1">
+      <c r="A61" s="3">
         <f t="shared" si="2"/>
         <v>1005</v>
       </c>
@@ -3640,7 +3694,7 @@
       </c>
     </row>
     <row r="62" s="1" customFormat="1" spans="1:11">
-      <c r="A62" s="1">
+      <c r="A62" s="3">
         <f t="shared" si="2"/>
         <v>1006</v>
       </c>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -1096,6 +1096,11 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1103,11 +1108,6 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -2066,7 +2066,7 @@
         <v>24</v>
       </c>
       <c r="G6" s="1">
-        <v>200017</v>
+        <v>200002</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
@@ -2095,7 +2095,7 @@
         <v>26</v>
       </c>
       <c r="G7" s="1">
-        <v>200002</v>
+        <v>200003</v>
       </c>
       <c r="H7" s="1">
         <v>10</v>
@@ -2124,7 +2124,7 @@
         <v>28</v>
       </c>
       <c r="G8" s="1">
-        <v>200018</v>
+        <v>200004</v>
       </c>
       <c r="H8" s="1">
         <v>20</v>
@@ -2153,7 +2153,7 @@
         <v>30</v>
       </c>
       <c r="G9" s="1">
-        <v>200003</v>
+        <v>200005</v>
       </c>
       <c r="H9" s="1">
         <v>30</v>
@@ -2182,7 +2182,7 @@
         <v>32</v>
       </c>
       <c r="G10" s="1">
-        <v>200019</v>
+        <v>200006</v>
       </c>
       <c r="H10" s="1">
         <v>40</v>
@@ -2211,7 +2211,7 @@
         <v>34</v>
       </c>
       <c r="G11" s="1">
-        <v>200004</v>
+        <v>200007</v>
       </c>
       <c r="H11" s="1">
         <v>50</v>
@@ -2240,7 +2240,7 @@
         <v>36</v>
       </c>
       <c r="G12" s="1">
-        <v>200020</v>
+        <v>200008</v>
       </c>
       <c r="H12" s="1">
         <v>60</v>
@@ -2269,7 +2269,7 @@
         <v>38</v>
       </c>
       <c r="G13" s="1">
-        <v>200005</v>
+        <v>200009</v>
       </c>
       <c r="H13" s="1">
         <v>70</v>
@@ -2298,7 +2298,7 @@
         <v>40</v>
       </c>
       <c r="G14" s="1">
-        <v>200021</v>
+        <v>200010</v>
       </c>
       <c r="H14" s="1">
         <v>80</v>
@@ -2327,7 +2327,7 @@
         <v>42</v>
       </c>
       <c r="G15" s="1">
-        <v>200006</v>
+        <v>200011</v>
       </c>
       <c r="H15" s="1">
         <v>90</v>
@@ -2356,7 +2356,7 @@
         <v>44</v>
       </c>
       <c r="G16" s="1">
-        <v>200022</v>
+        <v>200012</v>
       </c>
       <c r="H16" s="1">
         <v>100</v>
@@ -2385,7 +2385,7 @@
         <v>46</v>
       </c>
       <c r="G17" s="1">
-        <v>200007</v>
+        <v>200013</v>
       </c>
       <c r="H17" s="1">
         <v>120</v>
@@ -2414,7 +2414,7 @@
         <v>48</v>
       </c>
       <c r="G18" s="1">
-        <v>200023</v>
+        <v>200014</v>
       </c>
       <c r="H18" s="1">
         <v>140</v>
@@ -2443,7 +2443,7 @@
         <v>50</v>
       </c>
       <c r="G19" s="1">
-        <v>200008</v>
+        <v>200015</v>
       </c>
       <c r="H19" s="1">
         <v>160</v>
@@ -2472,7 +2472,7 @@
         <v>52</v>
       </c>
       <c r="G20" s="1">
-        <v>200024</v>
+        <v>200016</v>
       </c>
       <c r="H20" s="1">
         <v>180</v>
@@ -2501,7 +2501,7 @@
         <v>54</v>
       </c>
       <c r="G21" s="1">
-        <v>200009</v>
+        <v>200017</v>
       </c>
       <c r="H21" s="1">
         <v>200</v>
@@ -2530,7 +2530,7 @@
         <v>56</v>
       </c>
       <c r="G22" s="1">
-        <v>200025</v>
+        <v>200018</v>
       </c>
       <c r="H22" s="1">
         <v>220</v>
@@ -2559,7 +2559,7 @@
         <v>58</v>
       </c>
       <c r="G23" s="1">
-        <v>200010</v>
+        <v>200019</v>
       </c>
       <c r="H23" s="1">
         <v>240</v>
@@ -2588,7 +2588,7 @@
         <v>60</v>
       </c>
       <c r="G24" s="1">
-        <v>200026</v>
+        <v>200020</v>
       </c>
       <c r="H24" s="1">
         <v>260</v>
@@ -2617,7 +2617,7 @@
         <v>62</v>
       </c>
       <c r="G25" s="1">
-        <v>200011</v>
+        <v>200021</v>
       </c>
       <c r="H25" s="1">
         <v>280</v>
@@ -2646,7 +2646,7 @@
         <v>64</v>
       </c>
       <c r="G26" s="1">
-        <v>200027</v>
+        <v>200022</v>
       </c>
       <c r="H26" s="1">
         <v>300</v>
@@ -2675,7 +2675,7 @@
         <v>66</v>
       </c>
       <c r="G27" s="1">
-        <v>200012</v>
+        <v>200023</v>
       </c>
       <c r="H27" s="1">
         <v>320</v>
@@ -2704,7 +2704,7 @@
         <v>68</v>
       </c>
       <c r="G28" s="1">
-        <v>200028</v>
+        <v>200024</v>
       </c>
       <c r="H28" s="1">
         <v>340</v>
@@ -2733,7 +2733,7 @@
         <v>70</v>
       </c>
       <c r="G29" s="1">
-        <v>200013</v>
+        <v>200025</v>
       </c>
       <c r="H29" s="1">
         <v>360</v>
@@ -2762,7 +2762,7 @@
         <v>72</v>
       </c>
       <c r="G30" s="1">
-        <v>200029</v>
+        <v>200026</v>
       </c>
       <c r="H30" s="1">
         <v>380</v>
@@ -2791,7 +2791,7 @@
         <v>74</v>
       </c>
       <c r="G31" s="1">
-        <v>200014</v>
+        <v>200027</v>
       </c>
       <c r="H31" s="1">
         <v>400</v>
@@ -2820,7 +2820,7 @@
         <v>76</v>
       </c>
       <c r="G32" s="1">
-        <v>200030</v>
+        <v>200028</v>
       </c>
       <c r="H32" s="1">
         <v>450</v>
@@ -2849,7 +2849,7 @@
         <v>78</v>
       </c>
       <c r="G33" s="1">
-        <v>200015</v>
+        <v>200029</v>
       </c>
       <c r="H33" s="1">
         <v>500</v>
@@ -2878,7 +2878,7 @@
         <v>80</v>
       </c>
       <c r="G34" s="1">
-        <v>200031</v>
+        <v>200030</v>
       </c>
       <c r="H34" s="1">
         <v>550</v>
@@ -2907,7 +2907,7 @@
         <v>82</v>
       </c>
       <c r="G35" s="1">
-        <v>200016</v>
+        <v>200031</v>
       </c>
       <c r="H35" s="1">
         <v>600</v>
@@ -3168,7 +3168,7 @@
         <v>100</v>
       </c>
       <c r="G44" s="2">
-        <v>200014</v>
+        <v>200040</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2" t="s">
@@ -3199,7 +3199,7 @@
         <v>103</v>
       </c>
       <c r="G45" s="2">
-        <v>200030</v>
+        <v>200041</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2" t="s">
@@ -3230,7 +3230,7 @@
         <v>105</v>
       </c>
       <c r="G46" s="2">
-        <v>200015</v>
+        <v>200042</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2" t="s">
@@ -3261,7 +3261,7 @@
         <v>107</v>
       </c>
       <c r="G47" s="2">
-        <v>200031</v>
+        <v>200043</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2" t="s">
@@ -3292,7 +3292,7 @@
         <v>109</v>
       </c>
       <c r="G48" s="2">
-        <v>200016</v>
+        <v>200044</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2" t="s">
@@ -3323,7 +3323,7 @@
         <v>111</v>
       </c>
       <c r="G49" s="2">
-        <v>200032</v>
+        <v>200045</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2" t="s">
@@ -3354,7 +3354,7 @@
         <v>113</v>
       </c>
       <c r="G50" s="2">
-        <v>200033</v>
+        <v>200046</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2" t="s">
@@ -3385,7 +3385,7 @@
         <v>115</v>
       </c>
       <c r="G51" s="2">
-        <v>200034</v>
+        <v>200047</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2" t="s">
@@ -3416,7 +3416,7 @@
         <v>117</v>
       </c>
       <c r="G52" s="2">
-        <v>200035</v>
+        <v>200048</v>
       </c>
       <c r="H52" s="2"/>
       <c r="I52" s="2" t="s">
@@ -3447,7 +3447,7 @@
         <v>118</v>
       </c>
       <c r="G53" s="2">
-        <v>200036</v>
+        <v>200049</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2" t="s">
@@ -3478,7 +3478,7 @@
         <v>120</v>
       </c>
       <c r="G54" s="2">
-        <v>200037</v>
+        <v>200050</v>
       </c>
       <c r="H54" s="2"/>
       <c r="I54" s="2" t="s">
@@ -3509,7 +3509,7 @@
         <v>122</v>
       </c>
       <c r="G55" s="2">
-        <v>200038</v>
+        <v>200051</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2" t="s">
@@ -3540,7 +3540,7 @@
         <v>124</v>
       </c>
       <c r="G56" s="2">
-        <v>200039</v>
+        <v>200052</v>
       </c>
       <c r="H56" s="2"/>
       <c r="I56" s="2" t="s">

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="232">
   <si>
     <t>id</t>
   </si>
@@ -856,6 +856,24 @@
   </si>
   <si>
     <t>Flag_020.png</t>
+  </si>
+  <si>
+    <t>国旗21</t>
+  </si>
+  <si>
+    <t>Flag_021.png</t>
+  </si>
+  <si>
+    <t>国旗22</t>
+  </si>
+  <si>
+    <t>Flag_022.png</t>
+  </si>
+  <si>
+    <t>国旗23</t>
+  </si>
+  <si>
+    <t>Flag_023.png</t>
   </si>
   <si>
     <t>头衔1</t>
@@ -1096,11 +1114,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
@@ -1108,6 +1121,11 @@
     </font>
     <font>
       <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -1901,7 +1919,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L107"/>
+  <dimension ref="A1:L110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -4242,7 +4260,7 @@
         <v>202005</v>
       </c>
     </row>
-    <row r="81" s="1" customFormat="1" spans="1:10">
+    <row r="81" s="1" customFormat="1" spans="1:7">
       <c r="A81" s="1">
         <f t="shared" si="7"/>
         <v>2006</v>
@@ -4268,7 +4286,7 @@
         <v>202006</v>
       </c>
     </row>
-    <row r="82" s="1" customFormat="1" spans="1:10">
+    <row r="82" s="1" customFormat="1" spans="1:7">
       <c r="A82" s="1">
         <f t="shared" si="7"/>
         <v>2007</v>
@@ -4294,7 +4312,7 @@
         <v>202007</v>
       </c>
     </row>
-    <row r="83" s="1" customFormat="1" spans="1:10">
+    <row r="83" s="1" customFormat="1" spans="1:7">
       <c r="A83" s="1">
         <f t="shared" si="7"/>
         <v>2008</v>
@@ -4320,7 +4338,7 @@
         <v>202008</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" spans="1:10">
+    <row r="84" s="1" customFormat="1" spans="1:7">
       <c r="A84" s="1">
         <f t="shared" si="7"/>
         <v>2009</v>
@@ -4346,7 +4364,7 @@
         <v>202009</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" spans="1:10">
+    <row r="85" s="1" customFormat="1" spans="1:7">
       <c r="A85" s="1">
         <f t="shared" si="7"/>
         <v>2010</v>
@@ -4372,7 +4390,7 @@
         <v>202010</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" spans="1:10">
+    <row r="86" s="1" customFormat="1" spans="1:7">
       <c r="A86" s="1">
         <f t="shared" si="7"/>
         <v>2011</v>
@@ -4398,7 +4416,7 @@
         <v>202011</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" spans="1:10">
+    <row r="87" s="1" customFormat="1" spans="1:7">
       <c r="A87" s="1">
         <f t="shared" si="7"/>
         <v>2012</v>
@@ -4424,7 +4442,7 @@
         <v>202012</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" spans="1:10">
+    <row r="88" s="1" customFormat="1" spans="1:7">
       <c r="A88" s="1">
         <f t="shared" si="7"/>
         <v>2013</v>
@@ -4450,7 +4468,7 @@
         <v>202013</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" spans="1:10">
+    <row r="89" s="1" customFormat="1" spans="1:7">
       <c r="A89" s="1">
         <f t="shared" si="7"/>
         <v>2014</v>
@@ -4476,7 +4494,7 @@
         <v>202014</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" spans="1:10">
+    <row r="90" s="1" customFormat="1" spans="1:7">
       <c r="A90" s="1">
         <f t="shared" si="7"/>
         <v>2015</v>
@@ -4502,7 +4520,7 @@
         <v>202015</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" spans="1:10">
+    <row r="91" s="1" customFormat="1" spans="1:7">
       <c r="A91" s="1">
         <f t="shared" si="7"/>
         <v>2016</v>
@@ -4528,7 +4546,7 @@
         <v>202016</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" spans="1:10">
+    <row r="92" s="1" customFormat="1" spans="1:7">
       <c r="A92" s="1">
         <f t="shared" si="7"/>
         <v>2017</v>
@@ -4554,7 +4572,7 @@
         <v>202017</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" spans="1:10">
+    <row r="93" s="1" customFormat="1" spans="1:7">
       <c r="A93" s="1">
         <f t="shared" si="7"/>
         <v>2018</v>
@@ -4580,7 +4598,7 @@
         <v>202018</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" spans="1:10">
+    <row r="94" s="1" customFormat="1" spans="1:7">
       <c r="A94" s="1">
         <f t="shared" si="7"/>
         <v>2019</v>
@@ -4606,7 +4624,7 @@
         <v>202019</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" spans="1:10">
+    <row r="95" s="1" customFormat="1" spans="1:7">
       <c r="A95" s="1">
         <f t="shared" si="7"/>
         <v>2020</v>
@@ -4632,21 +4650,19 @@
         <v>202020</v>
       </c>
     </row>
-    <row r="96" s="1" customFormat="1" spans="1:10">
+    <row r="96" s="1" customFormat="1" spans="1:7">
       <c r="A96" s="1">
-        <f t="shared" si="7"/>
-        <v>3001</v>
+        <v>2021</v>
       </c>
       <c r="B96" s="1">
-        <f>COUNTIF($C$1:C96,C96)</f>
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="C96" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D96" s="1">
-        <f t="shared" si="6"/>
-        <v>103001</v>
+        <f>100000+C96*1000+B96</f>
+        <v>102021</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>205</v>
@@ -4655,29 +4671,22 @@
         <v>206</v>
       </c>
       <c r="G96" s="1">
-        <v>203001</v>
-      </c>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1">
-        <v>3</v>
+        <v>202021</v>
       </c>
     </row>
     <row r="97" s="1" customFormat="1" spans="1:10">
       <c r="A97" s="1">
-        <f t="shared" si="7"/>
-        <v>3002</v>
+        <v>2022</v>
       </c>
       <c r="B97" s="1">
-        <f>COUNTIF($C$1:C97,C97)</f>
+        <v>22</v>
+      </c>
+      <c r="C97" s="1">
         <v>2</v>
       </c>
-      <c r="C97" s="1">
-        <v>3</v>
-      </c>
       <c r="D97" s="1">
-        <f t="shared" si="6"/>
-        <v>103002</v>
+        <f>100000+C97*1000+B97</f>
+        <v>102022</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>207</v>
@@ -4686,27 +4695,22 @@
         <v>208</v>
       </c>
       <c r="G97" s="1">
-        <v>203002</v>
-      </c>
-      <c r="J97" s="1">
-        <v>6</v>
+        <v>202022</v>
       </c>
     </row>
     <row r="98" s="1" customFormat="1" spans="1:10">
       <c r="A98" s="1">
-        <f t="shared" si="7"/>
-        <v>3003</v>
+        <v>2023</v>
       </c>
       <c r="B98" s="1">
-        <f>COUNTIF($C$1:C98,C98)</f>
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="C98" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D98" s="1">
-        <f t="shared" si="6"/>
-        <v>103003</v>
+        <f>100000+C98*1000+B98</f>
+        <v>102023</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>209</v>
@@ -4715,27 +4719,24 @@
         <v>210</v>
       </c>
       <c r="G98" s="1">
-        <v>203003</v>
-      </c>
-      <c r="J98" s="1">
-        <v>9</v>
+        <v>202023</v>
       </c>
     </row>
     <row r="99" s="1" customFormat="1" spans="1:10">
       <c r="A99" s="1">
-        <f t="shared" si="7"/>
-        <v>4001</v>
+        <f>C99*1000+B99</f>
+        <v>3001</v>
       </c>
       <c r="B99" s="1">
         <f>COUNTIF($C$1:C99,C99)</f>
         <v>1</v>
       </c>
       <c r="C99" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D99" s="1">
-        <f t="shared" si="6"/>
-        <v>104001</v>
+        <f>100000+C99*1000+B99</f>
+        <v>103001</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>211</v>
@@ -4744,35 +4745,38 @@
         <v>212</v>
       </c>
       <c r="G99" s="1">
-        <f t="shared" ref="G99:G108" si="8">200000+A99</f>
-        <v>204001</v>
+        <v>203001</v>
+      </c>
+      <c r="H99" s="1"/>
+      <c r="I99" s="1"/>
+      <c r="J99" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="100" s="1" customFormat="1" spans="1:10">
       <c r="A100" s="1">
-        <f t="shared" si="7"/>
-        <v>4002</v>
+        <f>C100*1000+B100</f>
+        <v>3002</v>
       </c>
       <c r="B100" s="1">
         <f>COUNTIF($C$1:C100,C100)</f>
         <v>2</v>
       </c>
       <c r="C100" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D100" s="1">
-        <f t="shared" si="6"/>
-        <v>104002</v>
+        <f>100000+C100*1000+B100</f>
+        <v>103002</v>
       </c>
       <c r="E100" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G100" s="1">
-        <f t="shared" si="8"/>
-        <v>204002</v>
+        <v>203002</v>
       </c>
       <c r="J100" s="1">
         <v>6</v>
@@ -4780,29 +4784,28 @@
     </row>
     <row r="101" s="1" customFormat="1" spans="1:10">
       <c r="A101" s="1">
-        <f t="shared" si="7"/>
-        <v>4003</v>
+        <f>C101*1000+B101</f>
+        <v>3003</v>
       </c>
       <c r="B101" s="1">
         <f>COUNTIF($C$1:C101,C101)</f>
         <v>3</v>
       </c>
       <c r="C101" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D101" s="1">
-        <f t="shared" si="6"/>
-        <v>104003</v>
+        <f>100000+C101*1000+B101</f>
+        <v>103003</v>
       </c>
       <c r="E101" s="1" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G101" s="1">
-        <f t="shared" si="8"/>
-        <v>204003</v>
+        <v>203003</v>
       </c>
       <c r="J101" s="1">
         <v>9</v>
@@ -4810,56 +4813,56 @@
     </row>
     <row r="102" s="1" customFormat="1" spans="1:10">
       <c r="A102" s="1">
-        <f t="shared" ref="A102:A109" si="9">C102*1000+B102</f>
-        <v>5001</v>
+        <f>C102*1000+B102</f>
+        <v>4001</v>
       </c>
       <c r="B102" s="1">
         <f>COUNTIF($C$1:C102,C102)</f>
         <v>1</v>
       </c>
       <c r="C102" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D102" s="1">
-        <f t="shared" ref="D102:D109" si="10">100000+C102*1000+B102</f>
-        <v>105001</v>
+        <f>100000+C102*1000+B102</f>
+        <v>104001</v>
       </c>
       <c r="E102" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="G102" s="1">
-        <f t="shared" si="8"/>
-        <v>205001</v>
+        <f t="shared" ref="G102:G111" si="8">200000+A102</f>
+        <v>204001</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="1:10">
       <c r="A103" s="1">
-        <f t="shared" si="9"/>
-        <v>5002</v>
+        <f>C103*1000+B103</f>
+        <v>4002</v>
       </c>
       <c r="B103" s="1">
         <f>COUNTIF($C$1:C103,C103)</f>
         <v>2</v>
       </c>
       <c r="C103" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D103" s="1">
-        <f t="shared" si="10"/>
-        <v>105002</v>
+        <f>100000+C103*1000+B103</f>
+        <v>104002</v>
       </c>
       <c r="E103" s="1" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G103" s="1">
         <f t="shared" si="8"/>
-        <v>205002</v>
+        <v>204002</v>
       </c>
       <c r="J103" s="1">
         <v>6</v>
@@ -4867,29 +4870,29 @@
     </row>
     <row r="104" s="1" customFormat="1" spans="1:10">
       <c r="A104" s="1">
-        <f t="shared" si="9"/>
-        <v>5003</v>
+        <f>C104*1000+B104</f>
+        <v>4003</v>
       </c>
       <c r="B104" s="1">
         <f>COUNTIF($C$1:C104,C104)</f>
         <v>3</v>
       </c>
       <c r="C104" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D104" s="1">
-        <f t="shared" si="10"/>
-        <v>105003</v>
+        <f>100000+C104*1000+B104</f>
+        <v>104003</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G104" s="1">
         <f t="shared" si="8"/>
-        <v>205003</v>
+        <v>204003</v>
       </c>
       <c r="J104" s="1">
         <v>9</v>
@@ -4897,56 +4900,56 @@
     </row>
     <row r="105" s="1" customFormat="1" spans="1:10">
       <c r="A105" s="1">
-        <f t="shared" si="9"/>
-        <v>6001</v>
+        <f t="shared" ref="A105:A112" si="9">C105*1000+B105</f>
+        <v>5001</v>
       </c>
       <c r="B105" s="1">
         <f>COUNTIF($C$1:C105,C105)</f>
         <v>1</v>
       </c>
       <c r="C105" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" si="10"/>
-        <v>106001</v>
+        <f t="shared" ref="D105:D112" si="10">100000+C105*1000+B105</f>
+        <v>105001</v>
       </c>
       <c r="E105" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G105" s="1">
         <f t="shared" si="8"/>
-        <v>206001</v>
+        <v>205001</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="1:10">
       <c r="A106" s="1">
         <f t="shared" si="9"/>
-        <v>6002</v>
+        <v>5002</v>
       </c>
       <c r="B106" s="1">
         <f>COUNTIF($C$1:C106,C106)</f>
         <v>2</v>
       </c>
       <c r="C106" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D106" s="1">
         <f t="shared" si="10"/>
-        <v>106002</v>
+        <v>105002</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G106" s="1">
         <f t="shared" si="8"/>
-        <v>206002</v>
+        <v>205002</v>
       </c>
       <c r="J106" s="1">
         <v>6</v>
@@ -4955,30 +4958,117 @@
     <row r="107" s="1" customFormat="1" spans="1:10">
       <c r="A107" s="1">
         <f t="shared" si="9"/>
-        <v>6003</v>
+        <v>5003</v>
       </c>
       <c r="B107" s="1">
         <f>COUNTIF($C$1:C107,C107)</f>
         <v>3</v>
       </c>
       <c r="C107" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D107" s="1">
         <f t="shared" si="10"/>
-        <v>106003</v>
+        <v>105003</v>
       </c>
       <c r="E107" s="1" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G107" s="1">
         <f t="shared" si="8"/>
+        <v>205003</v>
+      </c>
+      <c r="J107" s="1">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108" s="1" customFormat="1" spans="1:10">
+      <c r="A108" s="1">
+        <f t="shared" si="9"/>
+        <v>6001</v>
+      </c>
+      <c r="B108" s="1">
+        <f>COUNTIF($C$1:C108,C108)</f>
+        <v>1</v>
+      </c>
+      <c r="C108" s="1">
+        <v>6</v>
+      </c>
+      <c r="D108" s="1">
+        <f t="shared" si="10"/>
+        <v>106001</v>
+      </c>
+      <c r="E108" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F108" s="1" t="s">
+        <v>228</v>
+      </c>
+      <c r="G108" s="1">
+        <f t="shared" si="8"/>
+        <v>206001</v>
+      </c>
+    </row>
+    <row r="109" s="1" customFormat="1" spans="1:10">
+      <c r="A109" s="1">
+        <f t="shared" si="9"/>
+        <v>6002</v>
+      </c>
+      <c r="B109" s="1">
+        <f>COUNTIF($C$1:C109,C109)</f>
+        <v>2</v>
+      </c>
+      <c r="C109" s="1">
+        <v>6</v>
+      </c>
+      <c r="D109" s="1">
+        <f t="shared" si="10"/>
+        <v>106002</v>
+      </c>
+      <c r="E109" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="F109" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="G109" s="1">
+        <f t="shared" si="8"/>
+        <v>206002</v>
+      </c>
+      <c r="J109" s="1">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="110" s="1" customFormat="1" spans="1:10">
+      <c r="A110" s="1">
+        <f t="shared" si="9"/>
+        <v>6003</v>
+      </c>
+      <c r="B110" s="1">
+        <f>COUNTIF($C$1:C110,C110)</f>
+        <v>3</v>
+      </c>
+      <c r="C110" s="1">
+        <v>6</v>
+      </c>
+      <c r="D110" s="1">
+        <f t="shared" si="10"/>
+        <v>106003</v>
+      </c>
+      <c r="E110" s="1" t="s">
+        <v>230</v>
+      </c>
+      <c r="F110" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="G110" s="1">
+        <f t="shared" si="8"/>
         <v>206003</v>
       </c>
-      <c r="J107" s="1">
+      <c r="J110" s="1">
         <v>9</v>
       </c>
     </row>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="avatar" sheetId="1" r:id="rId1"/>
@@ -1120,12 +1120,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
@@ -4661,7 +4661,7 @@
         <v>2</v>
       </c>
       <c r="D96" s="1">
-        <f>100000+C96*1000+B96</f>
+        <f t="shared" si="6"/>
         <v>102021</v>
       </c>
       <c r="E96" s="1" t="s">
@@ -4685,7 +4685,7 @@
         <v>2</v>
       </c>
       <c r="D97" s="1">
-        <f>100000+C97*1000+B97</f>
+        <f t="shared" si="6"/>
         <v>102022</v>
       </c>
       <c r="E97" s="1" t="s">
@@ -4709,7 +4709,7 @@
         <v>2</v>
       </c>
       <c r="D98" s="1">
-        <f>100000+C98*1000+B98</f>
+        <f t="shared" si="6"/>
         <v>102023</v>
       </c>
       <c r="E98" s="1" t="s">
@@ -4724,7 +4724,7 @@
     </row>
     <row r="99" s="1" customFormat="1" spans="1:10">
       <c r="A99" s="1">
-        <f>C99*1000+B99</f>
+        <f t="shared" ref="A99:A104" si="8">C99*1000+B99</f>
         <v>3001</v>
       </c>
       <c r="B99" s="1">
@@ -4735,7 +4735,7 @@
         <v>3</v>
       </c>
       <c r="D99" s="1">
-        <f>100000+C99*1000+B99</f>
+        <f t="shared" si="6"/>
         <v>103001</v>
       </c>
       <c r="E99" s="1" t="s">
@@ -4755,7 +4755,7 @@
     </row>
     <row r="100" s="1" customFormat="1" spans="1:10">
       <c r="A100" s="1">
-        <f>C100*1000+B100</f>
+        <f t="shared" si="8"/>
         <v>3002</v>
       </c>
       <c r="B100" s="1">
@@ -4766,7 +4766,7 @@
         <v>3</v>
       </c>
       <c r="D100" s="1">
-        <f>100000+C100*1000+B100</f>
+        <f t="shared" si="6"/>
         <v>103002</v>
       </c>
       <c r="E100" s="1" t="s">
@@ -4784,7 +4784,7 @@
     </row>
     <row r="101" s="1" customFormat="1" spans="1:10">
       <c r="A101" s="1">
-        <f>C101*1000+B101</f>
+        <f t="shared" si="8"/>
         <v>3003</v>
       </c>
       <c r="B101" s="1">
@@ -4795,7 +4795,7 @@
         <v>3</v>
       </c>
       <c r="D101" s="1">
-        <f>100000+C101*1000+B101</f>
+        <f t="shared" si="6"/>
         <v>103003</v>
       </c>
       <c r="E101" s="1" t="s">
@@ -4813,7 +4813,7 @@
     </row>
     <row r="102" s="1" customFormat="1" spans="1:10">
       <c r="A102" s="1">
-        <f>C102*1000+B102</f>
+        <f t="shared" si="8"/>
         <v>4001</v>
       </c>
       <c r="B102" s="1">
@@ -4824,7 +4824,7 @@
         <v>4</v>
       </c>
       <c r="D102" s="1">
-        <f>100000+C102*1000+B102</f>
+        <f t="shared" si="6"/>
         <v>104001</v>
       </c>
       <c r="E102" s="1" t="s">
@@ -4834,13 +4834,13 @@
         <v>218</v>
       </c>
       <c r="G102" s="1">
-        <f t="shared" ref="G102:G111" si="8">200000+A102</f>
+        <f t="shared" ref="G102:G111" si="9">200000+A102</f>
         <v>204001</v>
       </c>
     </row>
     <row r="103" s="1" customFormat="1" spans="1:10">
       <c r="A103" s="1">
-        <f>C103*1000+B103</f>
+        <f t="shared" si="8"/>
         <v>4002</v>
       </c>
       <c r="B103" s="1">
@@ -4851,7 +4851,7 @@
         <v>4</v>
       </c>
       <c r="D103" s="1">
-        <f>100000+C103*1000+B103</f>
+        <f t="shared" si="6"/>
         <v>104002</v>
       </c>
       <c r="E103" s="1" t="s">
@@ -4861,16 +4861,16 @@
         <v>219</v>
       </c>
       <c r="G103" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>204002</v>
       </c>
       <c r="J103" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="104" s="1" customFormat="1" spans="1:10">
       <c r="A104" s="1">
-        <f>C104*1000+B104</f>
+        <f t="shared" si="8"/>
         <v>4003</v>
       </c>
       <c r="B104" s="1">
@@ -4881,7 +4881,7 @@
         <v>4</v>
       </c>
       <c r="D104" s="1">
-        <f>100000+C104*1000+B104</f>
+        <f t="shared" si="6"/>
         <v>104003</v>
       </c>
       <c r="E104" s="1" t="s">
@@ -4891,16 +4891,16 @@
         <v>221</v>
       </c>
       <c r="G104" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>204003</v>
       </c>
       <c r="J104" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105" s="1" customFormat="1" spans="1:10">
       <c r="A105" s="1">
-        <f t="shared" ref="A105:A112" si="9">C105*1000+B105</f>
+        <f t="shared" ref="A105:A112" si="10">C105*1000+B105</f>
         <v>5001</v>
       </c>
       <c r="B105" s="1">
@@ -4911,7 +4911,7 @@
         <v>5</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" ref="D105:D112" si="10">100000+C105*1000+B105</f>
+        <f t="shared" ref="D105:D112" si="11">100000+C105*1000+B105</f>
         <v>105001</v>
       </c>
       <c r="E105" s="1" t="s">
@@ -4921,13 +4921,13 @@
         <v>223</v>
       </c>
       <c r="G105" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>205001</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="1:10">
       <c r="A106" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5002</v>
       </c>
       <c r="B106" s="1">
@@ -4938,7 +4938,7 @@
         <v>5</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>105002</v>
       </c>
       <c r="E106" s="1" t="s">
@@ -4948,16 +4948,16 @@
         <v>224</v>
       </c>
       <c r="G106" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>205002</v>
       </c>
       <c r="J106" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="107" s="1" customFormat="1" spans="1:10">
       <c r="A107" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5003</v>
       </c>
       <c r="B107" s="1">
@@ -4968,7 +4968,7 @@
         <v>5</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>105003</v>
       </c>
       <c r="E107" s="1" t="s">
@@ -4978,16 +4978,16 @@
         <v>226</v>
       </c>
       <c r="G107" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>205003</v>
       </c>
       <c r="J107" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="108" s="1" customFormat="1" spans="1:10">
       <c r="A108" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6001</v>
       </c>
       <c r="B108" s="1">
@@ -4998,7 +4998,7 @@
         <v>6</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>106001</v>
       </c>
       <c r="E108" s="1" t="s">
@@ -5008,13 +5008,13 @@
         <v>228</v>
       </c>
       <c r="G108" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>206001</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" spans="1:10">
       <c r="A109" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6002</v>
       </c>
       <c r="B109" s="1">
@@ -5025,7 +5025,7 @@
         <v>6</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>106002</v>
       </c>
       <c r="E109" s="1" t="s">
@@ -5035,7 +5035,7 @@
         <v>229</v>
       </c>
       <c r="G109" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>206002</v>
       </c>
       <c r="J109" s="1">
@@ -5044,7 +5044,7 @@
     </row>
     <row r="110" s="1" customFormat="1" spans="1:10">
       <c r="A110" s="1">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6003</v>
       </c>
       <c r="B110" s="1">
@@ -5055,7 +5055,7 @@
         <v>6</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>106003</v>
       </c>
       <c r="E110" s="1" t="s">
@@ -5065,7 +5065,7 @@
         <v>231</v>
       </c>
       <c r="G110" s="1">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>206003</v>
       </c>
       <c r="J110" s="1">

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="11925"/>
+    <workbookView windowWidth="27945" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="avatar" sheetId="1" r:id="rId1"/>
@@ -1114,17 +1114,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <sz val="12"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -4745,7 +4745,7 @@
         <v>212</v>
       </c>
       <c r="G99" s="1">
-        <v>203001</v>
+        <v>2031600</v>
       </c>
       <c r="H99" s="1"/>
       <c r="I99" s="1"/>
@@ -4776,7 +4776,7 @@
         <v>214</v>
       </c>
       <c r="G100" s="1">
-        <v>203002</v>
+        <v>2031601</v>
       </c>
       <c r="J100" s="1">
         <v>6</v>
@@ -4805,7 +4805,7 @@
         <v>216</v>
       </c>
       <c r="G101" s="1">
-        <v>203003</v>
+        <v>2031602</v>
       </c>
       <c r="J101" s="1">
         <v>9</v>
@@ -4834,7 +4834,7 @@
         <v>218</v>
       </c>
       <c r="G102" s="1">
-        <f t="shared" ref="G102:G111" si="9">200000+A102</f>
+        <f>200000+A102</f>
         <v>204001</v>
       </c>
     </row>
@@ -4861,8 +4861,7 @@
         <v>219</v>
       </c>
       <c r="G103" s="1">
-        <f t="shared" si="9"/>
-        <v>204002</v>
+        <v>2031801</v>
       </c>
       <c r="J103" s="1">
         <v>4</v>
@@ -4891,8 +4890,7 @@
         <v>221</v>
       </c>
       <c r="G104" s="1">
-        <f t="shared" si="9"/>
-        <v>204003</v>
+        <v>2031802</v>
       </c>
       <c r="J104" s="1">
         <v>7</v>
@@ -4900,7 +4898,7 @@
     </row>
     <row r="105" s="1" customFormat="1" spans="1:10">
       <c r="A105" s="1">
-        <f t="shared" ref="A105:A112" si="10">C105*1000+B105</f>
+        <f t="shared" ref="A105:A112" si="9">C105*1000+B105</f>
         <v>5001</v>
       </c>
       <c r="B105" s="1">
@@ -4911,7 +4909,7 @@
         <v>5</v>
       </c>
       <c r="D105" s="1">
-        <f t="shared" ref="D105:D112" si="11">100000+C105*1000+B105</f>
+        <f t="shared" ref="D105:D112" si="10">100000+C105*1000+B105</f>
         <v>105001</v>
       </c>
       <c r="E105" s="1" t="s">
@@ -4921,13 +4919,13 @@
         <v>223</v>
       </c>
       <c r="G105" s="1">
-        <f t="shared" si="9"/>
+        <f>200000+A105</f>
         <v>205001</v>
       </c>
     </row>
     <row r="106" s="1" customFormat="1" spans="1:10">
       <c r="A106" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5002</v>
       </c>
       <c r="B106" s="1">
@@ -4938,7 +4936,7 @@
         <v>5</v>
       </c>
       <c r="D106" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>105002</v>
       </c>
       <c r="E106" s="1" t="s">
@@ -4948,8 +4946,7 @@
         <v>224</v>
       </c>
       <c r="G106" s="1">
-        <f t="shared" si="9"/>
-        <v>205002</v>
+        <v>2032001</v>
       </c>
       <c r="J106" s="1">
         <v>5</v>
@@ -4957,7 +4954,7 @@
     </row>
     <row r="107" s="1" customFormat="1" spans="1:10">
       <c r="A107" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>5003</v>
       </c>
       <c r="B107" s="1">
@@ -4968,7 +4965,7 @@
         <v>5</v>
       </c>
       <c r="D107" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>105003</v>
       </c>
       <c r="E107" s="1" t="s">
@@ -4978,8 +4975,7 @@
         <v>226</v>
       </c>
       <c r="G107" s="1">
-        <f t="shared" si="9"/>
-        <v>205003</v>
+        <v>2032002</v>
       </c>
       <c r="J107" s="1">
         <v>8</v>
@@ -4987,7 +4983,7 @@
     </row>
     <row r="108" s="1" customFormat="1" spans="1:10">
       <c r="A108" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6001</v>
       </c>
       <c r="B108" s="1">
@@ -4998,7 +4994,7 @@
         <v>6</v>
       </c>
       <c r="D108" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>106001</v>
       </c>
       <c r="E108" s="1" t="s">
@@ -5008,13 +5004,13 @@
         <v>228</v>
       </c>
       <c r="G108" s="1">
-        <f t="shared" si="9"/>
+        <f>200000+A108</f>
         <v>206001</v>
       </c>
     </row>
     <row r="109" s="1" customFormat="1" spans="1:10">
       <c r="A109" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6002</v>
       </c>
       <c r="B109" s="1">
@@ -5025,7 +5021,7 @@
         <v>6</v>
       </c>
       <c r="D109" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>106002</v>
       </c>
       <c r="E109" s="1" t="s">
@@ -5035,8 +5031,7 @@
         <v>229</v>
       </c>
       <c r="G109" s="1">
-        <f t="shared" si="9"/>
-        <v>206002</v>
+        <v>2032201</v>
       </c>
       <c r="J109" s="1">
         <v>6</v>
@@ -5044,7 +5039,7 @@
     </row>
     <row r="110" s="1" customFormat="1" spans="1:10">
       <c r="A110" s="1">
-        <f t="shared" si="10"/>
+        <f t="shared" si="9"/>
         <v>6003</v>
       </c>
       <c r="B110" s="1">
@@ -5055,7 +5050,7 @@
         <v>6</v>
       </c>
       <c r="D110" s="1">
-        <f t="shared" si="11"/>
+        <f t="shared" si="10"/>
         <v>106003</v>
       </c>
       <c r="E110" s="1" t="s">
@@ -5065,8 +5060,7 @@
         <v>231</v>
       </c>
       <c r="G110" s="1">
-        <f t="shared" si="9"/>
-        <v>206003</v>
+        <v>2032202</v>
       </c>
       <c r="J110" s="1">
         <v>9</v>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -738,142 +738,142 @@
     <t>frame_017.png</t>
   </si>
   <si>
+    <t>国旗23</t>
+  </si>
+  <si>
+    <t>Flag_023.png</t>
+  </si>
+  <si>
+    <t>国旗2</t>
+  </si>
+  <si>
+    <t>Flag_002.png</t>
+  </si>
+  <si>
+    <t>国旗3</t>
+  </si>
+  <si>
+    <t>Flag_003.png</t>
+  </si>
+  <si>
+    <t>国旗4</t>
+  </si>
+  <si>
+    <t>Flag_004.png</t>
+  </si>
+  <si>
+    <t>国旗5</t>
+  </si>
+  <si>
+    <t>Flag_005.png</t>
+  </si>
+  <si>
+    <t>国旗6</t>
+  </si>
+  <si>
+    <t>Flag_006.png</t>
+  </si>
+  <si>
+    <t>国旗7</t>
+  </si>
+  <si>
+    <t>Flag_007.png</t>
+  </si>
+  <si>
+    <t>国旗8</t>
+  </si>
+  <si>
+    <t>Flag_008.png</t>
+  </si>
+  <si>
+    <t>国旗9</t>
+  </si>
+  <si>
+    <t>Flag_009.png</t>
+  </si>
+  <si>
+    <t>国旗10</t>
+  </si>
+  <si>
+    <t>Flag_010.png</t>
+  </si>
+  <si>
+    <t>国旗11</t>
+  </si>
+  <si>
+    <t>Flag_011.png</t>
+  </si>
+  <si>
+    <t>国旗12</t>
+  </si>
+  <si>
+    <t>Flag_012.png</t>
+  </si>
+  <si>
+    <t>国旗13</t>
+  </si>
+  <si>
+    <t>Flag_013.png</t>
+  </si>
+  <si>
+    <t>国旗14</t>
+  </si>
+  <si>
+    <t>Flag_014.png</t>
+  </si>
+  <si>
+    <t>国旗15</t>
+  </si>
+  <si>
+    <t>Flag_015.png</t>
+  </si>
+  <si>
+    <t>国旗16</t>
+  </si>
+  <si>
+    <t>Flag_016.png</t>
+  </si>
+  <si>
+    <t>国旗17</t>
+  </si>
+  <si>
+    <t>Flag_017.png</t>
+  </si>
+  <si>
+    <t>国旗18</t>
+  </si>
+  <si>
+    <t>Flag_018.png</t>
+  </si>
+  <si>
+    <t>国旗19</t>
+  </si>
+  <si>
+    <t>Flag_019.png</t>
+  </si>
+  <si>
+    <t>国旗20</t>
+  </si>
+  <si>
+    <t>Flag_020.png</t>
+  </si>
+  <si>
+    <t>国旗21</t>
+  </si>
+  <si>
+    <t>Flag_021.png</t>
+  </si>
+  <si>
+    <t>国旗22</t>
+  </si>
+  <si>
+    <t>Flag_022.png</t>
+  </si>
+  <si>
     <t>国旗1</t>
   </si>
   <si>
     <t>Flag_001.png</t>
-  </si>
-  <si>
-    <t>国旗2</t>
-  </si>
-  <si>
-    <t>Flag_002.png</t>
-  </si>
-  <si>
-    <t>国旗3</t>
-  </si>
-  <si>
-    <t>Flag_003.png</t>
-  </si>
-  <si>
-    <t>国旗4</t>
-  </si>
-  <si>
-    <t>Flag_004.png</t>
-  </si>
-  <si>
-    <t>国旗5</t>
-  </si>
-  <si>
-    <t>Flag_005.png</t>
-  </si>
-  <si>
-    <t>国旗6</t>
-  </si>
-  <si>
-    <t>Flag_006.png</t>
-  </si>
-  <si>
-    <t>国旗7</t>
-  </si>
-  <si>
-    <t>Flag_007.png</t>
-  </si>
-  <si>
-    <t>国旗8</t>
-  </si>
-  <si>
-    <t>Flag_008.png</t>
-  </si>
-  <si>
-    <t>国旗9</t>
-  </si>
-  <si>
-    <t>Flag_009.png</t>
-  </si>
-  <si>
-    <t>国旗10</t>
-  </si>
-  <si>
-    <t>Flag_010.png</t>
-  </si>
-  <si>
-    <t>国旗11</t>
-  </si>
-  <si>
-    <t>Flag_011.png</t>
-  </si>
-  <si>
-    <t>国旗12</t>
-  </si>
-  <si>
-    <t>Flag_012.png</t>
-  </si>
-  <si>
-    <t>国旗13</t>
-  </si>
-  <si>
-    <t>Flag_013.png</t>
-  </si>
-  <si>
-    <t>国旗14</t>
-  </si>
-  <si>
-    <t>Flag_014.png</t>
-  </si>
-  <si>
-    <t>国旗15</t>
-  </si>
-  <si>
-    <t>Flag_015.png</t>
-  </si>
-  <si>
-    <t>国旗16</t>
-  </si>
-  <si>
-    <t>Flag_016.png</t>
-  </si>
-  <si>
-    <t>国旗17</t>
-  </si>
-  <si>
-    <t>Flag_017.png</t>
-  </si>
-  <si>
-    <t>国旗18</t>
-  </si>
-  <si>
-    <t>Flag_018.png</t>
-  </si>
-  <si>
-    <t>国旗19</t>
-  </si>
-  <si>
-    <t>Flag_019.png</t>
-  </si>
-  <si>
-    <t>国旗20</t>
-  </si>
-  <si>
-    <t>Flag_020.png</t>
-  </si>
-  <si>
-    <t>国旗21</t>
-  </si>
-  <si>
-    <t>Flag_021.png</t>
-  </si>
-  <si>
-    <t>国旗22</t>
-  </si>
-  <si>
-    <t>Flag_022.png</t>
-  </si>
-  <si>
-    <t>国旗23</t>
-  </si>
-  <si>
-    <t>Flag_023.png</t>
   </si>
   <si>
     <t>头衔1</t>
@@ -949,7 +949,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -966,6 +966,12 @@
     <font>
       <sz val="11"/>
       <color theme="5" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1114,17 +1120,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1456,137 +1462,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1597,6 +1603,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4142,14 +4151,13 @@
       <c r="C76" s="1">
         <v>2</v>
       </c>
-      <c r="D76" s="1">
-        <f t="shared" ref="D76:D107" si="6">100000+C76*1000+B76</f>
-        <v>102001</v>
-      </c>
-      <c r="E76" s="1" t="s">
+      <c r="D76" s="4">
+        <v>102023</v>
+      </c>
+      <c r="E76" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="4" t="s">
         <v>166</v>
       </c>
       <c r="G76" s="1">
@@ -4169,7 +4177,7 @@
         <v>2</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D76:D107" si="6">100000+C77*1000+B77</f>
         <v>102002</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -4708,14 +4716,13 @@
       <c r="C98" s="1">
         <v>2</v>
       </c>
-      <c r="D98" s="1">
-        <f t="shared" si="6"/>
-        <v>102023</v>
-      </c>
-      <c r="E98" s="1" t="s">
+      <c r="D98" s="4">
+        <v>102001</v>
+      </c>
+      <c r="E98" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F98" s="4" t="s">
         <v>210</v>
       </c>
       <c r="G98" s="1">

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="avatar" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K61" authorId="0">
+    <comment ref="L61" authorId="0">
       <text>
         <r>
           <rPr>
@@ -211,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K62" authorId="0">
+    <comment ref="L62" authorId="0">
       <text>
         <r>
           <rPr>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="232">
   <si>
     <t>id</t>
   </si>
@@ -546,7 +546,7 @@
     <t>HeadDia_001.png</t>
   </si>
   <si>
-    <t>1980000_1800</t>
+    <t>1980000_90000</t>
   </si>
   <si>
     <t>头像41</t>
@@ -949,7 +949,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="25">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -966,6 +966,12 @@
     <font>
       <sz val="11"/>
       <color theme="5" tint="-0.25"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -1114,17 +1120,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1456,137 +1462,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1597,6 +1603,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1919,7 +1928,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -3318,7 +3327,7 @@
       </c>
       <c r="J48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1" spans="1:11">
+    <row r="49" s="1" customFormat="1" spans="1:12">
       <c r="A49" s="2">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -3349,7 +3358,7 @@
       </c>
       <c r="J49" s="2"/>
     </row>
-    <row r="50" s="1" customFormat="1" spans="1:11">
+    <row r="50" s="1" customFormat="1" spans="1:12">
       <c r="A50" s="2">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -3380,7 +3389,7 @@
       </c>
       <c r="J50" s="2"/>
     </row>
-    <row r="51" s="1" customFormat="1" spans="1:11">
+    <row r="51" s="1" customFormat="1" spans="1:12">
       <c r="A51" s="2">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -3411,7 +3420,7 @@
       </c>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" s="1" customFormat="1" spans="1:11">
+    <row r="52" s="1" customFormat="1" spans="1:12">
       <c r="A52" s="2">
         <f t="shared" si="2"/>
         <v>48</v>
@@ -3442,7 +3451,7 @@
       </c>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" s="1" customFormat="1" spans="1:11">
+    <row r="53" s="1" customFormat="1" spans="1:12">
       <c r="A53" s="2">
         <f t="shared" si="2"/>
         <v>49</v>
@@ -3473,7 +3482,7 @@
       </c>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" s="1" customFormat="1" spans="1:11">
+    <row r="54" s="1" customFormat="1" spans="1:12">
       <c r="A54" s="2">
         <f t="shared" si="2"/>
         <v>50</v>
@@ -3504,7 +3513,7 @@
       </c>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" s="1" customFormat="1" spans="1:11">
+    <row r="55" s="1" customFormat="1" spans="1:12">
       <c r="A55" s="2">
         <f t="shared" si="2"/>
         <v>51</v>
@@ -3535,7 +3544,7 @@
       </c>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" s="1" customFormat="1" spans="1:11">
+    <row r="56" s="1" customFormat="1" spans="1:12">
       <c r="A56" s="2">
         <f t="shared" si="2"/>
         <v>52</v>
@@ -3566,7 +3575,7 @@
       </c>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:12">
       <c r="A57" s="1">
         <f t="shared" si="2"/>
         <v>1001</v>
@@ -3595,7 +3604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:12">
       <c r="A58" s="1">
         <f t="shared" si="2"/>
         <v>1002</v>
@@ -3624,7 +3633,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:12">
       <c r="A59" s="1">
         <f t="shared" si="2"/>
         <v>1003</v>
@@ -3653,7 +3662,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:12">
       <c r="A60" s="1">
         <f t="shared" si="2"/>
         <v>1004</v>
@@ -3682,7 +3691,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="1:11">
+    <row r="61" s="1" customFormat="1" spans="1:12">
       <c r="A61" s="3">
         <f t="shared" si="2"/>
         <v>1005</v>
@@ -3707,11 +3716,14 @@
       <c r="G61" s="1">
         <v>201801</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="I61" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="1:11">
+    <row r="62" s="1" customFormat="1" spans="1:12">
       <c r="A62" s="3">
         <f t="shared" si="2"/>
         <v>1006</v>
@@ -3736,11 +3748,14 @@
       <c r="G62" s="1">
         <v>201802</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="I62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L62" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:12">
       <c r="A63" s="2">
         <f t="shared" si="2"/>
         <v>1007</v>
@@ -3770,7 +3785,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" spans="1:11">
+    <row r="64" s="2" customFormat="1" spans="1:12">
       <c r="A64" s="2">
         <f t="shared" ref="A64:A78" si="5">C64*1000+B64</f>
         <v>1008</v>
@@ -3800,7 +3815,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" spans="1:9">
+    <row r="65" s="2" customFormat="1" spans="1:14">
       <c r="A65" s="2">
         <f t="shared" si="5"/>
         <v>1009</v>
@@ -3830,7 +3845,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" spans="1:9">
+    <row r="66" s="2" customFormat="1" spans="1:14">
       <c r="A66" s="2">
         <f t="shared" si="5"/>
         <v>1010</v>
@@ -3860,7 +3875,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" spans="1:9">
+    <row r="67" s="2" customFormat="1" spans="1:14">
       <c r="A67" s="2">
         <f t="shared" si="5"/>
         <v>1011</v>
@@ -3890,7 +3905,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" spans="1:9">
+    <row r="68" s="2" customFormat="1" spans="1:14">
       <c r="A68" s="2">
         <f t="shared" si="5"/>
         <v>1012</v>
@@ -3920,7 +3935,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" spans="1:9">
+    <row r="69" s="2" customFormat="1" spans="1:14">
       <c r="A69" s="2">
         <f t="shared" si="5"/>
         <v>1013</v>
@@ -3950,7 +3965,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" spans="1:9">
+    <row r="70" s="2" customFormat="1" spans="1:14">
       <c r="A70" s="2">
         <f t="shared" si="5"/>
         <v>1014</v>
@@ -3980,7 +3995,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" spans="1:9">
+    <row r="71" s="2" customFormat="1" spans="1:14">
       <c r="A71" s="2">
         <f t="shared" si="5"/>
         <v>1015</v>
@@ -4010,7 +4025,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" spans="1:9">
+    <row r="72" s="2" customFormat="1" spans="1:14">
       <c r="A72" s="2">
         <f t="shared" si="5"/>
         <v>1016</v>
@@ -4040,7 +4055,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="73" s="2" customFormat="1" spans="1:9">
+    <row r="73" s="2" customFormat="1" spans="1:14">
       <c r="A73" s="2">
         <f t="shared" si="5"/>
         <v>1017</v>
@@ -4070,7 +4085,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="74" s="2" customFormat="1" spans="1:9">
+    <row r="74" s="2" customFormat="1" spans="1:14">
       <c r="A74" s="2">
         <f t="shared" si="5"/>
         <v>1018</v>
@@ -4100,7 +4115,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" s="2" customFormat="1" spans="1:9">
+    <row r="75" s="2" customFormat="1" spans="1:14">
       <c r="A75" s="2">
         <f t="shared" si="5"/>
         <v>1019</v>
@@ -4130,7 +4145,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="1:9">
+    <row r="76" s="1" customFormat="1" spans="1:14">
       <c r="A76" s="1">
         <f t="shared" si="5"/>
         <v>2001</v>
@@ -4142,21 +4157,24 @@
       <c r="C76" s="1">
         <v>2</v>
       </c>
-      <c r="D76" s="1">
-        <f t="shared" ref="D76:D107" si="6">100000+C76*1000+B76</f>
+      <c r="D76" s="4">
         <v>102001</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="4" t="s">
         <v>166</v>
       </c>
       <c r="G76" s="1">
         <v>202001</v>
       </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="1:9">
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:14">
       <c r="A77" s="1">
         <f t="shared" si="5"/>
         <v>2002</v>
@@ -4169,7 +4187,7 @@
         <v>2</v>
       </c>
       <c r="D77" s="1">
-        <f t="shared" si="6"/>
+        <f t="shared" ref="D76:D107" si="6">100000+C77*1000+B77</f>
         <v>102002</v>
       </c>
       <c r="E77" s="1" t="s">
@@ -4181,8 +4199,12 @@
       <c r="G77" s="1">
         <v>202002</v>
       </c>
-    </row>
-    <row r="78" s="1" customFormat="1" spans="1:9">
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:14">
       <c r="A78" s="1">
         <f t="shared" ref="A78:A107" si="7">C78*1000+B78</f>
         <v>2003</v>
@@ -4207,8 +4229,12 @@
       <c r="G78" s="1">
         <v>202003</v>
       </c>
-    </row>
-    <row r="79" s="1" customFormat="1" spans="1:9">
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="1:14">
       <c r="A79" s="1">
         <f t="shared" si="7"/>
         <v>2004</v>
@@ -4233,8 +4259,12 @@
       <c r="G79" s="1">
         <v>202004</v>
       </c>
-    </row>
-    <row r="80" s="1" customFormat="1" spans="1:9">
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="1:14">
       <c r="A80" s="1">
         <f t="shared" si="7"/>
         <v>2005</v>
@@ -4259,8 +4289,12 @@
       <c r="G80" s="1">
         <v>202005</v>
       </c>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="1:7">
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="1:14">
       <c r="A81" s="1">
         <f t="shared" si="7"/>
         <v>2006</v>
@@ -4285,8 +4319,12 @@
       <c r="G81" s="1">
         <v>202006</v>
       </c>
-    </row>
-    <row r="82" s="1" customFormat="1" spans="1:7">
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="1:14">
       <c r="A82" s="1">
         <f t="shared" si="7"/>
         <v>2007</v>
@@ -4311,8 +4349,12 @@
       <c r="G82" s="1">
         <v>202007</v>
       </c>
-    </row>
-    <row r="83" s="1" customFormat="1" spans="1:7">
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="1:14">
       <c r="A83" s="1">
         <f t="shared" si="7"/>
         <v>2008</v>
@@ -4338,7 +4380,7 @@
         <v>202008</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" spans="1:7">
+    <row r="84" s="1" customFormat="1" spans="1:14">
       <c r="A84" s="1">
         <f t="shared" si="7"/>
         <v>2009</v>
@@ -4364,7 +4406,7 @@
         <v>202009</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" spans="1:7">
+    <row r="85" s="1" customFormat="1" spans="1:14">
       <c r="A85" s="1">
         <f t="shared" si="7"/>
         <v>2010</v>
@@ -4390,7 +4432,7 @@
         <v>202010</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" spans="1:7">
+    <row r="86" s="1" customFormat="1" spans="1:14">
       <c r="A86" s="1">
         <f t="shared" si="7"/>
         <v>2011</v>
@@ -4416,7 +4458,7 @@
         <v>202011</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" spans="1:7">
+    <row r="87" s="1" customFormat="1" spans="1:14">
       <c r="A87" s="1">
         <f t="shared" si="7"/>
         <v>2012</v>
@@ -4442,7 +4484,7 @@
         <v>202012</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" spans="1:7">
+    <row r="88" s="1" customFormat="1" spans="1:14">
       <c r="A88" s="1">
         <f t="shared" si="7"/>
         <v>2013</v>
@@ -4468,7 +4510,7 @@
         <v>202013</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" spans="1:7">
+    <row r="89" s="1" customFormat="1" spans="1:14">
       <c r="A89" s="1">
         <f t="shared" si="7"/>
         <v>2014</v>
@@ -4494,7 +4536,7 @@
         <v>202014</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" spans="1:7">
+    <row r="90" s="1" customFormat="1" spans="1:14">
       <c r="A90" s="1">
         <f t="shared" si="7"/>
         <v>2015</v>
@@ -4520,7 +4562,7 @@
         <v>202015</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" spans="1:7">
+    <row r="91" s="1" customFormat="1" spans="1:14">
       <c r="A91" s="1">
         <f t="shared" si="7"/>
         <v>2016</v>
@@ -4546,7 +4588,7 @@
         <v>202016</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" spans="1:7">
+    <row r="92" s="1" customFormat="1" spans="1:14">
       <c r="A92" s="1">
         <f t="shared" si="7"/>
         <v>2017</v>
@@ -4572,7 +4614,7 @@
         <v>202017</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" spans="1:7">
+    <row r="93" s="1" customFormat="1" spans="1:14">
       <c r="A93" s="1">
         <f t="shared" si="7"/>
         <v>2018</v>
@@ -4598,7 +4640,7 @@
         <v>202018</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" spans="1:7">
+    <row r="94" s="1" customFormat="1" spans="1:14">
       <c r="A94" s="1">
         <f t="shared" si="7"/>
         <v>2019</v>
@@ -4624,7 +4666,7 @@
         <v>202019</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" spans="1:7">
+    <row r="95" s="1" customFormat="1" spans="1:14">
       <c r="A95" s="1">
         <f t="shared" si="7"/>
         <v>2020</v>
@@ -4650,7 +4692,7 @@
         <v>202020</v>
       </c>
     </row>
-    <row r="96" s="1" customFormat="1" spans="1:7">
+    <row r="96" s="1" customFormat="1" spans="1:14">
       <c r="A96" s="1">
         <v>2021</v>
       </c>
@@ -4708,14 +4750,13 @@
       <c r="C98" s="1">
         <v>2</v>
       </c>
-      <c r="D98" s="1">
-        <f t="shared" si="6"/>
+      <c r="D98" s="4">
         <v>102023</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E98" s="4" t="s">
         <v>209</v>
       </c>
-      <c r="F98" s="1" t="s">
+      <c r="F98" s="4" t="s">
         <v>210</v>
       </c>
       <c r="G98" s="1">
@@ -5068,10 +5109,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F53">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F76">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M76">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F98">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F52 F54:F1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="F1:F52 F54:F75 F77:F97 F99:F1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/hall/resources/sample/avatar.xlsx
+++ b/hall/resources/sample/avatar.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="avatar" sheetId="1" r:id="rId1"/>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K61" authorId="0">
+    <comment ref="L61" authorId="0">
       <text>
         <r>
           <rPr>
@@ -211,7 +211,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K62" authorId="0">
+    <comment ref="L62" authorId="0">
       <text>
         <r>
           <rPr>
@@ -241,7 +241,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="232">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="232">
   <si>
     <t>id</t>
   </si>
@@ -546,7 +546,7 @@
     <t>HeadDia_001.png</t>
   </si>
   <si>
-    <t>1980000_1800</t>
+    <t>1980000_90000</t>
   </si>
   <si>
     <t>头像41</t>
@@ -738,142 +738,142 @@
     <t>frame_017.png</t>
   </si>
   <si>
+    <t>国旗1</t>
+  </si>
+  <si>
+    <t>Flag_001.png</t>
+  </si>
+  <si>
+    <t>国旗2</t>
+  </si>
+  <si>
+    <t>Flag_002.png</t>
+  </si>
+  <si>
+    <t>国旗3</t>
+  </si>
+  <si>
+    <t>Flag_003.png</t>
+  </si>
+  <si>
+    <t>国旗4</t>
+  </si>
+  <si>
+    <t>Flag_004.png</t>
+  </si>
+  <si>
+    <t>国旗5</t>
+  </si>
+  <si>
+    <t>Flag_005.png</t>
+  </si>
+  <si>
+    <t>国旗6</t>
+  </si>
+  <si>
+    <t>Flag_006.png</t>
+  </si>
+  <si>
+    <t>国旗7</t>
+  </si>
+  <si>
+    <t>Flag_007.png</t>
+  </si>
+  <si>
+    <t>国旗8</t>
+  </si>
+  <si>
+    <t>Flag_008.png</t>
+  </si>
+  <si>
+    <t>国旗9</t>
+  </si>
+  <si>
+    <t>Flag_009.png</t>
+  </si>
+  <si>
+    <t>国旗10</t>
+  </si>
+  <si>
+    <t>Flag_010.png</t>
+  </si>
+  <si>
+    <t>国旗11</t>
+  </si>
+  <si>
+    <t>Flag_011.png</t>
+  </si>
+  <si>
+    <t>国旗12</t>
+  </si>
+  <si>
+    <t>Flag_012.png</t>
+  </si>
+  <si>
+    <t>国旗13</t>
+  </si>
+  <si>
+    <t>Flag_013.png</t>
+  </si>
+  <si>
+    <t>国旗14</t>
+  </si>
+  <si>
+    <t>Flag_014.png</t>
+  </si>
+  <si>
+    <t>国旗15</t>
+  </si>
+  <si>
+    <t>Flag_015.png</t>
+  </si>
+  <si>
+    <t>国旗16</t>
+  </si>
+  <si>
+    <t>Flag_016.png</t>
+  </si>
+  <si>
+    <t>国旗17</t>
+  </si>
+  <si>
+    <t>Flag_017.png</t>
+  </si>
+  <si>
+    <t>国旗18</t>
+  </si>
+  <si>
+    <t>Flag_018.png</t>
+  </si>
+  <si>
+    <t>国旗19</t>
+  </si>
+  <si>
+    <t>Flag_019.png</t>
+  </si>
+  <si>
+    <t>国旗20</t>
+  </si>
+  <si>
+    <t>Flag_020.png</t>
+  </si>
+  <si>
+    <t>国旗21</t>
+  </si>
+  <si>
+    <t>Flag_021.png</t>
+  </si>
+  <si>
+    <t>国旗22</t>
+  </si>
+  <si>
+    <t>Flag_022.png</t>
+  </si>
+  <si>
     <t>国旗23</t>
   </si>
   <si>
     <t>Flag_023.png</t>
-  </si>
-  <si>
-    <t>国旗2</t>
-  </si>
-  <si>
-    <t>Flag_002.png</t>
-  </si>
-  <si>
-    <t>国旗3</t>
-  </si>
-  <si>
-    <t>Flag_003.png</t>
-  </si>
-  <si>
-    <t>国旗4</t>
-  </si>
-  <si>
-    <t>Flag_004.png</t>
-  </si>
-  <si>
-    <t>国旗5</t>
-  </si>
-  <si>
-    <t>Flag_005.png</t>
-  </si>
-  <si>
-    <t>国旗6</t>
-  </si>
-  <si>
-    <t>Flag_006.png</t>
-  </si>
-  <si>
-    <t>国旗7</t>
-  </si>
-  <si>
-    <t>Flag_007.png</t>
-  </si>
-  <si>
-    <t>国旗8</t>
-  </si>
-  <si>
-    <t>Flag_008.png</t>
-  </si>
-  <si>
-    <t>国旗9</t>
-  </si>
-  <si>
-    <t>Flag_009.png</t>
-  </si>
-  <si>
-    <t>国旗10</t>
-  </si>
-  <si>
-    <t>Flag_010.png</t>
-  </si>
-  <si>
-    <t>国旗11</t>
-  </si>
-  <si>
-    <t>Flag_011.png</t>
-  </si>
-  <si>
-    <t>国旗12</t>
-  </si>
-  <si>
-    <t>Flag_012.png</t>
-  </si>
-  <si>
-    <t>国旗13</t>
-  </si>
-  <si>
-    <t>Flag_013.png</t>
-  </si>
-  <si>
-    <t>国旗14</t>
-  </si>
-  <si>
-    <t>Flag_014.png</t>
-  </si>
-  <si>
-    <t>国旗15</t>
-  </si>
-  <si>
-    <t>Flag_015.png</t>
-  </si>
-  <si>
-    <t>国旗16</t>
-  </si>
-  <si>
-    <t>Flag_016.png</t>
-  </si>
-  <si>
-    <t>国旗17</t>
-  </si>
-  <si>
-    <t>Flag_017.png</t>
-  </si>
-  <si>
-    <t>国旗18</t>
-  </si>
-  <si>
-    <t>Flag_018.png</t>
-  </si>
-  <si>
-    <t>国旗19</t>
-  </si>
-  <si>
-    <t>Flag_019.png</t>
-  </si>
-  <si>
-    <t>国旗20</t>
-  </si>
-  <si>
-    <t>Flag_020.png</t>
-  </si>
-  <si>
-    <t>国旗21</t>
-  </si>
-  <si>
-    <t>Flag_021.png</t>
-  </si>
-  <si>
-    <t>国旗22</t>
-  </si>
-  <si>
-    <t>Flag_022.png</t>
-  </si>
-  <si>
-    <t>国旗1</t>
-  </si>
-  <si>
-    <t>Flag_001.png</t>
   </si>
   <si>
     <t>头衔1</t>
@@ -1928,7 +1928,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:L110"/>
+  <dimension ref="A1:N110"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="2" width="9" style="1"/>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="J48" s="2"/>
     </row>
-    <row r="49" s="1" customFormat="1" spans="1:11">
+    <row r="49" s="1" customFormat="1" spans="1:12">
       <c r="A49" s="2">
         <f t="shared" si="2"/>
         <v>45</v>
@@ -3358,7 +3358,7 @@
       </c>
       <c r="J49" s="2"/>
     </row>
-    <row r="50" s="1" customFormat="1" spans="1:11">
+    <row r="50" s="1" customFormat="1" spans="1:12">
       <c r="A50" s="2">
         <f t="shared" si="2"/>
         <v>46</v>
@@ -3389,7 +3389,7 @@
       </c>
       <c r="J50" s="2"/>
     </row>
-    <row r="51" s="1" customFormat="1" spans="1:11">
+    <row r="51" s="1" customFormat="1" spans="1:12">
       <c r="A51" s="2">
         <f t="shared" si="2"/>
         <v>47</v>
@@ -3420,7 +3420,7 @@
       </c>
       <c r="J51" s="2"/>
     </row>
-    <row r="52" s="1" customFormat="1" spans="1:11">
+    <row r="52" s="1" customFormat="1" spans="1:12">
       <c r="A52" s="2">
         <f t="shared" si="2"/>
         <v>48</v>
@@ -3451,7 +3451,7 @@
       </c>
       <c r="J52" s="2"/>
     </row>
-    <row r="53" s="1" customFormat="1" spans="1:11">
+    <row r="53" s="1" customFormat="1" spans="1:12">
       <c r="A53" s="2">
         <f t="shared" si="2"/>
         <v>49</v>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="J53" s="2"/>
     </row>
-    <row r="54" s="1" customFormat="1" spans="1:11">
+    <row r="54" s="1" customFormat="1" spans="1:12">
       <c r="A54" s="2">
         <f t="shared" si="2"/>
         <v>50</v>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="J54" s="2"/>
     </row>
-    <row r="55" s="1" customFormat="1" spans="1:11">
+    <row r="55" s="1" customFormat="1" spans="1:12">
       <c r="A55" s="2">
         <f t="shared" si="2"/>
         <v>51</v>
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J55" s="2"/>
     </row>
-    <row r="56" s="1" customFormat="1" spans="1:11">
+    <row r="56" s="1" customFormat="1" spans="1:12">
       <c r="A56" s="2">
         <f t="shared" si="2"/>
         <v>52</v>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="J56" s="2"/>
     </row>
-    <row r="57" spans="1:11">
+    <row r="57" spans="1:12">
       <c r="A57" s="1">
         <f t="shared" si="2"/>
         <v>1001</v>
@@ -3604,7 +3604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:11">
+    <row r="58" spans="1:12">
       <c r="A58" s="1">
         <f t="shared" si="2"/>
         <v>1002</v>
@@ -3633,7 +3633,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="59" spans="1:11">
+    <row r="59" spans="1:12">
       <c r="A59" s="1">
         <f t="shared" si="2"/>
         <v>1003</v>
@@ -3662,7 +3662,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:11">
+    <row r="60" spans="1:12">
       <c r="A60" s="1">
         <f t="shared" si="2"/>
         <v>1004</v>
@@ -3691,7 +3691,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="61" s="1" customFormat="1" spans="1:11">
+    <row r="61" s="1" customFormat="1" spans="1:12">
       <c r="A61" s="3">
         <f t="shared" si="2"/>
         <v>1005</v>
@@ -3716,11 +3716,14 @@
       <c r="G61" s="1">
         <v>201801</v>
       </c>
-      <c r="K61" s="1" t="s">
+      <c r="I61" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L61" s="1" t="s">
         <v>135</v>
       </c>
     </row>
-    <row r="62" s="1" customFormat="1" spans="1:11">
+    <row r="62" s="1" customFormat="1" spans="1:12">
       <c r="A62" s="3">
         <f t="shared" si="2"/>
         <v>1006</v>
@@ -3745,11 +3748,14 @@
       <c r="G62" s="1">
         <v>201802</v>
       </c>
-      <c r="K62" s="1" t="s">
+      <c r="I62" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="L62" s="1" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="63" spans="1:11">
+    <row r="63" spans="1:12">
       <c r="A63" s="2">
         <f t="shared" si="2"/>
         <v>1007</v>
@@ -3779,7 +3785,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="64" s="2" customFormat="1" spans="1:11">
+    <row r="64" s="2" customFormat="1" spans="1:12">
       <c r="A64" s="2">
         <f t="shared" ref="A64:A78" si="5">C64*1000+B64</f>
         <v>1008</v>
@@ -3809,7 +3815,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="65" s="2" customFormat="1" spans="1:9">
+    <row r="65" s="2" customFormat="1" spans="1:14">
       <c r="A65" s="2">
         <f t="shared" si="5"/>
         <v>1009</v>
@@ -3839,7 +3845,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="66" s="2" customFormat="1" spans="1:9">
+    <row r="66" s="2" customFormat="1" spans="1:14">
       <c r="A66" s="2">
         <f t="shared" si="5"/>
         <v>1010</v>
@@ -3869,7 +3875,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="67" s="2" customFormat="1" spans="1:9">
+    <row r="67" s="2" customFormat="1" spans="1:14">
       <c r="A67" s="2">
         <f t="shared" si="5"/>
         <v>1011</v>
@@ -3899,7 +3905,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="68" s="2" customFormat="1" spans="1:9">
+    <row r="68" s="2" customFormat="1" spans="1:14">
       <c r="A68" s="2">
         <f t="shared" si="5"/>
         <v>1012</v>
@@ -3929,7 +3935,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="69" s="2" customFormat="1" spans="1:9">
+    <row r="69" s="2" customFormat="1" spans="1:14">
       <c r="A69" s="2">
         <f t="shared" si="5"/>
         <v>1013</v>
@@ -3959,7 +3965,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="70" s="2" customFormat="1" spans="1:9">
+    <row r="70" s="2" customFormat="1" spans="1:14">
       <c r="A70" s="2">
         <f t="shared" si="5"/>
         <v>1014</v>
@@ -3989,7 +3995,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="71" s="2" customFormat="1" spans="1:9">
+    <row r="71" s="2" customFormat="1" spans="1:14">
       <c r="A71" s="2">
         <f t="shared" si="5"/>
         <v>1015</v>
@@ -4019,7 +4025,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="72" s="2" customFormat="1" spans="1:9">
+    <row r="72" s="2" customFormat="1" spans="1:14">
       <c r="A72" s="2">
         <f t="shared" si="5"/>
         <v>1016</v>
@@ -4049,7 +4055,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="73" s="2" customFormat="1" spans="1:9">
+    <row r="73" s="2" customFormat="1" spans="1:14">
       <c r="A73" s="2">
         <f t="shared" si="5"/>
         <v>1017</v>
@@ -4079,7 +4085,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="74" s="2" customFormat="1" spans="1:9">
+    <row r="74" s="2" customFormat="1" spans="1:14">
       <c r="A74" s="2">
         <f t="shared" si="5"/>
         <v>1018</v>
@@ -4109,7 +4115,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" s="2" customFormat="1" spans="1:9">
+    <row r="75" s="2" customFormat="1" spans="1:14">
       <c r="A75" s="2">
         <f t="shared" si="5"/>
         <v>1019</v>
@@ -4139,7 +4145,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="76" s="1" customFormat="1" spans="1:9">
+    <row r="76" s="1" customFormat="1" spans="1:14">
       <c r="A76" s="1">
         <f t="shared" si="5"/>
         <v>2001</v>
@@ -4152,7 +4158,7 @@
         <v>2</v>
       </c>
       <c r="D76" s="4">
-        <v>102023</v>
+        <v>102001</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>165</v>
@@ -4163,8 +4169,12 @@
       <c r="G76" s="1">
         <v>202001</v>
       </c>
-    </row>
-    <row r="77" s="1" customFormat="1" spans="1:9">
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+    </row>
+    <row r="77" s="1" customFormat="1" spans="1:14">
       <c r="A77" s="1">
         <f t="shared" si="5"/>
         <v>2002</v>
@@ -4189,8 +4199,12 @@
       <c r="G77" s="1">
         <v>202002</v>
       </c>
-    </row>
-    <row r="78" s="1" customFormat="1" spans="1:9">
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+    </row>
+    <row r="78" s="1" customFormat="1" spans="1:14">
       <c r="A78" s="1">
         <f t="shared" ref="A78:A107" si="7">C78*1000+B78</f>
         <v>2003</v>
@@ -4215,8 +4229,12 @@
       <c r="G78" s="1">
         <v>202003</v>
       </c>
-    </row>
-    <row r="79" s="1" customFormat="1" spans="1:9">
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+    </row>
+    <row r="79" s="1" customFormat="1" spans="1:14">
       <c r="A79" s="1">
         <f t="shared" si="7"/>
         <v>2004</v>
@@ -4241,8 +4259,12 @@
       <c r="G79" s="1">
         <v>202004</v>
       </c>
-    </row>
-    <row r="80" s="1" customFormat="1" spans="1:9">
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+    </row>
+    <row r="80" s="1" customFormat="1" spans="1:14">
       <c r="A80" s="1">
         <f t="shared" si="7"/>
         <v>2005</v>
@@ -4267,8 +4289,12 @@
       <c r="G80" s="1">
         <v>202005</v>
       </c>
-    </row>
-    <row r="81" s="1" customFormat="1" spans="1:7">
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+    </row>
+    <row r="81" s="1" customFormat="1" spans="1:14">
       <c r="A81" s="1">
         <f t="shared" si="7"/>
         <v>2006</v>
@@ -4293,8 +4319,12 @@
       <c r="G81" s="1">
         <v>202006</v>
       </c>
-    </row>
-    <row r="82" s="1" customFormat="1" spans="1:7">
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+    </row>
+    <row r="82" s="1" customFormat="1" spans="1:14">
       <c r="A82" s="1">
         <f t="shared" si="7"/>
         <v>2007</v>
@@ -4319,8 +4349,12 @@
       <c r="G82" s="1">
         <v>202007</v>
       </c>
-    </row>
-    <row r="83" s="1" customFormat="1" spans="1:7">
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+    </row>
+    <row r="83" s="1" customFormat="1" spans="1:14">
       <c r="A83" s="1">
         <f t="shared" si="7"/>
         <v>2008</v>
@@ -4346,7 +4380,7 @@
         <v>202008</v>
       </c>
     </row>
-    <row r="84" s="1" customFormat="1" spans="1:7">
+    <row r="84" s="1" customFormat="1" spans="1:14">
       <c r="A84" s="1">
         <f t="shared" si="7"/>
         <v>2009</v>
@@ -4372,7 +4406,7 @@
         <v>202009</v>
       </c>
     </row>
-    <row r="85" s="1" customFormat="1" spans="1:7">
+    <row r="85" s="1" customFormat="1" spans="1:14">
       <c r="A85" s="1">
         <f t="shared" si="7"/>
         <v>2010</v>
@@ -4398,7 +4432,7 @@
         <v>202010</v>
       </c>
     </row>
-    <row r="86" s="1" customFormat="1" spans="1:7">
+    <row r="86" s="1" customFormat="1" spans="1:14">
       <c r="A86" s="1">
         <f t="shared" si="7"/>
         <v>2011</v>
@@ -4424,7 +4458,7 @@
         <v>202011</v>
       </c>
     </row>
-    <row r="87" s="1" customFormat="1" spans="1:7">
+    <row r="87" s="1" customFormat="1" spans="1:14">
       <c r="A87" s="1">
         <f t="shared" si="7"/>
         <v>2012</v>
@@ -4450,7 +4484,7 @@
         <v>202012</v>
       </c>
     </row>
-    <row r="88" s="1" customFormat="1" spans="1:7">
+    <row r="88" s="1" customFormat="1" spans="1:14">
       <c r="A88" s="1">
         <f t="shared" si="7"/>
         <v>2013</v>
@@ -4476,7 +4510,7 @@
         <v>202013</v>
       </c>
     </row>
-    <row r="89" s="1" customFormat="1" spans="1:7">
+    <row r="89" s="1" customFormat="1" spans="1:14">
       <c r="A89" s="1">
         <f t="shared" si="7"/>
         <v>2014</v>
@@ -4502,7 +4536,7 @@
         <v>202014</v>
       </c>
     </row>
-    <row r="90" s="1" customFormat="1" spans="1:7">
+    <row r="90" s="1" customFormat="1" spans="1:14">
       <c r="A90" s="1">
         <f t="shared" si="7"/>
         <v>2015</v>
@@ -4528,7 +4562,7 @@
         <v>202015</v>
       </c>
     </row>
-    <row r="91" s="1" customFormat="1" spans="1:7">
+    <row r="91" s="1" customFormat="1" spans="1:14">
       <c r="A91" s="1">
         <f t="shared" si="7"/>
         <v>2016</v>
@@ -4554,7 +4588,7 @@
         <v>202016</v>
       </c>
     </row>
-    <row r="92" s="1" customFormat="1" spans="1:7">
+    <row r="92" s="1" customFormat="1" spans="1:14">
       <c r="A92" s="1">
         <f t="shared" si="7"/>
         <v>2017</v>
@@ -4580,7 +4614,7 @@
         <v>202017</v>
       </c>
     </row>
-    <row r="93" s="1" customFormat="1" spans="1:7">
+    <row r="93" s="1" customFormat="1" spans="1:14">
       <c r="A93" s="1">
         <f t="shared" si="7"/>
         <v>2018</v>
@@ -4606,7 +4640,7 @@
         <v>202018</v>
       </c>
     </row>
-    <row r="94" s="1" customFormat="1" spans="1:7">
+    <row r="94" s="1" customFormat="1" spans="1:14">
       <c r="A94" s="1">
         <f t="shared" si="7"/>
         <v>2019</v>
@@ -4632,7 +4666,7 @@
         <v>202019</v>
       </c>
     </row>
-    <row r="95" s="1" customFormat="1" spans="1:7">
+    <row r="95" s="1" customFormat="1" spans="1:14">
       <c r="A95" s="1">
         <f t="shared" si="7"/>
         <v>2020</v>
@@ -4658,7 +4692,7 @@
         <v>202020</v>
       </c>
     </row>
-    <row r="96" s="1" customFormat="1" spans="1:7">
+    <row r="96" s="1" customFormat="1" spans="1:14">
       <c r="A96" s="1">
         <v>2021</v>
       </c>
@@ -4717,7 +4751,7 @@
         <v>2</v>
       </c>
       <c r="D98" s="4">
-        <v>102001</v>
+        <v>102023</v>
       </c>
       <c r="E98" s="4" t="s">
         <v>209</v>
@@ -5075,10 +5109,19 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="F53">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F76">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="M76">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F98">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F1:F52 F54:F1048576">
-    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  <conditionalFormatting sqref="F1:F52 F54:F75 F77:F97 F99:F1048576">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
